--- a/quizzes/peinture-18e.xlsx
+++ b/quizzes/peinture-18e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A5D3604-A742-4E22-9038-F355F981FE20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A57B23A-82F7-4947-AD62-CE8DEA0E5C70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4279" uniqueCount="1704">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4283" uniqueCount="1702">
   <si>
     <t>Prénom</t>
   </si>
@@ -3112,42 +3112,6 @@
     <t>Walker Art Gallery</t>
   </si>
   <si>
-    <t>La Mort de Nelson</t>
-  </si>
-  <si>
-    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d1/Benjamin_West_-_The_Death_of_Nelson_-_Google_Art_Project.jpg/1280px-Benjamin_West_-_The_Death_of_Nelson_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>The Death of Nelson</t>
-  </si>
-  <si>
-    <t>182.2 cm</t>
-  </si>
-  <si>
-    <t>247.3 cm</t>
-  </si>
-  <si>
-    <t>Américaine / Britannique</t>
-  </si>
-  <si>
-    <t>1816</t>
-  </si>
-  <si>
-    <t>Benjamin Franklin tirant l'électricité du ciel</t>
-  </si>
-  <si>
-    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/Benjamin_West%2C_English_%28born_America%29_-_Benjamin_Franklin_Drawing_Electricity_from_the_Sky_-_Google_Art_Project.jpg/960px-Benjamin_West%2C_English_%28born_America%29_-_Benjamin_Franklin_Drawing_Electricity_from_the_Sky_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>Benjamin Franklin Drawing Electricity from the Sky</t>
-  </si>
-  <si>
-    <t>34 cm</t>
-  </si>
-  <si>
-    <t>26 cm</t>
-  </si>
-  <si>
     <t>Richard</t>
   </si>
   <si>
@@ -3997,18 +3961,6 @@
     <t>Bildnis Gotthold Ephraim Lessing</t>
   </si>
   <si>
-    <t>Alte Nationalgalerie</t>
-  </si>
-  <si>
-    <t>Staatliche Museen zu Berlin</t>
-  </si>
-  <si>
-    <t>Portrait de Henri de Prusse</t>
-  </si>
-  <si>
-    <t>Bildnis Prinz Heinrich von Preußen</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/c/cd/Gotthold_Ephraim_Lessing.PNG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
   <si>
@@ -4027,9 +3979,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/75/Graff%2C_Anton_-_Self-portrait_at_the_age_of_58.jpg/500px-Graff%2C_Anton_-_Self-portrait_at_the_age_of_58.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/8/87/Graff_-_Prinz_Heinrich_-_Deutsches_Historisches_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/3/37/Anton_Graff_-_Zelfportret_van_Anton_Graff_%281736-1813%29_-_Gal.-Nr._2168_-_Staatliche_Kunstsammlungen_Dresden.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
   <si>
@@ -4066,9 +4015,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/2/20/Anne-Louis_Girodet_De_Roucy-Trioson_-_Ossian_Receiving_the_Ghosts_of_French_Heroes_-_WGA09512.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
   <si>
-    <t>v. 1780</t>
-  </si>
-  <si>
     <t>San Marino</t>
   </si>
   <si>
@@ -4084,9 +4030,6 @@
     <t>The Cottage Door</t>
   </si>
   <si>
-    <t>av. 1777</t>
-  </si>
-  <si>
     <t>L'Abreuvoir</t>
   </si>
   <si>
@@ -4159,9 +4102,6 @@
     <t>The Progress of Love: Love Letters</t>
   </si>
   <si>
-    <t>v. 1769</t>
-  </si>
-  <si>
     <t>Département des Peintures, Aile Sully</t>
   </si>
   <si>
@@ -4312,9 +4252,6 @@
     <t>59,5 cm</t>
   </si>
   <si>
-    <t>158 cm</t>
-  </si>
-  <si>
     <t>74,5 cm</t>
   </si>
   <si>
@@ -4567,9 +4504,6 @@
     <t>Palais d'Hiver</t>
   </si>
   <si>
-    <t>v. 1733</t>
-  </si>
-  <si>
     <t>La Fontaine de cuivre</t>
   </si>
   <si>
@@ -4624,15 +4558,12 @@
     <t>Ritratto di Antoine Watteau</t>
   </si>
   <si>
-    <t>v. 1725</t>
+    <t>Gemäldegalerie Alte Meister</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/0/0b/Rosalba_Carriera_Portrait_Antoine_Watteau.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
   <si>
-    <t>v. 1730</t>
-  </si>
-  <si>
     <t>Gallerie dell'Accademia</t>
   </si>
   <si>
@@ -4726,9 +4657,6 @@
     <t>The Stonemason's Yard</t>
   </si>
   <si>
-    <t>v. 1723</t>
-  </si>
-  <si>
     <t>Musée du XVIIIe siècle vénitien</t>
   </si>
   <si>
@@ -4738,9 +4666,6 @@
     <t>Il Canal Grande da Palazzo Balbi verso il Rialto</t>
   </si>
   <si>
-    <t>v. 1732</t>
-  </si>
-  <si>
     <t>Royal Collection Trust</t>
   </si>
   <si>
@@ -4750,9 +4675,6 @@
     <t>Il ritorno del Bucintoro al Molo il giorno dell'Ascensione</t>
   </si>
   <si>
-    <t>v. 1740</t>
-  </si>
-  <si>
     <t>Régate sur le Grand Canal</t>
   </si>
   <si>
@@ -4762,9 +4684,6 @@
     <t>182.8</t>
   </si>
   <si>
-    <t>v. 1728</t>
-  </si>
-  <si>
     <t>Grenoble</t>
   </si>
   <si>
@@ -4795,9 +4714,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5b/Canaletto_-_L%27Entr%C3%A9e_du_Grand_Canal%2C_vue_de_l%27extr%C3%A9mit%C3%A9_occidentale_du_M%C3%B4le.jpg/1280px-Canaletto_-_L%27Entr%C3%A9e_du_Grand_Canal%2C_vue_de_l%27extr%C3%A9mit%C3%A9_occidentale_du_M%C3%B4le.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>v. 1735</t>
-  </si>
-  <si>
     <t>La Fête de la Saint-Roch</t>
   </si>
   <si>
@@ -4978,9 +4894,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/98/William_Blake_-_Nebuchadnezzar_%28Tate_Britain%29.jpg/1280px-William_Blake_-_Nebuchadnezzar_%28Tate_Britain%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>v. 1736-1740</t>
-  </si>
-  <si>
     <t>Musée des Beaux-Arts de Lyon</t>
   </si>
   <si>
@@ -5132,13 +5045,94 @@
   </si>
   <si>
     <t>57.2 cm</t>
+  </si>
+  <si>
+    <t>1736-1740</t>
+  </si>
+  <si>
+    <t>1725 environ</t>
+  </si>
+  <si>
+    <t>1723 environ</t>
+  </si>
+  <si>
+    <t>1732 environ</t>
+  </si>
+  <si>
+    <t>1728 environ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1735 environ</t>
+  </si>
+  <si>
+    <t>1730 environ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1733 environ</t>
+  </si>
+  <si>
+    <t>1769 environ</t>
+  </si>
+  <si>
+    <t>1780 environ</t>
+  </si>
+  <si>
+    <t>1777 environ</t>
+  </si>
+  <si>
+    <t>Yale University Art Gallery</t>
+  </si>
+  <si>
+    <t>Département d'Art Britannique</t>
+  </si>
+  <si>
+    <t>Agrippine débarquant à Brindes avec les cendres de Germanicus</t>
+  </si>
+  <si>
+    <t>Agrippina Landing at Brundisium with the Ashes of Germanicus</t>
+  </si>
+  <si>
+    <t>Pylade et Oreste amenés en victimes devant Iphigénie</t>
+  </si>
+  <si>
+    <t>Pylades and Orestes Brought as Victims before Iphigenia</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/ea/Benjamin_West_-_Agrippina_Landing_at_Brundisium_with_the_Ashes_of_Germanicu_-_1947.16_-_Yale_University_Art_Gallery.jpg/1280px-Benjamin_West_-_Agrippina_Landing_at_Brundisium_with_the_Ashes_of_Germanicu_-_1947.16_-_Yale_University_Art_Gallery.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/71/Benjamin_West_-_Pylades_and_Orestes_Brought_as_Victims_before_Iphigenia_-_Google_Art_Project.jpg/1280px-Benjamin_West_-_Pylades_and_Orestes_Brought_as_Victims_before_Iphigenia_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>163.8 cm</t>
+  </si>
+  <si>
+    <t>240 cm</t>
+  </si>
+  <si>
+    <t>162.6 cm</t>
+  </si>
+  <si>
+    <t>242.6 cm</t>
+  </si>
+  <si>
+    <t>Staatliche Kunstsammlungen</t>
+  </si>
+  <si>
+    <t>Portrait de Frédéric II le Grand</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/81/Friedrich_der_Gro%C3%9Fe_%281781_or_1786%29_-_Google_Art_Project.jpg/960px-Friedrich_der_Gro%C3%9Fe_%281781_or_1786%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Bildnis Friedrich II. von Preußen</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5172,6 +5166,33 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -5188,7 +5209,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5361,7 +5382,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -5454,9 +5475,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5464,15 +5482,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -5503,6 +5512,59 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5818,12 +5880,12 @@
     <col min="5" max="5" width="8.140625" customWidth="1"/>
     <col min="6" max="6" width="8.42578125" customWidth="1"/>
     <col min="7" max="7" width="9.140625" customWidth="1"/>
-    <col min="8" max="8" width="10" style="11" customWidth="1"/>
+    <col min="8" max="8" width="24.42578125" style="11" customWidth="1"/>
     <col min="9" max="9" width="12" style="2" customWidth="1"/>
     <col min="10" max="10" width="22" customWidth="1"/>
     <col min="11" max="11" width="11.42578125" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="12.7109375" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="25.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="25.7109375" style="73" customWidth="1"/>
     <col min="14" max="14" width="16.28515625" customWidth="1"/>
     <col min="15" max="15" width="11.7109375" customWidth="1"/>
     <col min="16" max="16" width="17.140625" customWidth="1"/>
@@ -5873,7 +5935,7 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="56" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="2" t="s">
@@ -5933,7 +5995,7 @@
       </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
-      <c r="M2" s="3" t="s">
+      <c r="M2" s="56" t="s">
         <v>29</v>
       </c>
       <c r="N2" s="2" t="s">
@@ -5989,7 +6051,7 @@
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="56" t="s">
         <v>39</v>
       </c>
       <c r="N3" s="2" t="s">
@@ -6034,7 +6096,7 @@
       <c r="G4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="32" t="s">
         <v>374</v>
       </c>
       <c r="I4" s="2" t="s">
@@ -6045,18 +6107,18 @@
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2" t="s">
-        <v>1663</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>1664</v>
+        <v>1634</v>
+      </c>
+      <c r="M4" s="57" t="s">
+        <v>1635</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>1670</v>
+        <v>1641</v>
       </c>
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
       <c r="Q4" s="2" t="s">
-        <v>1665</v>
+        <v>1636</v>
       </c>
       <c r="R4" s="2" t="s">
         <v>558</v>
@@ -6065,16 +6127,16 @@
         <v>32</v>
       </c>
       <c r="T4" s="18" t="s">
-        <v>1672</v>
+        <v>1643</v>
       </c>
       <c r="U4" s="18" t="s">
-        <v>1673</v>
+        <v>1644</v>
       </c>
       <c r="V4" s="2" t="s">
         <v>870</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>1162</v>
+        <v>1150</v>
       </c>
       <c r="X4" s="2">
         <v>3</v>
@@ -6096,8 +6158,8 @@
       <c r="G5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>1666</v>
+      <c r="H5" s="32" t="s">
+        <v>1637</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>744</v>
@@ -6107,18 +6169,18 @@
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>1667</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>1668</v>
+        <v>1638</v>
+      </c>
+      <c r="M5" s="57" t="s">
+        <v>1639</v>
       </c>
       <c r="N5" s="5" t="s">
-        <v>1671</v>
+        <v>1642</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2" t="s">
-        <v>1669</v>
+        <v>1640</v>
       </c>
       <c r="R5" s="2" t="s">
         <v>558</v>
@@ -6127,16 +6189,16 @@
         <v>32</v>
       </c>
       <c r="T5" s="18" t="s">
-        <v>1674</v>
+        <v>1645</v>
       </c>
       <c r="U5" s="18" t="s">
-        <v>1675</v>
+        <v>1646</v>
       </c>
       <c r="V5" s="2" t="s">
         <v>870</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>1162</v>
+        <v>1150</v>
       </c>
       <c r="X5" s="2">
         <v>3</v>
@@ -6169,7 +6231,7 @@
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
-      <c r="M6" s="3" t="s">
+      <c r="M6" s="56" t="s">
         <v>51</v>
       </c>
       <c r="N6" s="2" t="s">
@@ -6222,7 +6284,7 @@
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
-      <c r="M7" s="3" t="s">
+      <c r="M7" s="56" t="s">
         <v>58</v>
       </c>
       <c r="N7" s="2" t="s">
@@ -6267,47 +6329,47 @@
       <c r="G8" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="H8" s="38" t="s">
-        <v>1652</v>
-      </c>
-      <c r="I8" s="38" t="s">
+      <c r="H8" s="37" t="s">
+        <v>1675</v>
+      </c>
+      <c r="I8" s="37" t="s">
         <v>933</v>
       </c>
-      <c r="J8" s="38" t="s">
-        <v>1653</v>
-      </c>
-      <c r="K8" s="38"/>
-      <c r="L8" s="38" t="s">
+      <c r="J8" s="37" t="s">
+        <v>1624</v>
+      </c>
+      <c r="K8" s="37"/>
+      <c r="L8" s="37" t="s">
         <v>640</v>
       </c>
-      <c r="M8" s="38" t="s">
-        <v>1654</v>
+      <c r="M8" s="58" t="s">
+        <v>1625</v>
       </c>
       <c r="N8" s="5" t="s">
-        <v>1661</v>
-      </c>
-      <c r="O8" s="38" t="s">
-        <v>1655</v>
-      </c>
-      <c r="P8" s="38"/>
-      <c r="Q8" s="38" t="s">
-        <v>1656</v>
-      </c>
-      <c r="R8" s="38" t="s">
+        <v>1632</v>
+      </c>
+      <c r="O8" s="37" t="s">
+        <v>1626</v>
+      </c>
+      <c r="P8" s="37"/>
+      <c r="Q8" s="37" t="s">
+        <v>1627</v>
+      </c>
+      <c r="R8" s="37" t="s">
         <v>558</v>
       </c>
-      <c r="S8" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="T8" s="39" t="s">
-        <v>1676</v>
-      </c>
-      <c r="U8" s="39" t="s">
-        <v>1677</v>
-      </c>
-      <c r="V8" s="38"/>
-      <c r="W8" s="38" t="s">
-        <v>1293</v>
+      <c r="S8" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="T8" s="38" t="s">
+        <v>1647</v>
+      </c>
+      <c r="U8" s="38" t="s">
+        <v>1648</v>
+      </c>
+      <c r="V8" s="37"/>
+      <c r="W8" s="37" t="s">
+        <v>1281</v>
       </c>
       <c r="X8" s="2">
         <v>3</v>
@@ -6329,47 +6391,47 @@
       <c r="G9" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="H9" s="38" t="s">
-        <v>1657</v>
-      </c>
-      <c r="I9" s="38" t="s">
+      <c r="H9" s="37" t="s">
+        <v>1628</v>
+      </c>
+      <c r="I9" s="37" t="s">
         <v>302</v>
       </c>
-      <c r="J9" s="38" t="s">
+      <c r="J9" s="37" t="s">
         <v>339</v>
       </c>
-      <c r="K9" s="38"/>
-      <c r="L9" s="38" t="s">
-        <v>1485</v>
-      </c>
-      <c r="M9" s="38" t="s">
-        <v>1658</v>
+      <c r="K9" s="37"/>
+      <c r="L9" s="37" t="s">
+        <v>1464</v>
+      </c>
+      <c r="M9" s="58" t="s">
+        <v>1629</v>
       </c>
       <c r="N9" s="5" t="s">
-        <v>1662</v>
-      </c>
-      <c r="O9" s="38" t="s">
-        <v>1659</v>
-      </c>
-      <c r="P9" s="38"/>
-      <c r="Q9" s="38" t="s">
-        <v>1660</v>
-      </c>
-      <c r="R9" s="38" t="s">
+        <v>1633</v>
+      </c>
+      <c r="O9" s="37" t="s">
+        <v>1630</v>
+      </c>
+      <c r="P9" s="37"/>
+      <c r="Q9" s="37" t="s">
+        <v>1631</v>
+      </c>
+      <c r="R9" s="37" t="s">
         <v>558</v>
       </c>
-      <c r="S9" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="T9" s="39" t="s">
-        <v>1678</v>
-      </c>
-      <c r="U9" s="39" t="s">
+      <c r="S9" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="T9" s="38" t="s">
+        <v>1649</v>
+      </c>
+      <c r="U9" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="V9" s="38"/>
-      <c r="W9" s="38" t="s">
-        <v>1293</v>
+      <c r="V9" s="37"/>
+      <c r="W9" s="37" t="s">
+        <v>1281</v>
       </c>
       <c r="X9" s="2">
         <v>3</v>
@@ -6391,18 +6453,18 @@
       <c r="G10" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="H10" s="54" t="s">
+      <c r="H10" s="48" t="s">
         <v>67</v>
       </c>
       <c r="I10" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="J10" s="55" t="s">
+      <c r="J10" s="49" t="s">
         <v>69</v>
       </c>
       <c r="K10" s="27"/>
       <c r="L10" s="27"/>
-      <c r="M10" s="56" t="s">
+      <c r="M10" s="59" t="s">
         <v>70</v>
       </c>
       <c r="N10" s="5" t="s">
@@ -6410,17 +6472,17 @@
       </c>
       <c r="O10" s="27"/>
       <c r="P10" s="27"/>
-      <c r="Q10" s="56" t="s">
+      <c r="Q10" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="R10" s="56"/>
-      <c r="S10" s="56" t="s">
+      <c r="R10" s="50"/>
+      <c r="S10" s="50" t="s">
         <v>73</v>
       </c>
-      <c r="T10" s="46" t="s">
+      <c r="T10" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="U10" s="46" t="s">
+      <c r="U10" s="40" t="s">
         <v>75</v>
       </c>
       <c r="V10" s="27"/>
@@ -6447,7 +6509,7 @@
       <c r="G11" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="32" t="s">
         <v>581</v>
       </c>
       <c r="I11" s="2" t="s">
@@ -6458,32 +6520,32 @@
       </c>
       <c r="K11" s="2"/>
       <c r="L11" s="2" t="s">
-        <v>1506</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>1643</v>
+        <v>1485</v>
+      </c>
+      <c r="M11" s="57" t="s">
+        <v>1615</v>
       </c>
       <c r="N11" s="5" t="s">
-        <v>1650</v>
+        <v>1622</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>1644</v>
+        <v>1616</v>
       </c>
       <c r="P11" s="2"/>
       <c r="Q11" s="2" t="s">
-        <v>1643</v>
+        <v>1615</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>1645</v>
+        <v>1617</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>1646</v>
+        <v>1618</v>
       </c>
       <c r="T11" s="18" t="s">
         <v>150</v>
       </c>
       <c r="U11" s="18" t="s">
-        <v>1413</v>
+        <v>1393</v>
       </c>
       <c r="V11" s="2"/>
       <c r="W11" s="2" t="s">
@@ -6509,7 +6571,7 @@
       <c r="G12" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="H12" s="32" t="s">
         <v>581</v>
       </c>
       <c r="I12" s="2" t="s">
@@ -6520,32 +6582,32 @@
       </c>
       <c r="K12" s="2"/>
       <c r="L12" s="2" t="s">
-        <v>1506</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>1647</v>
+        <v>1485</v>
+      </c>
+      <c r="M12" s="57" t="s">
+        <v>1619</v>
       </c>
       <c r="N12" s="5" t="s">
-        <v>1651</v>
+        <v>1623</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>1644</v>
+        <v>1616</v>
       </c>
       <c r="P12" s="2"/>
       <c r="Q12" s="2" t="s">
-        <v>1648</v>
+        <v>1620</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>1645</v>
+        <v>1617</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>1649</v>
+        <v>1621</v>
       </c>
       <c r="T12" s="18" t="s">
-        <v>1627</v>
+        <v>1599</v>
       </c>
       <c r="U12" s="18" t="s">
-        <v>1679</v>
+        <v>1650</v>
       </c>
       <c r="V12" s="2"/>
       <c r="W12" s="2" t="s">
@@ -6582,7 +6644,7 @@
       </c>
       <c r="K13" s="9"/>
       <c r="L13" s="9"/>
-      <c r="M13" s="10" t="s">
+      <c r="M13" s="60" t="s">
         <v>82</v>
       </c>
       <c r="N13" s="9" t="s">
@@ -6600,7 +6662,7 @@
       <c r="T13" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="U13" s="53" t="s">
+      <c r="U13" s="47" t="s">
         <v>86</v>
       </c>
       <c r="V13" s="9"/>
@@ -6627,27 +6689,27 @@
       <c r="G14" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H14" s="32" t="s">
         <v>67</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>316</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>1631</v>
+        <v>1603</v>
       </c>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
-      <c r="M14" s="2" t="s">
-        <v>1632</v>
+      <c r="M14" s="57" t="s">
+        <v>1604</v>
       </c>
       <c r="N14" s="5" t="s">
-        <v>1642</v>
+        <v>1614</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
       <c r="Q14" s="2" t="s">
-        <v>1633</v>
+        <v>1605</v>
       </c>
       <c r="R14" s="2" t="s">
         <v>558</v>
@@ -6659,7 +6721,7 @@
         <v>492</v>
       </c>
       <c r="U14" s="18" t="s">
-        <v>1641</v>
+        <v>1613</v>
       </c>
       <c r="V14" s="2"/>
       <c r="W14" s="2" t="s">
@@ -6685,27 +6747,27 @@
       <c r="G15" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="H15" s="32" t="s">
         <v>67</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>316</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>1631</v>
+        <v>1603</v>
       </c>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
-      <c r="M15" s="2" t="s">
-        <v>1638</v>
+      <c r="M15" s="57" t="s">
+        <v>1610</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>1637</v>
+        <v>1609</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
       <c r="Q15" s="2" t="s">
-        <v>1633</v>
+        <v>1605</v>
       </c>
       <c r="R15" s="2" t="s">
         <v>558</v>
@@ -6714,7 +6776,7 @@
         <v>32</v>
       </c>
       <c r="T15" s="18" t="s">
-        <v>1639</v>
+        <v>1611</v>
       </c>
       <c r="U15" s="18" t="s">
         <v>368</v>
@@ -6743,8 +6805,8 @@
       <c r="G16" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="H16" s="2" t="s">
-        <v>1063</v>
+      <c r="H16" s="32" t="s">
+        <v>1051</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>80</v>
@@ -6754,16 +6816,16 @@
       </c>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
-      <c r="M16" s="2" t="s">
-        <v>1634</v>
+      <c r="M16" s="57" t="s">
+        <v>1606</v>
       </c>
       <c r="N16" s="4" t="s">
-        <v>1636</v>
+        <v>1608</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
       <c r="Q16" s="2" t="s">
-        <v>1635</v>
+        <v>1607</v>
       </c>
       <c r="R16" s="2" t="s">
         <v>558</v>
@@ -6772,10 +6834,10 @@
         <v>32</v>
       </c>
       <c r="T16" s="18" t="s">
-        <v>1639</v>
+        <v>1611</v>
       </c>
       <c r="U16" s="18" t="s">
-        <v>1640</v>
+        <v>1612</v>
       </c>
       <c r="V16" s="2"/>
       <c r="W16" s="2" t="s">
@@ -6812,7 +6874,7 @@
       </c>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
-      <c r="M17" s="3" t="s">
+      <c r="M17" s="56" t="s">
         <v>95</v>
       </c>
       <c r="N17" s="2" t="s">
@@ -6866,7 +6928,7 @@
       </c>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
-      <c r="M18" s="3" t="s">
+      <c r="M18" s="56" t="s">
         <v>101</v>
       </c>
       <c r="N18" s="2" t="s">
@@ -6920,7 +6982,7 @@
       </c>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
-      <c r="M19" s="3" t="s">
+      <c r="M19" s="56" t="s">
         <v>108</v>
       </c>
       <c r="N19" s="2" t="s">
@@ -6974,7 +7036,7 @@
       </c>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
-      <c r="M20" s="3" t="s">
+      <c r="M20" s="56" t="s">
         <v>115</v>
       </c>
       <c r="N20" s="2" t="s">
@@ -7017,7 +7079,7 @@
       <c r="G21" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="H21" s="2" t="s">
+      <c r="H21" s="32" t="s">
         <v>606</v>
       </c>
       <c r="I21" s="2" t="s">
@@ -7028,16 +7090,16 @@
       </c>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
-      <c r="M21" s="2" t="s">
-        <v>1600</v>
+      <c r="M21" s="57" t="s">
+        <v>1572</v>
       </c>
       <c r="N21" s="5" t="s">
-        <v>1618</v>
+        <v>1590</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
       <c r="Q21" s="2" t="s">
-        <v>1600</v>
+        <v>1572</v>
       </c>
       <c r="R21" s="2" t="s">
         <v>558</v>
@@ -7049,7 +7111,7 @@
         <v>381</v>
       </c>
       <c r="U21" s="18" t="s">
-        <v>1626</v>
+        <v>1598</v>
       </c>
       <c r="V21" s="2"/>
       <c r="W21" s="2" t="s">
@@ -7075,8 +7137,8 @@
       <c r="G22" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="H22" s="2" t="s">
-        <v>1601</v>
+      <c r="H22" s="32" t="s">
+        <v>1573</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>113</v>
@@ -7086,18 +7148,18 @@
       </c>
       <c r="K22" s="2"/>
       <c r="L22" s="2" t="s">
-        <v>1602</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>1603</v>
+        <v>1574</v>
+      </c>
+      <c r="M22" s="57" t="s">
+        <v>1575</v>
       </c>
       <c r="N22" s="5" t="s">
-        <v>1619</v>
+        <v>1591</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
       <c r="Q22" s="2" t="s">
-        <v>1604</v>
+        <v>1576</v>
       </c>
       <c r="R22" s="2" t="s">
         <v>558</v>
@@ -7135,31 +7197,31 @@
       <c r="G23" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="H23" s="2" t="s">
+      <c r="H23" s="32" t="s">
         <v>543</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>125</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>1605</v>
+        <v>1577</v>
       </c>
       <c r="K23" s="2"/>
       <c r="L23" s="2" t="s">
-        <v>1606</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>1607</v>
+        <v>1578</v>
+      </c>
+      <c r="M23" s="57" t="s">
+        <v>1579</v>
       </c>
       <c r="N23" s="5" t="s">
-        <v>1620</v>
+        <v>1592</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>1235</v>
+        <v>1223</v>
       </c>
       <c r="P23" s="2"/>
       <c r="Q23" s="2" t="s">
-        <v>1608</v>
+        <v>1580</v>
       </c>
       <c r="R23" s="2" t="s">
         <v>558</v>
@@ -7168,10 +7230,10 @@
         <v>32</v>
       </c>
       <c r="T23" s="18" t="s">
-        <v>1627</v>
+        <v>1599</v>
       </c>
       <c r="U23" s="18" t="s">
-        <v>1628</v>
+        <v>1600</v>
       </c>
       <c r="V23" s="2"/>
       <c r="W23" s="2" t="s">
@@ -7197,31 +7259,31 @@
       <c r="G24" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="H24" s="32" t="s">
         <v>543</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>125</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>1605</v>
+        <v>1577</v>
       </c>
       <c r="K24" s="2"/>
       <c r="L24" s="2" t="s">
-        <v>1606</v>
-      </c>
-      <c r="M24" s="2" t="s">
-        <v>1609</v>
+        <v>1578</v>
+      </c>
+      <c r="M24" s="57" t="s">
+        <v>1581</v>
       </c>
       <c r="N24" s="5" t="s">
-        <v>1621</v>
+        <v>1593</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>1235</v>
+        <v>1223</v>
       </c>
       <c r="P24" s="2"/>
       <c r="Q24" s="2" t="s">
-        <v>1238</v>
+        <v>1226</v>
       </c>
       <c r="R24" s="2" t="s">
         <v>558</v>
@@ -7230,10 +7292,10 @@
         <v>32</v>
       </c>
       <c r="T24" s="18" t="s">
-        <v>1627</v>
+        <v>1599</v>
       </c>
       <c r="U24" s="18" t="s">
-        <v>1628</v>
+        <v>1600</v>
       </c>
       <c r="V24" s="2"/>
       <c r="W24" s="2" t="s">
@@ -7259,31 +7321,31 @@
       <c r="G25" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="H25" s="32" t="s">
         <v>543</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>125</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>1605</v>
+        <v>1577</v>
       </c>
       <c r="K25" s="2"/>
       <c r="L25" s="2" t="s">
-        <v>1606</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>1610</v>
+        <v>1578</v>
+      </c>
+      <c r="M25" s="57" t="s">
+        <v>1582</v>
       </c>
       <c r="N25" s="5" t="s">
-        <v>1622</v>
+        <v>1594</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>1235</v>
+        <v>1223</v>
       </c>
       <c r="P25" s="2"/>
       <c r="Q25" s="2" t="s">
-        <v>1611</v>
+        <v>1583</v>
       </c>
       <c r="R25" s="2" t="s">
         <v>558</v>
@@ -7292,10 +7354,10 @@
         <v>32</v>
       </c>
       <c r="T25" s="18" t="s">
-        <v>1627</v>
+        <v>1599</v>
       </c>
       <c r="U25" s="18" t="s">
-        <v>1628</v>
+        <v>1600</v>
       </c>
       <c r="V25" s="2"/>
       <c r="W25" s="2" t="s">
@@ -7321,31 +7383,31 @@
       <c r="G26" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="H26" s="2" t="s">
+      <c r="H26" s="32" t="s">
         <v>543</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>125</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>1605</v>
+        <v>1577</v>
       </c>
       <c r="K26" s="2"/>
       <c r="L26" s="2" t="s">
-        <v>1606</v>
-      </c>
-      <c r="M26" s="2" t="s">
-        <v>1612</v>
+        <v>1578</v>
+      </c>
+      <c r="M26" s="57" t="s">
+        <v>1584</v>
       </c>
       <c r="N26" s="5" t="s">
-        <v>1623</v>
+        <v>1595</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>1235</v>
+        <v>1223</v>
       </c>
       <c r="P26" s="2"/>
       <c r="Q26" s="2" t="s">
-        <v>1613</v>
+        <v>1585</v>
       </c>
       <c r="R26" s="2" t="s">
         <v>558</v>
@@ -7354,10 +7416,10 @@
         <v>32</v>
       </c>
       <c r="T26" s="18" t="s">
-        <v>1627</v>
+        <v>1599</v>
       </c>
       <c r="U26" s="18" t="s">
-        <v>1628</v>
+        <v>1600</v>
       </c>
       <c r="V26" s="2"/>
       <c r="W26" s="2" t="s">
@@ -7383,7 +7445,7 @@
       <c r="G27" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="H27" s="2" t="s">
+      <c r="H27" s="32" t="s">
         <v>905</v>
       </c>
       <c r="I27" s="2" t="s">
@@ -7394,18 +7456,18 @@
       </c>
       <c r="K27" s="2"/>
       <c r="L27" s="2" t="s">
-        <v>1519</v>
-      </c>
-      <c r="M27" s="2" t="s">
-        <v>1614</v>
+        <v>1497</v>
+      </c>
+      <c r="M27" s="57" t="s">
+        <v>1586</v>
       </c>
       <c r="N27" s="5" t="s">
-        <v>1624</v>
+        <v>1596</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" s="2"/>
       <c r="Q27" s="2" t="s">
-        <v>1614</v>
+        <v>1586</v>
       </c>
       <c r="R27" s="2" t="s">
         <v>558</v>
@@ -7443,29 +7505,29 @@
       <c r="G28" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="H28" s="2" t="s">
+      <c r="H28" s="32" t="s">
         <v>434</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>302</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>1615</v>
+        <v>1587</v>
       </c>
       <c r="K28" s="2"/>
       <c r="L28" s="2" t="s">
-        <v>1616</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>1617</v>
+        <v>1588</v>
+      </c>
+      <c r="M28" s="57" t="s">
+        <v>1589</v>
       </c>
       <c r="N28" s="5" t="s">
-        <v>1625</v>
+        <v>1597</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" s="2"/>
       <c r="Q28" s="2" t="s">
-        <v>1617</v>
+        <v>1589</v>
       </c>
       <c r="R28" s="2" t="s">
         <v>558</v>
@@ -7474,10 +7536,10 @@
         <v>32</v>
       </c>
       <c r="T28" s="18" t="s">
-        <v>1629</v>
+        <v>1601</v>
       </c>
       <c r="U28" s="18" t="s">
-        <v>1630</v>
+        <v>1602</v>
       </c>
       <c r="V28" s="2"/>
       <c r="W28" s="2" t="s">
@@ -7518,7 +7580,7 @@
       </c>
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
-      <c r="M29" s="3" t="s">
+      <c r="M29" s="56" t="s">
         <v>127</v>
       </c>
       <c r="N29" s="2" t="s">
@@ -7578,7 +7640,7 @@
       </c>
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
-      <c r="M30" s="3" t="s">
+      <c r="M30" s="56" t="s">
         <v>135</v>
       </c>
       <c r="N30" s="2" t="s">
@@ -7627,8 +7689,8 @@
       <c r="G31" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="H31" s="2" t="s">
-        <v>1534</v>
+      <c r="H31" s="32" t="s">
+        <v>1676</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>302</v>
@@ -7638,18 +7700,18 @@
       </c>
       <c r="K31" s="2"/>
       <c r="L31" s="2" t="s">
-        <v>1565</v>
-      </c>
-      <c r="M31" s="2" t="s">
-        <v>1566</v>
+        <v>1542</v>
+      </c>
+      <c r="M31" s="57" t="s">
+        <v>1543</v>
       </c>
       <c r="N31" s="5" t="s">
-        <v>1586</v>
+        <v>1559</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
       <c r="Q31" s="2" t="s">
-        <v>1567</v>
+        <v>1544</v>
       </c>
       <c r="R31" s="2" t="s">
         <v>558</v>
@@ -7658,14 +7720,14 @@
         <v>32</v>
       </c>
       <c r="T31" s="18" t="s">
-        <v>1428</v>
+        <v>1408</v>
       </c>
       <c r="U31" s="18" t="s">
         <v>382</v>
       </c>
       <c r="V31" s="2"/>
       <c r="W31" s="2" t="s">
-        <v>1162</v>
+        <v>1150</v>
       </c>
       <c r="X31" s="2">
         <v>2</v>
@@ -7691,8 +7753,8 @@
       <c r="G32" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="H32" s="2" t="s">
-        <v>1568</v>
+      <c r="H32" s="32" t="s">
+        <v>1677</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>487</v>
@@ -7702,18 +7764,18 @@
       </c>
       <c r="K32" s="2"/>
       <c r="L32" s="2" t="s">
-        <v>1569</v>
-      </c>
-      <c r="M32" s="2" t="s">
-        <v>1570</v>
+        <v>1545</v>
+      </c>
+      <c r="M32" s="57" t="s">
+        <v>1546</v>
       </c>
       <c r="N32" s="5" t="s">
-        <v>1587</v>
+        <v>1560</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
       <c r="Q32" s="2" t="s">
-        <v>1571</v>
+        <v>1547</v>
       </c>
       <c r="R32" s="2" t="s">
         <v>558</v>
@@ -7722,14 +7784,14 @@
         <v>32</v>
       </c>
       <c r="T32" s="18" t="s">
-        <v>1595</v>
+        <v>1567</v>
       </c>
       <c r="U32" s="18">
         <v>207</v>
       </c>
       <c r="V32" s="2"/>
       <c r="W32" s="2" t="s">
-        <v>1162</v>
+        <v>1150</v>
       </c>
       <c r="X32" s="2">
         <v>2</v>
@@ -7755,29 +7817,29 @@
       <c r="G33" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="H33" s="2" t="s">
-        <v>1572</v>
+      <c r="H33" s="32" t="s">
+        <v>1678</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>656</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>1225</v>
+        <v>1213</v>
       </c>
       <c r="K33" s="2"/>
       <c r="L33" s="2" t="s">
-        <v>1573</v>
-      </c>
-      <c r="M33" s="2" t="s">
-        <v>1574</v>
+        <v>1548</v>
+      </c>
+      <c r="M33" s="57" t="s">
+        <v>1549</v>
       </c>
       <c r="N33" s="5" t="s">
-        <v>1588</v>
+        <v>1561</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" s="2"/>
       <c r="Q33" s="2" t="s">
-        <v>1575</v>
+        <v>1550</v>
       </c>
       <c r="R33" s="2" t="s">
         <v>558</v>
@@ -7786,14 +7848,14 @@
         <v>32</v>
       </c>
       <c r="T33" s="18" t="s">
-        <v>1596</v>
+        <v>1568</v>
       </c>
       <c r="U33" s="18" t="s">
         <v>451</v>
       </c>
       <c r="V33" s="2"/>
       <c r="W33" s="2" t="s">
-        <v>1162</v>
+        <v>1150</v>
       </c>
       <c r="X33" s="2">
         <v>2</v>
@@ -7819,8 +7881,8 @@
       <c r="G34" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="H34" s="2" t="s">
-        <v>1576</v>
+      <c r="H34" s="32" t="s">
+        <v>1232</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>302</v>
@@ -7830,18 +7892,18 @@
       </c>
       <c r="K34" s="2"/>
       <c r="L34" s="2" t="s">
-        <v>1565</v>
-      </c>
-      <c r="M34" s="2" t="s">
-        <v>1577</v>
+        <v>1542</v>
+      </c>
+      <c r="M34" s="57" t="s">
+        <v>1551</v>
       </c>
       <c r="N34" s="5" t="s">
-        <v>1589</v>
+        <v>1562</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" s="2"/>
       <c r="Q34" s="2" t="s">
-        <v>1578</v>
+        <v>1552</v>
       </c>
       <c r="R34" s="2" t="s">
         <v>558</v>
@@ -7850,14 +7912,14 @@
         <v>32</v>
       </c>
       <c r="T34" s="18" t="s">
-        <v>1597</v>
+        <v>1569</v>
       </c>
       <c r="U34" s="18" t="s">
-        <v>1579</v>
+        <v>1553</v>
       </c>
       <c r="V34" s="2"/>
       <c r="W34" s="2" t="s">
-        <v>1162</v>
+        <v>1150</v>
       </c>
       <c r="X34" s="2">
         <v>2</v>
@@ -7883,29 +7945,29 @@
       <c r="G35" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="H35" s="2" t="s">
-        <v>1580</v>
+      <c r="H35" s="32" t="s">
+        <v>1679</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>1581</v>
+        <v>1554</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>1582</v>
+        <v>1555</v>
       </c>
       <c r="K35" s="2"/>
       <c r="L35" s="2" t="s">
-        <v>1583</v>
-      </c>
-      <c r="M35" s="2" t="s">
-        <v>1584</v>
+        <v>1556</v>
+      </c>
+      <c r="M35" s="57" t="s">
+        <v>1557</v>
       </c>
       <c r="N35" s="5" t="s">
-        <v>1590</v>
+        <v>1563</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" s="2"/>
       <c r="Q35" s="2" t="s">
-        <v>1585</v>
+        <v>1558</v>
       </c>
       <c r="R35" s="2" t="s">
         <v>558</v>
@@ -7914,14 +7976,14 @@
         <v>32</v>
       </c>
       <c r="T35" s="18" t="s">
-        <v>1680</v>
+        <v>1651</v>
       </c>
       <c r="U35" s="18" t="s">
         <v>139</v>
       </c>
       <c r="V35" s="2"/>
       <c r="W35" s="2" t="s">
-        <v>1162</v>
+        <v>1150</v>
       </c>
       <c r="X35" s="2">
         <v>2</v>
@@ -7947,8 +8009,8 @@
       <c r="G36" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="H36" s="2" t="s">
-        <v>1591</v>
+      <c r="H36" s="32" t="s">
+        <v>1680</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>302</v>
@@ -7958,18 +8020,18 @@
       </c>
       <c r="K36" s="2"/>
       <c r="L36" s="2" t="s">
-        <v>1565</v>
-      </c>
-      <c r="M36" s="2" t="s">
-        <v>1592</v>
+        <v>1542</v>
+      </c>
+      <c r="M36" s="57" t="s">
+        <v>1564</v>
       </c>
       <c r="N36" s="5" t="s">
-        <v>1594</v>
+        <v>1566</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" s="2"/>
       <c r="Q36" s="2" t="s">
-        <v>1593</v>
+        <v>1565</v>
       </c>
       <c r="R36" s="2" t="s">
         <v>558</v>
@@ -7978,14 +8040,14 @@
         <v>32</v>
       </c>
       <c r="T36" s="18" t="s">
-        <v>1598</v>
+        <v>1570</v>
       </c>
       <c r="U36" s="18" t="s">
-        <v>1599</v>
+        <v>1571</v>
       </c>
       <c r="V36" s="2"/>
       <c r="W36" s="2" t="s">
-        <v>1162</v>
+        <v>1150</v>
       </c>
       <c r="X36" s="2">
         <v>2</v>
@@ -8018,7 +8080,7 @@
       </c>
       <c r="K37" s="2"/>
       <c r="L37" s="2"/>
-      <c r="M37" s="3" t="s">
+      <c r="M37" s="56" t="s">
         <v>146</v>
       </c>
       <c r="N37" s="2" t="s">
@@ -8074,7 +8136,7 @@
       </c>
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
-      <c r="M38" s="3" t="s">
+      <c r="M38" s="56" t="s">
         <v>152</v>
       </c>
       <c r="N38" s="2" t="s">
@@ -8119,45 +8181,45 @@
       <c r="G39" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="H39" s="51" t="s">
+      <c r="H39" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="I39" s="52" t="s">
+      <c r="I39" s="46" t="s">
         <v>93</v>
       </c>
-      <c r="J39" s="52" t="s">
+      <c r="J39" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="K39" s="52"/>
-      <c r="L39" s="52" t="s">
-        <v>1246</v>
-      </c>
-      <c r="M39" s="52" t="s">
-        <v>1532</v>
+      <c r="K39" s="46"/>
+      <c r="L39" s="46" t="s">
+        <v>1234</v>
+      </c>
+      <c r="M39" s="61" t="s">
+        <v>1510</v>
       </c>
       <c r="N39" s="5" t="s">
-        <v>1535</v>
-      </c>
-      <c r="O39" s="52"/>
-      <c r="P39" s="52"/>
-      <c r="Q39" s="52" t="s">
-        <v>1533</v>
-      </c>
-      <c r="R39" s="52" t="s">
-        <v>1465</v>
-      </c>
-      <c r="S39" s="52" t="s">
+        <v>1513</v>
+      </c>
+      <c r="O39" s="46"/>
+      <c r="P39" s="46"/>
+      <c r="Q39" s="46" t="s">
+        <v>1511</v>
+      </c>
+      <c r="R39" s="46" t="s">
+        <v>1444</v>
+      </c>
+      <c r="S39" s="46" t="s">
         <v>619</v>
       </c>
-      <c r="T39" s="51" t="s">
-        <v>1541</v>
-      </c>
-      <c r="U39" s="51" t="s">
-        <v>1542</v>
-      </c>
-      <c r="V39" s="52"/>
-      <c r="W39" s="52" t="s">
-        <v>1162</v>
+      <c r="T39" s="45" t="s">
+        <v>1518</v>
+      </c>
+      <c r="U39" s="45" t="s">
+        <v>1519</v>
+      </c>
+      <c r="V39" s="46"/>
+      <c r="W39" s="46" t="s">
+        <v>1150</v>
       </c>
       <c r="X39" s="2">
         <v>3</v>
@@ -8179,43 +8241,43 @@
       <c r="G40" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="H40" s="49" t="s">
-        <v>1536</v>
-      </c>
-      <c r="I40" s="50" t="s">
+      <c r="H40" s="44" t="s">
+        <v>1681</v>
+      </c>
+      <c r="I40" s="44" t="s">
         <v>487</v>
       </c>
-      <c r="J40" s="50" t="s">
-        <v>1537</v>
-      </c>
-      <c r="K40" s="50"/>
-      <c r="L40" s="50"/>
-      <c r="M40" s="50" t="s">
-        <v>1538</v>
+      <c r="J40" s="44" t="s">
+        <v>1514</v>
+      </c>
+      <c r="K40" s="44"/>
+      <c r="L40" s="44"/>
+      <c r="M40" s="62" t="s">
+        <v>1515</v>
       </c>
       <c r="N40" s="5" t="s">
-        <v>1540</v>
-      </c>
-      <c r="O40" s="50"/>
-      <c r="P40" s="50"/>
-      <c r="Q40" s="50" t="s">
-        <v>1539</v>
-      </c>
-      <c r="R40" s="50" t="s">
-        <v>1465</v>
-      </c>
-      <c r="S40" s="50" t="s">
+        <v>1517</v>
+      </c>
+      <c r="O40" s="44"/>
+      <c r="P40" s="44"/>
+      <c r="Q40" s="44" t="s">
+        <v>1516</v>
+      </c>
+      <c r="R40" s="44" t="s">
+        <v>1444</v>
+      </c>
+      <c r="S40" s="44" t="s">
         <v>619</v>
       </c>
-      <c r="T40" s="49" t="s">
-        <v>1543</v>
-      </c>
-      <c r="U40" s="49" t="s">
-        <v>1544</v>
-      </c>
-      <c r="V40" s="50"/>
-      <c r="W40" s="50" t="s">
-        <v>1162</v>
+      <c r="T40" s="43" t="s">
+        <v>1520</v>
+      </c>
+      <c r="U40" s="43" t="s">
+        <v>1521</v>
+      </c>
+      <c r="V40" s="44"/>
+      <c r="W40" s="44" t="s">
+        <v>1150</v>
       </c>
       <c r="X40" s="2">
         <v>3</v>
@@ -8248,7 +8310,7 @@
       </c>
       <c r="K41" s="2"/>
       <c r="L41" s="2"/>
-      <c r="M41" s="3" t="s">
+      <c r="M41" s="56" t="s">
         <v>162</v>
       </c>
       <c r="N41" s="2" t="s">
@@ -8302,7 +8364,7 @@
       </c>
       <c r="K42" s="2"/>
       <c r="L42" s="2"/>
-      <c r="M42" s="3" t="s">
+      <c r="M42" s="56" t="s">
         <v>167</v>
       </c>
       <c r="N42" s="2" t="s">
@@ -8356,7 +8418,7 @@
       </c>
       <c r="K43" s="2"/>
       <c r="L43" s="2"/>
-      <c r="M43" s="3" t="s">
+      <c r="M43" s="56" t="s">
         <v>174</v>
       </c>
       <c r="N43" s="2" t="s">
@@ -8410,7 +8472,7 @@
       </c>
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
-      <c r="M44" s="3" t="s">
+      <c r="M44" s="56" t="s">
         <v>146</v>
       </c>
       <c r="N44" s="2" t="s">
@@ -8453,44 +8515,44 @@
       <c r="G45" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="H45" s="47" t="s">
+      <c r="H45" s="42" t="s">
         <v>161</v>
       </c>
-      <c r="I45" s="48" t="s">
+      <c r="I45" s="42" t="s">
         <v>93</v>
       </c>
-      <c r="J45" s="48" t="s">
+      <c r="J45" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="K45" s="48"/>
-      <c r="L45" s="48" t="s">
-        <v>1512</v>
-      </c>
-      <c r="M45" s="48" t="s">
-        <v>1513</v>
+      <c r="K45" s="42"/>
+      <c r="L45" s="42" t="s">
+        <v>1491</v>
+      </c>
+      <c r="M45" s="63" t="s">
+        <v>1492</v>
       </c>
       <c r="N45" s="5" t="s">
-        <v>1524</v>
-      </c>
-      <c r="O45" s="48"/>
-      <c r="P45" s="48"/>
-      <c r="Q45" s="48" t="s">
-        <v>1513</v>
-      </c>
-      <c r="R45" s="48" t="s">
+        <v>1502</v>
+      </c>
+      <c r="O45" s="42"/>
+      <c r="P45" s="42"/>
+      <c r="Q45" s="42" t="s">
+        <v>1492</v>
+      </c>
+      <c r="R45" s="42" t="s">
         <v>558</v>
       </c>
-      <c r="S45" s="48" t="s">
-        <v>32</v>
-      </c>
-      <c r="T45" s="47" t="s">
+      <c r="S45" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="T45" s="41" t="s">
         <v>715</v>
       </c>
-      <c r="U45" s="47" t="s">
+      <c r="U45" s="41" t="s">
         <v>967</v>
       </c>
-      <c r="V45" s="47"/>
-      <c r="W45" s="47" t="s">
+      <c r="V45" s="41"/>
+      <c r="W45" s="41" t="s">
         <v>561</v>
       </c>
       <c r="X45" s="2">
@@ -8513,44 +8575,44 @@
       <c r="G46" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="H46" s="47" t="s">
+      <c r="H46" s="42" t="s">
         <v>733</v>
       </c>
-      <c r="I46" s="48" t="s">
+      <c r="I46" s="42" t="s">
         <v>316</v>
       </c>
-      <c r="J46" s="48" t="s">
+      <c r="J46" s="42" t="s">
         <v>317</v>
       </c>
-      <c r="K46" s="48"/>
-      <c r="L46" s="48" t="s">
-        <v>1514</v>
-      </c>
-      <c r="M46" s="48" t="s">
-        <v>1310</v>
+      <c r="K46" s="42"/>
+      <c r="L46" s="42" t="s">
+        <v>1493</v>
+      </c>
+      <c r="M46" s="63" t="s">
+        <v>1298</v>
       </c>
       <c r="N46" s="5" t="s">
-        <v>1525</v>
-      </c>
-      <c r="O46" s="48"/>
-      <c r="P46" s="48"/>
-      <c r="Q46" s="48" t="s">
-        <v>1310</v>
-      </c>
-      <c r="R46" s="48" t="s">
+        <v>1503</v>
+      </c>
+      <c r="O46" s="42"/>
+      <c r="P46" s="42"/>
+      <c r="Q46" s="42" t="s">
+        <v>1298</v>
+      </c>
+      <c r="R46" s="42" t="s">
         <v>558</v>
       </c>
-      <c r="S46" s="48" t="s">
-        <v>32</v>
-      </c>
-      <c r="T46" s="47" t="s">
+      <c r="S46" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="T46" s="41" t="s">
         <v>515</v>
       </c>
-      <c r="U46" s="47" t="s">
-        <v>1489</v>
-      </c>
-      <c r="V46" s="47"/>
-      <c r="W46" s="47" t="s">
+      <c r="U46" s="41" t="s">
+        <v>1468</v>
+      </c>
+      <c r="V46" s="41"/>
+      <c r="W46" s="41" t="s">
         <v>561</v>
       </c>
       <c r="X46" s="2">
@@ -8573,44 +8635,44 @@
       <c r="G47" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="H47" s="47" t="s">
-        <v>1515</v>
-      </c>
-      <c r="I47" s="48" t="s">
+      <c r="H47" s="42" t="s">
+        <v>1682</v>
+      </c>
+      <c r="I47" s="42" t="s">
         <v>93</v>
       </c>
-      <c r="J47" s="48" t="s">
+      <c r="J47" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="K47" s="48"/>
-      <c r="L47" s="48" t="s">
-        <v>1512</v>
-      </c>
-      <c r="M47" s="48" t="s">
-        <v>1516</v>
+      <c r="K47" s="42"/>
+      <c r="L47" s="42" t="s">
+        <v>1491</v>
+      </c>
+      <c r="M47" s="63" t="s">
+        <v>1494</v>
       </c>
       <c r="N47" s="5" t="s">
-        <v>1526</v>
-      </c>
-      <c r="O47" s="48"/>
-      <c r="P47" s="48"/>
-      <c r="Q47" s="48" t="s">
-        <v>1516</v>
-      </c>
-      <c r="R47" s="48" t="s">
+        <v>1504</v>
+      </c>
+      <c r="O47" s="42"/>
+      <c r="P47" s="42"/>
+      <c r="Q47" s="42" t="s">
+        <v>1494</v>
+      </c>
+      <c r="R47" s="42" t="s">
         <v>558</v>
       </c>
-      <c r="S47" s="48" t="s">
-        <v>32</v>
-      </c>
-      <c r="T47" s="47" t="s">
-        <v>1545</v>
-      </c>
-      <c r="U47" s="47" t="s">
-        <v>1546</v>
-      </c>
-      <c r="V47" s="47"/>
-      <c r="W47" s="47" t="s">
+      <c r="S47" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="T47" s="41" t="s">
+        <v>1522</v>
+      </c>
+      <c r="U47" s="41" t="s">
+        <v>1523</v>
+      </c>
+      <c r="V47" s="41"/>
+      <c r="W47" s="41" t="s">
         <v>561</v>
       </c>
       <c r="X47" s="2">
@@ -8633,44 +8695,44 @@
       <c r="G48" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="H48" s="47" t="s">
+      <c r="H48" s="42" t="s">
         <v>280</v>
       </c>
-      <c r="I48" s="48" t="s">
+      <c r="I48" s="42" t="s">
         <v>302</v>
       </c>
-      <c r="J48" s="48" t="s">
+      <c r="J48" s="42" t="s">
         <v>339</v>
       </c>
-      <c r="K48" s="48"/>
-      <c r="L48" s="48" t="s">
-        <v>1435</v>
-      </c>
-      <c r="M48" s="48" t="s">
-        <v>1517</v>
+      <c r="K48" s="42"/>
+      <c r="L48" s="42" t="s">
+        <v>1414</v>
+      </c>
+      <c r="M48" s="63" t="s">
+        <v>1495</v>
       </c>
       <c r="N48" s="5" t="s">
-        <v>1527</v>
-      </c>
-      <c r="O48" s="48"/>
-      <c r="P48" s="48"/>
-      <c r="Q48" s="48" t="s">
-        <v>1518</v>
-      </c>
-      <c r="R48" s="48" t="s">
+        <v>1505</v>
+      </c>
+      <c r="O48" s="42"/>
+      <c r="P48" s="42"/>
+      <c r="Q48" s="42" t="s">
+        <v>1496</v>
+      </c>
+      <c r="R48" s="42" t="s">
         <v>558</v>
       </c>
-      <c r="S48" s="48" t="s">
-        <v>32</v>
-      </c>
-      <c r="T48" s="47" t="s">
-        <v>1547</v>
-      </c>
-      <c r="U48" s="47" t="s">
-        <v>1548</v>
-      </c>
-      <c r="V48" s="47"/>
-      <c r="W48" s="47" t="s">
+      <c r="S48" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="T48" s="41" t="s">
+        <v>1524</v>
+      </c>
+      <c r="U48" s="41" t="s">
+        <v>1525</v>
+      </c>
+      <c r="V48" s="41"/>
+      <c r="W48" s="41" t="s">
         <v>561</v>
       </c>
       <c r="X48" s="2">
@@ -8693,44 +8755,44 @@
       <c r="G49" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="H49" s="47" t="s">
+      <c r="H49" s="42" t="s">
         <v>905</v>
       </c>
-      <c r="I49" s="48" t="s">
+      <c r="I49" s="42" t="s">
         <v>93</v>
       </c>
-      <c r="J49" s="48" t="s">
+      <c r="J49" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="K49" s="48"/>
-      <c r="L49" s="48" t="s">
-        <v>1519</v>
-      </c>
-      <c r="M49" s="48" t="s">
-        <v>1520</v>
+      <c r="K49" s="42"/>
+      <c r="L49" s="42" t="s">
+        <v>1497</v>
+      </c>
+      <c r="M49" s="63" t="s">
+        <v>1498</v>
       </c>
       <c r="N49" s="5" t="s">
-        <v>1528</v>
-      </c>
-      <c r="O49" s="48"/>
-      <c r="P49" s="48"/>
-      <c r="Q49" s="48" t="s">
-        <v>1520</v>
-      </c>
-      <c r="R49" s="48" t="s">
+        <v>1506</v>
+      </c>
+      <c r="O49" s="42"/>
+      <c r="P49" s="42"/>
+      <c r="Q49" s="42" t="s">
+        <v>1498</v>
+      </c>
+      <c r="R49" s="42" t="s">
         <v>558</v>
       </c>
-      <c r="S49" s="48" t="s">
-        <v>32</v>
-      </c>
-      <c r="T49" s="47" t="s">
+      <c r="S49" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="T49" s="41" t="s">
         <v>268</v>
       </c>
-      <c r="U49" s="47" t="s">
+      <c r="U49" s="41" t="s">
         <v>269</v>
       </c>
-      <c r="V49" s="47"/>
-      <c r="W49" s="47" t="s">
+      <c r="V49" s="41"/>
+      <c r="W49" s="41" t="s">
         <v>561</v>
       </c>
       <c r="X49" s="2">
@@ -8753,44 +8815,44 @@
       <c r="G50" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="H50" s="47" t="s">
+      <c r="H50" s="42" t="s">
         <v>132</v>
       </c>
-      <c r="I50" s="48" t="s">
+      <c r="I50" s="42" t="s">
         <v>93</v>
       </c>
-      <c r="J50" s="48" t="s">
+      <c r="J50" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="K50" s="48"/>
-      <c r="L50" s="48" t="s">
-        <v>1512</v>
-      </c>
-      <c r="M50" s="48" t="s">
-        <v>1521</v>
+      <c r="K50" s="42"/>
+      <c r="L50" s="42" t="s">
+        <v>1491</v>
+      </c>
+      <c r="M50" s="63" t="s">
+        <v>1499</v>
       </c>
       <c r="N50" s="5" t="s">
-        <v>1529</v>
-      </c>
-      <c r="O50" s="48"/>
-      <c r="P50" s="48"/>
-      <c r="Q50" s="48" t="s">
-        <v>1521</v>
-      </c>
-      <c r="R50" s="48" t="s">
+        <v>1507</v>
+      </c>
+      <c r="O50" s="42"/>
+      <c r="P50" s="42"/>
+      <c r="Q50" s="42" t="s">
+        <v>1499</v>
+      </c>
+      <c r="R50" s="42" t="s">
         <v>558</v>
       </c>
-      <c r="S50" s="48" t="s">
-        <v>32</v>
-      </c>
-      <c r="T50" s="47" t="s">
+      <c r="S50" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="T50" s="41" t="s">
         <v>390</v>
       </c>
-      <c r="U50" s="47" t="s">
+      <c r="U50" s="41" t="s">
         <v>1008</v>
       </c>
-      <c r="V50" s="47"/>
-      <c r="W50" s="47" t="s">
+      <c r="V50" s="41"/>
+      <c r="W50" s="41" t="s">
         <v>561</v>
       </c>
       <c r="X50" s="2">
@@ -8813,44 +8875,44 @@
       <c r="G51" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="H51" s="47" t="s">
+      <c r="H51" s="42" t="s">
         <v>92</v>
       </c>
-      <c r="I51" s="48" t="s">
+      <c r="I51" s="42" t="s">
         <v>93</v>
       </c>
-      <c r="J51" s="48" t="s">
+      <c r="J51" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="K51" s="48"/>
-      <c r="L51" s="48" t="s">
-        <v>1512</v>
-      </c>
-      <c r="M51" s="48" t="s">
-        <v>1522</v>
+      <c r="K51" s="42"/>
+      <c r="L51" s="42" t="s">
+        <v>1491</v>
+      </c>
+      <c r="M51" s="63" t="s">
+        <v>1500</v>
       </c>
       <c r="N51" s="5" t="s">
-        <v>1530</v>
-      </c>
-      <c r="O51" s="48"/>
-      <c r="P51" s="48"/>
-      <c r="Q51" s="48" t="s">
-        <v>1522</v>
-      </c>
-      <c r="R51" s="48" t="s">
+        <v>1508</v>
+      </c>
+      <c r="O51" s="42"/>
+      <c r="P51" s="42"/>
+      <c r="Q51" s="42" t="s">
+        <v>1500</v>
+      </c>
+      <c r="R51" s="42" t="s">
         <v>558</v>
       </c>
-      <c r="S51" s="48" t="s">
-        <v>32</v>
-      </c>
-      <c r="T51" s="47" t="s">
+      <c r="S51" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="T51" s="41" t="s">
         <v>615</v>
       </c>
-      <c r="U51" s="47" t="s">
+      <c r="U51" s="41" t="s">
         <v>151</v>
       </c>
-      <c r="V51" s="47"/>
-      <c r="W51" s="47" t="s">
+      <c r="V51" s="41"/>
+      <c r="W51" s="41" t="s">
         <v>561</v>
       </c>
       <c r="X51" s="2">
@@ -8873,44 +8935,44 @@
       <c r="G52" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="H52" s="47" t="s">
+      <c r="H52" s="42" t="s">
         <v>606</v>
       </c>
-      <c r="I52" s="48" t="s">
+      <c r="I52" s="42" t="s">
         <v>93</v>
       </c>
-      <c r="J52" s="48" t="s">
+      <c r="J52" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="K52" s="48"/>
-      <c r="L52" s="48" t="s">
-        <v>1512</v>
-      </c>
-      <c r="M52" s="48" t="s">
-        <v>1523</v>
+      <c r="K52" s="42"/>
+      <c r="L52" s="42" t="s">
+        <v>1491</v>
+      </c>
+      <c r="M52" s="63" t="s">
+        <v>1501</v>
       </c>
       <c r="N52" s="5" t="s">
-        <v>1531</v>
-      </c>
-      <c r="O52" s="48"/>
-      <c r="P52" s="48"/>
-      <c r="Q52" s="48" t="s">
-        <v>1523</v>
-      </c>
-      <c r="R52" s="48" t="s">
+        <v>1509</v>
+      </c>
+      <c r="O52" s="42"/>
+      <c r="P52" s="42"/>
+      <c r="Q52" s="42" t="s">
+        <v>1501</v>
+      </c>
+      <c r="R52" s="42" t="s">
         <v>558</v>
       </c>
-      <c r="S52" s="48" t="s">
-        <v>32</v>
-      </c>
-      <c r="T52" s="47" t="s">
+      <c r="S52" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="T52" s="41" t="s">
         <v>493</v>
       </c>
-      <c r="U52" s="47" t="s">
+      <c r="U52" s="41" t="s">
         <v>151</v>
       </c>
-      <c r="V52" s="47"/>
-      <c r="W52" s="47" t="s">
+      <c r="V52" s="41"/>
+      <c r="W52" s="41" t="s">
         <v>561</v>
       </c>
       <c r="X52" s="2">
@@ -8944,7 +9006,7 @@
       </c>
       <c r="K53" s="2"/>
       <c r="L53" s="2"/>
-      <c r="M53" s="3" t="s">
+      <c r="M53" s="56" t="s">
         <v>184</v>
       </c>
       <c r="N53" s="2" t="s">
@@ -8989,7 +9051,7 @@
       <c r="G54" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="H54" s="2" t="s">
+      <c r="H54" s="32" t="s">
         <v>123</v>
       </c>
       <c r="I54" s="2" t="s">
@@ -9000,18 +9062,18 @@
       </c>
       <c r="K54" s="2"/>
       <c r="L54" s="2" t="s">
-        <v>1500</v>
-      </c>
-      <c r="M54" s="2" t="s">
-        <v>1501</v>
+        <v>1479</v>
+      </c>
+      <c r="M54" s="57" t="s">
+        <v>1480</v>
       </c>
       <c r="N54" s="5" t="s">
-        <v>1509</v>
+        <v>1488</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" s="2"/>
       <c r="Q54" s="2" t="s">
-        <v>1502</v>
+        <v>1481</v>
       </c>
       <c r="R54" s="2" t="s">
         <v>558</v>
@@ -9020,14 +9082,14 @@
         <v>32</v>
       </c>
       <c r="T54" s="18" t="s">
-        <v>1549</v>
+        <v>1526</v>
       </c>
       <c r="U54" s="18" t="s">
-        <v>1550</v>
+        <v>1527</v>
       </c>
       <c r="V54" s="2"/>
       <c r="W54" s="2" t="s">
-        <v>1503</v>
+        <v>1482</v>
       </c>
       <c r="X54" s="2">
         <v>3</v>
@@ -9049,7 +9111,7 @@
       <c r="G55" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="H55" s="2" t="s">
+      <c r="H55" s="32" t="s">
         <v>904</v>
       </c>
       <c r="I55" s="2" t="s">
@@ -9060,18 +9122,18 @@
       </c>
       <c r="K55" s="2"/>
       <c r="L55" s="2" t="s">
-        <v>1500</v>
-      </c>
-      <c r="M55" s="2" t="s">
-        <v>1504</v>
+        <v>1479</v>
+      </c>
+      <c r="M55" s="57" t="s">
+        <v>1483</v>
       </c>
       <c r="N55" s="5" t="s">
-        <v>1510</v>
+        <v>1489</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" s="2"/>
       <c r="Q55" s="2" t="s">
-        <v>1505</v>
+        <v>1484</v>
       </c>
       <c r="R55" s="2" t="s">
         <v>558</v>
@@ -9080,14 +9142,14 @@
         <v>32</v>
       </c>
       <c r="T55" s="18" t="s">
-        <v>1551</v>
+        <v>1528</v>
       </c>
       <c r="U55" s="18" t="s">
-        <v>1552</v>
+        <v>1529</v>
       </c>
       <c r="V55" s="2"/>
       <c r="W55" s="2" t="s">
-        <v>1503</v>
+        <v>1482</v>
       </c>
       <c r="X55" s="2">
         <v>3</v>
@@ -9109,7 +9171,7 @@
       <c r="G56" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="H56" s="2" t="s">
+      <c r="H56" s="32" t="s">
         <v>230</v>
       </c>
       <c r="I56" s="2" t="s">
@@ -9120,18 +9182,18 @@
       </c>
       <c r="K56" s="2"/>
       <c r="L56" s="2" t="s">
-        <v>1506</v>
-      </c>
-      <c r="M56" s="2" t="s">
-        <v>1507</v>
+        <v>1485</v>
+      </c>
+      <c r="M56" s="57" t="s">
+        <v>1486</v>
       </c>
       <c r="N56" s="5" t="s">
-        <v>1511</v>
+        <v>1490</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" s="2"/>
       <c r="Q56" s="2" t="s">
-        <v>1508</v>
+        <v>1487</v>
       </c>
       <c r="R56" s="2" t="s">
         <v>558</v>
@@ -9140,14 +9202,14 @@
         <v>32</v>
       </c>
       <c r="T56" s="18" t="s">
-        <v>1553</v>
+        <v>1530</v>
       </c>
       <c r="U56" s="18" t="s">
-        <v>1554</v>
+        <v>1531</v>
       </c>
       <c r="V56" s="2"/>
       <c r="W56" s="2" t="s">
-        <v>1503</v>
+        <v>1482</v>
       </c>
       <c r="X56" s="2">
         <v>3</v>
@@ -9180,7 +9242,7 @@
       </c>
       <c r="K57" s="2"/>
       <c r="L57" s="2"/>
-      <c r="M57" s="3" t="s">
+      <c r="M57" s="56" t="s">
         <v>193</v>
       </c>
       <c r="N57" s="2" t="s">
@@ -9231,7 +9293,7 @@
       </c>
       <c r="K58" s="2"/>
       <c r="L58" s="2"/>
-      <c r="M58" s="3" t="s">
+      <c r="M58" s="56" t="s">
         <v>199</v>
       </c>
       <c r="N58" s="2" t="s">
@@ -9285,7 +9347,7 @@
       </c>
       <c r="K59" s="2"/>
       <c r="L59" s="2"/>
-      <c r="M59" s="3" t="s">
+      <c r="M59" s="56" t="s">
         <v>207</v>
       </c>
       <c r="N59" s="2" t="s">
@@ -9339,7 +9401,7 @@
       </c>
       <c r="K60" s="2"/>
       <c r="L60" s="2"/>
-      <c r="M60" s="3" t="s">
+      <c r="M60" s="56" t="s">
         <v>146</v>
       </c>
       <c r="N60" s="2" t="s">
@@ -9393,7 +9455,7 @@
       </c>
       <c r="K61" s="2"/>
       <c r="L61" s="2"/>
-      <c r="M61" s="3" t="s">
+      <c r="M61" s="56" t="s">
         <v>213</v>
       </c>
       <c r="N61" s="2" t="s">
@@ -9447,7 +9509,7 @@
       </c>
       <c r="K62" s="2"/>
       <c r="L62" s="2"/>
-      <c r="M62" s="3" t="s">
+      <c r="M62" s="56" t="s">
         <v>224</v>
       </c>
       <c r="N62" s="2" t="s">
@@ -9503,7 +9565,7 @@
       </c>
       <c r="K63" s="2"/>
       <c r="L63" s="2"/>
-      <c r="M63" s="3" t="s">
+      <c r="M63" s="56" t="s">
         <v>146</v>
       </c>
       <c r="N63" s="2" t="s">
@@ -9559,7 +9621,7 @@
       </c>
       <c r="K64" s="2"/>
       <c r="L64" s="2"/>
-      <c r="M64" s="3" t="s">
+      <c r="M64" s="56" t="s">
         <v>236</v>
       </c>
       <c r="N64" s="2" t="s">
@@ -9615,7 +9677,7 @@
       </c>
       <c r="K65" s="2"/>
       <c r="L65" s="2"/>
-      <c r="M65" s="3" t="s">
+      <c r="M65" s="56" t="s">
         <v>243</v>
       </c>
       <c r="N65" s="2" t="s">
@@ -9660,8 +9722,8 @@
       <c r="G66" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="H66" s="2" t="s">
-        <v>1469</v>
+      <c r="H66" s="32" t="s">
+        <v>1448</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>222</v>
@@ -9671,18 +9733,18 @@
       </c>
       <c r="K66" s="2"/>
       <c r="L66" s="2"/>
-      <c r="M66" s="2" t="s">
-        <v>1470</v>
+      <c r="M66" s="57" t="s">
+        <v>1449</v>
       </c>
       <c r="N66" s="5" t="s">
-        <v>1492</v>
+        <v>1471</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>1471</v>
+        <v>1450</v>
       </c>
       <c r="P66" s="2"/>
       <c r="Q66" s="2" t="s">
-        <v>1472</v>
+        <v>1451</v>
       </c>
       <c r="R66" s="2" t="s">
         <v>558</v>
@@ -9698,7 +9760,7 @@
       </c>
       <c r="V66" s="2"/>
       <c r="W66" s="2" t="s">
-        <v>1154</v>
+        <v>1142</v>
       </c>
       <c r="X66" s="2">
         <v>1</v>
@@ -9720,8 +9782,8 @@
       <c r="G67" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="H67" s="2" t="s">
-        <v>1469</v>
+      <c r="H67" s="32" t="s">
+        <v>1448</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>222</v>
@@ -9731,18 +9793,18 @@
       </c>
       <c r="K67" s="2"/>
       <c r="L67" s="2"/>
-      <c r="M67" s="2" t="s">
-        <v>1473</v>
+      <c r="M67" s="57" t="s">
+        <v>1452</v>
       </c>
       <c r="N67" s="5" t="s">
-        <v>1493</v>
+        <v>1472</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>1471</v>
+        <v>1450</v>
       </c>
       <c r="P67" s="2"/>
       <c r="Q67" s="2" t="s">
-        <v>1474</v>
+        <v>1453</v>
       </c>
       <c r="R67" s="2" t="s">
         <v>558</v>
@@ -9751,14 +9813,14 @@
         <v>32</v>
       </c>
       <c r="T67" s="18" t="s">
-        <v>1555</v>
+        <v>1532</v>
       </c>
       <c r="U67" s="18" t="s">
-        <v>1556</v>
+        <v>1533</v>
       </c>
       <c r="V67" s="2"/>
       <c r="W67" s="2" t="s">
-        <v>1154</v>
+        <v>1142</v>
       </c>
       <c r="X67" s="2">
         <v>1</v>
@@ -9780,7 +9842,7 @@
       <c r="G68" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="H68" s="2" t="s">
+      <c r="H68" s="32" t="s">
         <v>251</v>
       </c>
       <c r="I68" s="2" t="s">
@@ -9791,16 +9853,16 @@
       </c>
       <c r="K68" s="2"/>
       <c r="L68" s="2"/>
-      <c r="M68" s="2" t="s">
-        <v>1475</v>
+      <c r="M68" s="57" t="s">
+        <v>1454</v>
       </c>
       <c r="N68" s="5" t="s">
-        <v>1494</v>
+        <v>1473</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" s="2"/>
       <c r="Q68" s="2" t="s">
-        <v>1476</v>
+        <v>1455</v>
       </c>
       <c r="R68" s="2" t="s">
         <v>558</v>
@@ -9809,14 +9871,14 @@
         <v>32</v>
       </c>
       <c r="T68" s="18" t="s">
-        <v>1194</v>
+        <v>1182</v>
       </c>
       <c r="U68" s="18" t="s">
         <v>846</v>
       </c>
       <c r="V68" s="2"/>
       <c r="W68" s="2" t="s">
-        <v>1154</v>
+        <v>1142</v>
       </c>
       <c r="X68" s="2">
         <v>1</v>
@@ -9838,7 +9900,7 @@
       <c r="G69" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="H69" s="2" t="s">
+      <c r="H69" s="32" t="s">
         <v>204</v>
       </c>
       <c r="I69" s="2" t="s">
@@ -9849,32 +9911,32 @@
       </c>
       <c r="K69" s="2"/>
       <c r="L69" s="2"/>
-      <c r="M69" s="2" t="s">
-        <v>1477</v>
+      <c r="M69" s="57" t="s">
+        <v>1456</v>
       </c>
       <c r="N69" s="5" t="s">
-        <v>1495</v>
+        <v>1474</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" s="2"/>
       <c r="Q69" s="2" t="s">
-        <v>1478</v>
+        <v>1457</v>
       </c>
       <c r="R69" s="2" t="s">
         <v>558</v>
       </c>
       <c r="S69" s="2" t="s">
-        <v>1479</v>
+        <v>1458</v>
       </c>
       <c r="T69" s="18" t="s">
-        <v>1557</v>
+        <v>1534</v>
       </c>
       <c r="U69" s="18" t="s">
-        <v>1681</v>
+        <v>1652</v>
       </c>
       <c r="V69" s="2"/>
       <c r="W69" s="2" t="s">
-        <v>1154</v>
+        <v>1142</v>
       </c>
       <c r="X69" s="2">
         <v>1</v>
@@ -9896,7 +9958,7 @@
       <c r="G70" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="H70" s="2" t="s">
+      <c r="H70" s="32" t="s">
         <v>581</v>
       </c>
       <c r="I70" s="2" t="s">
@@ -9907,16 +9969,16 @@
       </c>
       <c r="K70" s="2"/>
       <c r="L70" s="2"/>
-      <c r="M70" s="2" t="s">
-        <v>1480</v>
+      <c r="M70" s="57" t="s">
+        <v>1459</v>
       </c>
       <c r="N70" s="5" t="s">
-        <v>1496</v>
+        <v>1475</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" s="2"/>
       <c r="Q70" s="2" t="s">
-        <v>1481</v>
+        <v>1460</v>
       </c>
       <c r="R70" s="2" t="s">
         <v>558</v>
@@ -9925,14 +9987,14 @@
         <v>32</v>
       </c>
       <c r="T70" s="18" t="s">
-        <v>1558</v>
+        <v>1535</v>
       </c>
       <c r="U70" s="18" t="s">
         <v>210</v>
       </c>
       <c r="V70" s="2"/>
       <c r="W70" s="2" t="s">
-        <v>1154</v>
+        <v>1142</v>
       </c>
       <c r="X70" s="2">
         <v>1</v>
@@ -9954,27 +10016,27 @@
       <c r="G71" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="H71" s="2" t="s">
-        <v>1063</v>
+      <c r="H71" s="32" t="s">
+        <v>1051</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>125</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>1482</v>
+        <v>1461</v>
       </c>
       <c r="K71" s="2"/>
       <c r="L71" s="2"/>
-      <c r="M71" s="2" t="s">
-        <v>1483</v>
+      <c r="M71" s="57" t="s">
+        <v>1462</v>
       </c>
       <c r="N71" s="5" t="s">
-        <v>1497</v>
+        <v>1476</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" s="2"/>
       <c r="Q71" s="2" t="s">
-        <v>1484</v>
+        <v>1463</v>
       </c>
       <c r="R71" s="2" t="s">
         <v>558</v>
@@ -9983,14 +10045,14 @@
         <v>32</v>
       </c>
       <c r="T71" s="18" t="s">
-        <v>1560</v>
+        <v>1537</v>
       </c>
       <c r="U71" s="18" t="s">
-        <v>1559</v>
+        <v>1536</v>
       </c>
       <c r="V71" s="2"/>
       <c r="W71" s="2" t="s">
-        <v>1154</v>
+        <v>1142</v>
       </c>
       <c r="X71" s="2">
         <v>1</v>
@@ -10012,7 +10074,7 @@
       <c r="G72" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="H72" s="2" t="s">
+      <c r="H72" s="32" t="s">
         <v>241</v>
       </c>
       <c r="I72" s="2" t="s">
@@ -10023,20 +10085,20 @@
       </c>
       <c r="K72" s="2"/>
       <c r="L72" s="2" t="s">
-        <v>1485</v>
-      </c>
-      <c r="M72" s="2" t="s">
-        <v>1486</v>
+        <v>1464</v>
+      </c>
+      <c r="M72" s="57" t="s">
+        <v>1465</v>
       </c>
       <c r="N72" s="5" t="s">
-        <v>1498</v>
+        <v>1477</v>
       </c>
       <c r="O72" s="2" t="s">
-        <v>1487</v>
+        <v>1466</v>
       </c>
       <c r="P72" s="2"/>
       <c r="Q72" s="2" t="s">
-        <v>1488</v>
+        <v>1467</v>
       </c>
       <c r="R72" s="2" t="s">
         <v>558</v>
@@ -10045,14 +10107,14 @@
         <v>32</v>
       </c>
       <c r="T72" s="18" t="s">
-        <v>1561</v>
+        <v>1538</v>
       </c>
       <c r="U72" s="18" t="s">
-        <v>1562</v>
+        <v>1539</v>
       </c>
       <c r="V72" s="2"/>
       <c r="W72" s="2" t="s">
-        <v>1154</v>
+        <v>1142</v>
       </c>
       <c r="X72" s="2">
         <v>1</v>
@@ -10074,7 +10136,7 @@
       <c r="G73" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="H73" s="2" t="s">
+      <c r="H73" s="32" t="s">
         <v>241</v>
       </c>
       <c r="I73" s="2" t="s">
@@ -10085,18 +10147,18 @@
       </c>
       <c r="K73" s="2"/>
       <c r="L73" s="2"/>
-      <c r="M73" s="2" t="s">
-        <v>1490</v>
+      <c r="M73" s="57" t="s">
+        <v>1469</v>
       </c>
       <c r="N73" s="5" t="s">
-        <v>1499</v>
+        <v>1478</v>
       </c>
       <c r="O73" s="2" t="s">
-        <v>1487</v>
+        <v>1466</v>
       </c>
       <c r="P73" s="2"/>
       <c r="Q73" s="2" t="s">
-        <v>1491</v>
+        <v>1470</v>
       </c>
       <c r="R73" s="2" t="s">
         <v>558</v>
@@ -10105,14 +10167,14 @@
         <v>32</v>
       </c>
       <c r="T73" s="18" t="s">
-        <v>1564</v>
+        <v>1541</v>
       </c>
       <c r="U73" s="18" t="s">
-        <v>1563</v>
+        <v>1540</v>
       </c>
       <c r="V73" s="2"/>
       <c r="W73" s="2" t="s">
-        <v>1154</v>
+        <v>1142</v>
       </c>
       <c r="X73" s="2">
         <v>1</v>
@@ -10145,7 +10207,7 @@
       </c>
       <c r="K74" s="2"/>
       <c r="L74" s="2"/>
-      <c r="M74" s="3" t="s">
+      <c r="M74" s="56" t="s">
         <v>253</v>
       </c>
       <c r="N74" s="2" t="s">
@@ -10199,7 +10261,7 @@
       </c>
       <c r="K75" s="2"/>
       <c r="L75" s="2"/>
-      <c r="M75" s="3" t="s">
+      <c r="M75" s="56" t="s">
         <v>257</v>
       </c>
       <c r="N75" s="2" t="s">
@@ -10242,30 +10304,30 @@
       <c r="G76" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="H76" s="2" t="s">
+      <c r="H76" s="32" t="s">
         <v>256</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>463</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>1463</v>
+        <v>1442</v>
       </c>
       <c r="K76" s="2"/>
       <c r="L76" s="2"/>
-      <c r="M76" s="2" t="s">
-        <v>1464</v>
+      <c r="M76" s="57" t="s">
+        <v>1443</v>
       </c>
       <c r="N76" s="5" t="s">
-        <v>1467</v>
+        <v>1446</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" s="2"/>
       <c r="Q76" s="2" t="s">
-        <v>1464</v>
+        <v>1443</v>
       </c>
       <c r="R76" s="2" t="s">
-        <v>1465</v>
+        <v>1444</v>
       </c>
       <c r="S76" s="2" t="s">
         <v>619</v>
@@ -10300,7 +10362,7 @@
       <c r="G77" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="H77" s="2" t="s">
+      <c r="H77" s="32" t="s">
         <v>494</v>
       </c>
       <c r="I77" s="2" t="s">
@@ -10311,19 +10373,19 @@
       </c>
       <c r="K77" s="2"/>
       <c r="L77" s="2"/>
-      <c r="M77" s="2" t="s">
-        <v>1466</v>
+      <c r="M77" s="57" t="s">
+        <v>1445</v>
       </c>
       <c r="N77" s="5" t="s">
-        <v>1468</v>
+        <v>1447</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" s="2"/>
       <c r="Q77" s="2" t="s">
-        <v>1466</v>
+        <v>1445</v>
       </c>
       <c r="R77" s="2" t="s">
-        <v>1465</v>
+        <v>1444</v>
       </c>
       <c r="S77" s="2" t="s">
         <v>619</v>
@@ -10369,7 +10431,7 @@
       </c>
       <c r="K78" s="2"/>
       <c r="L78" s="2"/>
-      <c r="M78" s="3" t="s">
+      <c r="M78" s="56" t="s">
         <v>266</v>
       </c>
       <c r="N78" s="4" t="s">
@@ -10412,29 +10474,29 @@
       <c r="G79" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="H79" s="2" t="s">
+      <c r="H79" s="32" t="s">
         <v>91</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>1451</v>
+        <v>1430</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>232</v>
       </c>
       <c r="K79" s="2"/>
       <c r="L79" s="2" t="s">
-        <v>1452</v>
-      </c>
-      <c r="M79" s="2" t="s">
-        <v>1453</v>
+        <v>1431</v>
+      </c>
+      <c r="M79" s="57" t="s">
+        <v>1432</v>
       </c>
       <c r="N79" s="5" t="s">
-        <v>1460</v>
+        <v>1439</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" s="2"/>
       <c r="Q79" s="2" t="s">
-        <v>1453</v>
+        <v>1432</v>
       </c>
       <c r="R79" s="2" t="s">
         <v>558</v>
@@ -10443,10 +10505,10 @@
         <v>32</v>
       </c>
       <c r="T79" s="18" t="s">
-        <v>1457</v>
+        <v>1436</v>
       </c>
       <c r="U79" s="18" t="s">
-        <v>1120</v>
+        <v>1108</v>
       </c>
       <c r="V79" s="2"/>
       <c r="W79" s="2" t="s">
@@ -10472,7 +10534,7 @@
       <c r="G80" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="H80" s="2" t="s">
+      <c r="H80" s="32" t="s">
         <v>542</v>
       </c>
       <c r="I80" s="2" t="s">
@@ -10485,16 +10547,16 @@
       <c r="L80" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>1454</v>
+      <c r="M80" s="57" t="s">
+        <v>1433</v>
       </c>
       <c r="N80" s="5" t="s">
-        <v>1461</v>
+        <v>1440</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" s="2"/>
       <c r="Q80" s="2" t="s">
-        <v>1454</v>
+        <v>1433</v>
       </c>
       <c r="R80" s="2" t="s">
         <v>558</v>
@@ -10503,10 +10565,10 @@
         <v>32</v>
       </c>
       <c r="T80" s="18" t="s">
-        <v>1458</v>
+        <v>1437</v>
       </c>
       <c r="U80" s="18" t="s">
-        <v>1459</v>
+        <v>1438</v>
       </c>
       <c r="V80" s="2"/>
       <c r="W80" s="2" t="s">
@@ -10532,7 +10594,7 @@
       <c r="G81" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="H81" s="2" t="s">
+      <c r="H81" s="32" t="s">
         <v>143</v>
       </c>
       <c r="I81" s="2" t="s">
@@ -10543,16 +10605,16 @@
       </c>
       <c r="K81" s="2"/>
       <c r="L81" s="2"/>
-      <c r="M81" s="2" t="s">
-        <v>1455</v>
+      <c r="M81" s="57" t="s">
+        <v>1434</v>
       </c>
       <c r="N81" s="5" t="s">
-        <v>1462</v>
+        <v>1441</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" s="2"/>
       <c r="Q81" s="2" t="s">
-        <v>1456</v>
+        <v>1435</v>
       </c>
       <c r="R81" s="2" t="s">
         <v>558</v>
@@ -10601,11 +10663,11 @@
       </c>
       <c r="K82" s="9"/>
       <c r="L82" s="9"/>
-      <c r="M82" s="10" t="s">
+      <c r="M82" s="60" t="s">
         <v>275</v>
       </c>
       <c r="N82" s="5" t="s">
-        <v>1443</v>
+        <v>1422</v>
       </c>
       <c r="P82" s="9"/>
       <c r="Q82" s="10"/>
@@ -10643,8 +10705,8 @@
       <c r="G83" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="H83" s="2" t="s">
-        <v>1434</v>
+      <c r="H83" s="32" t="s">
+        <v>1413</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>302</v>
@@ -10654,18 +10716,18 @@
       </c>
       <c r="K83" s="2"/>
       <c r="L83" s="2" t="s">
-        <v>1435</v>
-      </c>
-      <c r="M83" s="2" t="s">
-        <v>1436</v>
+        <v>1414</v>
+      </c>
+      <c r="M83" s="57" t="s">
+        <v>1415</v>
       </c>
       <c r="N83" s="5" t="s">
-        <v>1442</v>
+        <v>1421</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" s="2"/>
       <c r="Q83" s="2" t="s">
-        <v>1437</v>
+        <v>1416</v>
       </c>
       <c r="R83" s="2" t="s">
         <v>558</v>
@@ -10674,10 +10736,10 @@
         <v>32</v>
       </c>
       <c r="T83" s="18" t="s">
-        <v>1446</v>
+        <v>1425</v>
       </c>
       <c r="U83" s="18" t="s">
-        <v>1447</v>
+        <v>1426</v>
       </c>
       <c r="V83" s="2"/>
       <c r="W83" s="2" t="s">
@@ -10703,7 +10765,7 @@
       <c r="G84" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="H84" s="2" t="s">
+      <c r="H84" s="32" t="s">
         <v>790</v>
       </c>
       <c r="I84" s="2" t="s">
@@ -10714,18 +10776,18 @@
       </c>
       <c r="K84" s="2"/>
       <c r="L84" s="2" t="s">
-        <v>1438</v>
-      </c>
-      <c r="M84" s="2" t="s">
-        <v>1439</v>
+        <v>1417</v>
+      </c>
+      <c r="M84" s="57" t="s">
+        <v>1418</v>
       </c>
       <c r="N84" s="5" t="s">
-        <v>1444</v>
+        <v>1423</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" s="2"/>
       <c r="Q84" s="2" t="s">
-        <v>1440</v>
+        <v>1419</v>
       </c>
       <c r="R84" s="2" t="s">
         <v>558</v>
@@ -10737,7 +10799,7 @@
         <v>381</v>
       </c>
       <c r="U84" s="18" t="s">
-        <v>1448</v>
+        <v>1427</v>
       </c>
       <c r="V84" s="2"/>
       <c r="W84" s="2" t="s">
@@ -10763,7 +10825,7 @@
       <c r="G85" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="H85" s="2" t="s">
+      <c r="H85" s="32" t="s">
         <v>112</v>
       </c>
       <c r="I85" s="2" t="s">
@@ -10774,18 +10836,18 @@
       </c>
       <c r="K85" s="2"/>
       <c r="L85" s="2" t="s">
-        <v>1361</v>
-      </c>
-      <c r="M85" s="2" t="s">
-        <v>1441</v>
+        <v>1342</v>
+      </c>
+      <c r="M85" s="57" t="s">
+        <v>1420</v>
       </c>
       <c r="N85" s="5" t="s">
-        <v>1445</v>
+        <v>1424</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" s="2"/>
       <c r="Q85" s="2" t="s">
-        <v>1441</v>
+        <v>1420</v>
       </c>
       <c r="R85" s="2" t="s">
         <v>558</v>
@@ -10794,10 +10856,10 @@
         <v>32</v>
       </c>
       <c r="T85" s="18" t="s">
-        <v>1449</v>
+        <v>1428</v>
       </c>
       <c r="U85" s="18" t="s">
-        <v>1450</v>
+        <v>1429</v>
       </c>
       <c r="V85" s="2"/>
       <c r="W85" s="2" t="s">
@@ -10834,7 +10896,7 @@
       </c>
       <c r="K86" s="2"/>
       <c r="L86" s="2"/>
-      <c r="M86" s="3" t="s">
+      <c r="M86" s="56" t="s">
         <v>283</v>
       </c>
       <c r="N86" s="2" t="s">
@@ -10888,7 +10950,7 @@
       </c>
       <c r="K87" s="2"/>
       <c r="L87" s="2"/>
-      <c r="M87" s="3" t="s">
+      <c r="M87" s="56" t="s">
         <v>287</v>
       </c>
       <c r="N87" s="5" t="s">
@@ -10931,8 +10993,8 @@
       <c r="G88" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="H88" t="s">
-        <v>1407</v>
+      <c r="H88" s="11" t="s">
+        <v>1387</v>
       </c>
       <c r="I88" t="s">
         <v>716</v>
@@ -10940,26 +11002,26 @@
       <c r="J88" t="s">
         <v>198</v>
       </c>
-      <c r="M88" t="s">
-        <v>1408</v>
+      <c r="M88" s="64" t="s">
+        <v>1388</v>
       </c>
       <c r="N88" s="5" t="s">
-        <v>1410</v>
+        <v>1390</v>
       </c>
       <c r="Q88" t="s">
-        <v>1409</v>
+        <v>1389</v>
       </c>
       <c r="R88" t="s">
         <v>558</v>
       </c>
       <c r="S88" t="s">
-        <v>1411</v>
+        <v>1391</v>
       </c>
       <c r="T88" s="21" t="s">
-        <v>1412</v>
+        <v>1392</v>
       </c>
       <c r="U88" s="21" t="s">
-        <v>1413</v>
+        <v>1393</v>
       </c>
       <c r="W88" t="s">
         <v>561</v>
@@ -10984,7 +11046,7 @@
       <c r="G89" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="H89" s="2" t="s">
+      <c r="H89" s="32" t="s">
         <v>26</v>
       </c>
       <c r="I89" s="2" t="s">
@@ -10995,16 +11057,16 @@
       </c>
       <c r="K89" s="2"/>
       <c r="L89" s="2"/>
-      <c r="M89" s="2" t="s">
-        <v>1405</v>
+      <c r="M89" s="57" t="s">
+        <v>1385</v>
       </c>
       <c r="N89" s="5" t="s">
-        <v>1433</v>
+        <v>1412</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" s="2"/>
       <c r="Q89" s="2" t="s">
-        <v>1406</v>
+        <v>1386</v>
       </c>
       <c r="R89" s="2" t="s">
         <v>558</v>
@@ -11053,7 +11115,7 @@
       </c>
       <c r="K90" s="2"/>
       <c r="L90" s="2"/>
-      <c r="M90" s="3" t="s">
+      <c r="M90" s="56" t="s">
         <v>295</v>
       </c>
       <c r="N90" s="2" t="s">
@@ -11096,29 +11158,29 @@
       <c r="G91" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="H91" s="2" t="s">
+      <c r="H91" s="32" t="s">
         <v>197</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>1396</v>
+        <v>1376</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>1397</v>
+        <v>1377</v>
       </c>
       <c r="K91" s="2"/>
       <c r="L91" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="M91" s="2" t="s">
-        <v>1398</v>
+      <c r="M91" s="57" t="s">
+        <v>1378</v>
       </c>
       <c r="N91" s="5" t="s">
-        <v>1402</v>
+        <v>1382</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" s="2"/>
       <c r="Q91" s="2" t="s">
-        <v>1398</v>
+        <v>1378</v>
       </c>
       <c r="R91" s="2" t="s">
         <v>558</v>
@@ -11156,7 +11218,7 @@
       <c r="G92" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="H92" s="2" t="s">
+      <c r="H92" s="32" t="s">
         <v>204</v>
       </c>
       <c r="I92" s="2" t="s">
@@ -11167,16 +11229,16 @@
       </c>
       <c r="K92" s="2"/>
       <c r="L92" s="2"/>
-      <c r="M92" s="2" t="s">
-        <v>1399</v>
+      <c r="M92" s="57" t="s">
+        <v>1379</v>
       </c>
       <c r="N92" s="5" t="s">
-        <v>1403</v>
+        <v>1383</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" s="2"/>
       <c r="Q92" s="2" t="s">
-        <v>1400</v>
+        <v>1380</v>
       </c>
       <c r="R92" s="2" t="s">
         <v>558</v>
@@ -11214,29 +11276,29 @@
       <c r="G93" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="H93" s="2" t="s">
+      <c r="H93" s="32" t="s">
         <v>734</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>1396</v>
+        <v>1376</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>1397</v>
+        <v>1377</v>
       </c>
       <c r="K93" s="2"/>
       <c r="L93" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="M93" s="2" t="s">
-        <v>1401</v>
+      <c r="M93" s="57" t="s">
+        <v>1381</v>
       </c>
       <c r="N93" s="5" t="s">
-        <v>1404</v>
+        <v>1384</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" s="2"/>
       <c r="Q93" s="2" t="s">
-        <v>1401</v>
+        <v>1381</v>
       </c>
       <c r="R93" s="2" t="s">
         <v>558</v>
@@ -11285,7 +11347,7 @@
       </c>
       <c r="K94" s="2"/>
       <c r="L94" s="2"/>
-      <c r="M94" s="3" t="s">
+      <c r="M94" s="56" t="s">
         <v>304</v>
       </c>
       <c r="N94" s="2" t="s">
@@ -11339,7 +11401,7 @@
       </c>
       <c r="K95" s="2"/>
       <c r="L95" s="2"/>
-      <c r="M95" s="3" t="s">
+      <c r="M95" s="56" t="s">
         <v>309</v>
       </c>
       <c r="N95" s="2" t="s">
@@ -11393,7 +11455,7 @@
       </c>
       <c r="K96" s="2"/>
       <c r="L96" s="2"/>
-      <c r="M96" s="3" t="s">
+      <c r="M96" s="56" t="s">
         <v>313</v>
       </c>
       <c r="N96" s="2" t="s">
@@ -11447,7 +11509,7 @@
       </c>
       <c r="K97" s="2"/>
       <c r="L97" s="2"/>
-      <c r="M97" s="3" t="s">
+      <c r="M97" s="56" t="s">
         <v>318</v>
       </c>
       <c r="N97" s="2" t="s">
@@ -11490,29 +11552,29 @@
       <c r="G98" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="H98" s="2" t="s">
+      <c r="H98" s="32" t="s">
         <v>1022</v>
       </c>
       <c r="I98" s="2" t="s">
         <v>125</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>1369</v>
+        <v>1350</v>
       </c>
       <c r="K98" s="2"/>
       <c r="L98" s="2" t="s">
-        <v>1370</v>
-      </c>
-      <c r="M98" s="2" t="s">
-        <v>1371</v>
+        <v>1351</v>
+      </c>
+      <c r="M98" s="57" t="s">
+        <v>1352</v>
       </c>
       <c r="N98" s="5" t="s">
-        <v>1388</v>
+        <v>1368</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" s="2"/>
       <c r="Q98" s="2" t="s">
-        <v>1372</v>
+        <v>1353</v>
       </c>
       <c r="R98" s="2" t="s">
         <v>558</v>
@@ -11521,10 +11583,10 @@
         <v>32</v>
       </c>
       <c r="T98" s="18" t="s">
-        <v>1414</v>
+        <v>1394</v>
       </c>
       <c r="U98" s="18" t="s">
-        <v>1415</v>
+        <v>1395</v>
       </c>
       <c r="V98" s="2"/>
       <c r="W98" s="2" t="s">
@@ -11550,29 +11612,29 @@
       <c r="G99" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="H99" s="2" t="s">
+      <c r="H99" s="32" t="s">
         <v>1022</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>125</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>1369</v>
+        <v>1350</v>
       </c>
       <c r="K99" s="2"/>
       <c r="L99" s="2" t="s">
-        <v>1370</v>
-      </c>
-      <c r="M99" s="2" t="s">
-        <v>1373</v>
+        <v>1351</v>
+      </c>
+      <c r="M99" s="57" t="s">
+        <v>1354</v>
       </c>
       <c r="N99" s="5" t="s">
-        <v>1389</v>
+        <v>1369</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" s="2"/>
       <c r="Q99" s="2" t="s">
-        <v>1374</v>
+        <v>1355</v>
       </c>
       <c r="R99" s="2" t="s">
         <v>558</v>
@@ -11581,10 +11643,10 @@
         <v>32</v>
       </c>
       <c r="T99" s="18" t="s">
-        <v>1414</v>
+        <v>1394</v>
       </c>
       <c r="U99" s="18" t="s">
-        <v>1416</v>
+        <v>1396</v>
       </c>
       <c r="V99" s="2"/>
       <c r="W99" s="2" t="s">
@@ -11610,29 +11672,29 @@
       <c r="G100" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="H100" s="2" t="s">
+      <c r="H100" s="32" t="s">
         <v>1022</v>
       </c>
       <c r="I100" s="2" t="s">
         <v>125</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>1369</v>
+        <v>1350</v>
       </c>
       <c r="K100" s="2"/>
       <c r="L100" s="2" t="s">
+        <v>1351</v>
+      </c>
+      <c r="M100" s="57" t="s">
+        <v>1356</v>
+      </c>
+      <c r="N100" s="5" t="s">
         <v>1370</v>
-      </c>
-      <c r="M100" s="2" t="s">
-        <v>1375</v>
-      </c>
-      <c r="N100" s="5" t="s">
-        <v>1390</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" s="2"/>
       <c r="Q100" s="2" t="s">
-        <v>1376</v>
+        <v>1357</v>
       </c>
       <c r="R100" s="2" t="s">
         <v>558</v>
@@ -11641,10 +11703,10 @@
         <v>32</v>
       </c>
       <c r="T100" s="18" t="s">
-        <v>1414</v>
+        <v>1394</v>
       </c>
       <c r="U100" s="18" t="s">
-        <v>1418</v>
+        <v>1398</v>
       </c>
       <c r="V100" s="2"/>
       <c r="W100" s="2" t="s">
@@ -11670,29 +11732,29 @@
       <c r="G101" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="H101" s="2" t="s">
+      <c r="H101" s="32" t="s">
         <v>1022</v>
       </c>
       <c r="I101" s="2" t="s">
         <v>125</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>1369</v>
+        <v>1350</v>
       </c>
       <c r="K101" s="2"/>
       <c r="L101" s="2" t="s">
-        <v>1370</v>
-      </c>
-      <c r="M101" s="2" t="s">
-        <v>1377</v>
+        <v>1351</v>
+      </c>
+      <c r="M101" s="57" t="s">
+        <v>1358</v>
       </c>
       <c r="N101" s="5" t="s">
-        <v>1391</v>
+        <v>1371</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" s="2"/>
       <c r="Q101" s="2" t="s">
-        <v>1378</v>
+        <v>1359</v>
       </c>
       <c r="R101" s="2" t="s">
         <v>558</v>
@@ -11701,10 +11763,10 @@
         <v>32</v>
       </c>
       <c r="T101" s="18" t="s">
-        <v>1414</v>
+        <v>1394</v>
       </c>
       <c r="U101" s="18" t="s">
-        <v>1417</v>
+        <v>1397</v>
       </c>
       <c r="V101" s="2"/>
       <c r="W101" s="2" t="s">
@@ -11730,8 +11792,8 @@
       <c r="G102" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="H102" s="2" t="s">
-        <v>1379</v>
+      <c r="H102" s="32" t="s">
+        <v>1683</v>
       </c>
       <c r="I102" s="2" t="s">
         <v>93</v>
@@ -11741,18 +11803,18 @@
       </c>
       <c r="K102" s="2"/>
       <c r="L102" s="2" t="s">
-        <v>1380</v>
-      </c>
-      <c r="M102" s="2" t="s">
-        <v>1381</v>
+        <v>1360</v>
+      </c>
+      <c r="M102" s="57" t="s">
+        <v>1361</v>
       </c>
       <c r="N102" s="5" t="s">
-        <v>1392</v>
+        <v>1372</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" s="2"/>
       <c r="Q102" s="2" t="s">
-        <v>1382</v>
+        <v>1362</v>
       </c>
       <c r="R102" s="2" t="s">
         <v>558</v>
@@ -11790,7 +11852,7 @@
       <c r="G103" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="H103" s="2" t="s">
+      <c r="H103" s="32" t="s">
         <v>26</v>
       </c>
       <c r="I103" s="2" t="s">
@@ -11801,18 +11863,18 @@
       </c>
       <c r="K103" s="2"/>
       <c r="L103" s="2" t="s">
-        <v>1380</v>
-      </c>
-      <c r="M103" s="2" t="s">
-        <v>1383</v>
+        <v>1360</v>
+      </c>
+      <c r="M103" s="57" t="s">
+        <v>1363</v>
       </c>
       <c r="N103" s="5" t="s">
-        <v>1393</v>
+        <v>1373</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" s="2"/>
       <c r="Q103" s="2" t="s">
-        <v>1384</v>
+        <v>1364</v>
       </c>
       <c r="R103" s="2" t="s">
         <v>558</v>
@@ -11850,7 +11912,7 @@
       <c r="G104" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="H104" s="2" t="s">
+      <c r="H104" s="32" t="s">
         <v>904</v>
       </c>
       <c r="I104" s="2" t="s">
@@ -11861,18 +11923,18 @@
       </c>
       <c r="K104" s="2"/>
       <c r="L104" s="2" t="s">
-        <v>1380</v>
-      </c>
-      <c r="M104" s="2" t="s">
-        <v>1385</v>
+        <v>1360</v>
+      </c>
+      <c r="M104" s="57" t="s">
+        <v>1365</v>
       </c>
       <c r="N104" s="5" t="s">
-        <v>1394</v>
+        <v>1374</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" s="2"/>
       <c r="Q104" s="2" t="s">
-        <v>1386</v>
+        <v>1366</v>
       </c>
       <c r="R104" s="2" t="s">
         <v>558</v>
@@ -11881,10 +11943,10 @@
         <v>32</v>
       </c>
       <c r="T104" s="18" t="s">
-        <v>1419</v>
+        <v>1399</v>
       </c>
       <c r="U104" s="18" t="s">
-        <v>1420</v>
+        <v>1400</v>
       </c>
       <c r="V104" s="2"/>
       <c r="W104" s="2" t="s">
@@ -11910,7 +11972,7 @@
       <c r="G105" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="H105" s="2" t="s">
+      <c r="H105" s="32" t="s">
         <v>904</v>
       </c>
       <c r="I105" s="2" t="s">
@@ -11921,18 +11983,18 @@
       </c>
       <c r="K105" s="2"/>
       <c r="L105" s="2" t="s">
-        <v>1380</v>
-      </c>
-      <c r="M105" s="2" t="s">
-        <v>1387</v>
+        <v>1360</v>
+      </c>
+      <c r="M105" s="57" t="s">
+        <v>1367</v>
       </c>
       <c r="N105" s="5" t="s">
-        <v>1395</v>
+        <v>1375</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" s="2"/>
       <c r="Q105" s="2" t="s">
-        <v>1387</v>
+        <v>1367</v>
       </c>
       <c r="R105" s="2" t="s">
         <v>558</v>
@@ -11978,7 +12040,7 @@
       </c>
       <c r="K106" s="2"/>
       <c r="L106" s="2"/>
-      <c r="M106" s="3" t="s">
+      <c r="M106" s="56" t="s">
         <v>326</v>
       </c>
       <c r="N106" s="2" t="s">
@@ -12034,7 +12096,7 @@
       </c>
       <c r="K107" s="2"/>
       <c r="L107" s="2"/>
-      <c r="M107" s="3" t="s">
+      <c r="M107" s="56" t="s">
         <v>332</v>
       </c>
       <c r="N107" s="2" t="s">
@@ -12079,31 +12141,31 @@
       <c r="G108" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="H108" s="2" t="s">
+      <c r="H108" s="32" t="s">
         <v>230</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>1359</v>
+        <v>1340</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>1360</v>
+        <v>1341</v>
       </c>
       <c r="K108" s="2"/>
       <c r="L108" s="2" t="s">
-        <v>1361</v>
-      </c>
-      <c r="M108" s="2" t="s">
-        <v>1368</v>
+        <v>1342</v>
+      </c>
+      <c r="M108" s="57" t="s">
+        <v>1349</v>
       </c>
       <c r="N108" s="4" t="s">
-        <v>1367</v>
+        <v>1348</v>
       </c>
       <c r="O108" s="2" t="s">
-        <v>1366</v>
+        <v>1347</v>
       </c>
       <c r="P108" s="2"/>
       <c r="Q108" s="2" t="s">
-        <v>1365</v>
+        <v>1346</v>
       </c>
       <c r="R108" s="2" t="s">
         <v>558</v>
@@ -12119,7 +12181,7 @@
       </c>
       <c r="V108" s="2"/>
       <c r="W108" s="2" t="s">
-        <v>1195</v>
+        <v>1183</v>
       </c>
       <c r="X108" s="2">
         <v>3</v>
@@ -12141,29 +12203,29 @@
       <c r="G109" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="H109" s="2" t="s">
+      <c r="H109" s="32" t="s">
         <v>212</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>1359</v>
+        <v>1340</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>1360</v>
+        <v>1341</v>
       </c>
       <c r="K109" s="2"/>
       <c r="L109" s="2" t="s">
-        <v>1361</v>
-      </c>
-      <c r="M109" s="2" t="s">
-        <v>1362</v>
+        <v>1342</v>
+      </c>
+      <c r="M109" s="57" t="s">
+        <v>1343</v>
       </c>
       <c r="N109" s="4" t="s">
-        <v>1364</v>
+        <v>1345</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" s="2"/>
       <c r="Q109" s="2" t="s">
-        <v>1363</v>
+        <v>1344</v>
       </c>
       <c r="R109" s="2" t="s">
         <v>558</v>
@@ -12175,11 +12237,11 @@
         <v>506</v>
       </c>
       <c r="U109" s="18" t="s">
-        <v>1423</v>
+        <v>1403</v>
       </c>
       <c r="V109" s="2"/>
       <c r="W109" s="2" t="s">
-        <v>1195</v>
+        <v>1183</v>
       </c>
       <c r="X109" s="2">
         <v>3</v>
@@ -12212,7 +12274,7 @@
       </c>
       <c r="K110" s="2"/>
       <c r="L110" s="2"/>
-      <c r="M110" s="3" t="s">
+      <c r="M110" s="56" t="s">
         <v>340</v>
       </c>
       <c r="N110" s="2" t="s">
@@ -12268,7 +12330,7 @@
       </c>
       <c r="K111" s="2"/>
       <c r="L111" s="2"/>
-      <c r="M111" s="3" t="s">
+      <c r="M111" s="56" t="s">
         <v>347</v>
       </c>
       <c r="N111" s="2" t="s">
@@ -12313,29 +12375,29 @@
       <c r="G112" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="H112" s="2" t="s">
-        <v>1348</v>
+      <c r="H112" s="32" t="s">
+        <v>1684</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>1349</v>
+        <v>1331</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>1350</v>
+        <v>1332</v>
       </c>
       <c r="K112" s="2"/>
       <c r="L112" s="2" t="s">
-        <v>1351</v>
-      </c>
-      <c r="M112" s="2" t="s">
-        <v>1352</v>
+        <v>1333</v>
+      </c>
+      <c r="M112" s="57" t="s">
+        <v>1334</v>
       </c>
       <c r="N112" s="5" t="s">
-        <v>1357</v>
+        <v>1338</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" s="2"/>
       <c r="Q112" s="2" t="s">
-        <v>1353</v>
+        <v>1335</v>
       </c>
       <c r="R112" s="2" t="s">
         <v>558</v>
@@ -12344,7 +12406,7 @@
         <v>32</v>
       </c>
       <c r="T112" s="18" t="s">
-        <v>1421</v>
+        <v>1401</v>
       </c>
       <c r="U112" s="18" t="s">
         <v>651</v>
@@ -12357,7 +12419,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>337</v>
       </c>
@@ -12373,8 +12435,8 @@
       <c r="G113" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="H113" s="2" t="s">
-        <v>1354</v>
+      <c r="H113" s="32" t="s">
+        <v>1685</v>
       </c>
       <c r="I113" s="2" t="s">
         <v>302</v>
@@ -12384,18 +12446,18 @@
       </c>
       <c r="K113" s="2"/>
       <c r="L113" s="2" t="s">
-        <v>1268</v>
-      </c>
-      <c r="M113" s="2" t="s">
-        <v>1355</v>
+        <v>1256</v>
+      </c>
+      <c r="M113" s="57" t="s">
+        <v>1336</v>
       </c>
       <c r="N113" s="5" t="s">
-        <v>1358</v>
+        <v>1339</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" s="2"/>
       <c r="Q113" s="2" t="s">
-        <v>1356</v>
+        <v>1337</v>
       </c>
       <c r="R113" s="2" t="s">
         <v>558</v>
@@ -12404,10 +12466,10 @@
         <v>32</v>
       </c>
       <c r="T113" s="18" t="s">
-        <v>1422</v>
+        <v>1402</v>
       </c>
       <c r="U113" s="18" t="s">
-        <v>1432</v>
+        <v>1411</v>
       </c>
       <c r="V113" s="2"/>
       <c r="W113" s="2" t="s">
@@ -12417,7 +12479,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>352</v>
       </c>
@@ -12444,7 +12506,7 @@
       </c>
       <c r="K114" s="2"/>
       <c r="L114" s="2"/>
-      <c r="M114" s="3" t="s">
+      <c r="M114" s="56" t="s">
         <v>355</v>
       </c>
       <c r="N114" s="2" t="s">
@@ -12471,7 +12533,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="115" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>352</v>
       </c>
@@ -12487,7 +12549,7 @@
       <c r="G115" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="H115" s="2" t="s">
+      <c r="H115" s="32" t="s">
         <v>300</v>
       </c>
       <c r="I115" s="2" t="s">
@@ -12498,18 +12560,18 @@
       </c>
       <c r="K115" s="2"/>
       <c r="L115" s="2" t="s">
-        <v>1337</v>
-      </c>
-      <c r="M115" s="2" t="s">
-        <v>1338</v>
+        <v>1320</v>
+      </c>
+      <c r="M115" s="57" t="s">
+        <v>1321</v>
       </c>
       <c r="N115" s="5" t="s">
-        <v>1345</v>
+        <v>1328</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" s="2"/>
       <c r="Q115" s="2" t="s">
-        <v>1338</v>
+        <v>1321</v>
       </c>
       <c r="R115" s="2" t="s">
         <v>558</v>
@@ -12518,10 +12580,10 @@
         <v>32</v>
       </c>
       <c r="T115" s="18" t="s">
-        <v>1424</v>
+        <v>1404</v>
       </c>
       <c r="U115" s="18" t="s">
-        <v>1427</v>
+        <v>1407</v>
       </c>
       <c r="V115" s="2"/>
       <c r="W115" s="2" t="s">
@@ -12531,7 +12593,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="116" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>352</v>
       </c>
@@ -12547,7 +12609,7 @@
       <c r="G116" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="H116" s="2" t="s">
+      <c r="H116" s="32" t="s">
         <v>734</v>
       </c>
       <c r="I116" s="2" t="s">
@@ -12558,18 +12620,18 @@
       </c>
       <c r="K116" s="2"/>
       <c r="L116" s="2" t="s">
-        <v>1337</v>
-      </c>
-      <c r="M116" s="2" t="s">
-        <v>1339</v>
+        <v>1320</v>
+      </c>
+      <c r="M116" s="57" t="s">
+        <v>1322</v>
       </c>
       <c r="N116" s="5" t="s">
-        <v>1346</v>
+        <v>1329</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" s="2"/>
       <c r="Q116" s="2" t="s">
-        <v>1339</v>
+        <v>1322</v>
       </c>
       <c r="R116" s="2" t="s">
         <v>558</v>
@@ -12578,7 +12640,7 @@
         <v>32</v>
       </c>
       <c r="T116" s="18" t="s">
-        <v>1425</v>
+        <v>1405</v>
       </c>
       <c r="U116" s="18" t="s">
         <v>239</v>
@@ -12591,7 +12653,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="117" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>352</v>
       </c>
@@ -12607,29 +12669,29 @@
       <c r="G117" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="H117" s="2" t="s">
-        <v>1340</v>
+      <c r="H117" s="32" t="s">
+        <v>1323</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>1341</v>
+        <v>1324</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>1342</v>
+        <v>1325</v>
       </c>
       <c r="K117" s="2"/>
       <c r="L117" s="2" t="s">
-        <v>1343</v>
-      </c>
-      <c r="M117" s="2" t="s">
-        <v>1344</v>
+        <v>1326</v>
+      </c>
+      <c r="M117" s="57" t="s">
+        <v>1327</v>
       </c>
       <c r="N117" s="5" t="s">
-        <v>1347</v>
+        <v>1330</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" s="2"/>
       <c r="Q117" s="2" t="s">
-        <v>1344</v>
+        <v>1327</v>
       </c>
       <c r="R117" s="2" t="s">
         <v>558</v>
@@ -12638,10 +12700,10 @@
         <v>32</v>
       </c>
       <c r="T117" s="18" t="s">
-        <v>1426</v>
+        <v>1406</v>
       </c>
       <c r="U117" s="18" t="s">
-        <v>1428</v>
+        <v>1408</v>
       </c>
       <c r="V117" s="2"/>
       <c r="W117" s="2" t="s">
@@ -12651,15 +12713,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>358</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="C118" s="40" t="s">
-        <v>1336</v>
+      <c r="C118" s="39" t="s">
+        <v>1319</v>
       </c>
       <c r="D118" s="2"/>
       <c r="E118" s="2"/>
@@ -12680,7 +12742,7 @@
       </c>
       <c r="K118" s="2"/>
       <c r="L118" s="2"/>
-      <c r="M118" s="3" t="s">
+      <c r="M118" s="56" t="s">
         <v>364</v>
       </c>
       <c r="N118" s="2" t="s">
@@ -12709,15 +12771,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="119" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>358</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="C119" s="40" t="s">
-        <v>1336</v>
+      <c r="C119" s="39" t="s">
+        <v>1319</v>
       </c>
       <c r="D119" s="2"/>
       <c r="E119" s="2"/>
@@ -12727,57 +12789,57 @@
       <c r="G119" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="H119" s="2" t="s">
+      <c r="H119" s="54" t="s">
         <v>178</v>
       </c>
-      <c r="I119" s="2" t="s">
-        <v>1321</v>
-      </c>
-      <c r="J119" s="2" t="s">
-        <v>1322</v>
-      </c>
-      <c r="K119" s="2"/>
-      <c r="L119" s="2"/>
-      <c r="M119" s="2" t="s">
-        <v>1323</v>
+      <c r="I119" s="7" t="s">
+        <v>1309</v>
+      </c>
+      <c r="J119" s="7" t="s">
+        <v>1310</v>
+      </c>
+      <c r="K119" s="7"/>
+      <c r="L119" s="7"/>
+      <c r="M119" s="65" t="s">
+        <v>1311</v>
       </c>
       <c r="N119" s="5" t="s">
-        <v>1329</v>
-      </c>
-      <c r="O119" s="2"/>
-      <c r="P119" s="2"/>
-      <c r="Q119" s="2" t="s">
-        <v>1324</v>
-      </c>
-      <c r="R119" s="2" t="s">
+        <v>1313</v>
+      </c>
+      <c r="O119" s="7"/>
+      <c r="P119" s="7"/>
+      <c r="Q119" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="R119" s="7" t="s">
         <v>558</v>
       </c>
-      <c r="S119" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="T119" s="18" t="s">
+      <c r="S119" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T119" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="U119" s="18" t="s">
+      <c r="U119" s="19" t="s">
         <v>483</v>
       </c>
-      <c r="V119" s="2"/>
-      <c r="W119" s="2" t="s">
-        <v>1195</v>
-      </c>
-      <c r="X119" s="2">
+      <c r="V119" s="7"/>
+      <c r="W119" s="7" t="s">
+        <v>1183</v>
+      </c>
+      <c r="X119" s="7">
         <v>3</v>
       </c>
     </row>
-    <row r="120" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>358</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="C120" s="40" t="s">
-        <v>1336</v>
+      <c r="C120" s="39" t="s">
+        <v>1319</v>
       </c>
       <c r="D120" s="2"/>
       <c r="E120" s="2"/>
@@ -12787,115 +12849,123 @@
       <c r="G120" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="H120" t="s">
+      <c r="H120" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="I120" t="s">
+      <c r="I120" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="J120" t="s">
-        <v>1330</v>
-      </c>
-      <c r="L120" t="s">
-        <v>1331</v>
-      </c>
-      <c r="M120" t="s">
-        <v>1332</v>
-      </c>
-      <c r="N120" s="5" t="s">
-        <v>1334</v>
-      </c>
-      <c r="Q120" t="s">
-        <v>1333</v>
-      </c>
-      <c r="R120" t="s">
+      <c r="J120" s="2" t="s">
+        <v>1314</v>
+      </c>
+      <c r="K120" s="2"/>
+      <c r="L120" s="2" t="s">
+        <v>1315</v>
+      </c>
+      <c r="M120" s="57" t="s">
+        <v>1316</v>
+      </c>
+      <c r="N120" s="4" t="s">
+        <v>1318</v>
+      </c>
+      <c r="O120" s="2"/>
+      <c r="P120" s="2"/>
+      <c r="Q120" s="2" t="s">
+        <v>1317</v>
+      </c>
+      <c r="R120" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="S120" t="s">
-        <v>32</v>
-      </c>
-      <c r="T120" s="21" t="s">
-        <v>1431</v>
-      </c>
-      <c r="U120" s="21" t="s">
-        <v>1429</v>
-      </c>
-      <c r="W120" t="s">
-        <v>1195</v>
-      </c>
-      <c r="X120" s="2"/>
-    </row>
-    <row r="121" spans="1:24" s="44" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="41" t="s">
+      <c r="S120" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="T120" s="18" t="s">
+        <v>1410</v>
+      </c>
+      <c r="U120" s="18" t="s">
+        <v>1409</v>
+      </c>
+      <c r="V120" s="2"/>
+      <c r="W120" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="X120" s="7">
+        <v>3</v>
+      </c>
+      <c r="Y120" s="2"/>
+    </row>
+    <row r="121" spans="1:25" s="53" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="51" t="s">
         <v>358</v>
       </c>
-      <c r="B121" s="41" t="s">
+      <c r="B121" s="51" t="s">
         <v>359</v>
       </c>
-      <c r="C121" s="43" t="s">
-        <v>1336</v>
-      </c>
-      <c r="D121" s="41"/>
-      <c r="E121" s="41"/>
-      <c r="F121" s="41" t="s">
+      <c r="C121" s="52" t="s">
+        <v>1319</v>
+      </c>
+      <c r="D121" s="51"/>
+      <c r="E121" s="51"/>
+      <c r="F121" s="51" t="s">
         <v>360</v>
       </c>
-      <c r="G121" s="41" t="s">
+      <c r="G121" s="51" t="s">
         <v>361</v>
       </c>
-      <c r="H121" s="41" t="s">
-        <v>293</v>
-      </c>
-      <c r="I121" s="41" t="s">
-        <v>896</v>
-      </c>
-      <c r="J121" s="41" t="s">
-        <v>1325</v>
-      </c>
-      <c r="K121" s="41"/>
-      <c r="L121" s="41" t="s">
-        <v>1326</v>
-      </c>
-      <c r="M121" s="41" t="s">
-        <v>1327</v>
-      </c>
-      <c r="N121" s="42" t="s">
-        <v>1335</v>
-      </c>
-      <c r="O121" s="41"/>
-      <c r="P121" s="41"/>
-      <c r="Q121" s="41" t="s">
-        <v>1328</v>
-      </c>
-      <c r="R121" s="41" t="s">
+      <c r="H121" s="51" t="s">
+        <v>324</v>
+      </c>
+      <c r="I121" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="J121" s="51" t="s">
+        <v>1512</v>
+      </c>
+      <c r="K121" s="51"/>
+      <c r="L121" s="51" t="s">
+        <v>1698</v>
+      </c>
+      <c r="M121" s="66" t="s">
+        <v>1699</v>
+      </c>
+      <c r="N121" s="55" t="s">
+        <v>1700</v>
+      </c>
+      <c r="O121" s="51"/>
+      <c r="P121" s="51"/>
+      <c r="Q121" s="51" t="s">
+        <v>1701</v>
+      </c>
+      <c r="R121" s="51" t="s">
         <v>558</v>
       </c>
-      <c r="S121" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="T121" s="45" t="s">
-        <v>1430</v>
-      </c>
-      <c r="U121" s="45" t="s">
-        <v>651</v>
-      </c>
-      <c r="V121" s="41"/>
-      <c r="W121" s="41" t="s">
-        <v>1195</v>
-      </c>
-      <c r="X121" s="41">
+      <c r="S121" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="T121" s="51" t="s">
+        <v>390</v>
+      </c>
+      <c r="U121" s="51" t="s">
+        <v>477</v>
+      </c>
+      <c r="V121" s="51"/>
+      <c r="W121" s="51" t="s">
+        <v>1183</v>
+      </c>
+      <c r="X121" s="51">
         <v>3</v>
       </c>
-    </row>
-    <row r="122" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Y121" s="51"/>
+    </row>
+    <row r="122" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>370</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="C122" s="40" t="s">
-        <v>1320</v>
+      <c r="C122" s="39" t="s">
+        <v>1308</v>
       </c>
       <c r="D122" s="2"/>
       <c r="E122" s="2"/>
@@ -12905,53 +12975,53 @@
       <c r="G122" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="H122" s="12" t="s">
+      <c r="H122" s="14" t="s">
         <v>374</v>
       </c>
-      <c r="I122" s="2" t="s">
+      <c r="I122" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="J122" s="15" t="s">
+      <c r="J122" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="K122" s="2"/>
-      <c r="L122" s="2"/>
-      <c r="M122" s="3" t="s">
+      <c r="K122" s="9"/>
+      <c r="L122" s="9"/>
+      <c r="M122" s="60" t="s">
         <v>375</v>
       </c>
-      <c r="N122" s="2" t="s">
+      <c r="N122" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="O122" s="2"/>
-      <c r="P122" s="2"/>
-      <c r="Q122" s="3"/>
-      <c r="R122" s="3"/>
-      <c r="S122" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="T122" s="18" t="s">
+      <c r="O122" s="9"/>
+      <c r="P122" s="9"/>
+      <c r="Q122" s="10"/>
+      <c r="R122" s="10"/>
+      <c r="S122" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T122" s="20" t="s">
         <v>377</v>
       </c>
-      <c r="U122" s="18" t="s">
+      <c r="U122" s="20" t="s">
         <v>378</v>
       </c>
-      <c r="V122" s="2"/>
-      <c r="W122" s="2" t="s">
+      <c r="V122" s="9"/>
+      <c r="W122" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="X122" s="2">
+      <c r="X122" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>370</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="C123" s="40" t="s">
-        <v>1320</v>
+      <c r="C123" s="39" t="s">
+        <v>1308</v>
       </c>
       <c r="D123" s="2"/>
       <c r="E123" s="2"/>
@@ -12972,7 +13042,7 @@
       </c>
       <c r="K123" s="2"/>
       <c r="L123" s="2"/>
-      <c r="M123" s="3" t="s">
+      <c r="M123" s="56" t="s">
         <v>379</v>
       </c>
       <c r="N123" s="2" t="s">
@@ -12999,15 +13069,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>370</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="C124" s="40" t="s">
-        <v>1320</v>
+      <c r="C124" s="39" t="s">
+        <v>1308</v>
       </c>
       <c r="D124" s="2"/>
       <c r="E124" s="2"/>
@@ -13017,7 +13087,7 @@
       <c r="G124" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="H124" s="2" t="s">
+      <c r="H124" s="32" t="s">
         <v>543</v>
       </c>
       <c r="I124" s="2" t="s">
@@ -13028,16 +13098,16 @@
       </c>
       <c r="K124" s="2"/>
       <c r="L124" s="2"/>
-      <c r="M124" s="2" t="s">
-        <v>1300</v>
+      <c r="M124" s="57" t="s">
+        <v>1288</v>
       </c>
       <c r="N124" s="5" t="s">
-        <v>1314</v>
+        <v>1302</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" s="2"/>
       <c r="Q124" s="2" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="R124" s="2" t="s">
         <v>558</v>
@@ -13049,7 +13119,7 @@
         <v>306</v>
       </c>
       <c r="U124" s="18" t="s">
-        <v>1142</v>
+        <v>1130</v>
       </c>
       <c r="V124" s="2"/>
       <c r="W124" s="2" t="s">
@@ -13059,15 +13129,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>370</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="C125" s="40" t="s">
-        <v>1320</v>
+      <c r="C125" s="39" t="s">
+        <v>1308</v>
       </c>
       <c r="D125" s="2"/>
       <c r="E125" s="2"/>
@@ -13077,7 +13147,7 @@
       <c r="G125" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="H125" s="2" t="s">
+      <c r="H125" s="32" t="s">
         <v>904</v>
       </c>
       <c r="I125" s="2" t="s">
@@ -13088,16 +13158,16 @@
       </c>
       <c r="K125" s="2"/>
       <c r="L125" s="2"/>
-      <c r="M125" s="2" t="s">
-        <v>1301</v>
+      <c r="M125" s="57" t="s">
+        <v>1289</v>
       </c>
       <c r="N125" s="5" t="s">
-        <v>1315</v>
+        <v>1303</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" s="2"/>
       <c r="Q125" s="2" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="R125" s="2" t="s">
         <v>558</v>
@@ -13119,15 +13189,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>370</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="C126" s="40" t="s">
-        <v>1320</v>
+      <c r="C126" s="39" t="s">
+        <v>1308</v>
       </c>
       <c r="D126" s="2"/>
       <c r="E126" s="2"/>
@@ -13137,7 +13207,7 @@
       <c r="G126" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="H126" s="2" t="s">
+      <c r="H126" s="32" t="s">
         <v>904</v>
       </c>
       <c r="I126" s="2" t="s">
@@ -13148,16 +13218,16 @@
       </c>
       <c r="K126" s="2"/>
       <c r="L126" s="2"/>
-      <c r="M126" s="2" t="s">
-        <v>1302</v>
+      <c r="M126" s="57" t="s">
+        <v>1290</v>
       </c>
       <c r="N126" s="5" t="s">
-        <v>1316</v>
+        <v>1304</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" s="2"/>
       <c r="Q126" s="2" t="s">
-        <v>1303</v>
+        <v>1291</v>
       </c>
       <c r="R126" s="2" t="s">
         <v>558</v>
@@ -13166,10 +13236,10 @@
         <v>32</v>
       </c>
       <c r="T126" s="18" t="s">
-        <v>1304</v>
+        <v>1292</v>
       </c>
       <c r="U126" s="18" t="s">
-        <v>1305</v>
+        <v>1293</v>
       </c>
       <c r="V126" s="2"/>
       <c r="W126" s="2" t="s">
@@ -13179,15 +13249,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>370</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="C127" s="40" t="s">
-        <v>1320</v>
+      <c r="C127" s="39" t="s">
+        <v>1308</v>
       </c>
       <c r="D127" s="2"/>
       <c r="E127" s="2"/>
@@ -13197,7 +13267,7 @@
       <c r="G127" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="H127" s="2" t="s">
+      <c r="H127" s="32" t="s">
         <v>183</v>
       </c>
       <c r="I127" s="2" t="s">
@@ -13208,16 +13278,16 @@
       </c>
       <c r="K127" s="2"/>
       <c r="L127" s="2"/>
-      <c r="M127" s="2" t="s">
-        <v>1306</v>
+      <c r="M127" s="57" t="s">
+        <v>1294</v>
       </c>
       <c r="N127" s="5" t="s">
-        <v>1317</v>
+        <v>1305</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" s="2"/>
       <c r="Q127" s="2" t="s">
-        <v>1306</v>
+        <v>1294</v>
       </c>
       <c r="R127" s="2" t="s">
         <v>558</v>
@@ -13226,7 +13296,7 @@
         <v>32</v>
       </c>
       <c r="T127" s="18" t="s">
-        <v>1307</v>
+        <v>1295</v>
       </c>
       <c r="U127" s="18" t="s">
         <v>946</v>
@@ -13239,15 +13309,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>370</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="C128" s="40" t="s">
-        <v>1320</v>
+      <c r="C128" s="39" t="s">
+        <v>1308</v>
       </c>
       <c r="D128" s="2"/>
       <c r="E128" s="2"/>
@@ -13257,7 +13327,7 @@
       <c r="G128" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="H128" s="2" t="s">
+      <c r="H128" s="32" t="s">
         <v>417</v>
       </c>
       <c r="I128" s="2" t="s">
@@ -13268,16 +13338,16 @@
       </c>
       <c r="K128" s="2"/>
       <c r="L128" s="2"/>
-      <c r="M128" s="2" t="s">
-        <v>1308</v>
+      <c r="M128" s="57" t="s">
+        <v>1296</v>
       </c>
       <c r="N128" s="5" t="s">
-        <v>1318</v>
+        <v>1306</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" s="2"/>
       <c r="Q128" s="2" t="s">
-        <v>1308</v>
+        <v>1296</v>
       </c>
       <c r="R128" s="2" t="s">
         <v>558</v>
@@ -13286,7 +13356,7 @@
         <v>32</v>
       </c>
       <c r="T128" s="18" t="s">
-        <v>1309</v>
+        <v>1297</v>
       </c>
       <c r="U128" s="18" t="s">
         <v>742</v>
@@ -13306,8 +13376,8 @@
       <c r="B129" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="C129" s="40" t="s">
-        <v>1320</v>
+      <c r="C129" s="39" t="s">
+        <v>1308</v>
       </c>
       <c r="D129" s="2"/>
       <c r="E129" s="2"/>
@@ -13317,7 +13387,7 @@
       <c r="G129" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="H129" s="2" t="s">
+      <c r="H129" s="32" t="s">
         <v>790</v>
       </c>
       <c r="I129" s="2" t="s">
@@ -13328,16 +13398,16 @@
       </c>
       <c r="K129" s="2"/>
       <c r="L129" s="2"/>
-      <c r="M129" s="2" t="s">
-        <v>1310</v>
+      <c r="M129" s="57" t="s">
+        <v>1298</v>
       </c>
       <c r="N129" s="5" t="s">
-        <v>1319</v>
+        <v>1307</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" s="2"/>
       <c r="Q129" s="2" t="s">
-        <v>1311</v>
+        <v>1299</v>
       </c>
       <c r="R129" s="2" t="s">
         <v>558</v>
@@ -13346,10 +13416,10 @@
         <v>32</v>
       </c>
       <c r="T129" s="18" t="s">
-        <v>1312</v>
+        <v>1300</v>
       </c>
       <c r="U129" s="18" t="s">
-        <v>1313</v>
+        <v>1301</v>
       </c>
       <c r="V129" s="2"/>
       <c r="W129" s="2" t="s">
@@ -13386,7 +13456,7 @@
       </c>
       <c r="K130" s="2"/>
       <c r="L130" s="2"/>
-      <c r="M130" s="3" t="s">
+      <c r="M130" s="56" t="s">
         <v>387</v>
       </c>
       <c r="N130" s="2" t="s">
@@ -13442,7 +13512,7 @@
       </c>
       <c r="K131" s="2"/>
       <c r="L131" s="2"/>
-      <c r="M131" s="3" t="s">
+      <c r="M131" s="56" t="s">
         <v>127</v>
       </c>
       <c r="N131" s="2" t="s">
@@ -13487,8 +13557,8 @@
       <c r="G132" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="H132" s="2" t="s">
-        <v>1288</v>
+      <c r="H132" s="32" t="s">
+        <v>1276</v>
       </c>
       <c r="I132" s="2" t="s">
         <v>487</v>
@@ -13498,16 +13568,16 @@
       </c>
       <c r="K132" s="2"/>
       <c r="L132" s="2"/>
-      <c r="M132" s="2" t="s">
-        <v>1289</v>
+      <c r="M132" s="57" t="s">
+        <v>1277</v>
       </c>
       <c r="N132" s="5" t="s">
-        <v>1298</v>
+        <v>1286</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" s="2"/>
       <c r="Q132" s="2" t="s">
-        <v>1290</v>
+        <v>1278</v>
       </c>
       <c r="R132" s="2" t="s">
         <v>558</v>
@@ -13516,14 +13586,14 @@
         <v>32</v>
       </c>
       <c r="T132" s="18" t="s">
-        <v>1291</v>
+        <v>1279</v>
       </c>
       <c r="U132" s="18" t="s">
-        <v>1292</v>
+        <v>1280</v>
       </c>
       <c r="V132" s="2"/>
       <c r="W132" s="2" t="s">
-        <v>1293</v>
+        <v>1281</v>
       </c>
       <c r="X132" s="2">
         <v>3</v>
@@ -13545,7 +13615,7 @@
       <c r="G133" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="H133" s="2" t="s">
+      <c r="H133" s="32" t="s">
         <v>834</v>
       </c>
       <c r="I133" s="2" t="s">
@@ -13556,16 +13626,16 @@
       </c>
       <c r="K133" s="2"/>
       <c r="L133" s="2"/>
-      <c r="M133" s="2" t="s">
-        <v>1294</v>
+      <c r="M133" s="57" t="s">
+        <v>1282</v>
       </c>
       <c r="N133" s="5" t="s">
-        <v>1299</v>
+        <v>1287</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" s="2"/>
       <c r="Q133" s="2" t="s">
-        <v>1295</v>
+        <v>1283</v>
       </c>
       <c r="R133" s="2" t="s">
         <v>558</v>
@@ -13574,14 +13644,14 @@
         <v>32</v>
       </c>
       <c r="T133" s="18" t="s">
-        <v>1296</v>
+        <v>1284</v>
       </c>
       <c r="U133" s="18" t="s">
-        <v>1297</v>
+        <v>1285</v>
       </c>
       <c r="V133" s="2"/>
       <c r="W133" s="2" t="s">
-        <v>1293</v>
+        <v>1281</v>
       </c>
       <c r="X133" s="2">
         <v>3</v>
@@ -13614,7 +13684,7 @@
       </c>
       <c r="K134" s="2"/>
       <c r="L134" s="2"/>
-      <c r="M134" s="3" t="s">
+      <c r="M134" s="56" t="s">
         <v>399</v>
       </c>
       <c r="N134" s="2" t="s">
@@ -13670,7 +13740,7 @@
       </c>
       <c r="K135" s="2"/>
       <c r="L135" s="2"/>
-      <c r="M135" s="3" t="s">
+      <c r="M135" s="56" t="s">
         <v>405</v>
       </c>
       <c r="N135" s="2" t="s">
@@ -13726,7 +13796,7 @@
       </c>
       <c r="K136" s="2"/>
       <c r="L136" s="2"/>
-      <c r="M136" s="3" t="s">
+      <c r="M136" s="56" t="s">
         <v>410</v>
       </c>
       <c r="N136" s="2" t="s">
@@ -13771,7 +13841,7 @@
       <c r="G137" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="H137" s="2" t="s">
+      <c r="H137" s="32" t="s">
         <v>404</v>
       </c>
       <c r="I137" s="2" t="s">
@@ -13782,20 +13852,20 @@
       </c>
       <c r="K137" s="2"/>
       <c r="L137" s="2" t="s">
-        <v>1268</v>
-      </c>
-      <c r="M137" s="2" t="s">
-        <v>1269</v>
+        <v>1256</v>
+      </c>
+      <c r="M137" s="57" t="s">
+        <v>1257</v>
       </c>
       <c r="N137" s="5" t="s">
-        <v>1284</v>
+        <v>1272</v>
       </c>
       <c r="O137" s="2" t="s">
-        <v>1270</v>
+        <v>1258</v>
       </c>
       <c r="P137" s="2"/>
       <c r="Q137" s="2" t="s">
-        <v>1271</v>
+        <v>1259</v>
       </c>
       <c r="R137" s="2" t="s">
         <v>558</v>
@@ -13804,14 +13874,14 @@
         <v>32</v>
       </c>
       <c r="T137" s="18" t="s">
-        <v>1272</v>
+        <v>1260</v>
       </c>
       <c r="U137" s="18" t="s">
-        <v>1273</v>
+        <v>1261</v>
       </c>
       <c r="V137" s="2"/>
       <c r="W137" s="2" t="s">
-        <v>1274</v>
+        <v>1262</v>
       </c>
       <c r="X137" s="2">
         <v>2</v>
@@ -13833,7 +13903,7 @@
       <c r="G138" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="H138" s="2" t="s">
+      <c r="H138" s="32" t="s">
         <v>404</v>
       </c>
       <c r="I138" s="2" t="s">
@@ -13844,20 +13914,20 @@
       </c>
       <c r="K138" s="2"/>
       <c r="L138" s="2" t="s">
-        <v>1268</v>
-      </c>
-      <c r="M138" s="2" t="s">
-        <v>1275</v>
+        <v>1256</v>
+      </c>
+      <c r="M138" s="57" t="s">
+        <v>1263</v>
       </c>
       <c r="N138" s="5" t="s">
-        <v>1285</v>
+        <v>1273</v>
       </c>
       <c r="O138" s="2" t="s">
-        <v>1270</v>
+        <v>1258</v>
       </c>
       <c r="P138" s="2"/>
       <c r="Q138" s="2" t="s">
-        <v>1276</v>
+        <v>1264</v>
       </c>
       <c r="R138" s="2" t="s">
         <v>558</v>
@@ -13866,14 +13936,14 @@
         <v>32</v>
       </c>
       <c r="T138" s="18" t="s">
-        <v>1272</v>
+        <v>1260</v>
       </c>
       <c r="U138" s="18" t="s">
-        <v>1273</v>
+        <v>1261</v>
       </c>
       <c r="V138" s="2"/>
       <c r="W138" s="2" t="s">
-        <v>1274</v>
+        <v>1262</v>
       </c>
       <c r="X138" s="2">
         <v>2</v>
@@ -13895,7 +13965,7 @@
       <c r="G139" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="H139" s="2" t="s">
+      <c r="H139" s="32" t="s">
         <v>404</v>
       </c>
       <c r="I139" s="2" t="s">
@@ -13906,20 +13976,20 @@
       </c>
       <c r="K139" s="2"/>
       <c r="L139" s="2" t="s">
-        <v>1268</v>
-      </c>
-      <c r="M139" s="2" t="s">
-        <v>1277</v>
+        <v>1256</v>
+      </c>
+      <c r="M139" s="57" t="s">
+        <v>1265</v>
       </c>
       <c r="N139" s="5" t="s">
-        <v>1286</v>
+        <v>1274</v>
       </c>
       <c r="O139" s="2" t="s">
-        <v>1270</v>
+        <v>1258</v>
       </c>
       <c r="P139" s="2"/>
       <c r="Q139" s="2" t="s">
-        <v>1278</v>
+        <v>1266</v>
       </c>
       <c r="R139" s="2" t="s">
         <v>558</v>
@@ -13928,14 +13998,14 @@
         <v>32</v>
       </c>
       <c r="T139" s="18" t="s">
-        <v>1279</v>
+        <v>1267</v>
       </c>
       <c r="U139" s="18" t="s">
-        <v>1273</v>
+        <v>1261</v>
       </c>
       <c r="V139" s="2"/>
       <c r="W139" s="2" t="s">
-        <v>1274</v>
+        <v>1262</v>
       </c>
       <c r="X139" s="2">
         <v>2</v>
@@ -13957,7 +14027,7 @@
       <c r="G140" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="H140" s="2" t="s">
+      <c r="H140" s="32" t="s">
         <v>404</v>
       </c>
       <c r="I140" s="2" t="s">
@@ -13968,20 +14038,20 @@
       </c>
       <c r="K140" s="2"/>
       <c r="L140" s="2" t="s">
+        <v>1256</v>
+      </c>
+      <c r="M140" s="57" t="s">
         <v>1268</v>
       </c>
-      <c r="M140" s="2" t="s">
-        <v>1280</v>
-      </c>
       <c r="N140" s="5" t="s">
-        <v>1287</v>
+        <v>1275</v>
       </c>
       <c r="O140" s="2" t="s">
-        <v>1270</v>
+        <v>1258</v>
       </c>
       <c r="P140" s="2"/>
       <c r="Q140" s="2" t="s">
-        <v>1281</v>
+        <v>1269</v>
       </c>
       <c r="R140" s="2" t="s">
         <v>558</v>
@@ -13990,14 +14060,14 @@
         <v>32</v>
       </c>
       <c r="T140" s="18" t="s">
-        <v>1279</v>
+        <v>1267</v>
       </c>
       <c r="U140" s="18" t="s">
-        <v>1273</v>
+        <v>1261</v>
       </c>
       <c r="V140" s="2"/>
       <c r="W140" s="2" t="s">
-        <v>1274</v>
+        <v>1262</v>
       </c>
       <c r="X140" s="2">
         <v>2</v>
@@ -14019,7 +14089,7 @@
       <c r="G141" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="H141" s="2" t="s">
+      <c r="H141" s="32" t="s">
         <v>404</v>
       </c>
       <c r="I141" s="2" t="s">
@@ -14030,18 +14100,18 @@
       </c>
       <c r="K141" s="2"/>
       <c r="L141" s="2" t="s">
-        <v>1268</v>
-      </c>
-      <c r="M141" s="2" t="s">
-        <v>1282</v>
+        <v>1256</v>
+      </c>
+      <c r="M141" s="57" t="s">
+        <v>1270</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2" t="s">
-        <v>1270</v>
+        <v>1258</v>
       </c>
       <c r="P141" s="2"/>
       <c r="Q141" s="2" t="s">
-        <v>1283</v>
+        <v>1271</v>
       </c>
       <c r="R141" s="2" t="s">
         <v>558</v>
@@ -14050,14 +14120,14 @@
         <v>32</v>
       </c>
       <c r="T141" s="18" t="s">
-        <v>1272</v>
+        <v>1260</v>
       </c>
       <c r="U141" s="18" t="s">
-        <v>1273</v>
+        <v>1261</v>
       </c>
       <c r="V141" s="2"/>
       <c r="W141" s="2" t="s">
-        <v>1274</v>
+        <v>1262</v>
       </c>
       <c r="X141" s="2">
         <v>2</v>
@@ -14090,7 +14160,7 @@
       </c>
       <c r="K142" s="2"/>
       <c r="L142" s="2"/>
-      <c r="M142" s="3" t="s">
+      <c r="M142" s="56" t="s">
         <v>420</v>
       </c>
       <c r="N142" s="2" t="s">
@@ -14146,7 +14216,7 @@
       </c>
       <c r="K143" s="2"/>
       <c r="L143" s="2"/>
-      <c r="M143" s="3" t="s">
+      <c r="M143" s="56" t="s">
         <v>427</v>
       </c>
       <c r="N143" s="2" t="s">
@@ -14192,46 +14262,46 @@
         <v>416</v>
       </c>
       <c r="H144" s="37" t="s">
-        <v>1254</v>
-      </c>
-      <c r="I144" s="38" t="s">
+        <v>1242</v>
+      </c>
+      <c r="I144" s="37" t="s">
         <v>302</v>
       </c>
-      <c r="J144" s="38" t="s">
+      <c r="J144" s="37" t="s">
+        <v>1243</v>
+      </c>
+      <c r="K144" s="37"/>
+      <c r="L144" s="37" t="s">
+        <v>1244</v>
+      </c>
+      <c r="M144" s="58" t="s">
+        <v>1245</v>
+      </c>
+      <c r="N144" s="5" t="s">
         <v>1255</v>
       </c>
-      <c r="K144" s="38"/>
-      <c r="L144" s="38" t="s">
-        <v>1256</v>
-      </c>
-      <c r="M144" s="38" t="s">
-        <v>1257</v>
-      </c>
-      <c r="N144" s="5" t="s">
-        <v>1267</v>
-      </c>
-      <c r="O144" s="38" t="s">
-        <v>1258</v>
-      </c>
-      <c r="P144" s="38"/>
-      <c r="Q144" s="38" t="s">
-        <v>1259</v>
-      </c>
-      <c r="R144" s="38" t="s">
+      <c r="O144" s="37" t="s">
+        <v>1246</v>
+      </c>
+      <c r="P144" s="37"/>
+      <c r="Q144" s="37" t="s">
+        <v>1247</v>
+      </c>
+      <c r="R144" s="37" t="s">
         <v>558</v>
       </c>
-      <c r="S144" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="T144" s="39" t="s">
+      <c r="S144" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="T144" s="38" t="s">
         <v>451</v>
       </c>
-      <c r="U144" s="39" t="s">
-        <v>1260</v>
-      </c>
-      <c r="V144" s="38"/>
-      <c r="W144" s="39" t="s">
-        <v>1261</v>
+      <c r="U144" s="38" t="s">
+        <v>1248</v>
+      </c>
+      <c r="V144" s="37"/>
+      <c r="W144" s="38" t="s">
+        <v>1249</v>
       </c>
       <c r="X144" s="2">
         <v>3</v>
@@ -14256,40 +14326,40 @@
       <c r="H145" s="37" t="s">
         <v>230</v>
       </c>
-      <c r="I145" s="38" t="s">
+      <c r="I145" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="J145" s="38" t="s">
+      <c r="J145" s="37" t="s">
         <v>752</v>
       </c>
-      <c r="K145" s="38"/>
-      <c r="L145" s="38"/>
-      <c r="M145" s="38" t="s">
-        <v>1262</v>
+      <c r="K145" s="37"/>
+      <c r="L145" s="37"/>
+      <c r="M145" s="58" t="s">
+        <v>1250</v>
       </c>
       <c r="N145" s="5" t="s">
-        <v>1266</v>
-      </c>
-      <c r="O145" s="38"/>
-      <c r="P145" s="38"/>
-      <c r="Q145" s="38" t="s">
-        <v>1263</v>
-      </c>
-      <c r="R145" s="38" t="s">
+        <v>1254</v>
+      </c>
+      <c r="O145" s="37"/>
+      <c r="P145" s="37"/>
+      <c r="Q145" s="37" t="s">
+        <v>1251</v>
+      </c>
+      <c r="R145" s="37" t="s">
         <v>558</v>
       </c>
-      <c r="S145" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="T145" s="39" t="s">
-        <v>1264</v>
-      </c>
-      <c r="U145" s="39" t="s">
-        <v>1265</v>
-      </c>
-      <c r="V145" s="38"/>
-      <c r="W145" s="39" t="s">
-        <v>1261</v>
+      <c r="S145" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="T145" s="38" t="s">
+        <v>1252</v>
+      </c>
+      <c r="U145" s="38" t="s">
+        <v>1253</v>
+      </c>
+      <c r="V145" s="37"/>
+      <c r="W145" s="38" t="s">
+        <v>1249</v>
       </c>
       <c r="X145" s="2">
         <v>3</v>
@@ -14322,7 +14392,7 @@
       </c>
       <c r="K146" s="2"/>
       <c r="L146" s="2"/>
-      <c r="M146" s="3" t="s">
+      <c r="M146" s="56" t="s">
         <v>436</v>
       </c>
       <c r="N146" s="2" t="s">
@@ -14373,7 +14443,7 @@
       </c>
       <c r="K147" s="2"/>
       <c r="L147" s="2"/>
-      <c r="M147" s="3" t="s">
+      <c r="M147" s="56" t="s">
         <v>441</v>
       </c>
       <c r="N147" s="2" t="s">
@@ -14416,7 +14486,7 @@
       <c r="G148" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="H148" s="33" t="s">
+      <c r="H148" s="34" t="s">
         <v>834</v>
       </c>
       <c r="I148" s="34" t="s">
@@ -14427,27 +14497,27 @@
       </c>
       <c r="K148" s="34"/>
       <c r="L148" s="34" t="s">
-        <v>1246</v>
-      </c>
-      <c r="M148" s="34" t="s">
-        <v>1247</v>
+        <v>1234</v>
+      </c>
+      <c r="M148" s="67" t="s">
+        <v>1235</v>
       </c>
       <c r="N148" s="5" t="s">
-        <v>1252</v>
+        <v>1240</v>
       </c>
       <c r="O148" s="34"/>
       <c r="P148" s="34"/>
       <c r="Q148" s="34" t="s">
-        <v>1248</v>
+        <v>1236</v>
       </c>
       <c r="R148" s="34" t="s">
-        <v>1249</v>
+        <v>1237</v>
       </c>
       <c r="S148" s="34" t="s">
         <v>619</v>
       </c>
       <c r="T148" s="33" t="s">
-        <v>1250</v>
+        <v>1238</v>
       </c>
       <c r="U148" s="33" t="s">
         <v>498</v>
@@ -14476,7 +14546,7 @@
       <c r="G149" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="H149" s="35" t="s">
+      <c r="H149" s="36" t="s">
         <v>581</v>
       </c>
       <c r="I149" s="36" t="s">
@@ -14489,16 +14559,16 @@
       <c r="L149" s="36" t="s">
         <v>640</v>
       </c>
-      <c r="M149" s="36" t="s">
-        <v>1251</v>
+      <c r="M149" s="61" t="s">
+        <v>1239</v>
       </c>
       <c r="N149" s="5" t="s">
-        <v>1253</v>
+        <v>1241</v>
       </c>
       <c r="O149" s="36"/>
       <c r="P149" s="36"/>
       <c r="Q149" s="36" t="s">
-        <v>1251</v>
+        <v>1239</v>
       </c>
       <c r="R149" s="36" t="s">
         <v>558</v>
@@ -14544,7 +14614,7 @@
       </c>
       <c r="K150" s="2"/>
       <c r="L150" s="2"/>
-      <c r="M150" s="3" t="s">
+      <c r="M150" s="56" t="s">
         <v>448</v>
       </c>
       <c r="N150" s="2" t="s">
@@ -14587,8 +14657,8 @@
       <c r="G151" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="H151" s="2" t="s">
-        <v>1232</v>
+      <c r="H151" s="32" t="s">
+        <v>1220</v>
       </c>
       <c r="I151" s="2" t="s">
         <v>302</v>
@@ -14598,16 +14668,16 @@
       </c>
       <c r="K151" s="2"/>
       <c r="L151" s="2"/>
-      <c r="M151" s="2" t="s">
-        <v>1233</v>
+      <c r="M151" s="57" t="s">
+        <v>1221</v>
       </c>
       <c r="N151" s="5" t="s">
-        <v>1239</v>
+        <v>1227</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" s="2"/>
       <c r="Q151" s="2" t="s">
-        <v>1234</v>
+        <v>1222</v>
       </c>
       <c r="R151" s="2" t="s">
         <v>558</v>
@@ -14616,7 +14686,7 @@
         <v>32</v>
       </c>
       <c r="T151" s="18" t="s">
-        <v>1153</v>
+        <v>1141</v>
       </c>
       <c r="U151" s="18" t="s">
         <v>259</v>
@@ -14645,24 +14715,24 @@
       <c r="G152" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="H152" s="2" t="s">
-        <v>1244</v>
+      <c r="H152" s="32" t="s">
+        <v>1232</v>
       </c>
       <c r="I152" s="2" t="s">
-        <v>1241</v>
+        <v>1229</v>
       </c>
       <c r="J152" s="2" t="s">
-        <v>1242</v>
+        <v>1230</v>
       </c>
       <c r="K152" s="2"/>
       <c r="L152" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="M152" s="2" t="s">
-        <v>1243</v>
+      <c r="M152" s="57" t="s">
+        <v>1231</v>
       </c>
       <c r="N152" s="5" t="s">
-        <v>1240</v>
+        <v>1228</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" s="2"/>
@@ -14674,10 +14744,10 @@
         <v>32</v>
       </c>
       <c r="T152" s="18" t="s">
-        <v>1193</v>
+        <v>1181</v>
       </c>
       <c r="U152" s="18" t="s">
-        <v>1236</v>
+        <v>1224</v>
       </c>
       <c r="V152" s="2"/>
       <c r="W152" s="2" t="s">
@@ -14703,7 +14773,7 @@
       <c r="G153" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="H153" s="2" t="s">
+      <c r="H153" s="32" t="s">
         <v>132</v>
       </c>
       <c r="I153" s="2" t="s">
@@ -14716,18 +14786,18 @@
       <c r="L153" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="M153" s="2" t="s">
-        <v>1238</v>
+      <c r="M153" s="57" t="s">
+        <v>1226</v>
       </c>
       <c r="N153" s="5" t="s">
-        <v>1245</v>
+        <v>1233</v>
       </c>
       <c r="O153" s="2" t="s">
-        <v>1235</v>
+        <v>1223</v>
       </c>
       <c r="P153" s="2"/>
       <c r="Q153" s="2" t="s">
-        <v>1238</v>
+        <v>1226</v>
       </c>
       <c r="R153" s="2" t="s">
         <v>558</v>
@@ -14736,10 +14806,10 @@
         <v>32</v>
       </c>
       <c r="T153" s="18" t="s">
-        <v>1236</v>
+        <v>1224</v>
       </c>
       <c r="U153" s="18" t="s">
-        <v>1237</v>
+        <v>1225</v>
       </c>
       <c r="V153" s="2"/>
       <c r="W153" s="2" t="s">
@@ -14776,7 +14846,7 @@
       </c>
       <c r="K154" s="2"/>
       <c r="L154" s="2"/>
-      <c r="M154" s="3" t="s">
+      <c r="M154" s="56" t="s">
         <v>454</v>
       </c>
       <c r="N154" s="2" t="s">
@@ -14821,7 +14891,7 @@
       <c r="G155" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="H155" s="2" t="s">
+      <c r="H155" s="32" t="s">
         <v>473</v>
       </c>
       <c r="I155" s="2" t="s">
@@ -14832,16 +14902,16 @@
       </c>
       <c r="K155" s="2"/>
       <c r="L155" s="2"/>
-      <c r="M155" s="2" t="s">
-        <v>1228</v>
+      <c r="M155" s="57" t="s">
+        <v>1216</v>
       </c>
       <c r="N155" s="5" t="s">
-        <v>1229</v>
+        <v>1217</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" s="2"/>
       <c r="Q155" s="2" t="s">
-        <v>1227</v>
+        <v>1215</v>
       </c>
       <c r="R155" s="2" t="s">
         <v>558</v>
@@ -14850,7 +14920,7 @@
         <v>32</v>
       </c>
       <c r="T155" s="18" t="s">
-        <v>1226</v>
+        <v>1214</v>
       </c>
       <c r="U155" s="18" t="s">
         <v>689</v>
@@ -14879,29 +14949,29 @@
       <c r="G156" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="H156" s="2" t="s">
+      <c r="H156" s="32" t="s">
         <v>182</v>
       </c>
       <c r="I156" s="2" t="s">
         <v>656</v>
       </c>
       <c r="J156" s="2" t="s">
-        <v>1225</v>
+        <v>1213</v>
       </c>
       <c r="K156" s="2"/>
       <c r="L156" s="2" t="s">
-        <v>1224</v>
-      </c>
-      <c r="M156" s="2" t="s">
-        <v>1223</v>
+        <v>1212</v>
+      </c>
+      <c r="M156" s="57" t="s">
+        <v>1211</v>
       </c>
       <c r="N156" s="5" t="s">
-        <v>1230</v>
+        <v>1218</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" s="2"/>
       <c r="Q156" s="2" t="s">
-        <v>1222</v>
+        <v>1210</v>
       </c>
       <c r="R156" s="2" t="s">
         <v>558</v>
@@ -14910,10 +14980,10 @@
         <v>32</v>
       </c>
       <c r="T156" s="18" t="s">
-        <v>1221</v>
+        <v>1209</v>
       </c>
       <c r="U156" s="18" t="s">
-        <v>1220</v>
+        <v>1208</v>
       </c>
       <c r="V156" s="2"/>
       <c r="W156" s="2" t="s">
@@ -14939,7 +15009,7 @@
       <c r="G157" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="H157" s="2" t="s">
+      <c r="H157" s="32" t="s">
         <v>79</v>
       </c>
       <c r="I157" s="2" t="s">
@@ -14950,16 +15020,16 @@
       </c>
       <c r="K157" s="2"/>
       <c r="L157" s="2"/>
-      <c r="M157" s="2" t="s">
+      <c r="M157" s="57" t="s">
+        <v>1207</v>
+      </c>
+      <c r="N157" s="5" t="s">
         <v>1219</v>
-      </c>
-      <c r="N157" s="5" t="s">
-        <v>1231</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" s="2"/>
       <c r="Q157" s="2" t="s">
-        <v>1218</v>
+        <v>1206</v>
       </c>
       <c r="R157" s="2" t="s">
         <v>558</v>
@@ -14968,10 +15038,10 @@
         <v>32</v>
       </c>
       <c r="T157" s="18" t="s">
-        <v>1217</v>
+        <v>1205</v>
       </c>
       <c r="U157" s="18" t="s">
-        <v>1216</v>
+        <v>1204</v>
       </c>
       <c r="V157" s="2"/>
       <c r="W157" s="2" t="s">
@@ -15008,7 +15078,7 @@
       </c>
       <c r="K158" s="2"/>
       <c r="L158" s="2"/>
-      <c r="M158" s="3" t="s">
+      <c r="M158" s="56" t="s">
         <v>465</v>
       </c>
       <c r="N158" s="2" t="s">
@@ -15053,7 +15123,7 @@
       <c r="G159" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="H159" s="2" t="s">
+      <c r="H159" s="32" t="s">
         <v>695</v>
       </c>
       <c r="I159" s="2" t="s">
@@ -15064,16 +15134,16 @@
       </c>
       <c r="K159" s="2"/>
       <c r="L159" s="2"/>
-      <c r="M159" s="2" t="s">
-        <v>1202</v>
+      <c r="M159" s="57" t="s">
+        <v>1190</v>
       </c>
       <c r="N159" s="5" t="s">
-        <v>1213</v>
+        <v>1201</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" s="2"/>
       <c r="Q159" s="2" t="s">
-        <v>1203</v>
+        <v>1191</v>
       </c>
       <c r="R159" s="2" t="s">
         <v>558</v>
@@ -15082,7 +15152,7 @@
         <v>32</v>
       </c>
       <c r="T159" s="18" t="s">
-        <v>1204</v>
+        <v>1192</v>
       </c>
       <c r="U159" s="18" t="s">
         <v>984</v>
@@ -15111,7 +15181,7 @@
       <c r="G160" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="H160" s="2" t="s">
+      <c r="H160" s="32" t="s">
         <v>230</v>
       </c>
       <c r="I160" s="2" t="s">
@@ -15122,16 +15192,16 @@
       </c>
       <c r="K160" s="2"/>
       <c r="L160" s="2"/>
-      <c r="M160" s="2" t="s">
-        <v>1205</v>
+      <c r="M160" s="57" t="s">
+        <v>1193</v>
       </c>
       <c r="N160" s="5" t="s">
-        <v>1214</v>
+        <v>1202</v>
       </c>
       <c r="O160" s="2"/>
       <c r="P160" s="2"/>
       <c r="Q160" s="2" t="s">
-        <v>1206</v>
+        <v>1194</v>
       </c>
       <c r="R160" s="2" t="s">
         <v>558</v>
@@ -15169,31 +15239,31 @@
       <c r="G161" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="H161" s="2" t="s">
+      <c r="H161" s="32" t="s">
         <v>695</v>
       </c>
       <c r="I161" s="2" t="s">
         <v>316</v>
       </c>
       <c r="J161" s="2" t="s">
-        <v>1207</v>
+        <v>1195</v>
       </c>
       <c r="K161" s="2"/>
       <c r="L161" s="2" t="s">
-        <v>1208</v>
-      </c>
-      <c r="M161" s="2" t="s">
-        <v>1209</v>
+        <v>1196</v>
+      </c>
+      <c r="M161" s="57" t="s">
+        <v>1197</v>
       </c>
       <c r="N161" s="5" t="s">
-        <v>1215</v>
+        <v>1203</v>
       </c>
       <c r="O161" s="2" t="s">
-        <v>1210</v>
+        <v>1198</v>
       </c>
       <c r="P161" s="2"/>
       <c r="Q161" s="2" t="s">
-        <v>1211</v>
+        <v>1199</v>
       </c>
       <c r="R161" s="2" t="s">
         <v>558</v>
@@ -15202,10 +15272,10 @@
         <v>32</v>
       </c>
       <c r="T161" s="18" t="s">
-        <v>1212</v>
+        <v>1200</v>
       </c>
       <c r="U161" s="18" t="s">
-        <v>1120</v>
+        <v>1108</v>
       </c>
       <c r="V161" s="2"/>
       <c r="W161" s="2" t="s">
@@ -15242,7 +15312,7 @@
       </c>
       <c r="K162" s="2"/>
       <c r="L162" s="2"/>
-      <c r="M162" s="3" t="s">
+      <c r="M162" s="56" t="s">
         <v>475</v>
       </c>
       <c r="N162" s="2" t="s">
@@ -15296,7 +15366,7 @@
       </c>
       <c r="K163" s="2"/>
       <c r="L163" s="2"/>
-      <c r="M163" s="3" t="s">
+      <c r="M163" s="56" t="s">
         <v>479</v>
       </c>
       <c r="N163" s="2" t="s">
@@ -15339,27 +15409,27 @@
       <c r="G164" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="H164" s="2" t="s">
+      <c r="H164" s="32" t="s">
         <v>219</v>
       </c>
       <c r="I164" s="2" t="s">
-        <v>1189</v>
+        <v>1177</v>
       </c>
       <c r="J164" s="2" t="s">
-        <v>1190</v>
+        <v>1178</v>
       </c>
       <c r="K164" s="2"/>
       <c r="L164" s="2"/>
-      <c r="M164" s="2" t="s">
-        <v>1191</v>
+      <c r="M164" s="57" t="s">
+        <v>1179</v>
       </c>
       <c r="N164" s="5" t="s">
-        <v>1200</v>
+        <v>1188</v>
       </c>
       <c r="O164" s="2"/>
       <c r="P164" s="2"/>
       <c r="Q164" s="2" t="s">
-        <v>1192</v>
+        <v>1180</v>
       </c>
       <c r="R164" s="2" t="s">
         <v>558</v>
@@ -15368,14 +15438,14 @@
         <v>481</v>
       </c>
       <c r="T164" s="18" t="s">
-        <v>1193</v>
+        <v>1181</v>
       </c>
       <c r="U164" s="18" t="s">
-        <v>1194</v>
+        <v>1182</v>
       </c>
       <c r="V164" s="2"/>
       <c r="W164" s="2" t="s">
-        <v>1195</v>
+        <v>1183</v>
       </c>
       <c r="X164" s="2">
         <v>3</v>
@@ -15397,8 +15467,8 @@
       <c r="G165" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="H165" s="2" t="s">
-        <v>1196</v>
+      <c r="H165" s="32" t="s">
+        <v>1184</v>
       </c>
       <c r="I165" s="2" t="s">
         <v>463</v>
@@ -15408,16 +15478,16 @@
       </c>
       <c r="K165" s="2"/>
       <c r="L165" s="2"/>
-      <c r="M165" s="2" t="s">
-        <v>1197</v>
+      <c r="M165" s="57" t="s">
+        <v>1185</v>
       </c>
       <c r="N165" s="5" t="s">
-        <v>1201</v>
+        <v>1189</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" s="2"/>
       <c r="Q165" s="2" t="s">
-        <v>1197</v>
+        <v>1185</v>
       </c>
       <c r="R165" s="2" t="s">
         <v>558</v>
@@ -15426,14 +15496,14 @@
         <v>32</v>
       </c>
       <c r="T165" s="18" t="s">
-        <v>1198</v>
+        <v>1186</v>
       </c>
       <c r="U165" s="18" t="s">
-        <v>1199</v>
+        <v>1187</v>
       </c>
       <c r="V165" s="2"/>
       <c r="W165" s="2" t="s">
-        <v>1195</v>
+        <v>1183</v>
       </c>
       <c r="X165" s="2">
         <v>3</v>
@@ -15466,7 +15536,7 @@
       </c>
       <c r="K166" s="2"/>
       <c r="L166" s="2"/>
-      <c r="M166" s="3" t="s">
+      <c r="M166" s="56" t="s">
         <v>489</v>
       </c>
       <c r="N166" s="2" t="s">
@@ -15522,7 +15592,7 @@
       </c>
       <c r="K167" s="2"/>
       <c r="L167" s="2"/>
-      <c r="M167" s="3" t="s">
+      <c r="M167" s="56" t="s">
         <v>495</v>
       </c>
       <c r="N167" s="2" t="s">
@@ -15567,7 +15637,7 @@
       <c r="G168" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="H168" s="2" t="s">
+      <c r="H168" s="32" t="s">
         <v>219</v>
       </c>
       <c r="I168" s="2" t="s">
@@ -15578,16 +15648,16 @@
       </c>
       <c r="K168" s="2"/>
       <c r="L168" s="2"/>
-      <c r="M168" s="2" t="s">
-        <v>1182</v>
+      <c r="M168" s="57" t="s">
+        <v>1170</v>
       </c>
       <c r="N168" s="5" t="s">
-        <v>1185</v>
+        <v>1173</v>
       </c>
       <c r="O168" s="2"/>
       <c r="P168" s="2"/>
       <c r="Q168" s="2" t="s">
-        <v>1183</v>
+        <v>1171</v>
       </c>
       <c r="R168" s="2" t="s">
         <v>558</v>
@@ -15603,7 +15673,7 @@
       </c>
       <c r="V168" s="2"/>
       <c r="W168" s="2" t="s">
-        <v>1162</v>
+        <v>1150</v>
       </c>
       <c r="X168" s="2">
         <v>3</v>
@@ -15625,7 +15695,7 @@
       <c r="G169" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="H169" s="2" t="s">
+      <c r="H169" s="32" t="s">
         <v>386</v>
       </c>
       <c r="I169" s="2" t="s">
@@ -15636,16 +15706,16 @@
       </c>
       <c r="K169" s="2"/>
       <c r="L169" s="2"/>
-      <c r="M169" s="2" t="s">
-        <v>1187</v>
+      <c r="M169" s="57" t="s">
+        <v>1175</v>
       </c>
       <c r="N169" s="5" t="s">
-        <v>1186</v>
+        <v>1174</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" s="2"/>
       <c r="Q169" s="2" t="s">
-        <v>1184</v>
+        <v>1172</v>
       </c>
       <c r="R169" s="2" t="s">
         <v>558</v>
@@ -15654,14 +15724,14 @@
         <v>32</v>
       </c>
       <c r="T169" s="18" t="s">
-        <v>1188</v>
+        <v>1176</v>
       </c>
       <c r="U169" s="18" t="s">
         <v>615</v>
       </c>
       <c r="V169" s="2"/>
       <c r="W169" s="2" t="s">
-        <v>1162</v>
+        <v>1150</v>
       </c>
       <c r="X169" s="2">
         <v>3</v>
@@ -15694,7 +15764,7 @@
       </c>
       <c r="K170" s="2"/>
       <c r="L170" s="2"/>
-      <c r="M170" s="3" t="s">
+      <c r="M170" s="56" t="s">
         <v>503</v>
       </c>
       <c r="N170" s="2" t="s">
@@ -15739,23 +15809,23 @@
       <c r="G171" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="H171" t="s">
-        <v>1171</v>
+      <c r="H171" s="11" t="s">
+        <v>1159</v>
       </c>
       <c r="I171" t="s">
-        <v>1172</v>
+        <v>1160</v>
       </c>
       <c r="J171" t="s">
-        <v>1173</v>
-      </c>
-      <c r="M171" t="s">
-        <v>1174</v>
+        <v>1161</v>
+      </c>
+      <c r="M171" s="64" t="s">
+        <v>1162</v>
       </c>
       <c r="N171" s="5" t="s">
-        <v>1176</v>
+        <v>1164</v>
       </c>
       <c r="Q171" t="s">
-        <v>1175</v>
+        <v>1163</v>
       </c>
       <c r="R171" t="s">
         <v>558</v>
@@ -15764,13 +15834,13 @@
         <v>32</v>
       </c>
       <c r="T171" s="21" t="s">
-        <v>1165</v>
+        <v>1153</v>
       </c>
       <c r="U171" s="21" t="s">
         <v>357</v>
       </c>
       <c r="W171" t="s">
-        <v>1162</v>
+        <v>1150</v>
       </c>
       <c r="X171" s="2">
         <v>3</v>
@@ -15792,8 +15862,8 @@
       <c r="G172" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="H172" s="2" t="s">
-        <v>1163</v>
+      <c r="H172" s="32" t="s">
+        <v>1151</v>
       </c>
       <c r="I172" s="2" t="s">
         <v>93</v>
@@ -15803,16 +15873,16 @@
       </c>
       <c r="K172" s="2"/>
       <c r="L172" s="2"/>
-      <c r="M172" s="2" t="s">
-        <v>1164</v>
+      <c r="M172" s="57" t="s">
+        <v>1152</v>
       </c>
       <c r="N172" s="5" t="s">
-        <v>1170</v>
+        <v>1158</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" s="2"/>
       <c r="Q172" s="2" t="s">
-        <v>1164</v>
+        <v>1152</v>
       </c>
       <c r="R172" s="2" t="s">
         <v>558</v>
@@ -15821,14 +15891,14 @@
         <v>32</v>
       </c>
       <c r="T172" s="18" t="s">
-        <v>1165</v>
+        <v>1153</v>
       </c>
       <c r="U172" s="18" t="s">
-        <v>1166</v>
+        <v>1154</v>
       </c>
       <c r="V172" s="2"/>
       <c r="W172" s="2" t="s">
-        <v>1162</v>
+        <v>1150</v>
       </c>
       <c r="X172" s="2">
         <v>3</v>
@@ -15850,8 +15920,8 @@
       <c r="G173" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="H173" s="2" t="s">
-        <v>1167</v>
+      <c r="H173" s="32" t="s">
+        <v>1155</v>
       </c>
       <c r="I173" s="2" t="s">
         <v>93</v>
@@ -15861,16 +15931,16 @@
       </c>
       <c r="K173" s="2"/>
       <c r="L173" s="2"/>
-      <c r="M173" s="2" t="s">
-        <v>1168</v>
+      <c r="M173" s="57" t="s">
+        <v>1156</v>
       </c>
       <c r="N173" s="5" t="s">
-        <v>1169</v>
+        <v>1157</v>
       </c>
       <c r="O173" s="2"/>
       <c r="P173" s="2"/>
       <c r="Q173" s="2" t="s">
-        <v>1168</v>
+        <v>1156</v>
       </c>
       <c r="R173" s="2" t="s">
         <v>558</v>
@@ -15886,7 +15956,7 @@
       </c>
       <c r="V173" s="2"/>
       <c r="W173" s="2" t="s">
-        <v>1162</v>
+        <v>1150</v>
       </c>
       <c r="X173" s="2">
         <v>3</v>
@@ -15919,7 +15989,7 @@
       </c>
       <c r="K174" s="2"/>
       <c r="L174" s="2"/>
-      <c r="M174" s="3" t="s">
+      <c r="M174" s="56" t="s">
         <v>146</v>
       </c>
       <c r="N174" s="2" t="s">
@@ -15975,7 +16045,7 @@
       </c>
       <c r="K175" s="2"/>
       <c r="L175" s="2"/>
-      <c r="M175" s="3" t="s">
+      <c r="M175" s="56" t="s">
         <v>512</v>
       </c>
       <c r="N175" s="2" t="s">
@@ -16020,7 +16090,7 @@
       <c r="G176" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="H176" s="30" t="s">
+      <c r="H176" s="31" t="s">
         <v>589</v>
       </c>
       <c r="I176" s="30" t="s">
@@ -16031,18 +16101,18 @@
       </c>
       <c r="K176" s="31"/>
       <c r="L176" s="31"/>
-      <c r="M176" s="31" t="s">
-        <v>1150</v>
+      <c r="M176" s="68" t="s">
+        <v>1138</v>
       </c>
       <c r="N176" s="5" t="s">
-        <v>1155</v>
+        <v>1143</v>
       </c>
       <c r="O176" s="31" t="s">
-        <v>1151</v>
+        <v>1139</v>
       </c>
       <c r="P176" s="31"/>
       <c r="Q176" s="31" t="s">
-        <v>1152</v>
+        <v>1140</v>
       </c>
       <c r="R176" s="31" t="s">
         <v>558</v>
@@ -16051,14 +16121,14 @@
         <v>32</v>
       </c>
       <c r="T176" s="30" t="s">
-        <v>1153</v>
+        <v>1141</v>
       </c>
       <c r="U176" s="30" t="s">
         <v>276</v>
       </c>
       <c r="V176" s="30"/>
       <c r="W176" s="30" t="s">
-        <v>1154</v>
+        <v>1142</v>
       </c>
       <c r="X176" s="2">
         <v>3</v>
@@ -16080,8 +16150,8 @@
       <c r="G177" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="H177" s="28" t="s">
-        <v>1156</v>
+      <c r="H177" s="29" t="s">
+        <v>1144</v>
       </c>
       <c r="I177" s="28" t="s">
         <v>222</v>
@@ -16091,18 +16161,18 @@
       </c>
       <c r="K177" s="29"/>
       <c r="L177" s="29"/>
-      <c r="M177" s="29" t="s">
-        <v>1157</v>
+      <c r="M177" s="69" t="s">
+        <v>1145</v>
       </c>
       <c r="N177" s="5" t="s">
-        <v>1161</v>
+        <v>1149</v>
       </c>
       <c r="O177" s="29" t="s">
-        <v>1151</v>
+        <v>1139</v>
       </c>
       <c r="P177" s="29"/>
       <c r="Q177" s="29" t="s">
-        <v>1158</v>
+        <v>1146</v>
       </c>
       <c r="R177" s="29" t="s">
         <v>558</v>
@@ -16111,14 +16181,14 @@
         <v>32</v>
       </c>
       <c r="T177" s="28" t="s">
-        <v>1159</v>
+        <v>1147</v>
       </c>
       <c r="U177" s="28" t="s">
-        <v>1160</v>
+        <v>1148</v>
       </c>
       <c r="V177" s="28"/>
       <c r="W177" s="28" t="s">
-        <v>1154</v>
+        <v>1142</v>
       </c>
       <c r="X177" s="2">
         <v>3</v>
@@ -16151,7 +16221,7 @@
       </c>
       <c r="K178" s="2"/>
       <c r="L178" s="2"/>
-      <c r="M178" s="3" t="s">
+      <c r="M178" s="56" t="s">
         <v>520</v>
       </c>
       <c r="N178" s="2" t="s">
@@ -16207,7 +16277,7 @@
       </c>
       <c r="K179" s="2"/>
       <c r="L179" s="2"/>
-      <c r="M179" s="3" t="s">
+      <c r="M179" s="56" t="s">
         <v>146</v>
       </c>
       <c r="N179" s="2" t="s">
@@ -16252,7 +16322,7 @@
       <c r="G180" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="H180" s="2" t="s">
+      <c r="H180" s="32" t="s">
         <v>904</v>
       </c>
       <c r="I180" s="2" t="s">
@@ -16263,16 +16333,16 @@
       </c>
       <c r="K180" s="2"/>
       <c r="L180" s="2"/>
-      <c r="M180" s="2" t="s">
-        <v>1139</v>
+      <c r="M180" s="57" t="s">
+        <v>1127</v>
       </c>
       <c r="N180" s="5" t="s">
-        <v>1148</v>
+        <v>1136</v>
       </c>
       <c r="O180" s="2"/>
       <c r="P180" s="2"/>
       <c r="Q180" s="2" t="s">
-        <v>1140</v>
+        <v>1128</v>
       </c>
       <c r="R180" s="2" t="s">
         <v>558</v>
@@ -16281,14 +16351,14 @@
         <v>32</v>
       </c>
       <c r="T180" s="18" t="s">
-        <v>1141</v>
+        <v>1129</v>
       </c>
       <c r="U180" s="18" t="s">
-        <v>1142</v>
+        <v>1130</v>
       </c>
       <c r="V180" s="2"/>
       <c r="W180" s="2" t="s">
-        <v>1143</v>
+        <v>1131</v>
       </c>
       <c r="X180" s="2">
         <v>3</v>
@@ -16310,7 +16380,7 @@
       <c r="G181" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="H181" s="2" t="s">
+      <c r="H181" s="32" t="s">
         <v>26</v>
       </c>
       <c r="I181" s="2" t="s">
@@ -16321,16 +16391,16 @@
       </c>
       <c r="K181" s="2"/>
       <c r="L181" s="2"/>
-      <c r="M181" s="2" t="s">
-        <v>1144</v>
+      <c r="M181" s="57" t="s">
+        <v>1132</v>
       </c>
       <c r="N181" s="5" t="s">
-        <v>1149</v>
+        <v>1137</v>
       </c>
       <c r="O181" s="2"/>
       <c r="P181" s="2"/>
       <c r="Q181" s="2" t="s">
-        <v>1145</v>
+        <v>1133</v>
       </c>
       <c r="R181" s="2" t="s">
         <v>558</v>
@@ -16339,14 +16409,14 @@
         <v>32</v>
       </c>
       <c r="T181" s="18" t="s">
-        <v>1146</v>
+        <v>1134</v>
       </c>
       <c r="U181" s="18" t="s">
-        <v>1147</v>
+        <v>1135</v>
       </c>
       <c r="V181" s="2"/>
       <c r="W181" s="2" t="s">
-        <v>1143</v>
+        <v>1131</v>
       </c>
       <c r="X181" s="2">
         <v>3</v>
@@ -16377,7 +16447,7 @@
       </c>
       <c r="K182" s="9"/>
       <c r="L182" s="9"/>
-      <c r="M182" s="10" t="s">
+      <c r="M182" s="60" t="s">
         <v>532</v>
       </c>
       <c r="N182" s="5" t="s">
@@ -16420,7 +16490,7 @@
       <c r="G183" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="H183" s="2" t="s">
+      <c r="H183" s="32" t="s">
         <v>409</v>
       </c>
       <c r="I183" s="2" t="s">
@@ -16433,16 +16503,16 @@
       <c r="L183" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="M183" s="2" t="s">
-        <v>1132</v>
+      <c r="M183" s="57" t="s">
+        <v>1120</v>
       </c>
       <c r="N183" s="5" t="s">
-        <v>1133</v>
+        <v>1121</v>
       </c>
       <c r="O183" s="2"/>
       <c r="P183" s="2"/>
       <c r="Q183" s="2" t="s">
-        <v>1132</v>
+        <v>1120</v>
       </c>
       <c r="R183" s="2" t="s">
         <v>558</v>
@@ -16451,7 +16521,7 @@
         <v>32</v>
       </c>
       <c r="T183" s="18" t="s">
-        <v>1131</v>
+        <v>1119</v>
       </c>
       <c r="U183" s="18" t="s">
         <v>720</v>
@@ -16480,8 +16550,8 @@
       <c r="G184" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="H184" s="2" t="s">
-        <v>1130</v>
+      <c r="H184" s="32" t="s">
+        <v>1118</v>
       </c>
       <c r="I184" s="2" t="s">
         <v>93</v>
@@ -16493,16 +16563,16 @@
       <c r="L184" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="M184" s="2" t="s">
-        <v>1129</v>
+      <c r="M184" s="57" t="s">
+        <v>1117</v>
       </c>
       <c r="N184" s="5" t="s">
-        <v>1134</v>
+        <v>1122</v>
       </c>
       <c r="O184" s="2"/>
       <c r="P184" s="2"/>
       <c r="Q184" s="2" t="s">
-        <v>1129</v>
+        <v>1117</v>
       </c>
       <c r="R184" s="2" t="s">
         <v>558</v>
@@ -16511,10 +16581,10 @@
         <v>32</v>
       </c>
       <c r="T184" s="18" t="s">
-        <v>1128</v>
+        <v>1116</v>
       </c>
       <c r="U184" s="18" t="s">
-        <v>1127</v>
+        <v>1115</v>
       </c>
       <c r="V184" s="2"/>
       <c r="W184" s="2" t="s">
@@ -16526,10 +16596,10 @@
     </row>
     <row r="185" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>1135</v>
+        <v>1123</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>1136</v>
+        <v>1124</v>
       </c>
       <c r="C185" s="3"/>
       <c r="D185" s="2"/>
@@ -16540,33 +16610,33 @@
       <c r="G185" s="32">
         <v>1777</v>
       </c>
-      <c r="H185" s="21" t="s">
-        <v>1137</v>
+      <c r="H185" s="11" t="s">
+        <v>1125</v>
       </c>
       <c r="I185" s="27" t="s">
-        <v>1178</v>
+        <v>1166</v>
       </c>
       <c r="J185" s="27" t="s">
-        <v>1179</v>
+        <v>1167</v>
       </c>
       <c r="L185" t="s">
-        <v>1138</v>
-      </c>
-      <c r="M185" s="27" t="s">
-        <v>1180</v>
+        <v>1126</v>
+      </c>
+      <c r="M185" s="70" t="s">
+        <v>1168</v>
       </c>
       <c r="N185" s="5" t="s">
-        <v>1177</v>
+        <v>1165</v>
       </c>
       <c r="Q185"/>
       <c r="R185"/>
       <c r="S185" t="s">
         <v>32</v>
       </c>
-      <c r="T185" s="46" t="s">
-        <v>1181</v>
-      </c>
-      <c r="U185" s="46" t="s">
+      <c r="T185" s="40" t="s">
+        <v>1169</v>
+      </c>
+      <c r="U185" s="40" t="s">
         <v>320</v>
       </c>
       <c r="W185" t="s">
@@ -16600,7 +16670,7 @@
       </c>
       <c r="K186" s="2"/>
       <c r="L186" s="2"/>
-      <c r="M186" s="3" t="s">
+      <c r="M186" s="56" t="s">
         <v>538</v>
       </c>
       <c r="N186" s="5" t="s">
@@ -16643,7 +16713,7 @@
       <c r="G187" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="H187" s="2" t="s">
+      <c r="H187" s="32" t="s">
         <v>48</v>
       </c>
       <c r="I187" s="2" t="s">
@@ -16656,16 +16726,16 @@
       <c r="L187" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="M187" s="2" t="s">
-        <v>1114</v>
+      <c r="M187" s="57" t="s">
+        <v>1102</v>
       </c>
       <c r="N187" s="5" t="s">
-        <v>1124</v>
+        <v>1112</v>
       </c>
       <c r="O187" s="2"/>
       <c r="P187" s="2"/>
       <c r="Q187" s="2" t="s">
-        <v>1115</v>
+        <v>1103</v>
       </c>
       <c r="R187" s="2" t="s">
         <v>558</v>
@@ -16677,7 +16747,7 @@
         <v>795</v>
       </c>
       <c r="U187" s="18" t="s">
-        <v>1116</v>
+        <v>1104</v>
       </c>
       <c r="V187" s="2"/>
       <c r="W187" s="2" t="s">
@@ -16703,7 +16773,7 @@
       <c r="G188" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="H188" s="2" t="s">
+      <c r="H188" s="32" t="s">
         <v>100</v>
       </c>
       <c r="I188" s="2" t="s">
@@ -16714,16 +16784,16 @@
       </c>
       <c r="K188" s="2"/>
       <c r="L188" s="2"/>
-      <c r="M188" s="2" t="s">
-        <v>1117</v>
+      <c r="M188" s="57" t="s">
+        <v>1105</v>
       </c>
       <c r="N188" s="5" t="s">
-        <v>1125</v>
+        <v>1113</v>
       </c>
       <c r="O188" s="2"/>
       <c r="P188" s="2"/>
       <c r="Q188" s="2" t="s">
-        <v>1118</v>
+        <v>1106</v>
       </c>
       <c r="R188" s="2" t="s">
         <v>558</v>
@@ -16732,10 +16802,10 @@
         <v>32</v>
       </c>
       <c r="T188" s="18" t="s">
-        <v>1119</v>
+        <v>1107</v>
       </c>
       <c r="U188" s="18" t="s">
-        <v>1120</v>
+        <v>1108</v>
       </c>
       <c r="V188" s="2"/>
       <c r="W188" s="2" t="s">
@@ -16761,27 +16831,27 @@
       <c r="G189" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="H189" s="2" t="s">
+      <c r="H189" s="32" t="s">
         <v>256</v>
       </c>
       <c r="I189" s="2" t="s">
         <v>716</v>
       </c>
       <c r="J189" s="2" t="s">
-        <v>1121</v>
+        <v>1109</v>
       </c>
       <c r="K189" s="2"/>
       <c r="L189" s="2"/>
-      <c r="M189" s="2" t="s">
-        <v>1122</v>
+      <c r="M189" s="57" t="s">
+        <v>1110</v>
       </c>
       <c r="N189" s="5" t="s">
-        <v>1126</v>
+        <v>1114</v>
       </c>
       <c r="O189" s="2"/>
       <c r="P189" s="2"/>
       <c r="Q189" s="2" t="s">
-        <v>1122</v>
+        <v>1110</v>
       </c>
       <c r="R189" s="2" t="s">
         <v>558</v>
@@ -16793,7 +16863,7 @@
         <v>210</v>
       </c>
       <c r="U189" s="18" t="s">
-        <v>1123</v>
+        <v>1111</v>
       </c>
       <c r="V189" s="2"/>
       <c r="W189" s="2" t="s">
@@ -16830,7 +16900,7 @@
       </c>
       <c r="K190" s="2"/>
       <c r="L190" s="2"/>
-      <c r="M190" s="3" t="s">
+      <c r="M190" s="56" t="s">
         <v>544</v>
       </c>
       <c r="N190" s="2" t="s">
@@ -16881,7 +16951,7 @@
       </c>
       <c r="K191" s="2"/>
       <c r="L191" s="2"/>
-      <c r="M191" s="3" t="s">
+      <c r="M191" s="56" t="s">
         <v>549</v>
       </c>
       <c r="N191" s="2" t="s">
@@ -16924,7 +16994,7 @@
       <c r="G192" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="H192" s="2" t="s">
+      <c r="H192" s="32" t="s">
         <v>92</v>
       </c>
       <c r="I192" s="2" t="s">
@@ -16935,7 +17005,7 @@
       </c>
       <c r="K192" s="2"/>
       <c r="L192" s="2"/>
-      <c r="M192" s="2" t="s">
+      <c r="M192" s="57" t="s">
         <v>555</v>
       </c>
       <c r="N192" s="4" t="s">
@@ -16982,7 +17052,7 @@
       <c r="G193" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="H193" s="2" t="s">
+      <c r="H193" s="32" t="s">
         <v>46</v>
       </c>
       <c r="I193" s="2" t="s">
@@ -16993,7 +17063,7 @@
       </c>
       <c r="K193" s="2"/>
       <c r="L193" s="2"/>
-      <c r="M193" s="2" t="s">
+      <c r="M193" s="57" t="s">
         <v>564</v>
       </c>
       <c r="N193" s="4" t="s">
@@ -17046,7 +17116,7 @@
       </c>
       <c r="K194" s="2"/>
       <c r="L194" s="2"/>
-      <c r="M194" s="3" t="s">
+      <c r="M194" s="56" t="s">
         <v>571</v>
       </c>
       <c r="N194" s="2" t="s">
@@ -17102,7 +17172,7 @@
       </c>
       <c r="K195" s="2"/>
       <c r="L195" s="2"/>
-      <c r="M195" s="3" t="s">
+      <c r="M195" s="56" t="s">
         <v>576</v>
       </c>
       <c r="N195" s="2" t="s">
@@ -17147,7 +17217,7 @@
       <c r="G196" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="H196" s="2" t="s">
+      <c r="H196" s="32" t="s">
         <v>581</v>
       </c>
       <c r="I196" s="2" t="s">
@@ -17158,7 +17228,7 @@
       </c>
       <c r="K196" s="2"/>
       <c r="L196" s="2"/>
-      <c r="M196" s="2" t="s">
+      <c r="M196" s="57" t="s">
         <v>583</v>
       </c>
       <c r="N196" s="4" t="s">
@@ -17205,7 +17275,7 @@
       <c r="G197" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="H197" s="2" t="s">
+      <c r="H197" s="32" t="s">
         <v>589</v>
       </c>
       <c r="I197" s="2" t="s">
@@ -17216,7 +17286,7 @@
       </c>
       <c r="K197" s="2"/>
       <c r="L197" s="2"/>
-      <c r="M197" s="2" t="s">
+      <c r="M197" s="57" t="s">
         <v>592</v>
       </c>
       <c r="N197" s="4" t="s">
@@ -17263,7 +17333,7 @@
       <c r="G198" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="H198" t="s">
+      <c r="H198" s="11" t="s">
         <v>597</v>
       </c>
       <c r="I198" t="s">
@@ -17272,7 +17342,7 @@
       <c r="J198" t="s">
         <v>232</v>
       </c>
-      <c r="M198" t="s">
+      <c r="M198" s="64" t="s">
         <v>599</v>
       </c>
       <c r="N198" s="5" t="s">
@@ -17327,7 +17397,7 @@
       </c>
       <c r="K199" s="2"/>
       <c r="L199" s="2"/>
-      <c r="M199" s="3" t="s">
+      <c r="M199" s="56" t="s">
         <v>608</v>
       </c>
       <c r="N199" s="2" t="s">
@@ -17370,7 +17440,7 @@
       <c r="G200" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="H200" s="2" t="s">
+      <c r="H200" s="32" t="s">
         <v>610</v>
       </c>
       <c r="I200" s="2" t="s">
@@ -17381,7 +17451,7 @@
       </c>
       <c r="K200" s="2"/>
       <c r="L200" s="2"/>
-      <c r="M200" s="2" t="s">
+      <c r="M200" s="57" t="s">
         <v>611</v>
       </c>
       <c r="N200" s="4" t="s">
@@ -17428,7 +17498,7 @@
       <c r="G201" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="H201" t="s">
+      <c r="H201" s="11" t="s">
         <v>404</v>
       </c>
       <c r="I201" t="s">
@@ -17437,7 +17507,7 @@
       <c r="J201" t="s">
         <v>339</v>
       </c>
-      <c r="M201" t="s">
+      <c r="M201" s="64" t="s">
         <v>616</v>
       </c>
       <c r="N201" s="5" t="s">
@@ -17481,7 +17551,7 @@
       <c r="G202" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="H202" s="2" t="s">
+      <c r="H202" s="32" t="s">
         <v>610</v>
       </c>
       <c r="I202" s="2" t="s">
@@ -17492,7 +17562,7 @@
       </c>
       <c r="K202" s="2"/>
       <c r="L202" s="2"/>
-      <c r="M202" s="2" t="s">
+      <c r="M202" s="57" t="s">
         <v>622</v>
       </c>
       <c r="N202" s="4" t="s">
@@ -17550,7 +17620,7 @@
       </c>
       <c r="K203" s="2"/>
       <c r="L203" s="2"/>
-      <c r="M203" s="3" t="s">
+      <c r="M203" s="56" t="s">
         <v>630</v>
       </c>
       <c r="N203" s="2" t="s">
@@ -17604,7 +17674,7 @@
       </c>
       <c r="K204" s="2"/>
       <c r="L204" s="2"/>
-      <c r="M204" s="3" t="s">
+      <c r="M204" s="56" t="s">
         <v>636</v>
       </c>
       <c r="N204" s="2" t="s">
@@ -17649,7 +17719,7 @@
       <c r="G205" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="H205" t="s">
+      <c r="H205" s="11" t="s">
         <v>204</v>
       </c>
       <c r="I205" t="s">
@@ -17661,7 +17731,7 @@
       <c r="L205" t="s">
         <v>640</v>
       </c>
-      <c r="M205" t="s">
+      <c r="M205" s="64" t="s">
         <v>641</v>
       </c>
       <c r="N205" s="5" t="s">
@@ -17705,7 +17775,7 @@
       <c r="G206" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="H206" s="2" t="s">
+      <c r="H206" s="32" t="s">
         <v>647</v>
       </c>
       <c r="I206" s="2" t="s">
@@ -17716,7 +17786,7 @@
       </c>
       <c r="K206" s="2"/>
       <c r="L206" s="2"/>
-      <c r="M206" s="2" t="s">
+      <c r="M206" s="57" t="s">
         <v>648</v>
       </c>
       <c r="N206" s="4" t="s">
@@ -17770,7 +17840,7 @@
       </c>
       <c r="K207" s="2"/>
       <c r="L207" s="2"/>
-      <c r="M207" s="3" t="s">
+      <c r="M207" s="56" t="s">
         <v>658</v>
       </c>
       <c r="N207" s="2" t="s">
@@ -17826,7 +17896,7 @@
       </c>
       <c r="K208" s="2"/>
       <c r="L208" s="2"/>
-      <c r="M208" s="3" t="s">
+      <c r="M208" s="56" t="s">
         <v>664</v>
       </c>
       <c r="N208" s="2" t="s">
@@ -17871,7 +17941,7 @@
       <c r="G209" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="H209" s="2" t="s">
+      <c r="H209" s="32" t="s">
         <v>669</v>
       </c>
       <c r="I209" s="2" t="s">
@@ -17882,7 +17952,7 @@
       </c>
       <c r="K209" s="2"/>
       <c r="L209" s="2"/>
-      <c r="M209" s="2" t="s">
+      <c r="M209" s="57" t="s">
         <v>670</v>
       </c>
       <c r="N209" s="4" t="s">
@@ -17929,7 +17999,7 @@
       <c r="G210" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="H210" s="2" t="s">
+      <c r="H210" s="32" t="s">
         <v>293</v>
       </c>
       <c r="I210" s="2" t="s">
@@ -17940,7 +18010,7 @@
       </c>
       <c r="K210" s="2"/>
       <c r="L210" s="2"/>
-      <c r="M210" s="2" t="s">
+      <c r="M210" s="57" t="s">
         <v>676</v>
       </c>
       <c r="N210" s="4" t="s">
@@ -17998,7 +18068,7 @@
       </c>
       <c r="K211" s="2"/>
       <c r="L211" s="2"/>
-      <c r="M211" s="3" t="s">
+      <c r="M211" s="56" t="s">
         <v>685</v>
       </c>
       <c r="N211" s="2" t="s">
@@ -18054,7 +18124,7 @@
       </c>
       <c r="K212" s="2"/>
       <c r="L212" s="2"/>
-      <c r="M212" s="3" t="s">
+      <c r="M212" s="56" t="s">
         <v>691</v>
       </c>
       <c r="N212" s="2" t="s">
@@ -18097,7 +18167,7 @@
       <c r="G213" s="2" t="s">
         <v>682</v>
       </c>
-      <c r="H213" s="2" t="s">
+      <c r="H213" s="32" t="s">
         <v>695</v>
       </c>
       <c r="I213" s="2" t="s">
@@ -18108,7 +18178,7 @@
       </c>
       <c r="K213" s="2"/>
       <c r="L213" s="2"/>
-      <c r="M213" s="2" t="s">
+      <c r="M213" s="57" t="s">
         <v>696</v>
       </c>
       <c r="N213" s="4" t="s">
@@ -18155,7 +18225,7 @@
       <c r="G214" s="2" t="s">
         <v>682</v>
       </c>
-      <c r="H214" s="2" t="s">
+      <c r="H214" s="32" t="s">
         <v>702</v>
       </c>
       <c r="I214" s="2" t="s">
@@ -18166,7 +18236,7 @@
       </c>
       <c r="K214" s="2"/>
       <c r="L214" s="2"/>
-      <c r="M214" s="2" t="s">
+      <c r="M214" s="57" t="s">
         <v>703</v>
       </c>
       <c r="N214" s="4" t="s">
@@ -18221,7 +18291,7 @@
       </c>
       <c r="K215" s="2"/>
       <c r="L215" s="2"/>
-      <c r="M215" s="3" t="s">
+      <c r="M215" s="56" t="s">
         <v>712</v>
       </c>
       <c r="N215" s="2" t="s">
@@ -18264,7 +18334,7 @@
       <c r="G216" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="H216" s="2" t="s">
+      <c r="H216" s="32" t="s">
         <v>605</v>
       </c>
       <c r="I216" s="2" t="s">
@@ -18275,7 +18345,7 @@
       </c>
       <c r="K216" s="2"/>
       <c r="L216" s="2"/>
-      <c r="M216" s="2" t="s">
+      <c r="M216" s="57" t="s">
         <v>718</v>
       </c>
       <c r="N216" s="4" t="s">
@@ -18322,7 +18392,7 @@
       <c r="G217" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="H217" s="2" t="s">
+      <c r="H217" s="32" t="s">
         <v>722</v>
       </c>
       <c r="I217" s="2" t="s">
@@ -18335,7 +18405,7 @@
       <c r="L217" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="M217" s="2" t="s">
+      <c r="M217" s="57" t="s">
         <v>723</v>
       </c>
       <c r="N217" s="4" t="s">
@@ -18382,7 +18452,7 @@
       <c r="G218" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="H218" s="2" t="s">
+      <c r="H218" s="32" t="s">
         <v>161</v>
       </c>
       <c r="I218" s="2" t="s">
@@ -18395,7 +18465,7 @@
       <c r="L218" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="M218" s="2" t="s">
+      <c r="M218" s="57" t="s">
         <v>728</v>
       </c>
       <c r="N218" s="4" t="s">
@@ -18453,7 +18523,7 @@
       </c>
       <c r="K219" s="2"/>
       <c r="L219" s="2"/>
-      <c r="M219" s="2" t="s">
+      <c r="M219" s="57" t="s">
         <v>736</v>
       </c>
       <c r="N219" s="4" t="s">
@@ -18496,7 +18566,7 @@
       <c r="G220" s="2" t="s">
         <v>734</v>
       </c>
-      <c r="H220" s="2" t="s">
+      <c r="H220" s="32" t="s">
         <v>735</v>
       </c>
       <c r="I220" s="2" t="s">
@@ -18509,7 +18579,7 @@
       <c r="L220" s="2" t="s">
         <v>738</v>
       </c>
-      <c r="M220" s="2" t="s">
+      <c r="M220" s="57" t="s">
         <v>739</v>
       </c>
       <c r="N220" s="4" t="s">
@@ -18556,7 +18626,7 @@
       <c r="G221" s="2" t="s">
         <v>734</v>
       </c>
-      <c r="H221" t="s">
+      <c r="H221" s="11" t="s">
         <v>743</v>
       </c>
       <c r="I221" t="s">
@@ -18565,7 +18635,7 @@
       <c r="J221" t="s">
         <v>745</v>
       </c>
-      <c r="M221" t="s">
+      <c r="M221" s="64" t="s">
         <v>746</v>
       </c>
       <c r="N221" s="5" t="s">
@@ -18609,7 +18679,7 @@
       <c r="G222" s="2" t="s">
         <v>734</v>
       </c>
-      <c r="H222" s="2" t="s">
+      <c r="H222" s="32" t="s">
         <v>751</v>
       </c>
       <c r="I222" s="2" t="s">
@@ -18622,7 +18692,7 @@
       <c r="L222" s="2" t="s">
         <v>753</v>
       </c>
-      <c r="M222" s="2" t="s">
+      <c r="M222" s="57" t="s">
         <v>754</v>
       </c>
       <c r="N222" s="4" t="s">
@@ -18669,7 +18739,7 @@
       <c r="G223" s="2" t="s">
         <v>734</v>
       </c>
-      <c r="H223" s="2" t="s">
+      <c r="H223" s="32" t="s">
         <v>759</v>
       </c>
       <c r="I223" s="2" t="s">
@@ -18682,7 +18752,7 @@
       <c r="L223" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="M223" s="2" t="s">
+      <c r="M223" s="57" t="s">
         <v>760</v>
       </c>
       <c r="N223" s="4" t="s">
@@ -18729,7 +18799,7 @@
       <c r="G224" s="2" t="s">
         <v>734</v>
       </c>
-      <c r="H224" s="2" t="s">
+      <c r="H224" s="32" t="s">
         <v>25</v>
       </c>
       <c r="I224" s="2" t="s">
@@ -18742,7 +18812,7 @@
       <c r="L224" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="M224" s="2" t="s">
+      <c r="M224" s="57" t="s">
         <v>763</v>
       </c>
       <c r="N224" s="4" t="s">
@@ -18789,7 +18859,7 @@
       <c r="G225" s="2" t="s">
         <v>734</v>
       </c>
-      <c r="H225" s="2" t="s">
+      <c r="H225" s="32" t="s">
         <v>473</v>
       </c>
       <c r="I225" s="2" t="s">
@@ -18802,7 +18872,7 @@
       <c r="L225" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="M225" s="2" t="s">
+      <c r="M225" s="57" t="s">
         <v>765</v>
       </c>
       <c r="N225" s="4" t="s">
@@ -18849,7 +18919,7 @@
       <c r="G226" s="2" t="s">
         <v>734</v>
       </c>
-      <c r="H226" s="2" t="s">
+      <c r="H226" s="32" t="s">
         <v>768</v>
       </c>
       <c r="I226" s="2" t="s">
@@ -18860,7 +18930,7 @@
       </c>
       <c r="K226" s="2"/>
       <c r="L226" s="2"/>
-      <c r="M226" s="2" t="s">
+      <c r="M226" s="57" t="s">
         <v>769</v>
       </c>
       <c r="N226" s="4" t="s">
@@ -18918,7 +18988,7 @@
       </c>
       <c r="K227" s="2"/>
       <c r="L227" s="2"/>
-      <c r="M227" s="3" t="s">
+      <c r="M227" s="56" t="s">
         <v>775</v>
       </c>
       <c r="N227" s="2" t="s">
@@ -18963,7 +19033,7 @@
       <c r="G228" s="2" t="s">
         <v>781</v>
       </c>
-      <c r="H228" s="2" t="s">
+      <c r="H228" s="32" t="s">
         <v>589</v>
       </c>
       <c r="I228" s="2" t="s">
@@ -18974,7 +19044,7 @@
       </c>
       <c r="K228" s="2"/>
       <c r="L228" s="2"/>
-      <c r="M228" s="2" t="s">
+      <c r="M228" s="57" t="s">
         <v>782</v>
       </c>
       <c r="N228" s="4" t="s">
@@ -19021,7 +19091,7 @@
       <c r="G229" s="2" t="s">
         <v>789</v>
       </c>
-      <c r="H229" s="2" t="s">
+      <c r="H229" s="32" t="s">
         <v>790</v>
       </c>
       <c r="I229" s="2" t="s">
@@ -19032,7 +19102,7 @@
       </c>
       <c r="K229" s="2"/>
       <c r="L229" s="2"/>
-      <c r="M229" s="2" t="s">
+      <c r="M229" s="57" t="s">
         <v>791</v>
       </c>
       <c r="N229" s="4" t="s">
@@ -19079,7 +19149,7 @@
       <c r="G230" s="2" t="s">
         <v>797</v>
       </c>
-      <c r="H230" t="s">
+      <c r="H230" s="11" t="s">
         <v>171</v>
       </c>
       <c r="I230" t="s">
@@ -19088,7 +19158,7 @@
       <c r="J230" t="s">
         <v>81</v>
       </c>
-      <c r="M230" t="s">
+      <c r="M230" s="64" t="s">
         <v>798</v>
       </c>
       <c r="N230" s="5" t="s">
@@ -19143,7 +19213,7 @@
       </c>
       <c r="K231" s="2"/>
       <c r="L231" s="2"/>
-      <c r="M231" s="3" t="s">
+      <c r="M231" s="56" t="s">
         <v>807</v>
       </c>
       <c r="N231" s="2" t="s">
@@ -19199,7 +19269,7 @@
       </c>
       <c r="K232" s="2"/>
       <c r="L232" s="2"/>
-      <c r="M232" s="3" t="s">
+      <c r="M232" s="56" t="s">
         <v>146</v>
       </c>
       <c r="N232" s="2" t="s">
@@ -19244,7 +19314,7 @@
       <c r="G233" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="H233" s="2" t="s">
+      <c r="H233" s="32" t="s">
         <v>273</v>
       </c>
       <c r="I233" s="2" t="s">
@@ -19255,7 +19325,7 @@
       </c>
       <c r="K233" s="2"/>
       <c r="L233" s="2"/>
-      <c r="M233" s="2" t="s">
+      <c r="M233" s="57" t="s">
         <v>815</v>
       </c>
       <c r="N233" s="4" t="s">
@@ -19302,7 +19372,7 @@
       <c r="G234" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="H234" s="2" t="s">
+      <c r="H234" s="32" t="s">
         <v>790</v>
       </c>
       <c r="I234" s="2" t="s">
@@ -19313,7 +19383,7 @@
       </c>
       <c r="K234" s="2"/>
       <c r="L234" s="2"/>
-      <c r="M234" s="2" t="s">
+      <c r="M234" s="57" t="s">
         <v>821</v>
       </c>
       <c r="N234" s="4" t="s">
@@ -19371,7 +19441,7 @@
       </c>
       <c r="K235" s="2"/>
       <c r="L235" s="2"/>
-      <c r="M235" s="3" t="s">
+      <c r="M235" s="56" t="s">
         <v>829</v>
       </c>
       <c r="N235" s="2" t="s">
@@ -19416,7 +19486,7 @@
       <c r="G236" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="H236" s="2" t="s">
+      <c r="H236" s="32" t="s">
         <v>834</v>
       </c>
       <c r="I236" s="2" t="s">
@@ -19427,7 +19497,7 @@
       </c>
       <c r="K236" s="2"/>
       <c r="L236" s="2"/>
-      <c r="M236" s="2" t="s">
+      <c r="M236" s="57" t="s">
         <v>835</v>
       </c>
       <c r="N236" s="4" t="s">
@@ -19474,7 +19544,7 @@
       <c r="G237" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="H237" s="2" t="s">
+      <c r="H237" s="32" t="s">
         <v>735</v>
       </c>
       <c r="I237" s="2" t="s">
@@ -19485,7 +19555,7 @@
       </c>
       <c r="K237" s="2"/>
       <c r="L237" s="2"/>
-      <c r="M237" s="2" t="s">
+      <c r="M237" s="57" t="s">
         <v>842</v>
       </c>
       <c r="N237" s="4" t="s">
@@ -19532,7 +19602,7 @@
       <c r="G238" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="H238" s="2" t="s">
+      <c r="H238" s="32" t="s">
         <v>847</v>
       </c>
       <c r="I238" s="2" t="s">
@@ -19543,7 +19613,7 @@
       </c>
       <c r="K238" s="2"/>
       <c r="L238" s="2"/>
-      <c r="M238" s="2" t="s">
+      <c r="M238" s="57" t="s">
         <v>848</v>
       </c>
       <c r="N238" s="4" t="s">
@@ -19601,7 +19671,7 @@
       </c>
       <c r="K239" s="2"/>
       <c r="L239" s="2"/>
-      <c r="M239" s="3" t="s">
+      <c r="M239" s="56" t="s">
         <v>856</v>
       </c>
       <c r="N239" s="2" t="s">
@@ -19655,7 +19725,7 @@
       </c>
       <c r="K240" s="2"/>
       <c r="L240" s="2"/>
-      <c r="M240" s="3" t="s">
+      <c r="M240" s="56" t="s">
         <v>862</v>
       </c>
       <c r="N240" s="2" t="s">
@@ -19700,7 +19770,7 @@
       <c r="G241" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="H241" s="2" t="s">
+      <c r="H241" s="32" t="s">
         <v>655</v>
       </c>
       <c r="I241" s="2" t="s">
@@ -19711,7 +19781,7 @@
       </c>
       <c r="K241" s="2"/>
       <c r="L241" s="2"/>
-      <c r="M241" s="2" t="s">
+      <c r="M241" s="57" t="s">
         <v>867</v>
       </c>
       <c r="N241" s="4" t="s">
@@ -19729,10 +19799,10 @@
         <v>32</v>
       </c>
       <c r="T241" s="18" t="s">
-        <v>1682</v>
+        <v>1653</v>
       </c>
       <c r="U241" s="18" t="s">
-        <v>1683</v>
+        <v>1654</v>
       </c>
       <c r="V241" t="s">
         <v>870</v>
@@ -19760,7 +19830,7 @@
       <c r="G242" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="H242" s="2" t="s">
+      <c r="H242" s="32" t="s">
         <v>417</v>
       </c>
       <c r="I242" s="2" t="s">
@@ -19771,7 +19841,7 @@
       </c>
       <c r="K242" s="2"/>
       <c r="L242" s="2"/>
-      <c r="M242" s="2" t="s">
+      <c r="M242" s="57" t="s">
         <v>871</v>
       </c>
       <c r="N242" s="4" t="s">
@@ -19789,10 +19859,10 @@
         <v>32</v>
       </c>
       <c r="T242" s="18" t="s">
-        <v>1684</v>
+        <v>1655</v>
       </c>
       <c r="U242" s="18" t="s">
-        <v>1687</v>
+        <v>1658</v>
       </c>
       <c r="V242" t="s">
         <v>870</v>
@@ -19831,7 +19901,7 @@
       </c>
       <c r="K243" s="2"/>
       <c r="L243" s="2"/>
-      <c r="M243" s="3" t="s">
+      <c r="M243" s="56" t="s">
         <v>880</v>
       </c>
       <c r="N243" s="2" t="s">
@@ -19876,7 +19946,7 @@
       <c r="G244" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="H244" s="24" t="s">
+      <c r="H244" s="25" t="s">
         <v>885</v>
       </c>
       <c r="I244" s="25" t="s">
@@ -19889,7 +19959,7 @@
       <c r="L244" s="25" t="s">
         <v>886</v>
       </c>
-      <c r="M244" s="25" t="s">
+      <c r="M244" s="71" t="s">
         <v>887</v>
       </c>
       <c r="N244" s="26" t="s">
@@ -19907,10 +19977,10 @@
         <v>32</v>
       </c>
       <c r="T244" s="24" t="s">
-        <v>1686</v>
+        <v>1657</v>
       </c>
       <c r="U244" s="24" t="s">
-        <v>1685</v>
+        <v>1656</v>
       </c>
       <c r="V244" s="2"/>
       <c r="W244" s="2" t="s">
@@ -19936,7 +20006,7 @@
       <c r="G245" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="H245" s="24" t="s">
+      <c r="H245" s="25" t="s">
         <v>890</v>
       </c>
       <c r="I245" s="25" t="s">
@@ -19949,7 +20019,7 @@
       <c r="L245" s="25" t="s">
         <v>891</v>
       </c>
-      <c r="M245" s="25" t="s">
+      <c r="M245" s="71" t="s">
         <v>892</v>
       </c>
       <c r="N245" s="26" t="s">
@@ -19969,10 +20039,10 @@
         <v>32</v>
       </c>
       <c r="T245" s="24" t="s">
-        <v>1690</v>
+        <v>1661</v>
       </c>
       <c r="U245" s="24" t="s">
-        <v>1689</v>
+        <v>1660</v>
       </c>
       <c r="V245" s="2"/>
       <c r="W245" s="2" t="s">
@@ -19998,7 +20068,7 @@
       <c r="G246" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="H246" s="24" t="s">
+      <c r="H246" s="25" t="s">
         <v>543</v>
       </c>
       <c r="I246" s="25" t="s">
@@ -20011,7 +20081,7 @@
       <c r="L246" s="25" t="s">
         <v>897</v>
       </c>
-      <c r="M246" s="25" t="s">
+      <c r="M246" s="71" t="s">
         <v>898</v>
       </c>
       <c r="N246" s="26" t="s">
@@ -20029,10 +20099,10 @@
         <v>32</v>
       </c>
       <c r="T246" s="24" t="s">
-        <v>1688</v>
+        <v>1659</v>
       </c>
       <c r="U246" s="24" t="s">
-        <v>1691</v>
+        <v>1662</v>
       </c>
       <c r="V246" s="2"/>
       <c r="W246" s="2" t="s">
@@ -20069,7 +20139,7 @@
       </c>
       <c r="K247" s="2"/>
       <c r="L247" s="2"/>
-      <c r="M247" s="3" t="s">
+      <c r="M247" s="56" t="s">
         <v>906</v>
       </c>
       <c r="N247" s="2" t="s">
@@ -20123,7 +20193,7 @@
       </c>
       <c r="K248" s="2"/>
       <c r="L248" s="2"/>
-      <c r="M248" s="3" t="s">
+      <c r="M248" s="56" t="s">
         <v>910</v>
       </c>
       <c r="N248" s="2" t="s">
@@ -20166,7 +20236,7 @@
       <c r="G249" s="2" t="s">
         <v>904</v>
       </c>
-      <c r="H249" s="2" t="s">
+      <c r="H249" s="32" t="s">
         <v>323</v>
       </c>
       <c r="I249" s="2" t="s">
@@ -20177,7 +20247,7 @@
       </c>
       <c r="K249" s="2"/>
       <c r="L249" s="2"/>
-      <c r="M249" s="2" t="s">
+      <c r="M249" s="57" t="s">
         <v>915</v>
       </c>
       <c r="N249" s="4" t="s">
@@ -20195,10 +20265,10 @@
         <v>32</v>
       </c>
       <c r="T249" s="18" t="s">
-        <v>1692</v>
+        <v>1663</v>
       </c>
       <c r="U249" s="18" t="s">
-        <v>1693</v>
+        <v>1664</v>
       </c>
       <c r="V249" s="2"/>
       <c r="W249" s="2" t="s">
@@ -20224,7 +20294,7 @@
       <c r="G250" s="2" t="s">
         <v>904</v>
       </c>
-      <c r="H250" s="2" t="s">
+      <c r="H250" s="32" t="s">
         <v>219</v>
       </c>
       <c r="I250" s="2" t="s">
@@ -20235,7 +20305,7 @@
       </c>
       <c r="K250" s="2"/>
       <c r="L250" s="2"/>
-      <c r="M250" s="2" t="s">
+      <c r="M250" s="57" t="s">
         <v>917</v>
       </c>
       <c r="N250" s="4" t="s">
@@ -20253,7 +20323,7 @@
         <v>32</v>
       </c>
       <c r="T250" s="18" t="s">
-        <v>1694</v>
+        <v>1665</v>
       </c>
       <c r="U250" s="18" t="s">
         <v>720</v>
@@ -20293,7 +20363,7 @@
       </c>
       <c r="K251" s="2"/>
       <c r="L251" s="2"/>
-      <c r="M251" s="3" t="s">
+      <c r="M251" s="56" t="s">
         <v>923</v>
       </c>
       <c r="N251" s="2" t="s">
@@ -20347,7 +20417,7 @@
       </c>
       <c r="K252" s="2"/>
       <c r="L252" s="2"/>
-      <c r="M252" s="3" t="s">
+      <c r="M252" s="56" t="s">
         <v>926</v>
       </c>
       <c r="N252" s="2" t="s">
@@ -20401,7 +20471,7 @@
       </c>
       <c r="K253" s="2"/>
       <c r="L253" s="2"/>
-      <c r="M253" s="3" t="s">
+      <c r="M253" s="56" t="s">
         <v>930</v>
       </c>
       <c r="N253" s="2" t="s">
@@ -20444,7 +20514,7 @@
       <c r="G254" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="H254" t="s">
+      <c r="H254" s="11" t="s">
         <v>256</v>
       </c>
       <c r="I254" t="s">
@@ -20453,7 +20523,7 @@
       <c r="J254" t="s">
         <v>232</v>
       </c>
-      <c r="M254" t="s">
+      <c r="M254" s="64" t="s">
         <v>934</v>
       </c>
       <c r="N254" s="5" t="s">
@@ -20466,10 +20536,10 @@
         <v>32</v>
       </c>
       <c r="T254" s="21" t="s">
-        <v>1696</v>
+        <v>1667</v>
       </c>
       <c r="U254" s="21" t="s">
-        <v>1697</v>
+        <v>1668</v>
       </c>
       <c r="V254" t="s">
         <v>870</v>
@@ -20508,7 +20578,7 @@
       </c>
       <c r="K255" s="2"/>
       <c r="L255" s="2"/>
-      <c r="M255" s="3" t="s">
+      <c r="M255" s="56" t="s">
         <v>940</v>
       </c>
       <c r="N255" s="2" t="s">
@@ -20559,7 +20629,7 @@
       </c>
       <c r="K256" s="2"/>
       <c r="L256" s="2"/>
-      <c r="M256" s="3" t="s">
+      <c r="M256" s="56" t="s">
         <v>944</v>
       </c>
       <c r="N256" s="2" t="s">
@@ -20613,7 +20683,7 @@
       </c>
       <c r="K257" s="2"/>
       <c r="L257" s="2"/>
-      <c r="M257" s="3" t="s">
+      <c r="M257" s="56" t="s">
         <v>947</v>
       </c>
       <c r="N257" s="2" t="s">
@@ -20656,7 +20726,7 @@
       <c r="G258" s="2" t="s">
         <v>938</v>
       </c>
-      <c r="H258" s="2" t="s">
+      <c r="H258" s="32" t="s">
         <v>25</v>
       </c>
       <c r="J258" s="2" t="s">
@@ -20664,7 +20734,7 @@
       </c>
       <c r="K258" s="2"/>
       <c r="L258" s="2"/>
-      <c r="M258" s="2" t="s">
+      <c r="M258" s="57" t="s">
         <v>950</v>
       </c>
       <c r="N258" s="4" t="s">
@@ -20678,10 +20748,10 @@
         <v>32</v>
       </c>
       <c r="T258" s="18" t="s">
-        <v>1555</v>
+        <v>1532</v>
       </c>
       <c r="U258" s="18" t="s">
-        <v>1695</v>
+        <v>1666</v>
       </c>
       <c r="V258" s="2"/>
       <c r="W258" s="2" t="s">
@@ -20707,7 +20777,7 @@
       <c r="G259" s="2" t="s">
         <v>938</v>
       </c>
-      <c r="H259" s="2" t="s">
+      <c r="H259" s="32" t="s">
         <v>473</v>
       </c>
       <c r="I259" s="2" t="s">
@@ -20718,7 +20788,7 @@
       </c>
       <c r="K259" s="2"/>
       <c r="L259" s="2"/>
-      <c r="M259" s="2" t="s">
+      <c r="M259" s="57" t="s">
         <v>952</v>
       </c>
       <c r="N259" s="4" t="s">
@@ -20732,10 +20802,10 @@
         <v>32</v>
       </c>
       <c r="T259" s="18" t="s">
-        <v>1698</v>
+        <v>1669</v>
       </c>
       <c r="U259" s="18" t="s">
-        <v>1699</v>
+        <v>1670</v>
       </c>
       <c r="V259" s="2"/>
       <c r="W259" s="2" t="s">
@@ -20761,7 +20831,7 @@
       <c r="G260" s="2" t="s">
         <v>938</v>
       </c>
-      <c r="H260" s="2" t="s">
+      <c r="H260" s="32" t="s">
         <v>47</v>
       </c>
       <c r="I260" s="2" t="s">
@@ -20772,7 +20842,7 @@
       </c>
       <c r="K260" s="2"/>
       <c r="L260" s="2"/>
-      <c r="M260" s="2" t="s">
+      <c r="M260" s="57" t="s">
         <v>954</v>
       </c>
       <c r="N260" s="4" t="s">
@@ -20786,10 +20856,10 @@
         <v>32</v>
       </c>
       <c r="T260" s="18" t="s">
-        <v>1700</v>
+        <v>1671</v>
       </c>
       <c r="U260" s="18" t="s">
-        <v>1701</v>
+        <v>1672</v>
       </c>
       <c r="V260" s="2"/>
       <c r="W260" s="2" t="s">
@@ -20815,7 +20885,7 @@
       <c r="G261" s="2" t="s">
         <v>938</v>
       </c>
-      <c r="H261" s="2" t="s">
+      <c r="H261" s="32" t="s">
         <v>251</v>
       </c>
       <c r="I261" s="2" t="s">
@@ -20826,7 +20896,7 @@
       </c>
       <c r="K261" s="2"/>
       <c r="L261" s="2"/>
-      <c r="M261" s="2" t="s">
+      <c r="M261" s="57" t="s">
         <v>956</v>
       </c>
       <c r="N261" s="4" t="s">
@@ -20840,10 +20910,10 @@
         <v>949</v>
       </c>
       <c r="T261" s="18" t="s">
-        <v>1702</v>
+        <v>1673</v>
       </c>
       <c r="U261" s="18" t="s">
-        <v>1198</v>
+        <v>1186</v>
       </c>
       <c r="V261" s="2"/>
       <c r="W261" s="2" t="s">
@@ -20869,7 +20939,7 @@
       <c r="G262" s="2" t="s">
         <v>938</v>
       </c>
-      <c r="H262" s="2" t="s">
+      <c r="H262" s="32" t="s">
         <v>682</v>
       </c>
       <c r="J262" s="2" t="s">
@@ -20877,7 +20947,7 @@
       </c>
       <c r="K262" s="2"/>
       <c r="L262" s="2"/>
-      <c r="M262" s="2" t="s">
+      <c r="M262" s="57" t="s">
         <v>959</v>
       </c>
       <c r="N262" s="4" t="s">
@@ -20894,7 +20964,7 @@
         <v>104</v>
       </c>
       <c r="U262" s="18" t="s">
-        <v>1703</v>
+        <v>1674</v>
       </c>
       <c r="V262" s="2"/>
       <c r="W262" s="2" t="s">
@@ -20931,7 +21001,7 @@
       </c>
       <c r="K263" s="2"/>
       <c r="L263" s="2"/>
-      <c r="M263" s="3" t="s">
+      <c r="M263" s="56" t="s">
         <v>965</v>
       </c>
       <c r="N263" s="2" t="s">
@@ -20985,7 +21055,7 @@
       </c>
       <c r="K264" s="2"/>
       <c r="L264" s="2"/>
-      <c r="M264" s="3" t="s">
+      <c r="M264" s="56" t="s">
         <v>968</v>
       </c>
       <c r="N264" s="2" t="s">
@@ -21039,7 +21109,7 @@
       </c>
       <c r="K265" s="2"/>
       <c r="L265" s="2"/>
-      <c r="M265" s="3" t="s">
+      <c r="M265" s="56" t="s">
         <v>973</v>
       </c>
       <c r="N265" s="2" t="s">
@@ -21093,7 +21163,7 @@
       </c>
       <c r="K266" s="2"/>
       <c r="L266" s="2"/>
-      <c r="M266" s="3" t="s">
+      <c r="M266" s="56" t="s">
         <v>978</v>
       </c>
       <c r="N266" s="2" t="s">
@@ -21147,7 +21217,7 @@
       </c>
       <c r="K267" s="2"/>
       <c r="L267" s="2"/>
-      <c r="M267" s="3" t="s">
+      <c r="M267" s="56" t="s">
         <v>982</v>
       </c>
       <c r="N267" s="2" t="s">
@@ -21190,7 +21260,7 @@
       <c r="G268" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H268" s="2" t="s">
+      <c r="H268" s="32" t="s">
         <v>385</v>
       </c>
       <c r="I268" s="2" t="s">
@@ -21201,7 +21271,7 @@
       </c>
       <c r="K268" s="2"/>
       <c r="L268" s="2"/>
-      <c r="M268" s="2" t="s">
+      <c r="M268" s="57" t="s">
         <v>986</v>
       </c>
       <c r="N268" s="4" t="s">
@@ -21244,7 +21314,7 @@
       <c r="G269" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H269" s="2" t="s">
+      <c r="H269" s="32" t="s">
         <v>990</v>
       </c>
       <c r="I269" s="2" t="s">
@@ -21255,7 +21325,7 @@
       </c>
       <c r="K269" s="2"/>
       <c r="L269" s="2"/>
-      <c r="M269" s="2" t="s">
+      <c r="M269" s="57" t="s">
         <v>992</v>
       </c>
       <c r="N269" s="4" t="s">
@@ -21298,7 +21368,7 @@
       <c r="G270" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H270" s="2" t="s">
+      <c r="H270" s="32" t="s">
         <v>964</v>
       </c>
       <c r="I270" s="2" t="s">
@@ -21309,7 +21379,7 @@
       </c>
       <c r="K270" s="2"/>
       <c r="L270" s="2"/>
-      <c r="M270" s="2" t="s">
+      <c r="M270" s="57" t="s">
         <v>996</v>
       </c>
       <c r="N270" s="4" t="s">
@@ -21352,7 +21422,7 @@
       <c r="G271" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H271" s="2" t="s">
+      <c r="H271" s="32" t="s">
         <v>510</v>
       </c>
       <c r="I271" s="2" t="s">
@@ -21363,7 +21433,7 @@
       </c>
       <c r="K271" s="2"/>
       <c r="L271" s="2"/>
-      <c r="M271" s="2" t="s">
+      <c r="M271" s="57" t="s">
         <v>998</v>
       </c>
       <c r="N271" s="4" t="s">
@@ -21406,7 +21476,7 @@
       <c r="G272" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H272" s="2" t="s">
+      <c r="H272" s="32" t="s">
         <v>605</v>
       </c>
       <c r="I272" s="2" t="s">
@@ -21417,7 +21487,7 @@
       </c>
       <c r="K272" s="2"/>
       <c r="L272" s="2"/>
-      <c r="M272" s="2" t="s">
+      <c r="M272" s="57" t="s">
         <v>1002</v>
       </c>
       <c r="N272" s="4" t="s">
@@ -21460,7 +21530,7 @@
       <c r="G273" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H273" s="2" t="s">
+      <c r="H273" s="32" t="s">
         <v>964</v>
       </c>
       <c r="I273" s="2" t="s">
@@ -21471,7 +21541,7 @@
       </c>
       <c r="K273" s="2"/>
       <c r="L273" s="2"/>
-      <c r="M273" s="2" t="s">
+      <c r="M273" s="57" t="s">
         <v>1005</v>
       </c>
       <c r="N273" s="4" t="s">
@@ -21514,7 +21584,7 @@
       <c r="G274" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H274" s="2" t="s">
+      <c r="H274" s="32" t="s">
         <v>510</v>
       </c>
       <c r="I274" s="2" t="s">
@@ -21525,7 +21595,7 @@
       </c>
       <c r="K274" s="2"/>
       <c r="L274" s="2"/>
-      <c r="M274" s="2" t="s">
+      <c r="M274" s="57" t="s">
         <v>1009</v>
       </c>
       <c r="N274" s="4" t="s">
@@ -21579,7 +21649,7 @@
       </c>
       <c r="K275" s="2"/>
       <c r="L275" s="2"/>
-      <c r="M275" s="3" t="s">
+      <c r="M275" s="56" t="s">
         <v>1017</v>
       </c>
       <c r="N275" s="2" t="s">
@@ -21635,7 +21705,7 @@
       </c>
       <c r="K276" s="2"/>
       <c r="L276" s="2"/>
-      <c r="M276" s="3" t="s">
+      <c r="M276" s="56" t="s">
         <v>1023</v>
       </c>
       <c r="N276" s="2" t="s">
@@ -21680,41 +21750,45 @@
       <c r="G277" s="2" t="s">
         <v>1014</v>
       </c>
-      <c r="H277" t="s">
-        <v>300</v>
+      <c r="H277" s="2" t="s">
+        <v>123</v>
       </c>
       <c r="I277" s="2" t="s">
-        <v>1028</v>
+        <v>860</v>
       </c>
       <c r="J277" s="2" t="s">
-        <v>1029</v>
+        <v>1686</v>
       </c>
       <c r="K277" s="2"/>
-      <c r="L277" s="2"/>
-      <c r="M277" s="2" t="s">
-        <v>1030</v>
-      </c>
-      <c r="N277" s="4" t="s">
-        <v>1031</v>
+      <c r="L277" s="2" t="s">
+        <v>1687</v>
+      </c>
+      <c r="M277" s="57" t="s">
+        <v>1688</v>
+      </c>
+      <c r="N277" s="5" t="s">
+        <v>1692</v>
       </c>
       <c r="O277" s="2"/>
       <c r="P277" s="2"/>
       <c r="Q277" s="2" t="s">
-        <v>1032</v>
-      </c>
-      <c r="R277" s="2"/>
+        <v>1689</v>
+      </c>
+      <c r="R277" s="2" t="s">
+        <v>558</v>
+      </c>
       <c r="S277" s="2" t="s">
         <v>32</v>
       </c>
       <c r="T277" s="18" t="s">
-        <v>1033</v>
+        <v>1694</v>
       </c>
       <c r="U277" s="18" t="s">
-        <v>1034</v>
+        <v>1695</v>
       </c>
       <c r="V277" s="2"/>
       <c r="W277" s="2" t="s">
-        <v>1035</v>
+        <v>189</v>
       </c>
       <c r="X277" s="2">
         <v>3</v>
@@ -21736,41 +21810,45 @@
       <c r="G278" s="2" t="s">
         <v>1014</v>
       </c>
-      <c r="H278" t="s">
-        <v>1036</v>
+      <c r="H278" s="2" t="s">
+        <v>293</v>
       </c>
       <c r="I278" s="2" t="s">
-        <v>574</v>
+        <v>302</v>
       </c>
       <c r="J278" s="2" t="s">
-        <v>582</v>
+        <v>336</v>
       </c>
       <c r="K278" s="2"/>
-      <c r="L278" s="2"/>
-      <c r="M278" s="2" t="s">
-        <v>1037</v>
-      </c>
-      <c r="N278" s="4" t="s">
-        <v>1038</v>
+      <c r="L278" s="2" t="s">
+        <v>1485</v>
+      </c>
+      <c r="M278" s="57" t="s">
+        <v>1690</v>
+      </c>
+      <c r="N278" s="5" t="s">
+        <v>1693</v>
       </c>
       <c r="O278" s="2"/>
       <c r="P278" s="2"/>
       <c r="Q278" s="2" t="s">
-        <v>1039</v>
-      </c>
-      <c r="R278" s="2"/>
+        <v>1691</v>
+      </c>
+      <c r="R278" s="2" t="s">
+        <v>558</v>
+      </c>
       <c r="S278" s="2" t="s">
         <v>32</v>
       </c>
       <c r="T278" s="18" t="s">
-        <v>1040</v>
+        <v>1696</v>
       </c>
       <c r="U278" s="18" t="s">
-        <v>1041</v>
+        <v>1697</v>
       </c>
       <c r="V278" s="2"/>
       <c r="W278" s="2" t="s">
-        <v>1035</v>
+        <v>189</v>
       </c>
       <c r="X278" s="2">
         <v>3</v>
@@ -21778,10 +21856,10 @@
     </row>
     <row r="279" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
-        <v>1042</v>
+        <v>1030</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>1043</v>
+        <v>1031</v>
       </c>
       <c r="C279" s="3"/>
       <c r="D279" s="2"/>
@@ -21803,26 +21881,26 @@
       </c>
       <c r="K279" s="2"/>
       <c r="L279" s="2"/>
-      <c r="M279" s="3" t="s">
-        <v>1044</v>
+      <c r="M279" s="56" t="s">
+        <v>1032</v>
       </c>
       <c r="N279" s="2" t="s">
-        <v>1045</v>
+        <v>1033</v>
       </c>
       <c r="O279" s="2"/>
       <c r="P279" s="2"/>
       <c r="Q279" s="3" t="s">
-        <v>1044</v>
+        <v>1032</v>
       </c>
       <c r="R279" s="3"/>
       <c r="S279" s="3" t="s">
         <v>32</v>
       </c>
       <c r="T279" s="18" t="s">
-        <v>1046</v>
+        <v>1034</v>
       </c>
       <c r="U279" s="22" t="s">
-        <v>1047</v>
+        <v>1035</v>
       </c>
       <c r="V279" s="2"/>
       <c r="W279" s="2" t="s">
@@ -21834,10 +21912,10 @@
     </row>
     <row r="280" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
-        <v>1042</v>
+        <v>1030</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>1043</v>
+        <v>1031</v>
       </c>
       <c r="C280" s="3"/>
       <c r="D280" s="2"/>
@@ -21859,11 +21937,11 @@
       </c>
       <c r="K280" s="2"/>
       <c r="L280" s="2"/>
-      <c r="M280" s="3" t="s">
-        <v>1048</v>
+      <c r="M280" s="56" t="s">
+        <v>1036</v>
       </c>
       <c r="N280" s="2" t="s">
-        <v>1049</v>
+        <v>1037</v>
       </c>
       <c r="O280" s="2"/>
       <c r="P280" s="2"/>
@@ -21873,10 +21951,10 @@
         <v>32</v>
       </c>
       <c r="T280" s="18" t="s">
-        <v>1050</v>
+        <v>1038</v>
       </c>
       <c r="U280" s="18" t="s">
-        <v>1051</v>
+        <v>1039</v>
       </c>
       <c r="V280" s="2"/>
       <c r="W280" s="2" t="s">
@@ -21888,10 +21966,10 @@
     </row>
     <row r="281" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
-        <v>1042</v>
+        <v>1030</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>1043</v>
+        <v>1031</v>
       </c>
       <c r="C281" s="3"/>
       <c r="D281" s="2"/>
@@ -21913,23 +21991,23 @@
       </c>
       <c r="K281" s="2"/>
       <c r="L281" s="2"/>
-      <c r="M281" s="2" t="s">
-        <v>1052</v>
+      <c r="M281" s="57" t="s">
+        <v>1040</v>
       </c>
       <c r="N281" s="4" t="s">
-        <v>1053</v>
+        <v>1041</v>
       </c>
       <c r="O281" s="2"/>
       <c r="P281" s="2"/>
       <c r="Q281" s="2" t="s">
-        <v>1054</v>
+        <v>1042</v>
       </c>
       <c r="R281" s="2"/>
       <c r="S281" s="2" t="s">
         <v>32</v>
       </c>
       <c r="T281" s="18" t="s">
-        <v>1055</v>
+        <v>1043</v>
       </c>
       <c r="U281" s="18" t="s">
         <v>423</v>
@@ -21943,10 +22021,10 @@
     </row>
     <row r="282" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
-        <v>1042</v>
+        <v>1030</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>1043</v>
+        <v>1031</v>
       </c>
       <c r="C282" s="3"/>
       <c r="D282" s="2"/>
@@ -21968,26 +22046,26 @@
       </c>
       <c r="K282" s="2"/>
       <c r="L282" s="2"/>
-      <c r="M282" s="2" t="s">
-        <v>1056</v>
+      <c r="M282" s="57" t="s">
+        <v>1044</v>
       </c>
       <c r="N282" s="4" t="s">
-        <v>1057</v>
+        <v>1045</v>
       </c>
       <c r="O282" s="2"/>
       <c r="P282" s="2"/>
       <c r="Q282" s="2" t="s">
-        <v>1058</v>
+        <v>1046</v>
       </c>
       <c r="R282" s="2"/>
       <c r="S282" s="2" t="s">
         <v>32</v>
       </c>
       <c r="T282" s="18" t="s">
-        <v>1059</v>
+        <v>1047</v>
       </c>
       <c r="U282" s="18" t="s">
-        <v>1060</v>
+        <v>1048</v>
       </c>
       <c r="W282" s="2" t="s">
         <v>76</v>
@@ -22001,16 +22079,16 @@
         <v>278</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>1061</v>
+        <v>1049</v>
       </c>
       <c r="C283" s="3"/>
       <c r="D283" s="2"/>
       <c r="E283" s="2"/>
       <c r="F283" s="2" t="s">
-        <v>1062</v>
+        <v>1050</v>
       </c>
       <c r="G283" s="2" t="s">
-        <v>1063</v>
+        <v>1051</v>
       </c>
       <c r="H283" s="12" t="s">
         <v>123</v>
@@ -22023,26 +22101,26 @@
       </c>
       <c r="K283" s="2"/>
       <c r="L283" s="2"/>
-      <c r="M283" s="3" t="s">
-        <v>1064</v>
+      <c r="M283" s="56" t="s">
+        <v>1052</v>
       </c>
       <c r="N283" s="2" t="s">
-        <v>1065</v>
+        <v>1053</v>
       </c>
       <c r="O283" s="2"/>
       <c r="P283" s="2"/>
       <c r="Q283" s="3" t="s">
-        <v>1066</v>
+        <v>1054</v>
       </c>
       <c r="R283" s="3"/>
       <c r="S283" s="3" t="s">
         <v>32</v>
       </c>
       <c r="T283" s="18" t="s">
-        <v>1067</v>
+        <v>1055</v>
       </c>
       <c r="U283" s="18" t="s">
-        <v>1068</v>
+        <v>1056</v>
       </c>
       <c r="V283" s="2"/>
       <c r="W283" s="2" t="s">
@@ -22057,19 +22135,19 @@
         <v>278</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>1061</v>
+        <v>1049</v>
       </c>
       <c r="C284" s="3"/>
       <c r="D284" s="2"/>
       <c r="E284" s="2"/>
       <c r="F284" s="2" t="s">
-        <v>1062</v>
+        <v>1050</v>
       </c>
       <c r="G284" s="2" t="s">
-        <v>1063</v>
+        <v>1051</v>
       </c>
       <c r="H284" s="13" t="s">
-        <v>1069</v>
+        <v>1057</v>
       </c>
       <c r="I284" s="2" t="s">
         <v>302</v>
@@ -22079,16 +22157,16 @@
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
-      <c r="M284" s="8" t="s">
-        <v>1070</v>
+      <c r="M284" s="72" t="s">
+        <v>1058</v>
       </c>
       <c r="N284" s="7" t="s">
-        <v>1071</v>
+        <v>1059</v>
       </c>
       <c r="O284" s="7"/>
       <c r="P284" s="7"/>
       <c r="Q284" s="8" t="s">
-        <v>1072</v>
+        <v>1060</v>
       </c>
       <c r="R284" s="8"/>
       <c r="S284" s="8" t="s">
@@ -22098,7 +22176,7 @@
         <v>351</v>
       </c>
       <c r="U284" s="23" t="s">
-        <v>1073</v>
+        <v>1061</v>
       </c>
       <c r="V284" s="7"/>
       <c r="W284" s="7" t="s">
@@ -22114,38 +22192,38 @@
         <v>278</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>1061</v>
+        <v>1049</v>
       </c>
       <c r="C285" s="3"/>
       <c r="D285" s="2"/>
       <c r="E285" s="2"/>
       <c r="F285" s="2" t="s">
-        <v>1062</v>
+        <v>1050</v>
       </c>
       <c r="G285" s="2" t="s">
-        <v>1063</v>
+        <v>1051</v>
       </c>
       <c r="H285" s="12" t="s">
         <v>178</v>
       </c>
       <c r="I285" s="2" t="s">
-        <v>1074</v>
+        <v>1062</v>
       </c>
       <c r="J285" s="15" t="s">
-        <v>1075</v>
+        <v>1063</v>
       </c>
       <c r="K285" s="2"/>
       <c r="L285" s="2"/>
-      <c r="M285" s="2" t="s">
-        <v>1076</v>
+      <c r="M285" s="57" t="s">
+        <v>1064</v>
       </c>
       <c r="N285" s="4" t="s">
-        <v>1077</v>
+        <v>1065</v>
       </c>
       <c r="O285" s="2"/>
       <c r="P285" s="2"/>
       <c r="Q285" s="2" t="s">
-        <v>1078</v>
+        <v>1066</v>
       </c>
       <c r="R285" s="2"/>
       <c r="S285" s="2" t="s">
@@ -22155,7 +22233,7 @@
         <v>423</v>
       </c>
       <c r="U285" s="18" t="s">
-        <v>1079</v>
+        <v>1067</v>
       </c>
       <c r="V285" s="2"/>
       <c r="W285" s="2" t="s">
@@ -22171,16 +22249,16 @@
         <v>278</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>1061</v>
+        <v>1049</v>
       </c>
       <c r="C286" s="3"/>
       <c r="D286" s="2"/>
       <c r="E286" s="2"/>
       <c r="F286" s="2" t="s">
-        <v>1062</v>
+        <v>1050</v>
       </c>
       <c r="G286" s="2" t="s">
-        <v>1063</v>
+        <v>1051</v>
       </c>
       <c r="H286" s="12" t="s">
         <v>589</v>
@@ -22193,26 +22271,26 @@
       </c>
       <c r="K286" s="2"/>
       <c r="L286" s="2"/>
-      <c r="M286" s="2" t="s">
-        <v>1080</v>
+      <c r="M286" s="57" t="s">
+        <v>1068</v>
       </c>
       <c r="N286" s="4" t="s">
-        <v>1081</v>
+        <v>1069</v>
       </c>
       <c r="O286" s="2"/>
       <c r="P286" s="2"/>
       <c r="Q286" s="2" t="s">
-        <v>1082</v>
+        <v>1070</v>
       </c>
       <c r="R286" s="2"/>
       <c r="S286" s="2" t="s">
         <v>32</v>
       </c>
       <c r="T286" s="18" t="s">
-        <v>1083</v>
+        <v>1071</v>
       </c>
       <c r="U286" s="18" t="s">
-        <v>1084</v>
+        <v>1072</v>
       </c>
       <c r="V286" s="2"/>
       <c r="W286" s="2" t="s">
@@ -22224,13 +22302,13 @@
     </row>
     <row r="287" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
-        <v>1085</v>
+        <v>1073</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>1086</v>
+        <v>1074</v>
       </c>
       <c r="C287" s="6" t="s">
-        <v>1087</v>
+        <v>1075</v>
       </c>
       <c r="D287" s="2"/>
       <c r="E287" s="2"/>
@@ -22251,23 +22329,23 @@
       </c>
       <c r="K287" s="9"/>
       <c r="L287" s="9"/>
-      <c r="M287" s="10" t="s">
-        <v>1088</v>
+      <c r="M287" s="60" t="s">
+        <v>1076</v>
       </c>
       <c r="N287" s="9" t="s">
-        <v>1089</v>
+        <v>1077</v>
       </c>
       <c r="O287" s="9"/>
       <c r="P287" s="9"/>
       <c r="Q287" s="10" t="s">
-        <v>1090</v>
+        <v>1078</v>
       </c>
       <c r="R287" s="10"/>
       <c r="S287" s="10" t="s">
         <v>32</v>
       </c>
       <c r="T287" s="20" t="s">
-        <v>1091</v>
+        <v>1079</v>
       </c>
       <c r="U287" s="20" t="s">
         <v>430</v>
@@ -22282,13 +22360,13 @@
     </row>
     <row r="288" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
-        <v>1085</v>
+        <v>1073</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>1086</v>
+        <v>1074</v>
       </c>
       <c r="C288" s="6" t="s">
-        <v>1087</v>
+        <v>1075</v>
       </c>
       <c r="D288" s="2"/>
       <c r="E288" s="2"/>
@@ -22299,7 +22377,7 @@
         <v>789</v>
       </c>
       <c r="H288" s="12" t="s">
-        <v>1092</v>
+        <v>1080</v>
       </c>
       <c r="I288" s="2" t="s">
         <v>656</v>
@@ -22309,26 +22387,26 @@
       </c>
       <c r="K288" s="2"/>
       <c r="L288" s="2"/>
-      <c r="M288" s="3" t="s">
-        <v>1093</v>
+      <c r="M288" s="56" t="s">
+        <v>1081</v>
       </c>
       <c r="N288" s="2" t="s">
-        <v>1094</v>
+        <v>1082</v>
       </c>
       <c r="O288" s="2"/>
       <c r="P288" s="2"/>
       <c r="Q288" s="3" t="s">
-        <v>1095</v>
+        <v>1083</v>
       </c>
       <c r="R288" s="3"/>
       <c r="S288" s="3" t="s">
         <v>32</v>
       </c>
       <c r="T288" s="18" t="s">
-        <v>1096</v>
+        <v>1084</v>
       </c>
       <c r="U288" s="18" t="s">
-        <v>1097</v>
+        <v>1085</v>
       </c>
       <c r="V288" s="2"/>
       <c r="W288" s="2" t="s">
@@ -22340,13 +22418,13 @@
     </row>
     <row r="289" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
-        <v>1085</v>
+        <v>1073</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>1086</v>
+        <v>1074</v>
       </c>
       <c r="C289" s="6" t="s">
-        <v>1087</v>
+        <v>1075</v>
       </c>
       <c r="D289" s="2"/>
       <c r="E289" s="2"/>
@@ -22360,25 +22438,25 @@
         <v>834</v>
       </c>
       <c r="I289" s="2" t="s">
-        <v>1098</v>
+        <v>1086</v>
       </c>
       <c r="J289" s="15" t="s">
-        <v>1099</v>
+        <v>1087</v>
       </c>
       <c r="K289" s="2"/>
       <c r="L289" s="2" t="s">
-        <v>1100</v>
-      </c>
-      <c r="M289" s="3" t="s">
-        <v>1101</v>
+        <v>1088</v>
+      </c>
+      <c r="M289" s="56" t="s">
+        <v>1089</v>
       </c>
       <c r="N289" s="4" t="s">
-        <v>1102</v>
+        <v>1090</v>
       </c>
       <c r="O289" s="2"/>
       <c r="P289" s="2"/>
       <c r="Q289" s="2" t="s">
-        <v>1103</v>
+        <v>1091</v>
       </c>
       <c r="R289" s="2"/>
       <c r="S289" s="2" t="s">
@@ -22388,11 +22466,11 @@
         <v>423</v>
       </c>
       <c r="U289" s="18" t="s">
-        <v>1104</v>
+        <v>1092</v>
       </c>
       <c r="V289" s="2"/>
       <c r="W289" s="2" t="s">
-        <v>1105</v>
+        <v>1093</v>
       </c>
       <c r="X289" s="2">
         <v>3</v>
@@ -22400,13 +22478,13 @@
     </row>
     <row r="290" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
-        <v>1085</v>
+        <v>1073</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>1086</v>
+        <v>1074</v>
       </c>
       <c r="C290" s="6" t="s">
-        <v>1087</v>
+        <v>1075</v>
       </c>
       <c r="D290" s="2"/>
       <c r="E290" s="2"/>
@@ -22417,7 +22495,7 @@
         <v>789</v>
       </c>
       <c r="H290" s="12" t="s">
-        <v>1106</v>
+        <v>1094</v>
       </c>
       <c r="I290" s="2" t="s">
         <v>302</v>
@@ -22427,32 +22505,32 @@
       </c>
       <c r="K290" s="2"/>
       <c r="L290" s="2" t="s">
-        <v>1107</v>
-      </c>
-      <c r="M290" s="3" t="s">
-        <v>1108</v>
+        <v>1095</v>
+      </c>
+      <c r="M290" s="56" t="s">
+        <v>1096</v>
       </c>
       <c r="N290" s="4" t="s">
-        <v>1109</v>
+        <v>1097</v>
       </c>
       <c r="O290" s="2"/>
       <c r="P290" s="2"/>
       <c r="Q290" s="2" t="s">
-        <v>1110</v>
+        <v>1098</v>
       </c>
       <c r="R290" s="2"/>
       <c r="S290" s="2" t="s">
         <v>32</v>
       </c>
       <c r="T290" s="18" t="s">
-        <v>1111</v>
+        <v>1099</v>
       </c>
       <c r="U290" s="18" t="s">
-        <v>1112</v>
+        <v>1100</v>
       </c>
       <c r="V290" s="2"/>
       <c r="W290" s="2" t="s">
-        <v>1105</v>
+        <v>1093</v>
       </c>
       <c r="X290" s="2">
         <v>3</v>
@@ -22460,7 +22538,7 @@
     </row>
     <row r="292" spans="1:24" x14ac:dyDescent="0.25">
       <c r="T292" s="21" t="s">
-        <v>1113</v>
+        <v>1101</v>
       </c>
     </row>
   </sheetData>
@@ -22519,140 +22597,140 @@
     <hyperlink ref="N272" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
     <hyperlink ref="N273" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
     <hyperlink ref="N274" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="N277" r:id="rId55" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d1/Benjamin_West_-_The_Death_of_Nelson_-_Google_Art_Project.jpg/1280px-Benjamin_West_-_The_Death_of_Nelson_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="N278" r:id="rId56" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/Benjamin_West%2C_English_%28born_America%29_-_Benjamin_Franklin_Drawing_Electricity_from_the_Sky_-_Google_Art_Project.jpg/960px-Benjamin_West%2C_English_%28born_America%29_-_Benjamin_Franklin_Drawing_Electricity_from_the_Sky_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="N281" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="N282" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="N285" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="N286" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="N289" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="N290" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="N187" r:id="rId63" xr:uid="{D059BB66-E4EC-435C-B1F8-B71071405B22}"/>
-    <hyperlink ref="N188" r:id="rId64" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f1/Jean-Marc_Nattier_-_Portrait_of_Madame_Bonnier_de_la_Mosson_as_Diana_%28Constance-Gabrielle-Magdeleine_du_Monciel_de_Lauraille_-_77.PA.87_-_J._Paul_Getty_Museum.jpg/960px-thumbnail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A4C23C36-51B7-41CB-964C-F47A12F1EA11}"/>
-    <hyperlink ref="N189" r:id="rId65" xr:uid="{27C77560-6BC3-4FC4-BEF7-D1485A62DF83}"/>
-    <hyperlink ref="N183" r:id="rId66" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/11/Le_Triomphe_de_Bacchus_-_Charles-Joseph_Natoire_-_Mus%C3%A9e_du_Louvre_Peintures_INV_6854_%3B_MR_2201.jpg/1280px-Le_Triomphe_de_Bacchus_-_Charles-Joseph_Natoire_-_Mus%C3%A9e_du_Louvre_Peintures_INV_6854_%3B_MR_2201.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FC20F30A-D010-4DB8-BEE3-2D701B5A70D6}"/>
-    <hyperlink ref="N184" r:id="rId67" xr:uid="{8AF388F1-B762-4742-B842-563BC9A0B7CD}"/>
-    <hyperlink ref="N182" r:id="rId68" xr:uid="{4B64CC3E-8979-4E7B-80B4-14F23B40891A}"/>
-    <hyperlink ref="N186" r:id="rId69" xr:uid="{C4619B65-4A95-4563-BB23-DDB03C0A04FB}"/>
-    <hyperlink ref="N180" r:id="rId70" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/57/Portrait_of_King_Charles_III_of_Spain_%28by_Anton_Raphael_Mengs%29.jpg/960px-Portrait_of_King_Charles_III_of_Spain_%28by_Anton_Raphael_Mengs%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{36FA56BD-6990-4BC2-8D30-4FCD2DA8FD33}"/>
-    <hyperlink ref="N181" r:id="rId71" xr:uid="{EF7AFC89-41ED-4B24-8EE8-723D524FE13B}"/>
-    <hyperlink ref="N176" r:id="rId72" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/50/Luis_Melendez%2C_Still_Life_with_Salmon%2CLemon_and_three_Vessels%2C1772_Museo_del_Prado_Madrid.jpg/1280px-Luis_Melendez%2C_Still_Life_with_Salmon%2CLemon_and_three_Vessels%2C1772_Museo_del_Prado_Madrid.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A7A1EE79-7372-4238-B1C8-51A4FA3F139A}"/>
-    <hyperlink ref="N177" r:id="rId73" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/Luis_Mel%C3%A9ndez_-_Still_Life_with_Oranges%2C_Jars%2C_and_Boxes_of_Sweets_-_Google_Art_Project.jpg/1920px-Luis_Mel%C3%A9ndez_-_Still_Life_with_Oranges%2C_Jars%2C_and_Boxes_of_Sweets_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1BF8EB21-E243-46B8-BCFF-C0D4016AE1B6}"/>
-    <hyperlink ref="N173" r:id="rId74" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9c/Alessandro_Magnasco_dit_il_Lissandrino_-_Fun%C3%A9railles_juives%2C_1720_-_Mus%C3%A9e_d%27art_et_d%27histoire_du_Juda%C3%AFsme.jpg/1280px-Alessandro_Magnasco_dit_il_Lissandrino_-_Fun%C3%A9railles_juives%2C_1720_-_Mus%C3%A9e_d%27art_et_d%27histoire_du_Juda%C3%AFsme.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A4B1DE95-2D9C-4974-81E5-87800C88A4B2}"/>
-    <hyperlink ref="N172" r:id="rId75" xr:uid="{BBFEF0F6-BCBA-459A-B98C-4236B1C377F4}"/>
-    <hyperlink ref="N171" r:id="rId76" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0a/Alessandro_Magnasco_-_Garden_Party_in_Albaro_-_Google_Art_Project.jpg/1280px-Alessandro_Magnasco_-_Garden_Party_in_Albaro_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{73587CC3-03C2-44EA-A494-09AEA82982F3}"/>
-    <hyperlink ref="N185" r:id="rId77" xr:uid="{B5ACCC80-4665-4288-9C8D-6C42B2157CB3}"/>
-    <hyperlink ref="N168" r:id="rId78" xr:uid="{7D865810-64E7-4ABF-A896-3B006A8C05B6}"/>
-    <hyperlink ref="N169" r:id="rId79" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d4/Pietro_Longhi_La_cioccolata_del_mattino_The_Morning_Chocolate_1775-1780.jpg/960px-Pietro_Longhi_La_cioccolata_del_mattino_The_Morning_Chocolate_1775-1780.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{863D6A93-4A79-46C2-B4C0-B330BBE3C66A}"/>
-    <hyperlink ref="N164" r:id="rId80" xr:uid="{62279D71-2D38-4C86-8725-ED9DF05704C5}"/>
-    <hyperlink ref="N165" r:id="rId81" xr:uid="{5AED8D7D-EC30-429D-BAF0-95E3EBDD352B}"/>
-    <hyperlink ref="N159" r:id="rId82" xr:uid="{B21374E9-C4D9-44DF-944F-68BC24FB39E5}"/>
-    <hyperlink ref="N160" r:id="rId83" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/01/Dmitry_Levitsky_-_Portrait_of_Catherine_II_the_Legislatress_in_the_Temple_of_the_Goddess_of_Justice_-_Google_Art_Project.jpg/960px-Dmitry_Levitsky_-_Portrait_of_Catherine_II_the_Legislatress_in_the_Temple_of_the_Goddess_of_Justice_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4E860578-3860-4471-B86B-61F42721C0C9}"/>
-    <hyperlink ref="N161" r:id="rId84" xr:uid="{8D23F0D8-B16D-4B16-8733-97F2B557E4F1}"/>
-    <hyperlink ref="N155" r:id="rId85" xr:uid="{D07706FD-E253-40CE-A841-272F41E442AE}"/>
-    <hyperlink ref="N156" r:id="rId86" xr:uid="{2AB510D7-C2AF-48BB-B4B2-2026B9255F47}"/>
-    <hyperlink ref="N157" r:id="rId87" xr:uid="{31710272-A200-4E72-8E50-D4B214238FA4}"/>
-    <hyperlink ref="N151" r:id="rId88" xr:uid="{9E2A9698-BDF1-4496-9276-C7C62590C0D2}"/>
-    <hyperlink ref="N152" r:id="rId89" xr:uid="{AAA01183-C01B-4197-88FB-9209D5B08B97}"/>
-    <hyperlink ref="N153" r:id="rId90" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/L%27%C3%89t%C3%A9_-_Nicolas_Lancret_-_Mus%C3%A9e_du_Louvre_-_INV_5598.jpg/1280px-L%27%C3%89t%C3%A9_-_Nicolas_Lancret_-_Mus%C3%A9e_du_Louvre_-_INV_5598.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0310F23C-EF73-464D-8642-775293BDA214}"/>
-    <hyperlink ref="N148" r:id="rId91" xr:uid="{191298AC-C4DA-4C5A-950B-E871DE4C15EC}"/>
-    <hyperlink ref="N149" r:id="rId92" xr:uid="{BE1FF6CD-977D-4266-A6E8-4AA75513B5DA}"/>
-    <hyperlink ref="N145" r:id="rId93" xr:uid="{6EFC7096-8323-4901-9118-54E5B96B1F3F}"/>
-    <hyperlink ref="N144" r:id="rId94" xr:uid="{204DE62A-DDA4-4872-8B96-BE87C229FBA9}"/>
-    <hyperlink ref="N137" r:id="rId95" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8c/Marriage_A-la-Mode_2%2C_The_T%C3%AAte_%C3%A0_T%C3%AAte_-_William_Hogarth.jpg/1280px-Marriage_A-la-Mode_2%2C_The_T%C3%AAte_%C3%A0_T%C3%AAte_-_William_Hogarth.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E8E1157D-1D08-40F6-A92C-B605A46B43AF}"/>
-    <hyperlink ref="N138" r:id="rId96" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/dd/Marriage_A-la-Mode_3%2C_The_Inspection_-_William_Hogarth.jpg/1280px-Marriage_A-la-Mode_3%2C_The_Inspection_-_William_Hogarth.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5079D862-1C2C-45FC-B9B8-32DEBD957F31}"/>
-    <hyperlink ref="N139" r:id="rId97" xr:uid="{376CC3A3-F52E-4ECF-912E-384633B7E269}"/>
-    <hyperlink ref="N140" r:id="rId98" xr:uid="{0774708F-3FCD-4707-A4D5-5AF0EE0228CC}"/>
-    <hyperlink ref="N132" r:id="rId99" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/37/Francesco_Guardi_-_The_Parlor_of_the_Nuns_at_San_Zaccaria_-_WGA10827.jpg/1280px-Francesco_Guardi_-_The_Parlor_of_the_Nuns_at_San_Zaccaria_-_WGA10827.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{87896DB2-3324-49E8-B26A-4C097EF64349}"/>
-    <hyperlink ref="N133" r:id="rId100" xr:uid="{8F20E6E9-5719-4D43-97E9-CCECEB4D5062}"/>
-    <hyperlink ref="N124" r:id="rId101" xr:uid="{E769C8C6-507B-4E96-8F0B-0D013618BE65}"/>
-    <hyperlink ref="N125" r:id="rId102" xr:uid="{CCE735FD-891C-4D02-9A1D-8DEB4A788353}"/>
-    <hyperlink ref="N126" r:id="rId103" xr:uid="{E01C2C21-9BF0-40A3-A847-BF569250076A}"/>
-    <hyperlink ref="N127" r:id="rId104" xr:uid="{FC86BF97-E910-4CA1-B899-46C6EF9065B3}"/>
-    <hyperlink ref="N128" r:id="rId105" xr:uid="{FCE95188-94B4-448E-A793-E24F507058DC}"/>
-    <hyperlink ref="N129" r:id="rId106" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a6/Jean-Baptiste_Greuze_%28French_-_The_Laundress_%28La_Blanchisseuse%29_-_Google_Art_Project.jpg/960px-Jean-Baptiste_Greuze_%28French_-_The_Laundress_%28La_Blanchisseuse%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0A7CFD44-125D-4942-9E2B-8C779BAE2C5A}"/>
-    <hyperlink ref="C122" r:id="rId107" xr:uid="{514A2AD1-7F9D-469F-BB42-99285A759971}"/>
-    <hyperlink ref="C123:C129" r:id="rId108" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c9/Jean-Baptiste_Greuze_self-portrait_in_pastels.jpg/960px-Jean-Baptiste_Greuze_self-portrait_in_pastels.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F8BC7389-3BE8-46F1-B976-783102E47A34}"/>
-    <hyperlink ref="N119" r:id="rId109" xr:uid="{BD263C40-274A-491B-B580-1037B1A527F7}"/>
-    <hyperlink ref="N120" r:id="rId110" xr:uid="{D40FBB86-915F-40DE-AFC0-438CE2964327}"/>
-    <hyperlink ref="N121" r:id="rId111" xr:uid="{F12C7AD5-852E-4892-82AF-B50A30D20DC6}"/>
-    <hyperlink ref="C118" r:id="rId112" xr:uid="{F9A84F81-ED36-419F-B7DD-0B11A828DC7A}"/>
-    <hyperlink ref="C119:C121" r:id="rId113" display="https://upload.wikimedia.org/wikipedia/commons/3/37/Anton_Graff_-_Zelfportret_van_Anton_Graff_%281736-1813%29_-_Gal.-Nr._2168_-_Staatliche_Kunstsammlungen_Dresden.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{46150356-57C1-4990-ACE8-54AD2634D4E1}"/>
-    <hyperlink ref="N115" r:id="rId114" xr:uid="{C489FD6D-03AE-497C-B45D-3A103D0D7EC1}"/>
-    <hyperlink ref="N116" r:id="rId115" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4f/Atala_au_tombeau%2C1808%2CGirodet_de_Roussy_-Trioson%2C_Louvre..JPG/1280px-Atala_au_tombeau%2C1808%2CGirodet_de_Roussy_-Trioson%2C_Louvre..JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1E1B7A22-985C-4536-81C7-5BC8B5BE2B45}"/>
-    <hyperlink ref="N117" r:id="rId116" xr:uid="{7CD23D3D-E6A8-48D4-959F-03ABD02AA6E1}"/>
-    <hyperlink ref="N112" r:id="rId117" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4f/Thomas_Gainsborough_-_The_Cottage_Door_-_Google_Art_Project.jpg/1280px-Thomas_Gainsborough_-_The_Cottage_Door_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6C742C55-909E-47F0-A689-96CA4FDFF6B2}"/>
-    <hyperlink ref="N113" r:id="rId118" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Thomas_Gainsborough_-_The_Watering_Place_%28before_1777%29.jpg/1280px-Thomas_Gainsborough_-_The_Watering_Place_%28before_1777%29.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{042F65BD-27C1-43BD-831F-42B025DD2318}"/>
-    <hyperlink ref="N109" r:id="rId119" xr:uid="{75099A45-1B1E-4625-8A3B-075B3259D154}"/>
-    <hyperlink ref="N108" r:id="rId120" xr:uid="{C4BF7976-4D50-4E6D-AEA9-A7729EF6CE06}"/>
-    <hyperlink ref="N98" r:id="rId121" xr:uid="{040965B8-3EB0-441F-9C0F-F622C0CFBADE}"/>
-    <hyperlink ref="N99" r:id="rId122" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/26/Jean-Honor%C3%A9_Fragonard_-_Les_Progr%C3%A8s_de_l%27amour_-_Le_rendez-vous_-_Google_Art_Project.jpg/960px-Jean-Honor%C3%A9_Fragonard_-_Les_Progr%C3%A8s_de_l%27amour_-_Le_rendez-vous_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{3CE0E24E-F125-4AFC-A984-09505DDC643B}"/>
-    <hyperlink ref="N100" r:id="rId123" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/39/The_Progress_of_Love_-_The_Lover_Crowned_-_Fragonard_1771-72.jpg/960px-The_Progress_of_Love_-_The_Lover_Crowned_-_Fragonard_1771-72.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6D8A369B-026E-4421-941D-782FC44A65EA}"/>
-    <hyperlink ref="N101" r:id="rId124" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/84/The_Progress_of_Love_-_Love_Letters_-_Fragonard_1771-72.jpg/960px-The_Progress_of_Love_-_Love_Letters_-_Fragonard_1771-72.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6F57409E-7829-4085-A145-CA8B512E9EA1}"/>
-    <hyperlink ref="N102" r:id="rId125" xr:uid="{9AA405D4-B423-4D92-BCDC-D3ECE5E37BB2}"/>
-    <hyperlink ref="N103" r:id="rId126" xr:uid="{F829974F-63C1-4E55-BB95-0256C0415578}"/>
-    <hyperlink ref="N104" r:id="rId127" xr:uid="{2D9130B1-476D-4B4A-AEE4-DEF810B149FC}"/>
-    <hyperlink ref="N105" r:id="rId128" xr:uid="{0C082CB3-8744-4836-B423-7F39A0680CA6}"/>
-    <hyperlink ref="N91" r:id="rId129" xr:uid="{B87F9F91-A36F-4CC6-97B7-CCA3D48695DB}"/>
-    <hyperlink ref="N92" r:id="rId130" xr:uid="{1B8074BA-1335-47C9-A869-429B6477355D}"/>
-    <hyperlink ref="N93" r:id="rId131" xr:uid="{116BA0FF-A724-4FA5-A997-3ED589300CA5}"/>
-    <hyperlink ref="N87" r:id="rId132" xr:uid="{F3C45E8B-537A-41C4-841A-D76103113445}"/>
-    <hyperlink ref="N88" r:id="rId133" xr:uid="{FAE3F4C6-9B29-4FE0-953B-EBEE615155BD}"/>
-    <hyperlink ref="N89" r:id="rId134" xr:uid="{322C2EDD-EFAC-4C96-BDFE-F294C6DA4438}"/>
-    <hyperlink ref="N83" r:id="rId135" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f8/Fran%C3%A7ois-Hubert_DROUAIS_1763-4._London_NG._Madame_de_Pompadour_at_her_Tambour_Frame..jpg/960px-Fran%C3%A7ois-Hubert_DROUAIS_1763-4._London_NG._Madame_de_Pompadour_at_her_Tambour_Frame..jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7BAFF45A-3E97-453B-9193-2E4643B96104}"/>
-    <hyperlink ref="N82" r:id="rId136" xr:uid="{676B976B-A222-4880-86DF-392FAAD178FC}"/>
-    <hyperlink ref="N84" r:id="rId137" xr:uid="{91BBBB20-4312-437C-AC03-56D6A60729FF}"/>
-    <hyperlink ref="N85" r:id="rId138" location="/media/File:Drouais_-_Le_marquis_de_Sourches_et_sa_famille.jpg" xr:uid="{DFD53E45-3B42-44EC-A12A-65C02E3B8446}"/>
-    <hyperlink ref="N79" r:id="rId139" xr:uid="{AB8CE14A-2FE1-4311-B819-3CFEC58E8079}"/>
-    <hyperlink ref="N80" r:id="rId140" xr:uid="{42E82ED5-AF5C-4BF3-B291-8359367702B5}"/>
-    <hyperlink ref="N81" r:id="rId141" xr:uid="{4E9BC4EE-E370-42E2-87EA-F57C3CF1A76E}"/>
-    <hyperlink ref="N76" r:id="rId142" xr:uid="{D9CC9073-7118-4B6C-9D09-4BD332D582DB}"/>
-    <hyperlink ref="N77" r:id="rId143" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1f/Maurice_Quentin_de_La_Tour_-_Self-portrait_with_frill%2C_c1750_-_Mus%C3%A9e_de_Picardie.jpg/960px-Maurice_Quentin_de_La_Tour_-_Self-portrait_with_frill%2C_c1750_-_Mus%C3%A9e_de_Picardie.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A0BAAE3E-98E1-452B-8211-257EEBAFE34F}"/>
-    <hyperlink ref="N66" r:id="rId144" xr:uid="{421D3603-A9E6-4EBF-84DC-7EFD2B974F60}"/>
-    <hyperlink ref="N67" r:id="rId145" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d6/Francisco_de_Goya_-_La_vendimia_o_El_Oto%C3%B1o_%281786%29.jpg/960px-Francisco_de_Goya_-_La_vendimia_o_El_Oto%C3%B1o_%281786%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A495F3AB-E4A0-4BFB-9D2B-D5ACCD7ECE31}"/>
-    <hyperlink ref="N68" r:id="rId146" xr:uid="{6953B915-EEEA-4939-85E0-354BFAE2BE9A}"/>
-    <hyperlink ref="N69" r:id="rId147" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/71/Francisco_de_Goya_-_La_casa_de_locos_-_Google_Art_Project.jpg/1280px-Francisco_de_Goya_-_La_casa_de_locos_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{58D8DAB0-7A95-4977-AF67-A551022C0342}"/>
-    <hyperlink ref="N70" r:id="rId148" xr:uid="{626392C4-75E6-49D1-8C3D-C0F3EDBE0F27}"/>
-    <hyperlink ref="N71" r:id="rId149" xr:uid="{E083E1DC-8C0E-49CD-B584-E9065547E55C}"/>
-    <hyperlink ref="N72" r:id="rId150" xr:uid="{E44FFE73-4938-4AA2-ADB3-5F22564B2B6B}"/>
-    <hyperlink ref="N73" r:id="rId151" xr:uid="{26E98ADB-531B-4BE1-A8F4-1DF326B1B25D}"/>
-    <hyperlink ref="N54" r:id="rId152" xr:uid="{3BAFBF20-4BEA-448F-9982-8B8A53EC07CC}"/>
-    <hyperlink ref="N55" r:id="rId153" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4d/John_Singleton_Copley_-_A_Boy_with_a_Flying_Squirrel_%28Henry_Pelham%29_-_Google_Art_Project.jpg/960px-John_Singleton_Copley_-_A_Boy_with_a_Flying_Squirrel_%28Henry_Pelham%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6806F7F5-72FE-4536-BD33-BFD81FBE9926}"/>
-    <hyperlink ref="N56" r:id="rId154" xr:uid="{6FCA2C83-F067-42B9-BDAF-38BF49CE424B}"/>
-    <hyperlink ref="N45" r:id="rId155" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/56/Le_Buffet_-_Jean_Baptiste_Sim%C3%A9on_Chardin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3198.jpg/960px-Le_Buffet_-_Jean_Baptiste_Sim%C3%A9on_Chardin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3198.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{54B65FB7-24C6-414A-AD88-DB9A26E7B568}"/>
-    <hyperlink ref="N46" r:id="rId156" xr:uid="{8E12A444-0690-4202-989C-3A44525914D6}"/>
-    <hyperlink ref="N47" r:id="rId157" xr:uid="{5C47FF1F-CF54-4DA9-811B-7182737A2DCB}"/>
-    <hyperlink ref="N48" r:id="rId158" xr:uid="{38A6C784-8556-4ECA-8EC5-9B02649F8361}"/>
-    <hyperlink ref="N49" r:id="rId159" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9c/Jeune_dessinateur_taillant_son_crayon_-_Jean_Baptiste_Sim%C3%A9on_Chardin_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1944_4.jpg/960px-Jeune_dessinateur_taillant_son_crayon_-_Jean_Baptiste_Sim%C3%A9on_Chardin_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1944_4.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{205F5316-F9B4-464C-8304-786C1756A1B3}"/>
-    <hyperlink ref="N50" r:id="rId160" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cb/L%27Enfant_au_toton_-_Jean_Baptiste_Sim%C3%A9on_Chardin_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1705.jpg/1280px-L%27Enfant_au_toton_-_Jean_Baptiste_Sim%C3%A9on_Chardin_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1705.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1594937C-13EA-4C16-B148-4B811DA6ADF2}"/>
-    <hyperlink ref="N51" r:id="rId161" xr:uid="{FCEC6F2D-11C8-47DA-A7AA-EC3F7F6364F8}"/>
-    <hyperlink ref="N52" r:id="rId162" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/44/Le_B%C3%A9n%C3%A9dicit%C3%A9_de_Jean_Sim%C3%A9on_Chardin.jpg/960px-Le_B%C3%A9n%C3%A9dicit%C3%A9_de_Jean_Sim%C3%A9on_Chardin.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C65CEEE6-2B8E-4950-95D0-D0A82C1A36AF}"/>
-    <hyperlink ref="N39" r:id="rId163" xr:uid="{57C524C0-D16F-436D-87F8-365B40BC976A}"/>
-    <hyperlink ref="N40" r:id="rId164" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e8/%28Venice%29_Portrait_of_boy_by_Rosalba_Carriera_-_Gallerie_Accademia.jpg/960px-%28Venice%29_Portrait_of_boy_by_Rosalba_Carriera_-_Gallerie_Accademia.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{48866090-5338-428E-BB43-170DFB1CFCC0}"/>
-    <hyperlink ref="N31" r:id="rId165" xr:uid="{43795563-C178-43C1-A594-4675AA0E48E4}"/>
-    <hyperlink ref="N32" r:id="rId166" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f0/Canal_-_The_Grand_Canal_from_Ca%E2%80%99_Balbi_Looking_towards_Rialto_-_Ca%27_Rezzonico_-_Museum_of_the_18_century_Venice.jpg/1280px-Canal_-_The_Grand_Canal_from_Ca%E2%80%99_Balbi_Looking_towards_Rialto_-_Ca%27_Rezzonico_-_Museum_of_the_18_century_Venice.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F8AF70A3-02D5-4776-BF32-D7487EC0E123}"/>
-    <hyperlink ref="N33" r:id="rId167" display="https://upload.wikimedia.org/wikipedia/commons/6/6e/Canal%2C_Giovanni_Antonio_%28Canaletto%29_-_Return_of_the_Bucentoro_to_the_Molo_on_Ascension_Day%2C_c._1733-4._Royal_Collection_Buckingham_Palace.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{F33A4850-BDB2-448E-B5F2-5C7E32111AB5}"/>
-    <hyperlink ref="N34" r:id="rId168" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/eb/Canal%2C_Giovanni_Antonio_Canal_-_Venice%2C_A_Regatta_on_the_Grand_Canal_-_National_Gallery_NG938.jpg/1280px-Canal%2C_Giovanni_Antonio_Canal_-_Venice%2C_A_Regatta_on_the_Grand_Canal_-_National_Gallery_NG938.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{BB781835-BE3A-4F82-8372-AB82EF3DF829}"/>
-    <hyperlink ref="N35" r:id="rId169" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5b/Canaletto_-_L%27Entr%C3%A9e_du_Grand_Canal%2C_vue_de_l%27extr%C3%A9mit%C3%A9_occidentale_du_M%C3%B4le.jpg/1280px-Canaletto_-_L%27Entr%C3%A9e_du_Grand_Canal%2C_vue_de_l%27extr%C3%A9mit%C3%A9_occidentale_du_M%C3%B4le.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8C323DC1-4CC5-4308-B81E-6663CED84AB5}"/>
-    <hyperlink ref="N36" r:id="rId170" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/da/Giovanni_Antonio_Canal%2C_il_Canaletto_-_The_Feast_Day_of_St_Roch_-_WGA03905.jpg/1280px-Giovanni_Antonio_Canal%2C_il_Canaletto_-_The_Feast_Day_of_St_Roch_-_WGA03905.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8BE72704-117D-4667-9EDB-81BA85F7457D}"/>
-    <hyperlink ref="N21" r:id="rId171" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ad/Fran%C3%A7ois_Boucher_-_The_Triumph_of_Venus_-_Google_Art_Project.jpg/1280px-Fran%C3%A7ois_Boucher_-_The_Triumph_of_Venus_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{C1592AFA-9937-4F90-8766-081343BC52FB}"/>
-    <hyperlink ref="N22" r:id="rId172" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Resting_Girl_by_Fran%C3%A7ois_Boucher_%281753%29_-_Alte_Pinakothek_-_Munich_-_Germany_2017_%28crop%29.jpg/1280px-Resting_Girl_by_Fran%C3%A7ois_Boucher_%281753%29_-_Alte_Pinakothek_-_Munich_-_Germany_2017_%28crop%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{130D0F5E-E1F1-4C69-98D8-C3E05734694E}"/>
-    <hyperlink ref="N23" r:id="rId173" xr:uid="{8135991B-C28C-45A6-9A3F-65E832E58431}"/>
-    <hyperlink ref="N24" r:id="rId174" xr:uid="{D78B1CE8-49BD-440B-B9A0-D725C7CF8EF3}"/>
-    <hyperlink ref="N25" r:id="rId175" xr:uid="{FDD9ACAB-9CFC-4564-BC9D-981F1BA56DED}"/>
-    <hyperlink ref="N26" r:id="rId176" xr:uid="{2E3500CB-55A3-46DD-B1F2-4B3FA8E8FA24}"/>
-    <hyperlink ref="N27" r:id="rId177" xr:uid="{8EB3CC17-B517-4703-ABFD-D3AB687601AE}"/>
-    <hyperlink ref="N28" r:id="rId178" xr:uid="{554A99B6-13C5-4D64-995E-585F216727E2}"/>
-    <hyperlink ref="N16" r:id="rId179" xr:uid="{71F6799B-486A-4755-BD2A-45870DCB264D}"/>
-    <hyperlink ref="N15" r:id="rId180" xr:uid="{ACB07B7D-D5AA-43B1-B510-E5A5495DF9CF}"/>
-    <hyperlink ref="N14" r:id="rId181" xr:uid="{492EB0B2-9ADA-4845-B51C-3FD530970C61}"/>
-    <hyperlink ref="N10" r:id="rId182" xr:uid="{E4382E49-C2AF-4767-83E6-6B0DD8A483BD}"/>
-    <hyperlink ref="N11" r:id="rId183" xr:uid="{BA18D35A-8E5A-40DA-8832-389C459DA2AE}"/>
-    <hyperlink ref="N12" r:id="rId184" xr:uid="{BB5AA1A6-D51B-4250-9A22-E9551488F0AA}"/>
-    <hyperlink ref="N8" r:id="rId185" xr:uid="{58971869-D035-4055-8A28-48A6EFDBA15F}"/>
-    <hyperlink ref="N9" r:id="rId186" xr:uid="{C34AEABF-7D83-4E5F-9BE5-38D407AB89A5}"/>
-    <hyperlink ref="N4" r:id="rId187" xr:uid="{B5E44C97-C22A-4A06-B166-3791B208E4E3}"/>
-    <hyperlink ref="N5" r:id="rId188" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/42/Pompeo_Batoni_-_Tempo_di_inaugurazione_verit%C3%A0_%28Art_Institute_of_Chicago%29.jpg/960px-Pompeo_Batoni_-_Tempo_di_inaugurazione_verit%C3%A0_%28Art_Institute_of_Chicago%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A085B8C4-4000-4273-9384-0FA007B650BE}"/>
+    <hyperlink ref="N281" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="N282" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="N285" r:id="rId57" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="N286" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="N289" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="N290" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="N187" r:id="rId61" xr:uid="{D059BB66-E4EC-435C-B1F8-B71071405B22}"/>
+    <hyperlink ref="N188" r:id="rId62" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f1/Jean-Marc_Nattier_-_Portrait_of_Madame_Bonnier_de_la_Mosson_as_Diana_%28Constance-Gabrielle-Magdeleine_du_Monciel_de_Lauraille_-_77.PA.87_-_J._Paul_Getty_Museum.jpg/960px-thumbnail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A4C23C36-51B7-41CB-964C-F47A12F1EA11}"/>
+    <hyperlink ref="N189" r:id="rId63" xr:uid="{27C77560-6BC3-4FC4-BEF7-D1485A62DF83}"/>
+    <hyperlink ref="N183" r:id="rId64" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/11/Le_Triomphe_de_Bacchus_-_Charles-Joseph_Natoire_-_Mus%C3%A9e_du_Louvre_Peintures_INV_6854_%3B_MR_2201.jpg/1280px-Le_Triomphe_de_Bacchus_-_Charles-Joseph_Natoire_-_Mus%C3%A9e_du_Louvre_Peintures_INV_6854_%3B_MR_2201.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FC20F30A-D010-4DB8-BEE3-2D701B5A70D6}"/>
+    <hyperlink ref="N184" r:id="rId65" xr:uid="{8AF388F1-B762-4742-B842-563BC9A0B7CD}"/>
+    <hyperlink ref="N182" r:id="rId66" xr:uid="{4B64CC3E-8979-4E7B-80B4-14F23B40891A}"/>
+    <hyperlink ref="N186" r:id="rId67" xr:uid="{C4619B65-4A95-4563-BB23-DDB03C0A04FB}"/>
+    <hyperlink ref="N180" r:id="rId68" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/57/Portrait_of_King_Charles_III_of_Spain_%28by_Anton_Raphael_Mengs%29.jpg/960px-Portrait_of_King_Charles_III_of_Spain_%28by_Anton_Raphael_Mengs%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{36FA56BD-6990-4BC2-8D30-4FCD2DA8FD33}"/>
+    <hyperlink ref="N181" r:id="rId69" xr:uid="{EF7AFC89-41ED-4B24-8EE8-723D524FE13B}"/>
+    <hyperlink ref="N176" r:id="rId70" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/50/Luis_Melendez%2C_Still_Life_with_Salmon%2CLemon_and_three_Vessels%2C1772_Museo_del_Prado_Madrid.jpg/1280px-Luis_Melendez%2C_Still_Life_with_Salmon%2CLemon_and_three_Vessels%2C1772_Museo_del_Prado_Madrid.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A7A1EE79-7372-4238-B1C8-51A4FA3F139A}"/>
+    <hyperlink ref="N177" r:id="rId71" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/Luis_Mel%C3%A9ndez_-_Still_Life_with_Oranges%2C_Jars%2C_and_Boxes_of_Sweets_-_Google_Art_Project.jpg/1920px-Luis_Mel%C3%A9ndez_-_Still_Life_with_Oranges%2C_Jars%2C_and_Boxes_of_Sweets_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1BF8EB21-E243-46B8-BCFF-C0D4016AE1B6}"/>
+    <hyperlink ref="N173" r:id="rId72" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9c/Alessandro_Magnasco_dit_il_Lissandrino_-_Fun%C3%A9railles_juives%2C_1720_-_Mus%C3%A9e_d%27art_et_d%27histoire_du_Juda%C3%AFsme.jpg/1280px-Alessandro_Magnasco_dit_il_Lissandrino_-_Fun%C3%A9railles_juives%2C_1720_-_Mus%C3%A9e_d%27art_et_d%27histoire_du_Juda%C3%AFsme.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A4B1DE95-2D9C-4974-81E5-87800C88A4B2}"/>
+    <hyperlink ref="N172" r:id="rId73" xr:uid="{BBFEF0F6-BCBA-459A-B98C-4236B1C377F4}"/>
+    <hyperlink ref="N171" r:id="rId74" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0a/Alessandro_Magnasco_-_Garden_Party_in_Albaro_-_Google_Art_Project.jpg/1280px-Alessandro_Magnasco_-_Garden_Party_in_Albaro_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{73587CC3-03C2-44EA-A494-09AEA82982F3}"/>
+    <hyperlink ref="N185" r:id="rId75" xr:uid="{B5ACCC80-4665-4288-9C8D-6C42B2157CB3}"/>
+    <hyperlink ref="N168" r:id="rId76" xr:uid="{7D865810-64E7-4ABF-A896-3B006A8C05B6}"/>
+    <hyperlink ref="N169" r:id="rId77" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d4/Pietro_Longhi_La_cioccolata_del_mattino_The_Morning_Chocolate_1775-1780.jpg/960px-Pietro_Longhi_La_cioccolata_del_mattino_The_Morning_Chocolate_1775-1780.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{863D6A93-4A79-46C2-B4C0-B330BBE3C66A}"/>
+    <hyperlink ref="N164" r:id="rId78" xr:uid="{62279D71-2D38-4C86-8725-ED9DF05704C5}"/>
+    <hyperlink ref="N165" r:id="rId79" xr:uid="{5AED8D7D-EC30-429D-BAF0-95E3EBDD352B}"/>
+    <hyperlink ref="N159" r:id="rId80" xr:uid="{B21374E9-C4D9-44DF-944F-68BC24FB39E5}"/>
+    <hyperlink ref="N160" r:id="rId81" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/01/Dmitry_Levitsky_-_Portrait_of_Catherine_II_the_Legislatress_in_the_Temple_of_the_Goddess_of_Justice_-_Google_Art_Project.jpg/960px-Dmitry_Levitsky_-_Portrait_of_Catherine_II_the_Legislatress_in_the_Temple_of_the_Goddess_of_Justice_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4E860578-3860-4471-B86B-61F42721C0C9}"/>
+    <hyperlink ref="N161" r:id="rId82" xr:uid="{8D23F0D8-B16D-4B16-8733-97F2B557E4F1}"/>
+    <hyperlink ref="N155" r:id="rId83" xr:uid="{D07706FD-E253-40CE-A841-272F41E442AE}"/>
+    <hyperlink ref="N156" r:id="rId84" xr:uid="{2AB510D7-C2AF-48BB-B4B2-2026B9255F47}"/>
+    <hyperlink ref="N157" r:id="rId85" xr:uid="{31710272-A200-4E72-8E50-D4B214238FA4}"/>
+    <hyperlink ref="N151" r:id="rId86" xr:uid="{9E2A9698-BDF1-4496-9276-C7C62590C0D2}"/>
+    <hyperlink ref="N152" r:id="rId87" xr:uid="{AAA01183-C01B-4197-88FB-9209D5B08B97}"/>
+    <hyperlink ref="N153" r:id="rId88" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/L%27%C3%89t%C3%A9_-_Nicolas_Lancret_-_Mus%C3%A9e_du_Louvre_-_INV_5598.jpg/1280px-L%27%C3%89t%C3%A9_-_Nicolas_Lancret_-_Mus%C3%A9e_du_Louvre_-_INV_5598.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0310F23C-EF73-464D-8642-775293BDA214}"/>
+    <hyperlink ref="N148" r:id="rId89" xr:uid="{191298AC-C4DA-4C5A-950B-E871DE4C15EC}"/>
+    <hyperlink ref="N149" r:id="rId90" xr:uid="{BE1FF6CD-977D-4266-A6E8-4AA75513B5DA}"/>
+    <hyperlink ref="N145" r:id="rId91" xr:uid="{6EFC7096-8323-4901-9118-54E5B96B1F3F}"/>
+    <hyperlink ref="N144" r:id="rId92" xr:uid="{204DE62A-DDA4-4872-8B96-BE87C229FBA9}"/>
+    <hyperlink ref="N137" r:id="rId93" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8c/Marriage_A-la-Mode_2%2C_The_T%C3%AAte_%C3%A0_T%C3%AAte_-_William_Hogarth.jpg/1280px-Marriage_A-la-Mode_2%2C_The_T%C3%AAte_%C3%A0_T%C3%AAte_-_William_Hogarth.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E8E1157D-1D08-40F6-A92C-B605A46B43AF}"/>
+    <hyperlink ref="N138" r:id="rId94" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/dd/Marriage_A-la-Mode_3%2C_The_Inspection_-_William_Hogarth.jpg/1280px-Marriage_A-la-Mode_3%2C_The_Inspection_-_William_Hogarth.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5079D862-1C2C-45FC-B9B8-32DEBD957F31}"/>
+    <hyperlink ref="N139" r:id="rId95" xr:uid="{376CC3A3-F52E-4ECF-912E-384633B7E269}"/>
+    <hyperlink ref="N140" r:id="rId96" xr:uid="{0774708F-3FCD-4707-A4D5-5AF0EE0228CC}"/>
+    <hyperlink ref="N132" r:id="rId97" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/37/Francesco_Guardi_-_The_Parlor_of_the_Nuns_at_San_Zaccaria_-_WGA10827.jpg/1280px-Francesco_Guardi_-_The_Parlor_of_the_Nuns_at_San_Zaccaria_-_WGA10827.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{87896DB2-3324-49E8-B26A-4C097EF64349}"/>
+    <hyperlink ref="N133" r:id="rId98" xr:uid="{8F20E6E9-5719-4D43-97E9-CCECEB4D5062}"/>
+    <hyperlink ref="N124" r:id="rId99" xr:uid="{E769C8C6-507B-4E96-8F0B-0D013618BE65}"/>
+    <hyperlink ref="N125" r:id="rId100" xr:uid="{CCE735FD-891C-4D02-9A1D-8DEB4A788353}"/>
+    <hyperlink ref="N126" r:id="rId101" xr:uid="{E01C2C21-9BF0-40A3-A847-BF569250076A}"/>
+    <hyperlink ref="N127" r:id="rId102" xr:uid="{FC86BF97-E910-4CA1-B899-46C6EF9065B3}"/>
+    <hyperlink ref="N128" r:id="rId103" xr:uid="{FCE95188-94B4-448E-A793-E24F507058DC}"/>
+    <hyperlink ref="N129" r:id="rId104" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a6/Jean-Baptiste_Greuze_%28French_-_The_Laundress_%28La_Blanchisseuse%29_-_Google_Art_Project.jpg/960px-Jean-Baptiste_Greuze_%28French_-_The_Laundress_%28La_Blanchisseuse%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0A7CFD44-125D-4942-9E2B-8C779BAE2C5A}"/>
+    <hyperlink ref="C122" r:id="rId105" xr:uid="{514A2AD1-7F9D-469F-BB42-99285A759971}"/>
+    <hyperlink ref="C123:C129" r:id="rId106" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c9/Jean-Baptiste_Greuze_self-portrait_in_pastels.jpg/960px-Jean-Baptiste_Greuze_self-portrait_in_pastels.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F8BC7389-3BE8-46F1-B976-783102E47A34}"/>
+    <hyperlink ref="N119" r:id="rId107" xr:uid="{BD263C40-274A-491B-B580-1037B1A527F7}"/>
+    <hyperlink ref="N120" r:id="rId108" xr:uid="{D40FBB86-915F-40DE-AFC0-438CE2964327}"/>
+    <hyperlink ref="C118" r:id="rId109" xr:uid="{F9A84F81-ED36-419F-B7DD-0B11A828DC7A}"/>
+    <hyperlink ref="C119:C121" r:id="rId110" display="https://upload.wikimedia.org/wikipedia/commons/3/37/Anton_Graff_-_Zelfportret_van_Anton_Graff_%281736-1813%29_-_Gal.-Nr._2168_-_Staatliche_Kunstsammlungen_Dresden.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{46150356-57C1-4990-ACE8-54AD2634D4E1}"/>
+    <hyperlink ref="N115" r:id="rId111" xr:uid="{C489FD6D-03AE-497C-B45D-3A103D0D7EC1}"/>
+    <hyperlink ref="N116" r:id="rId112" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4f/Atala_au_tombeau%2C1808%2CGirodet_de_Roussy_-Trioson%2C_Louvre..JPG/1280px-Atala_au_tombeau%2C1808%2CGirodet_de_Roussy_-Trioson%2C_Louvre..JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1E1B7A22-985C-4536-81C7-5BC8B5BE2B45}"/>
+    <hyperlink ref="N117" r:id="rId113" xr:uid="{7CD23D3D-E6A8-48D4-959F-03ABD02AA6E1}"/>
+    <hyperlink ref="N112" r:id="rId114" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4f/Thomas_Gainsborough_-_The_Cottage_Door_-_Google_Art_Project.jpg/1280px-Thomas_Gainsborough_-_The_Cottage_Door_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6C742C55-909E-47F0-A689-96CA4FDFF6B2}"/>
+    <hyperlink ref="N113" r:id="rId115" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Thomas_Gainsborough_-_The_Watering_Place_%28before_1777%29.jpg/1280px-Thomas_Gainsborough_-_The_Watering_Place_%28before_1777%29.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{042F65BD-27C1-43BD-831F-42B025DD2318}"/>
+    <hyperlink ref="N109" r:id="rId116" xr:uid="{75099A45-1B1E-4625-8A3B-075B3259D154}"/>
+    <hyperlink ref="N108" r:id="rId117" xr:uid="{C4BF7976-4D50-4E6D-AEA9-A7729EF6CE06}"/>
+    <hyperlink ref="N98" r:id="rId118" xr:uid="{040965B8-3EB0-441F-9C0F-F622C0CFBADE}"/>
+    <hyperlink ref="N99" r:id="rId119" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/26/Jean-Honor%C3%A9_Fragonard_-_Les_Progr%C3%A8s_de_l%27amour_-_Le_rendez-vous_-_Google_Art_Project.jpg/960px-Jean-Honor%C3%A9_Fragonard_-_Les_Progr%C3%A8s_de_l%27amour_-_Le_rendez-vous_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{3CE0E24E-F125-4AFC-A984-09505DDC643B}"/>
+    <hyperlink ref="N100" r:id="rId120" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/39/The_Progress_of_Love_-_The_Lover_Crowned_-_Fragonard_1771-72.jpg/960px-The_Progress_of_Love_-_The_Lover_Crowned_-_Fragonard_1771-72.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6D8A369B-026E-4421-941D-782FC44A65EA}"/>
+    <hyperlink ref="N101" r:id="rId121" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/84/The_Progress_of_Love_-_Love_Letters_-_Fragonard_1771-72.jpg/960px-The_Progress_of_Love_-_Love_Letters_-_Fragonard_1771-72.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6F57409E-7829-4085-A145-CA8B512E9EA1}"/>
+    <hyperlink ref="N102" r:id="rId122" xr:uid="{9AA405D4-B423-4D92-BCDC-D3ECE5E37BB2}"/>
+    <hyperlink ref="N103" r:id="rId123" xr:uid="{F829974F-63C1-4E55-BB95-0256C0415578}"/>
+    <hyperlink ref="N104" r:id="rId124" xr:uid="{2D9130B1-476D-4B4A-AEE4-DEF810B149FC}"/>
+    <hyperlink ref="N105" r:id="rId125" xr:uid="{0C082CB3-8744-4836-B423-7F39A0680CA6}"/>
+    <hyperlink ref="N91" r:id="rId126" xr:uid="{B87F9F91-A36F-4CC6-97B7-CCA3D48695DB}"/>
+    <hyperlink ref="N92" r:id="rId127" xr:uid="{1B8074BA-1335-47C9-A869-429B6477355D}"/>
+    <hyperlink ref="N93" r:id="rId128" xr:uid="{116BA0FF-A724-4FA5-A997-3ED589300CA5}"/>
+    <hyperlink ref="N87" r:id="rId129" xr:uid="{F3C45E8B-537A-41C4-841A-D76103113445}"/>
+    <hyperlink ref="N88" r:id="rId130" xr:uid="{FAE3F4C6-9B29-4FE0-953B-EBEE615155BD}"/>
+    <hyperlink ref="N89" r:id="rId131" xr:uid="{322C2EDD-EFAC-4C96-BDFE-F294C6DA4438}"/>
+    <hyperlink ref="N83" r:id="rId132" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f8/Fran%C3%A7ois-Hubert_DROUAIS_1763-4._London_NG._Madame_de_Pompadour_at_her_Tambour_Frame..jpg/960px-Fran%C3%A7ois-Hubert_DROUAIS_1763-4._London_NG._Madame_de_Pompadour_at_her_Tambour_Frame..jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7BAFF45A-3E97-453B-9193-2E4643B96104}"/>
+    <hyperlink ref="N82" r:id="rId133" xr:uid="{676B976B-A222-4880-86DF-392FAAD178FC}"/>
+    <hyperlink ref="N84" r:id="rId134" xr:uid="{91BBBB20-4312-437C-AC03-56D6A60729FF}"/>
+    <hyperlink ref="N85" r:id="rId135" location="/media/File:Drouais_-_Le_marquis_de_Sourches_et_sa_famille.jpg" xr:uid="{DFD53E45-3B42-44EC-A12A-65C02E3B8446}"/>
+    <hyperlink ref="N79" r:id="rId136" xr:uid="{AB8CE14A-2FE1-4311-B819-3CFEC58E8079}"/>
+    <hyperlink ref="N80" r:id="rId137" xr:uid="{42E82ED5-AF5C-4BF3-B291-8359367702B5}"/>
+    <hyperlink ref="N81" r:id="rId138" xr:uid="{4E9BC4EE-E370-42E2-87EA-F57C3CF1A76E}"/>
+    <hyperlink ref="N76" r:id="rId139" xr:uid="{D9CC9073-7118-4B6C-9D09-4BD332D582DB}"/>
+    <hyperlink ref="N77" r:id="rId140" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1f/Maurice_Quentin_de_La_Tour_-_Self-portrait_with_frill%2C_c1750_-_Mus%C3%A9e_de_Picardie.jpg/960px-Maurice_Quentin_de_La_Tour_-_Self-portrait_with_frill%2C_c1750_-_Mus%C3%A9e_de_Picardie.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A0BAAE3E-98E1-452B-8211-257EEBAFE34F}"/>
+    <hyperlink ref="N66" r:id="rId141" xr:uid="{421D3603-A9E6-4EBF-84DC-7EFD2B974F60}"/>
+    <hyperlink ref="N67" r:id="rId142" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d6/Francisco_de_Goya_-_La_vendimia_o_El_Oto%C3%B1o_%281786%29.jpg/960px-Francisco_de_Goya_-_La_vendimia_o_El_Oto%C3%B1o_%281786%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A495F3AB-E4A0-4BFB-9D2B-D5ACCD7ECE31}"/>
+    <hyperlink ref="N68" r:id="rId143" xr:uid="{6953B915-EEEA-4939-85E0-354BFAE2BE9A}"/>
+    <hyperlink ref="N69" r:id="rId144" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/71/Francisco_de_Goya_-_La_casa_de_locos_-_Google_Art_Project.jpg/1280px-Francisco_de_Goya_-_La_casa_de_locos_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{58D8DAB0-7A95-4977-AF67-A551022C0342}"/>
+    <hyperlink ref="N70" r:id="rId145" xr:uid="{626392C4-75E6-49D1-8C3D-C0F3EDBE0F27}"/>
+    <hyperlink ref="N71" r:id="rId146" xr:uid="{E083E1DC-8C0E-49CD-B584-E9065547E55C}"/>
+    <hyperlink ref="N72" r:id="rId147" xr:uid="{E44FFE73-4938-4AA2-ADB3-5F22564B2B6B}"/>
+    <hyperlink ref="N73" r:id="rId148" xr:uid="{26E98ADB-531B-4BE1-A8F4-1DF326B1B25D}"/>
+    <hyperlink ref="N54" r:id="rId149" xr:uid="{3BAFBF20-4BEA-448F-9982-8B8A53EC07CC}"/>
+    <hyperlink ref="N55" r:id="rId150" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4d/John_Singleton_Copley_-_A_Boy_with_a_Flying_Squirrel_%28Henry_Pelham%29_-_Google_Art_Project.jpg/960px-John_Singleton_Copley_-_A_Boy_with_a_Flying_Squirrel_%28Henry_Pelham%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6806F7F5-72FE-4536-BD33-BFD81FBE9926}"/>
+    <hyperlink ref="N56" r:id="rId151" xr:uid="{6FCA2C83-F067-42B9-BDAF-38BF49CE424B}"/>
+    <hyperlink ref="N45" r:id="rId152" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/56/Le_Buffet_-_Jean_Baptiste_Sim%C3%A9on_Chardin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3198.jpg/960px-Le_Buffet_-_Jean_Baptiste_Sim%C3%A9on_Chardin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3198.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{54B65FB7-24C6-414A-AD88-DB9A26E7B568}"/>
+    <hyperlink ref="N46" r:id="rId153" xr:uid="{8E12A444-0690-4202-989C-3A44525914D6}"/>
+    <hyperlink ref="N47" r:id="rId154" xr:uid="{5C47FF1F-CF54-4DA9-811B-7182737A2DCB}"/>
+    <hyperlink ref="N48" r:id="rId155" xr:uid="{38A6C784-8556-4ECA-8EC5-9B02649F8361}"/>
+    <hyperlink ref="N49" r:id="rId156" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9c/Jeune_dessinateur_taillant_son_crayon_-_Jean_Baptiste_Sim%C3%A9on_Chardin_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1944_4.jpg/960px-Jeune_dessinateur_taillant_son_crayon_-_Jean_Baptiste_Sim%C3%A9on_Chardin_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1944_4.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{205F5316-F9B4-464C-8304-786C1756A1B3}"/>
+    <hyperlink ref="N50" r:id="rId157" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cb/L%27Enfant_au_toton_-_Jean_Baptiste_Sim%C3%A9on_Chardin_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1705.jpg/1280px-L%27Enfant_au_toton_-_Jean_Baptiste_Sim%C3%A9on_Chardin_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1705.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1594937C-13EA-4C16-B148-4B811DA6ADF2}"/>
+    <hyperlink ref="N51" r:id="rId158" xr:uid="{FCEC6F2D-11C8-47DA-A7AA-EC3F7F6364F8}"/>
+    <hyperlink ref="N52" r:id="rId159" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/44/Le_B%C3%A9n%C3%A9dicit%C3%A9_de_Jean_Sim%C3%A9on_Chardin.jpg/960px-Le_B%C3%A9n%C3%A9dicit%C3%A9_de_Jean_Sim%C3%A9on_Chardin.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C65CEEE6-2B8E-4950-95D0-D0A82C1A36AF}"/>
+    <hyperlink ref="N39" r:id="rId160" xr:uid="{57C524C0-D16F-436D-87F8-365B40BC976A}"/>
+    <hyperlink ref="N40" r:id="rId161" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e8/%28Venice%29_Portrait_of_boy_by_Rosalba_Carriera_-_Gallerie_Accademia.jpg/960px-%28Venice%29_Portrait_of_boy_by_Rosalba_Carriera_-_Gallerie_Accademia.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{48866090-5338-428E-BB43-170DFB1CFCC0}"/>
+    <hyperlink ref="N31" r:id="rId162" xr:uid="{43795563-C178-43C1-A594-4675AA0E48E4}"/>
+    <hyperlink ref="N32" r:id="rId163" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f0/Canal_-_The_Grand_Canal_from_Ca%E2%80%99_Balbi_Looking_towards_Rialto_-_Ca%27_Rezzonico_-_Museum_of_the_18_century_Venice.jpg/1280px-Canal_-_The_Grand_Canal_from_Ca%E2%80%99_Balbi_Looking_towards_Rialto_-_Ca%27_Rezzonico_-_Museum_of_the_18_century_Venice.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F8AF70A3-02D5-4776-BF32-D7487EC0E123}"/>
+    <hyperlink ref="N33" r:id="rId164" display="https://upload.wikimedia.org/wikipedia/commons/6/6e/Canal%2C_Giovanni_Antonio_%28Canaletto%29_-_Return_of_the_Bucentoro_to_the_Molo_on_Ascension_Day%2C_c._1733-4._Royal_Collection_Buckingham_Palace.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{F33A4850-BDB2-448E-B5F2-5C7E32111AB5}"/>
+    <hyperlink ref="N34" r:id="rId165" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/eb/Canal%2C_Giovanni_Antonio_Canal_-_Venice%2C_A_Regatta_on_the_Grand_Canal_-_National_Gallery_NG938.jpg/1280px-Canal%2C_Giovanni_Antonio_Canal_-_Venice%2C_A_Regatta_on_the_Grand_Canal_-_National_Gallery_NG938.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{BB781835-BE3A-4F82-8372-AB82EF3DF829}"/>
+    <hyperlink ref="N35" r:id="rId166" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5b/Canaletto_-_L%27Entr%C3%A9e_du_Grand_Canal%2C_vue_de_l%27extr%C3%A9mit%C3%A9_occidentale_du_M%C3%B4le.jpg/1280px-Canaletto_-_L%27Entr%C3%A9e_du_Grand_Canal%2C_vue_de_l%27extr%C3%A9mit%C3%A9_occidentale_du_M%C3%B4le.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8C323DC1-4CC5-4308-B81E-6663CED84AB5}"/>
+    <hyperlink ref="N36" r:id="rId167" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/da/Giovanni_Antonio_Canal%2C_il_Canaletto_-_The_Feast_Day_of_St_Roch_-_WGA03905.jpg/1280px-Giovanni_Antonio_Canal%2C_il_Canaletto_-_The_Feast_Day_of_St_Roch_-_WGA03905.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8BE72704-117D-4667-9EDB-81BA85F7457D}"/>
+    <hyperlink ref="N21" r:id="rId168" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ad/Fran%C3%A7ois_Boucher_-_The_Triumph_of_Venus_-_Google_Art_Project.jpg/1280px-Fran%C3%A7ois_Boucher_-_The_Triumph_of_Venus_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{C1592AFA-9937-4F90-8766-081343BC52FB}"/>
+    <hyperlink ref="N22" r:id="rId169" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Resting_Girl_by_Fran%C3%A7ois_Boucher_%281753%29_-_Alte_Pinakothek_-_Munich_-_Germany_2017_%28crop%29.jpg/1280px-Resting_Girl_by_Fran%C3%A7ois_Boucher_%281753%29_-_Alte_Pinakothek_-_Munich_-_Germany_2017_%28crop%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{130D0F5E-E1F1-4C69-98D8-C3E05734694E}"/>
+    <hyperlink ref="N23" r:id="rId170" xr:uid="{8135991B-C28C-45A6-9A3F-65E832E58431}"/>
+    <hyperlink ref="N24" r:id="rId171" xr:uid="{D78B1CE8-49BD-440B-B9A0-D725C7CF8EF3}"/>
+    <hyperlink ref="N25" r:id="rId172" xr:uid="{FDD9ACAB-9CFC-4564-BC9D-981F1BA56DED}"/>
+    <hyperlink ref="N26" r:id="rId173" xr:uid="{2E3500CB-55A3-46DD-B1F2-4B3FA8E8FA24}"/>
+    <hyperlink ref="N27" r:id="rId174" xr:uid="{8EB3CC17-B517-4703-ABFD-D3AB687601AE}"/>
+    <hyperlink ref="N28" r:id="rId175" xr:uid="{554A99B6-13C5-4D64-995E-585F216727E2}"/>
+    <hyperlink ref="N16" r:id="rId176" xr:uid="{71F6799B-486A-4755-BD2A-45870DCB264D}"/>
+    <hyperlink ref="N15" r:id="rId177" xr:uid="{ACB07B7D-D5AA-43B1-B510-E5A5495DF9CF}"/>
+    <hyperlink ref="N14" r:id="rId178" xr:uid="{492EB0B2-9ADA-4845-B51C-3FD530970C61}"/>
+    <hyperlink ref="N10" r:id="rId179" xr:uid="{E4382E49-C2AF-4767-83E6-6B0DD8A483BD}"/>
+    <hyperlink ref="N11" r:id="rId180" xr:uid="{BA18D35A-8E5A-40DA-8832-389C459DA2AE}"/>
+    <hyperlink ref="N12" r:id="rId181" xr:uid="{BB5AA1A6-D51B-4250-9A22-E9551488F0AA}"/>
+    <hyperlink ref="N8" r:id="rId182" xr:uid="{58971869-D035-4055-8A28-48A6EFDBA15F}"/>
+    <hyperlink ref="N9" r:id="rId183" xr:uid="{C34AEABF-7D83-4E5F-9BE5-38D407AB89A5}"/>
+    <hyperlink ref="N4" r:id="rId184" xr:uid="{B5E44C97-C22A-4A06-B166-3791B208E4E3}"/>
+    <hyperlink ref="N5" r:id="rId185" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/42/Pompeo_Batoni_-_Tempo_di_inaugurazione_verit%C3%A0_%28Art_Institute_of_Chicago%29.jpg/960px-Pompeo_Batoni_-_Tempo_di_inaugurazione_verit%C3%A0_%28Art_Institute_of_Chicago%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A085B8C4-4000-4273-9384-0FA007B650BE}"/>
+    <hyperlink ref="N277" r:id="rId186" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/ea/Benjamin_West_-_Agrippina_Landing_at_Brundisium_with_the_Ashes_of_Germanicu_-_1947.16_-_Yale_University_Art_Gallery.jpg/1280px-Benjamin_West_-_Agrippina_Landing_at_Brundisium_with_the_Ashes_of_Germanicu_-_1947.16_-_Yale_University_Art_Gallery.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EFA2A01D-6F35-4BFF-96A3-171B6645BF33}"/>
+    <hyperlink ref="N278" r:id="rId187" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/71/Benjamin_West_-_Pylades_and_Orestes_Brought_as_Victims_before_Iphigenia_-_Google_Art_Project.jpg/1280px-Benjamin_West_-_Pylades_and_Orestes_Brought_as_Victims_before_Iphigenia_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E00B6E87-0455-4320-8EE7-BEC2E50C4DA2}"/>
+    <hyperlink ref="N121" r:id="rId188" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/81/Friedrich_der_Gro%C3%9Fe_%281781_or_1786%29_-_Google_Art_Project.jpg/960px-Friedrich_der_Gro%C3%9Fe_%281781_or_1786%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C88B28A9-D5FE-4F31-921B-1F1BA325A866}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/quizzes/peinture-18e.xlsx
+++ b/quizzes/peinture-18e.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{925915D0-2837-4811-93C6-9EFA6FDA531C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2E98D93-EEB3-4FBC-B9E1-36FFF8A99D5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="390" windowWidth="28800" windowHeight="15060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2567" uniqueCount="1190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2566" uniqueCount="1190">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -3612,12 +3612,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -3636,7 +3642,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3646,6 +3652,13 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3985,70 +3998,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="6" t="s">
         <v>21</v>
       </c>
     </row>
@@ -8764,8 +8777,8 @@
       <c r="B127" t="s">
         <v>550</v>
       </c>
-      <c r="C127" t="s">
-        <v>271</v>
+      <c r="C127">
+        <v>1771</v>
       </c>
       <c r="D127" t="s">
         <v>118</v>
@@ -14855,17 +14868,6 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:V290">
-    <cfRule type="expression" dxfId="2" priority="1">
-      <formula>IFERROR(--$V2,0)=1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>IFERROR(--$V2,0)=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="3">
-      <formula>IFERROR(--$V2,0)=3</formula>
-    </cfRule>
-  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="K2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="K3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>

--- a/quizzes/peinture-18e.xlsx
+++ b/quizzes/peinture-18e.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84B11729-41A4-4AE0-80DD-04ED9B28D1BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EEDF940-899B-4547-891E-35755279AEC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="345" yWindow="345" windowWidth="16275" windowHeight="15060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2856" uniqueCount="1195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2856" uniqueCount="1194">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -2865,9 +2865,6 @@
   </si>
   <si>
     <t>1787-1788</t>
-  </si>
-  <si>
-    <t>Art Institute of Chicago</t>
   </si>
   <si>
     <t>Les Fontaines</t>
@@ -11683,7 +11680,7 @@
         <v>411</v>
       </c>
       <c r="F188" s="8" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="J188" s="8" t="s">
         <v>806</v>
@@ -13000,16 +12997,16 @@
         <v>48</v>
       </c>
       <c r="F221" t="s">
+        <v>49</v>
+      </c>
+      <c r="J221" t="s">
         <v>944</v>
       </c>
-      <c r="J221" t="s">
+      <c r="K221" t="s">
         <v>945</v>
       </c>
-      <c r="K221" t="s">
+      <c r="L221" s="3" t="s">
         <v>946</v>
-      </c>
-      <c r="L221" s="3" t="s">
-        <v>947</v>
       </c>
       <c r="R221" t="s">
         <v>31</v>
@@ -13035,7 +13032,7 @@
         <v>937</v>
       </c>
       <c r="D222" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="E222" t="s">
         <v>42</v>
@@ -13044,13 +13041,13 @@
         <v>570</v>
       </c>
       <c r="J222" t="s">
+        <v>948</v>
+      </c>
+      <c r="K222" t="s">
         <v>949</v>
       </c>
-      <c r="K222" t="s">
+      <c r="L222" s="3" t="s">
         <v>950</v>
-      </c>
-      <c r="L222" s="3" t="s">
-        <v>951</v>
       </c>
       <c r="R222" t="s">
         <v>31</v>
@@ -13076,7 +13073,7 @@
         <v>937</v>
       </c>
       <c r="D223" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E223" t="s">
         <v>121</v>
@@ -13085,13 +13082,13 @@
         <v>122</v>
       </c>
       <c r="J223" t="s">
+        <v>952</v>
+      </c>
+      <c r="K223" t="s">
+        <v>952</v>
+      </c>
+      <c r="L223" s="3" t="s">
         <v>953</v>
-      </c>
-      <c r="K223" t="s">
-        <v>953</v>
-      </c>
-      <c r="L223" s="3" t="s">
-        <v>954</v>
       </c>
       <c r="R223" t="s">
         <v>31</v>
@@ -13117,7 +13114,7 @@
         <v>937</v>
       </c>
       <c r="D224" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E224" t="s">
         <v>121</v>
@@ -13126,13 +13123,13 @@
         <v>122</v>
       </c>
       <c r="J224" t="s">
+        <v>955</v>
+      </c>
+      <c r="K224" t="s">
+        <v>955</v>
+      </c>
+      <c r="L224" s="3" t="s">
         <v>956</v>
-      </c>
-      <c r="K224" t="s">
-        <v>956</v>
-      </c>
-      <c r="L224" s="3" t="s">
-        <v>957</v>
       </c>
       <c r="R224" t="s">
         <v>31</v>
@@ -13167,13 +13164,13 @@
         <v>122</v>
       </c>
       <c r="J225" t="s">
+        <v>957</v>
+      </c>
+      <c r="K225" t="s">
+        <v>957</v>
+      </c>
+      <c r="L225" s="3" t="s">
         <v>958</v>
-      </c>
-      <c r="K225" t="s">
-        <v>958</v>
-      </c>
-      <c r="L225" s="3" t="s">
-        <v>959</v>
       </c>
       <c r="R225" t="s">
         <v>31</v>
@@ -13202,16 +13199,16 @@
         <v>1780</v>
       </c>
       <c r="F226" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="J226" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="K226" t="s">
+        <v>959</v>
+      </c>
+      <c r="L226" s="3" t="s">
         <v>960</v>
-      </c>
-      <c r="L226" s="3" t="s">
-        <v>961</v>
       </c>
       <c r="R226" t="s">
         <v>31</v>
@@ -13231,13 +13228,13 @@
     </row>
     <row r="227" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
+        <v>961</v>
+      </c>
+      <c r="B227" t="s">
         <v>962</v>
       </c>
-      <c r="B227" t="s">
+      <c r="D227" t="s">
         <v>963</v>
-      </c>
-      <c r="D227" t="s">
-        <v>964</v>
       </c>
       <c r="E227" t="s">
         <v>102</v>
@@ -13246,13 +13243,13 @@
         <v>103</v>
       </c>
       <c r="J227" t="s">
+        <v>964</v>
+      </c>
+      <c r="K227" t="s">
         <v>965</v>
       </c>
-      <c r="K227" t="s">
+      <c r="L227" s="3" t="s">
         <v>966</v>
-      </c>
-      <c r="L227" s="3" t="s">
-        <v>967</v>
       </c>
       <c r="R227" t="s">
         <v>31</v>
@@ -13272,10 +13269,10 @@
     </row>
     <row r="228" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
+        <v>961</v>
+      </c>
+      <c r="B228" t="s">
         <v>962</v>
-      </c>
-      <c r="B228" t="s">
-        <v>963</v>
       </c>
       <c r="D228" t="s">
         <v>756</v>
@@ -13287,13 +13284,13 @@
         <v>103</v>
       </c>
       <c r="J228" t="s">
+        <v>967</v>
+      </c>
+      <c r="K228" t="s">
         <v>968</v>
       </c>
-      <c r="K228" t="s">
+      <c r="L228" s="3" t="s">
         <v>969</v>
-      </c>
-      <c r="L228" s="3" t="s">
-        <v>970</v>
       </c>
       <c r="R228" t="s">
         <v>31</v>
@@ -13313,10 +13310,10 @@
     </row>
     <row r="229" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
+        <v>961</v>
+      </c>
+      <c r="B229" t="s">
         <v>962</v>
-      </c>
-      <c r="B229" t="s">
-        <v>963</v>
       </c>
       <c r="D229" t="s">
         <v>402</v>
@@ -13328,13 +13325,13 @@
         <v>103</v>
       </c>
       <c r="J229" t="s">
+        <v>970</v>
+      </c>
+      <c r="K229" t="s">
         <v>971</v>
       </c>
-      <c r="K229" t="s">
+      <c r="L229" s="3" t="s">
         <v>972</v>
-      </c>
-      <c r="L229" s="3" t="s">
-        <v>973</v>
       </c>
       <c r="R229" t="s">
         <v>31</v>
@@ -13354,10 +13351,10 @@
     </row>
     <row r="230" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
+        <v>961</v>
+      </c>
+      <c r="B230" t="s">
         <v>962</v>
-      </c>
-      <c r="B230" t="s">
-        <v>963</v>
       </c>
       <c r="D230" t="s">
         <v>243</v>
@@ -13369,13 +13366,13 @@
         <v>103</v>
       </c>
       <c r="J230" t="s">
+        <v>973</v>
+      </c>
+      <c r="K230" t="s">
         <v>974</v>
       </c>
-      <c r="K230" t="s">
+      <c r="L230" s="3" t="s">
         <v>975</v>
-      </c>
-      <c r="L230" s="3" t="s">
-        <v>976</v>
       </c>
       <c r="R230" t="s">
         <v>31</v>
@@ -13395,10 +13392,10 @@
     </row>
     <row r="231" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
+        <v>976</v>
+      </c>
+      <c r="B231" t="s">
         <v>977</v>
-      </c>
-      <c r="B231" t="s">
-        <v>978</v>
       </c>
       <c r="D231" t="s">
         <v>278</v>
@@ -13410,13 +13407,13 @@
         <v>140</v>
       </c>
       <c r="J231" t="s">
+        <v>978</v>
+      </c>
+      <c r="K231" t="s">
         <v>979</v>
       </c>
-      <c r="K231" t="s">
+      <c r="L231" s="3" t="s">
         <v>980</v>
-      </c>
-      <c r="L231" s="3" t="s">
-        <v>981</v>
       </c>
       <c r="R231" t="s">
         <v>31</v>
@@ -13436,10 +13433,10 @@
     </row>
     <row r="232" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
+        <v>976</v>
+      </c>
+      <c r="B232" t="s">
         <v>977</v>
-      </c>
-      <c r="B232" t="s">
-        <v>978</v>
       </c>
       <c r="D232" t="s">
         <v>507</v>
@@ -13448,16 +13445,16 @@
         <v>121</v>
       </c>
       <c r="F232" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="J232" t="s">
         <v>218</v>
       </c>
       <c r="K232" t="s">
+        <v>982</v>
+      </c>
+      <c r="L232" s="3" t="s">
         <v>983</v>
-      </c>
-      <c r="L232" s="3" t="s">
-        <v>984</v>
       </c>
       <c r="R232" t="s">
         <v>31</v>
@@ -13477,28 +13474,28 @@
     </row>
     <row r="233" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
+        <v>976</v>
+      </c>
+      <c r="B233" t="s">
         <v>977</v>
-      </c>
-      <c r="B233" t="s">
-        <v>978</v>
       </c>
       <c r="D233" t="s">
         <v>773</v>
       </c>
       <c r="E233" t="s">
+        <v>984</v>
+      </c>
+      <c r="F233" t="s">
         <v>985</v>
       </c>
-      <c r="F233" t="s">
+      <c r="J233" t="s">
         <v>986</v>
       </c>
-      <c r="J233" t="s">
+      <c r="K233" t="s">
         <v>987</v>
       </c>
-      <c r="K233" t="s">
+      <c r="L233" s="3" t="s">
         <v>988</v>
-      </c>
-      <c r="L233" s="3" t="s">
-        <v>989</v>
       </c>
       <c r="R233" t="s">
         <v>31</v>
@@ -13518,28 +13515,28 @@
     </row>
     <row r="234" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
+        <v>976</v>
+      </c>
+      <c r="B234" t="s">
         <v>977</v>
-      </c>
-      <c r="B234" t="s">
-        <v>978</v>
       </c>
       <c r="D234" t="s">
         <v>402</v>
       </c>
       <c r="E234" t="s">
+        <v>989</v>
+      </c>
+      <c r="F234" t="s">
         <v>990</v>
       </c>
-      <c r="F234" t="s">
+      <c r="J234" t="s">
         <v>991</v>
       </c>
-      <c r="J234" t="s">
+      <c r="K234" t="s">
         <v>992</v>
       </c>
-      <c r="K234" t="s">
+      <c r="L234" s="3" t="s">
         <v>993</v>
-      </c>
-      <c r="L234" s="3" t="s">
-        <v>994</v>
       </c>
       <c r="R234" t="s">
         <v>31</v>
@@ -13559,10 +13556,10 @@
     </row>
     <row r="235" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
+        <v>994</v>
+      </c>
+      <c r="B235" t="s">
         <v>995</v>
-      </c>
-      <c r="B235" t="s">
-        <v>996</v>
       </c>
       <c r="D235" t="s">
         <v>938</v>
@@ -13571,16 +13568,16 @@
         <v>129</v>
       </c>
       <c r="F235" t="s">
+        <v>996</v>
+      </c>
+      <c r="J235" t="s">
         <v>997</v>
       </c>
-      <c r="J235" t="s">
+      <c r="K235" t="s">
         <v>998</v>
       </c>
-      <c r="K235" t="s">
+      <c r="L235" s="3" t="s">
         <v>999</v>
-      </c>
-      <c r="L235" s="3" t="s">
-        <v>1000</v>
       </c>
       <c r="R235" t="s">
         <v>31</v>
@@ -13600,10 +13597,10 @@
     </row>
     <row r="236" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
+        <v>994</v>
+      </c>
+      <c r="B236" t="s">
         <v>995</v>
-      </c>
-      <c r="B236" t="s">
-        <v>996</v>
       </c>
       <c r="D236" t="s">
         <v>586</v>
@@ -13615,13 +13612,13 @@
         <v>130</v>
       </c>
       <c r="J236" t="s">
+        <v>1000</v>
+      </c>
+      <c r="K236" t="s">
         <v>1001</v>
       </c>
-      <c r="K236" t="s">
+      <c r="L236" s="3" t="s">
         <v>1002</v>
-      </c>
-      <c r="L236" s="3" t="s">
-        <v>1003</v>
       </c>
       <c r="R236" t="s">
         <v>31</v>
@@ -13641,28 +13638,28 @@
     </row>
     <row r="237" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
+        <v>994</v>
+      </c>
+      <c r="B237" t="s">
         <v>995</v>
-      </c>
-      <c r="B237" t="s">
-        <v>996</v>
       </c>
       <c r="D237" t="s">
         <v>938</v>
       </c>
       <c r="E237" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F237" t="s">
         <v>1004</v>
       </c>
-      <c r="F237" t="s">
+      <c r="J237" t="s">
         <v>1005</v>
       </c>
-      <c r="J237" t="s">
+      <c r="K237" t="s">
         <v>1006</v>
       </c>
-      <c r="K237" t="s">
+      <c r="L237" s="3" t="s">
         <v>1007</v>
-      </c>
-      <c r="L237" s="3" t="s">
-        <v>1008</v>
       </c>
       <c r="R237" t="s">
         <v>31</v>
@@ -13682,13 +13679,13 @@
     </row>
     <row r="238" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
+        <v>994</v>
+      </c>
+      <c r="B238" t="s">
         <v>995</v>
       </c>
-      <c r="B238" t="s">
-        <v>996</v>
-      </c>
       <c r="D238" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="E238" t="s">
         <v>42</v>
@@ -13697,13 +13694,13 @@
         <v>570</v>
       </c>
       <c r="J238" t="s">
+        <v>1009</v>
+      </c>
+      <c r="K238" t="s">
         <v>1010</v>
       </c>
-      <c r="K238" t="s">
+      <c r="L238" s="3" t="s">
         <v>1011</v>
-      </c>
-      <c r="L238" s="3" t="s">
-        <v>1012</v>
       </c>
       <c r="R238" t="s">
         <v>31</v>
@@ -13723,10 +13720,10 @@
     </row>
     <row r="239" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B239" t="s">
         <v>1013</v>
-      </c>
-      <c r="B239" t="s">
-        <v>1014</v>
       </c>
       <c r="D239" t="s">
         <v>887</v>
@@ -13738,10 +13735,10 @@
         <v>75</v>
       </c>
       <c r="J239" t="s">
+        <v>1014</v>
+      </c>
+      <c r="L239" s="3" t="s">
         <v>1015</v>
-      </c>
-      <c r="L239" s="3" t="s">
-        <v>1016</v>
       </c>
       <c r="R239" t="s">
         <v>31</v>
@@ -13761,28 +13758,28 @@
     </row>
     <row r="240" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B240" t="s">
         <v>1013</v>
-      </c>
-      <c r="B240" t="s">
-        <v>1014</v>
       </c>
       <c r="D240" t="s">
         <v>887</v>
       </c>
       <c r="E240" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F240" t="s">
         <v>1017</v>
       </c>
-      <c r="F240" t="s">
+      <c r="J240" t="s">
         <v>1018</v>
       </c>
-      <c r="J240" t="s">
+      <c r="K240" t="s">
         <v>1019</v>
       </c>
-      <c r="K240" t="s">
+      <c r="L240" s="3" t="s">
         <v>1020</v>
-      </c>
-      <c r="L240" s="3" t="s">
-        <v>1021</v>
       </c>
       <c r="R240" t="s">
         <v>31</v>
@@ -13802,28 +13799,28 @@
     </row>
     <row r="241" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B241" t="s">
         <v>1013</v>
-      </c>
-      <c r="B241" t="s">
-        <v>1014</v>
       </c>
       <c r="D241" t="s">
         <v>887</v>
       </c>
       <c r="E241" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F241" t="s">
         <v>1017</v>
       </c>
-      <c r="F241" t="s">
-        <v>1018</v>
-      </c>
       <c r="J241" t="s">
+        <v>1021</v>
+      </c>
+      <c r="K241" t="s">
         <v>1022</v>
       </c>
-      <c r="K241" t="s">
+      <c r="L241" s="3" t="s">
         <v>1023</v>
-      </c>
-      <c r="L241" s="3" t="s">
-        <v>1024</v>
       </c>
       <c r="R241" t="s">
         <v>31</v>
@@ -13843,10 +13840,10 @@
     </row>
     <row r="242" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B242" t="s">
         <v>1013</v>
-      </c>
-      <c r="B242" t="s">
-        <v>1014</v>
       </c>
       <c r="D242" t="s">
         <v>567</v>
@@ -13858,13 +13855,13 @@
         <v>91</v>
       </c>
       <c r="J242" t="s">
+        <v>1024</v>
+      </c>
+      <c r="K242" t="s">
         <v>1025</v>
       </c>
-      <c r="K242" t="s">
+      <c r="L242" s="3" t="s">
         <v>1026</v>
-      </c>
-      <c r="L242" s="3" t="s">
-        <v>1027</v>
       </c>
       <c r="R242" t="s">
         <v>31</v>
@@ -13884,28 +13881,28 @@
     </row>
     <row r="243" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B243" t="s">
         <v>1028</v>
       </c>
-      <c r="B243" t="s">
+      <c r="D243" t="s">
         <v>1029</v>
       </c>
-      <c r="D243" t="s">
+      <c r="E243" t="s">
         <v>1030</v>
       </c>
-      <c r="E243" t="s">
+      <c r="F243" t="s">
         <v>1031</v>
       </c>
-      <c r="F243" t="s">
+      <c r="J243" t="s">
         <v>1032</v>
       </c>
-      <c r="J243" t="s">
+      <c r="K243" t="s">
         <v>1033</v>
       </c>
-      <c r="K243" t="s">
+      <c r="L243" s="3" t="s">
         <v>1034</v>
-      </c>
-      <c r="L243" s="3" t="s">
-        <v>1035</v>
       </c>
       <c r="R243" t="s">
         <v>31</v>
@@ -13925,13 +13922,13 @@
     </row>
     <row r="244" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B244" t="s">
         <v>1028</v>
       </c>
-      <c r="B244" t="s">
-        <v>1029</v>
-      </c>
       <c r="D244" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="E244" t="s">
         <v>312</v>
@@ -13940,13 +13937,13 @@
         <v>313</v>
       </c>
       <c r="J244" t="s">
+        <v>1036</v>
+      </c>
+      <c r="K244" t="s">
         <v>1037</v>
       </c>
-      <c r="K244" t="s">
+      <c r="L244" s="3" t="s">
         <v>1038</v>
-      </c>
-      <c r="L244" s="3" t="s">
-        <v>1039</v>
       </c>
       <c r="R244" t="s">
         <v>31</v>
@@ -13966,13 +13963,13 @@
     </row>
     <row r="245" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B245" t="s">
         <v>1028</v>
       </c>
-      <c r="B245" t="s">
-        <v>1029</v>
-      </c>
       <c r="D245" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E245" t="s">
         <v>42</v>
@@ -13981,16 +13978,16 @@
         <v>43</v>
       </c>
       <c r="J245" t="s">
+        <v>1040</v>
+      </c>
+      <c r="K245" t="s">
         <v>1041</v>
       </c>
-      <c r="K245" t="s">
+      <c r="L245" s="3" t="s">
         <v>1042</v>
       </c>
-      <c r="L245" s="3" t="s">
+      <c r="M245" t="s">
         <v>1043</v>
-      </c>
-      <c r="M245" t="s">
-        <v>1044</v>
       </c>
       <c r="R245" t="s">
         <v>31</v>
@@ -14010,28 +14007,28 @@
     </row>
     <row r="246" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B246" t="s">
         <v>1028</v>
-      </c>
-      <c r="B246" t="s">
-        <v>1029</v>
       </c>
       <c r="D246" t="s">
         <v>147</v>
       </c>
       <c r="E246" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="F246" t="s">
         <v>57</v>
       </c>
       <c r="J246" t="s">
+        <v>1045</v>
+      </c>
+      <c r="K246" t="s">
         <v>1046</v>
       </c>
-      <c r="K246" t="s">
+      <c r="L246" s="3" t="s">
         <v>1047</v>
-      </c>
-      <c r="L246" s="3" t="s">
-        <v>1048</v>
       </c>
       <c r="R246" t="s">
         <v>31</v>
@@ -14051,10 +14048,10 @@
     </row>
     <row r="247" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B247" t="s">
         <v>1049</v>
-      </c>
-      <c r="B247" t="s">
-        <v>1050</v>
       </c>
       <c r="D247" t="s">
         <v>162</v>
@@ -14066,10 +14063,10 @@
         <v>122</v>
       </c>
       <c r="J247" t="s">
+        <v>1050</v>
+      </c>
+      <c r="L247" s="3" t="s">
         <v>1051</v>
-      </c>
-      <c r="L247" s="3" t="s">
-        <v>1052</v>
       </c>
       <c r="R247" t="s">
         <v>31</v>
@@ -14089,10 +14086,10 @@
     </row>
     <row r="248" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B248" t="s">
         <v>1049</v>
-      </c>
-      <c r="B248" t="s">
-        <v>1050</v>
       </c>
       <c r="D248" t="s">
         <v>147</v>
@@ -14104,10 +14101,10 @@
         <v>253</v>
       </c>
       <c r="J248" t="s">
+        <v>1052</v>
+      </c>
+      <c r="L248" s="3" t="s">
         <v>1053</v>
-      </c>
-      <c r="L248" s="3" t="s">
-        <v>1054</v>
       </c>
       <c r="R248" t="s">
         <v>31</v>
@@ -14127,13 +14124,13 @@
     </row>
     <row r="249" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B249" t="s">
         <v>1049</v>
       </c>
-      <c r="B249" t="s">
-        <v>1050</v>
-      </c>
       <c r="D249" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E249" t="s">
         <v>373</v>
@@ -14142,13 +14139,13 @@
         <v>374</v>
       </c>
       <c r="J249" t="s">
+        <v>1055</v>
+      </c>
+      <c r="K249" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L249" s="3" t="s">
         <v>1056</v>
-      </c>
-      <c r="K249" t="s">
-        <v>1056</v>
-      </c>
-      <c r="L249" s="3" t="s">
-        <v>1057</v>
       </c>
       <c r="R249" t="s">
         <v>31</v>
@@ -14168,10 +14165,10 @@
     </row>
     <row r="250" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B250" t="s">
         <v>1049</v>
-      </c>
-      <c r="B250" t="s">
-        <v>1050</v>
       </c>
       <c r="D250" t="s">
         <v>709</v>
@@ -14183,13 +14180,13 @@
         <v>296</v>
       </c>
       <c r="J250" t="s">
+        <v>1057</v>
+      </c>
+      <c r="K250" t="s">
+        <v>1057</v>
+      </c>
+      <c r="L250" s="3" t="s">
         <v>1058</v>
-      </c>
-      <c r="K250" t="s">
-        <v>1058</v>
-      </c>
-      <c r="L250" s="3" t="s">
-        <v>1059</v>
       </c>
       <c r="R250" t="s">
         <v>31</v>
@@ -14209,10 +14206,10 @@
     </row>
     <row r="251" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B251" t="s">
         <v>1060</v>
-      </c>
-      <c r="B251" t="s">
-        <v>1061</v>
       </c>
       <c r="D251" t="s">
         <v>897</v>
@@ -14221,13 +14218,13 @@
         <v>121</v>
       </c>
       <c r="F251" t="s">
+        <v>1061</v>
+      </c>
+      <c r="J251" t="s">
         <v>1062</v>
       </c>
-      <c r="J251" t="s">
+      <c r="L251" s="3" t="s">
         <v>1063</v>
-      </c>
-      <c r="L251" s="3" t="s">
-        <v>1064</v>
       </c>
       <c r="R251" t="s">
         <v>31</v>
@@ -14247,10 +14244,10 @@
     </row>
     <row r="252" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B252" t="s">
         <v>1060</v>
-      </c>
-      <c r="B252" t="s">
-        <v>1061</v>
       </c>
       <c r="D252" t="s">
         <v>756</v>
@@ -14262,10 +14259,10 @@
         <v>130</v>
       </c>
       <c r="J252" t="s">
+        <v>1064</v>
+      </c>
+      <c r="L252" s="3" t="s">
         <v>1065</v>
-      </c>
-      <c r="L252" s="3" t="s">
-        <v>1066</v>
       </c>
       <c r="R252" t="s">
         <v>31</v>
@@ -14285,10 +14282,10 @@
     </row>
     <row r="253" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B253" t="s">
         <v>1060</v>
-      </c>
-      <c r="B253" t="s">
-        <v>1061</v>
       </c>
       <c r="D253" t="s">
         <v>688</v>
@@ -14300,10 +14297,10 @@
         <v>75</v>
       </c>
       <c r="J253" t="s">
+        <v>1066</v>
+      </c>
+      <c r="L253" s="3" t="s">
         <v>1067</v>
-      </c>
-      <c r="L253" s="3" t="s">
-        <v>1068</v>
       </c>
       <c r="R253" t="s">
         <v>31</v>
@@ -14323,10 +14320,10 @@
     </row>
     <row r="254" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B254" t="s">
         <v>1060</v>
-      </c>
-      <c r="B254" t="s">
-        <v>1061</v>
       </c>
       <c r="D254" t="s">
         <v>365</v>
@@ -14338,10 +14335,10 @@
         <v>68</v>
       </c>
       <c r="J254" t="s">
+        <v>1068</v>
+      </c>
+      <c r="L254" s="3" t="s">
         <v>1069</v>
-      </c>
-      <c r="L254" s="3" t="s">
-        <v>1070</v>
       </c>
       <c r="R254" t="s">
         <v>31</v>
@@ -14361,13 +14358,13 @@
     </row>
     <row r="255" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B255" t="s">
         <v>1071</v>
       </c>
-      <c r="B255" t="s">
+      <c r="D255" t="s">
         <v>1072</v>
-      </c>
-      <c r="D255" t="s">
-        <v>1073</v>
       </c>
       <c r="E255" t="s">
         <v>74</v>
@@ -14376,10 +14373,10 @@
         <v>75</v>
       </c>
       <c r="J255" t="s">
+        <v>1073</v>
+      </c>
+      <c r="L255" s="3" t="s">
         <v>1074</v>
-      </c>
-      <c r="L255" s="3" t="s">
-        <v>1075</v>
       </c>
       <c r="R255" t="s">
         <v>31</v>
@@ -14399,10 +14396,10 @@
     </row>
     <row r="256" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B256" t="s">
         <v>1071</v>
-      </c>
-      <c r="B256" t="s">
-        <v>1072</v>
       </c>
       <c r="D256" t="s">
         <v>286</v>
@@ -14411,10 +14408,10 @@
         <v>296</v>
       </c>
       <c r="J256" t="s">
+        <v>1075</v>
+      </c>
+      <c r="L256" s="3" t="s">
         <v>1076</v>
-      </c>
-      <c r="L256" s="3" t="s">
-        <v>1077</v>
       </c>
       <c r="R256" t="s">
         <v>31</v>
@@ -14434,10 +14431,10 @@
     </row>
     <row r="257" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B257" t="s">
         <v>1071</v>
-      </c>
-      <c r="B257" t="s">
-        <v>1072</v>
       </c>
       <c r="D257" t="s">
         <v>669</v>
@@ -14449,16 +14446,16 @@
         <v>122</v>
       </c>
       <c r="J257" t="s">
+        <v>1077</v>
+      </c>
+      <c r="L257" s="3" t="s">
         <v>1078</v>
       </c>
-      <c r="L257" s="3" t="s">
+      <c r="R257" t="s">
+        <v>31</v>
+      </c>
+      <c r="S257" t="s">
         <v>1079</v>
-      </c>
-      <c r="R257" t="s">
-        <v>31</v>
-      </c>
-      <c r="S257" t="s">
-        <v>1080</v>
       </c>
       <c r="T257" s="1">
         <v>130</v>
@@ -14472,22 +14469,22 @@
     </row>
     <row r="258" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B258" t="s">
         <v>1071</v>
       </c>
-      <c r="B258" t="s">
-        <v>1072</v>
-      </c>
       <c r="D258" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="F258" t="s">
         <v>296</v>
       </c>
       <c r="J258" t="s">
+        <v>1080</v>
+      </c>
+      <c r="L258" s="3" t="s">
         <v>1081</v>
-      </c>
-      <c r="L258" s="3" t="s">
-        <v>1082</v>
       </c>
       <c r="R258" t="s">
         <v>31</v>
@@ -14507,10 +14504,10 @@
     </row>
     <row r="259" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B259" t="s">
         <v>1071</v>
-      </c>
-      <c r="B259" t="s">
-        <v>1072</v>
       </c>
       <c r="D259" t="s">
         <v>669</v>
@@ -14522,10 +14519,10 @@
         <v>122</v>
       </c>
       <c r="J259" t="s">
+        <v>1082</v>
+      </c>
+      <c r="L259" s="3" t="s">
         <v>1083</v>
-      </c>
-      <c r="L259" s="3" t="s">
-        <v>1084</v>
       </c>
       <c r="R259" t="s">
         <v>31</v>
@@ -14545,13 +14542,13 @@
     </row>
     <row r="260" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B260" t="s">
         <v>1071</v>
       </c>
-      <c r="B260" t="s">
-        <v>1072</v>
-      </c>
       <c r="D260" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="E260" t="s">
         <v>121</v>
@@ -14560,10 +14557,10 @@
         <v>122</v>
       </c>
       <c r="J260" t="s">
+        <v>1085</v>
+      </c>
+      <c r="L260" s="3" t="s">
         <v>1086</v>
-      </c>
-      <c r="L260" s="3" t="s">
-        <v>1087</v>
       </c>
       <c r="R260" t="s">
         <v>31</v>
@@ -14583,10 +14580,10 @@
     </row>
     <row r="261" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B261" t="s">
         <v>1071</v>
-      </c>
-      <c r="B261" t="s">
-        <v>1072</v>
       </c>
       <c r="D261" t="s">
         <v>337</v>
@@ -14598,16 +14595,16 @@
         <v>122</v>
       </c>
       <c r="J261" t="s">
+        <v>1087</v>
+      </c>
+      <c r="L261" s="3" t="s">
         <v>1088</v>
       </c>
-      <c r="L261" s="3" t="s">
-        <v>1089</v>
-      </c>
       <c r="R261" t="s">
         <v>31</v>
       </c>
       <c r="S261" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="T261" s="1">
         <v>105</v>
@@ -14621,22 +14618,22 @@
     </row>
     <row r="262" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B262" t="s">
         <v>1071</v>
       </c>
-      <c r="B262" t="s">
-        <v>1072</v>
-      </c>
       <c r="D262" t="s">
+        <v>1089</v>
+      </c>
+      <c r="F262" t="s">
         <v>1090</v>
       </c>
-      <c r="F262" t="s">
+      <c r="J262" t="s">
         <v>1091</v>
       </c>
-      <c r="J262" t="s">
+      <c r="L262" s="3" t="s">
         <v>1092</v>
-      </c>
-      <c r="L262" s="3" t="s">
-        <v>1093</v>
       </c>
       <c r="R262" t="s">
         <v>31</v>
@@ -14656,13 +14653,13 @@
     </row>
     <row r="263" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B263" t="s">
         <v>1094</v>
       </c>
-      <c r="B263" t="s">
+      <c r="D263" t="s">
         <v>1095</v>
-      </c>
-      <c r="D263" t="s">
-        <v>1096</v>
       </c>
       <c r="E263" t="s">
         <v>121</v>
@@ -14671,10 +14668,10 @@
         <v>122</v>
       </c>
       <c r="J263" t="s">
+        <v>1096</v>
+      </c>
+      <c r="L263" s="3" t="s">
         <v>1097</v>
-      </c>
-      <c r="L263" s="3" t="s">
-        <v>1098</v>
       </c>
       <c r="R263" t="s">
         <v>31</v>
@@ -14694,13 +14691,13 @@
     </row>
     <row r="264" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B264" t="s">
         <v>1094</v>
       </c>
-      <c r="B264" t="s">
+      <c r="D264" t="s">
         <v>1095</v>
-      </c>
-      <c r="D264" t="s">
-        <v>1096</v>
       </c>
       <c r="E264" t="s">
         <v>121</v>
@@ -14709,10 +14706,10 @@
         <v>122</v>
       </c>
       <c r="J264" t="s">
+        <v>1098</v>
+      </c>
+      <c r="L264" s="3" t="s">
         <v>1099</v>
-      </c>
-      <c r="L264" s="3" t="s">
-        <v>1100</v>
       </c>
       <c r="R264" t="s">
         <v>31</v>
@@ -14732,13 +14729,13 @@
     </row>
     <row r="265" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B265" t="s">
         <v>1094</v>
       </c>
-      <c r="B265" t="s">
-        <v>1095</v>
-      </c>
       <c r="D265" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="E265" t="s">
         <v>121</v>
@@ -14747,10 +14744,10 @@
         <v>122</v>
       </c>
       <c r="J265" t="s">
+        <v>1101</v>
+      </c>
+      <c r="L265" s="3" t="s">
         <v>1102</v>
-      </c>
-      <c r="L265" s="3" t="s">
-        <v>1103</v>
       </c>
       <c r="R265" t="s">
         <v>31</v>
@@ -14770,13 +14767,13 @@
     </row>
     <row r="266" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B266" t="s">
         <v>1094</v>
       </c>
-      <c r="B266" t="s">
-        <v>1095</v>
-      </c>
       <c r="D266" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="E266" t="s">
         <v>42</v>
@@ -14785,10 +14782,10 @@
         <v>43</v>
       </c>
       <c r="J266" t="s">
+        <v>1104</v>
+      </c>
+      <c r="L266" s="3" t="s">
         <v>1105</v>
-      </c>
-      <c r="L266" s="3" t="s">
-        <v>1106</v>
       </c>
       <c r="R266" t="s">
         <v>31</v>
@@ -14808,25 +14805,25 @@
     </row>
     <row r="267" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B267" t="s">
         <v>1094</v>
-      </c>
-      <c r="B267" t="s">
-        <v>1095</v>
       </c>
       <c r="D267" t="s">
         <v>171</v>
       </c>
       <c r="E267" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="F267" t="s">
+        <v>1106</v>
+      </c>
+      <c r="J267" t="s">
         <v>1107</v>
       </c>
-      <c r="J267" t="s">
+      <c r="L267" s="3" t="s">
         <v>1108</v>
-      </c>
-      <c r="L267" s="3" t="s">
-        <v>1109</v>
       </c>
       <c r="R267" t="s">
         <v>31</v>
@@ -14846,13 +14843,13 @@
     </row>
     <row r="268" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B268" t="s">
         <v>1094</v>
       </c>
-      <c r="B268" t="s">
-        <v>1095</v>
-      </c>
       <c r="D268" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="E268" t="s">
         <v>74</v>
@@ -14861,10 +14858,10 @@
         <v>75</v>
       </c>
       <c r="J268" t="s">
+        <v>1110</v>
+      </c>
+      <c r="L268" s="3" t="s">
         <v>1111</v>
-      </c>
-      <c r="L268" s="3" t="s">
-        <v>1112</v>
       </c>
       <c r="R268" t="s">
         <v>31</v>
@@ -14884,13 +14881,13 @@
     </row>
     <row r="269" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B269" t="s">
         <v>1094</v>
       </c>
-      <c r="B269" t="s">
-        <v>1095</v>
-      </c>
       <c r="D269" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="E269" t="s">
         <v>352</v>
@@ -14899,10 +14896,10 @@
         <v>390</v>
       </c>
       <c r="J269" t="s">
+        <v>1113</v>
+      </c>
+      <c r="L269" s="3" t="s">
         <v>1114</v>
-      </c>
-      <c r="L269" s="3" t="s">
-        <v>1115</v>
       </c>
       <c r="R269" t="s">
         <v>31</v>
@@ -14922,13 +14919,13 @@
     </row>
     <row r="270" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B270" t="s">
         <v>1094</v>
       </c>
-      <c r="B270" t="s">
+      <c r="D270" t="s">
         <v>1095</v>
-      </c>
-      <c r="D270" t="s">
-        <v>1096</v>
       </c>
       <c r="E270" t="s">
         <v>579</v>
@@ -14937,10 +14934,10 @@
         <v>875</v>
       </c>
       <c r="J270" t="s">
+        <v>1115</v>
+      </c>
+      <c r="L270" s="3" t="s">
         <v>1116</v>
-      </c>
-      <c r="L270" s="3" t="s">
-        <v>1117</v>
       </c>
       <c r="R270" t="s">
         <v>31</v>
@@ -14960,13 +14957,13 @@
     </row>
     <row r="271" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B271" t="s">
         <v>1094</v>
       </c>
-      <c r="B271" t="s">
-        <v>1095</v>
-      </c>
       <c r="D271" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="E271" t="s">
         <v>352</v>
@@ -14975,10 +14972,10 @@
         <v>390</v>
       </c>
       <c r="J271" t="s">
+        <v>1118</v>
+      </c>
+      <c r="L271" s="3" t="s">
         <v>1119</v>
-      </c>
-      <c r="L271" s="3" t="s">
-        <v>1120</v>
       </c>
       <c r="R271" t="s">
         <v>31</v>
@@ -14998,10 +14995,10 @@
     </row>
     <row r="272" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B272" t="s">
         <v>1094</v>
-      </c>
-      <c r="B272" t="s">
-        <v>1095</v>
       </c>
       <c r="D272" t="s">
         <v>926</v>
@@ -15013,10 +15010,10 @@
         <v>122</v>
       </c>
       <c r="J272" t="s">
+        <v>1120</v>
+      </c>
+      <c r="L272" s="3" t="s">
         <v>1121</v>
-      </c>
-      <c r="L272" s="3" t="s">
-        <v>1122</v>
       </c>
       <c r="R272" t="s">
         <v>31</v>
@@ -15036,13 +15033,13 @@
     </row>
     <row r="273" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B273" t="s">
         <v>1094</v>
       </c>
-      <c r="B273" t="s">
+      <c r="D273" t="s">
         <v>1095</v>
-      </c>
-      <c r="D273" t="s">
-        <v>1096</v>
       </c>
       <c r="E273" t="s">
         <v>129</v>
@@ -15051,10 +15048,10 @@
         <v>130</v>
       </c>
       <c r="J273" t="s">
+        <v>1122</v>
+      </c>
+      <c r="L273" s="3" t="s">
         <v>1123</v>
-      </c>
-      <c r="L273" s="3" t="s">
-        <v>1124</v>
       </c>
       <c r="R273" t="s">
         <v>31</v>
@@ -15074,13 +15071,13 @@
     </row>
     <row r="274" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B274" t="s">
         <v>1094</v>
       </c>
-      <c r="B274" t="s">
-        <v>1095</v>
-      </c>
       <c r="D274" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="E274" t="s">
         <v>176</v>
@@ -15089,10 +15086,10 @@
         <v>177</v>
       </c>
       <c r="J274" t="s">
+        <v>1124</v>
+      </c>
+      <c r="L274" s="3" t="s">
         <v>1125</v>
-      </c>
-      <c r="L274" s="3" t="s">
-        <v>1126</v>
       </c>
       <c r="R274" t="s">
         <v>31</v>
@@ -15112,28 +15109,28 @@
     </row>
     <row r="275" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B275" t="s">
         <v>1127</v>
-      </c>
-      <c r="B275" t="s">
-        <v>1128</v>
       </c>
       <c r="D275" t="s">
         <v>61</v>
       </c>
       <c r="E275" t="s">
+        <v>1128</v>
+      </c>
+      <c r="F275" t="s">
         <v>1129</v>
       </c>
-      <c r="F275" t="s">
+      <c r="J275" t="s">
         <v>1130</v>
       </c>
-      <c r="J275" t="s">
+      <c r="K275" t="s">
         <v>1131</v>
       </c>
-      <c r="K275" t="s">
+      <c r="L275" s="3" t="s">
         <v>1132</v>
-      </c>
-      <c r="L275" s="3" t="s">
-        <v>1133</v>
       </c>
       <c r="R275" t="s">
         <v>31</v>
@@ -15153,10 +15150,10 @@
     </row>
     <row r="276" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B276" t="s">
         <v>1127</v>
-      </c>
-      <c r="B276" t="s">
-        <v>1128</v>
       </c>
       <c r="D276" t="s">
         <v>452</v>
@@ -15168,13 +15165,13 @@
         <v>837</v>
       </c>
       <c r="J276" t="s">
+        <v>1133</v>
+      </c>
+      <c r="K276" t="s">
         <v>1134</v>
       </c>
-      <c r="K276" t="s">
+      <c r="L276" s="3" t="s">
         <v>1135</v>
-      </c>
-      <c r="L276" s="3" t="s">
-        <v>1136</v>
       </c>
       <c r="R276" t="s">
         <v>31</v>
@@ -15194,28 +15191,28 @@
     </row>
     <row r="277" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B277" t="s">
         <v>1127</v>
-      </c>
-      <c r="B277" t="s">
-        <v>1128</v>
       </c>
       <c r="D277" t="s">
         <v>278</v>
       </c>
       <c r="E277" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="F277" t="s">
+        <v>1136</v>
+      </c>
+      <c r="J277" t="s">
         <v>1137</v>
       </c>
-      <c r="J277" t="s">
+      <c r="K277" t="s">
         <v>1138</v>
       </c>
-      <c r="K277" t="s">
+      <c r="L277" s="3" t="s">
         <v>1139</v>
-      </c>
-      <c r="L277" s="3" t="s">
-        <v>1140</v>
       </c>
       <c r="R277" t="s">
         <v>31</v>
@@ -15235,10 +15232,10 @@
     </row>
     <row r="278" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B278" t="s">
         <v>1127</v>
-      </c>
-      <c r="B278" t="s">
-        <v>1128</v>
       </c>
       <c r="D278" t="s">
         <v>892</v>
@@ -15250,13 +15247,13 @@
         <v>91</v>
       </c>
       <c r="J278" t="s">
+        <v>1140</v>
+      </c>
+      <c r="K278" t="s">
         <v>1141</v>
       </c>
-      <c r="K278" t="s">
+      <c r="L278" s="3" t="s">
         <v>1142</v>
-      </c>
-      <c r="L278" s="3" t="s">
-        <v>1143</v>
       </c>
       <c r="R278" t="s">
         <v>31</v>
@@ -15276,28 +15273,28 @@
     </row>
     <row r="279" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B279" t="s">
         <v>1144</v>
-      </c>
-      <c r="B279" t="s">
-        <v>1145</v>
       </c>
       <c r="D279" t="s">
         <v>365</v>
       </c>
       <c r="E279" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F279" t="s">
         <v>1017</v>
       </c>
-      <c r="F279" t="s">
-        <v>1018</v>
-      </c>
       <c r="J279" t="s">
+        <v>1145</v>
+      </c>
+      <c r="K279" t="s">
+        <v>1145</v>
+      </c>
+      <c r="L279" s="3" t="s">
         <v>1146</v>
-      </c>
-      <c r="K279" t="s">
-        <v>1146</v>
-      </c>
-      <c r="L279" s="3" t="s">
-        <v>1147</v>
       </c>
       <c r="R279" t="s">
         <v>31</v>
@@ -15317,10 +15314,10 @@
     </row>
     <row r="280" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B280" t="s">
         <v>1144</v>
-      </c>
-      <c r="B280" t="s">
-        <v>1145</v>
       </c>
       <c r="D280" t="s">
         <v>35</v>
@@ -15332,10 +15329,10 @@
         <v>91</v>
       </c>
       <c r="J280" t="s">
+        <v>1147</v>
+      </c>
+      <c r="L280" s="3" t="s">
         <v>1148</v>
-      </c>
-      <c r="L280" s="3" t="s">
-        <v>1149</v>
       </c>
       <c r="R280" t="s">
         <v>31</v>
@@ -15355,28 +15352,28 @@
     </row>
     <row r="281" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B281" t="s">
         <v>1144</v>
       </c>
-      <c r="B281" t="s">
-        <v>1145</v>
-      </c>
       <c r="D281" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E281" t="s">
         <v>1190</v>
       </c>
-      <c r="E281" t="s">
+      <c r="F281" t="s">
         <v>1191</v>
       </c>
-      <c r="F281" t="s">
-        <v>1192</v>
-      </c>
       <c r="J281" t="s">
+        <v>1149</v>
+      </c>
+      <c r="K281" t="s">
         <v>1150</v>
       </c>
-      <c r="K281" t="s">
+      <c r="L281" s="3" t="s">
         <v>1151</v>
-      </c>
-      <c r="L281" s="3" t="s">
-        <v>1152</v>
       </c>
       <c r="R281" t="s">
         <v>31</v>
@@ -15396,10 +15393,10 @@
     </row>
     <row r="282" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B282" t="s">
         <v>1144</v>
-      </c>
-      <c r="B282" t="s">
-        <v>1145</v>
       </c>
       <c r="D282">
         <v>1714</v>
@@ -15411,13 +15408,13 @@
         <v>75</v>
       </c>
       <c r="J282" t="s">
+        <v>1152</v>
+      </c>
+      <c r="K282" t="s">
         <v>1153</v>
       </c>
-      <c r="K282" t="s">
+      <c r="L282" s="3" t="s">
         <v>1154</v>
-      </c>
-      <c r="L282" s="3" t="s">
-        <v>1155</v>
       </c>
       <c r="R282" t="s">
         <v>31</v>
@@ -15440,7 +15437,7 @@
         <v>409</v>
       </c>
       <c r="B283" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="D283" t="s">
         <v>278</v>
@@ -15452,13 +15449,13 @@
         <v>75</v>
       </c>
       <c r="J283" t="s">
+        <v>1156</v>
+      </c>
+      <c r="K283" t="s">
         <v>1157</v>
       </c>
-      <c r="K283" t="s">
+      <c r="L283" s="3" t="s">
         <v>1158</v>
-      </c>
-      <c r="L283" s="3" t="s">
-        <v>1159</v>
       </c>
       <c r="R283" t="s">
         <v>31</v>
@@ -15481,10 +15478,10 @@
         <v>409</v>
       </c>
       <c r="B284" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="D284" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="E284" t="s">
         <v>74</v>
@@ -15493,13 +15490,13 @@
         <v>91</v>
       </c>
       <c r="J284" t="s">
+        <v>1160</v>
+      </c>
+      <c r="K284" t="s">
         <v>1161</v>
       </c>
-      <c r="K284" t="s">
+      <c r="L284" s="3" t="s">
         <v>1162</v>
-      </c>
-      <c r="L284" s="3" t="s">
-        <v>1163</v>
       </c>
       <c r="R284" t="s">
         <v>31</v>
@@ -15522,25 +15519,25 @@
         <v>409</v>
       </c>
       <c r="B285" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="D285" t="s">
         <v>248</v>
       </c>
       <c r="E285" t="s">
+        <v>1163</v>
+      </c>
+      <c r="F285" t="s">
         <v>1164</v>
       </c>
-      <c r="F285" t="s">
+      <c r="J285" t="s">
         <v>1165</v>
       </c>
-      <c r="J285" t="s">
+      <c r="K285" t="s">
         <v>1166</v>
       </c>
-      <c r="K285" t="s">
+      <c r="L285" s="3" t="s">
         <v>1167</v>
-      </c>
-      <c r="L285" s="3" t="s">
-        <v>1168</v>
       </c>
       <c r="R285" t="s">
         <v>31</v>
@@ -15563,7 +15560,7 @@
         <v>409</v>
       </c>
       <c r="B286" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="D286" t="s">
         <v>756</v>
@@ -15575,13 +15572,13 @@
         <v>91</v>
       </c>
       <c r="J286" t="s">
+        <v>1168</v>
+      </c>
+      <c r="K286" t="s">
         <v>1169</v>
       </c>
-      <c r="K286" t="s">
+      <c r="L286" s="3" t="s">
         <v>1170</v>
-      </c>
-      <c r="L286" s="3" t="s">
-        <v>1171</v>
       </c>
       <c r="R286" t="s">
         <v>31</v>
@@ -15601,10 +15598,10 @@
     </row>
     <row r="287" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B287" t="s">
         <v>1172</v>
-      </c>
-      <c r="B287" t="s">
-        <v>1173</v>
       </c>
       <c r="D287" t="s">
         <v>452</v>
@@ -15616,13 +15613,13 @@
         <v>888</v>
       </c>
       <c r="J287" t="s">
+        <v>1173</v>
+      </c>
+      <c r="K287" t="s">
         <v>1174</v>
       </c>
-      <c r="K287" t="s">
+      <c r="L287" s="3" t="s">
         <v>1175</v>
-      </c>
-      <c r="L287" s="3" t="s">
-        <v>1176</v>
       </c>
       <c r="R287" t="s">
         <v>31</v>
@@ -15642,13 +15639,13 @@
     </row>
     <row r="288" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B288" t="s">
         <v>1172</v>
       </c>
-      <c r="B288" t="s">
-        <v>1173</v>
-      </c>
       <c r="D288" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="E288" t="s">
         <v>193</v>
@@ -15657,13 +15654,13 @@
         <v>888</v>
       </c>
       <c r="J288" t="s">
+        <v>1177</v>
+      </c>
+      <c r="K288" t="s">
         <v>1178</v>
       </c>
-      <c r="K288" t="s">
+      <c r="L288" s="3" t="s">
         <v>1179</v>
-      </c>
-      <c r="L288" s="3" t="s">
-        <v>1180</v>
       </c>
       <c r="R288" t="s">
         <v>31</v>
@@ -15683,28 +15680,28 @@
     </row>
     <row r="289" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B289" t="s">
         <v>1172</v>
-      </c>
-      <c r="B289" t="s">
-        <v>1173</v>
       </c>
       <c r="D289" t="s">
         <v>586</v>
       </c>
       <c r="E289" t="s">
+        <v>1180</v>
+      </c>
+      <c r="F289" t="s">
         <v>1181</v>
       </c>
-      <c r="F289" t="s">
+      <c r="J289" t="s">
         <v>1182</v>
       </c>
-      <c r="J289" t="s">
+      <c r="K289" t="s">
         <v>1183</v>
       </c>
-      <c r="K289" t="s">
+      <c r="L289" s="3" t="s">
         <v>1184</v>
-      </c>
-      <c r="L289" s="3" t="s">
-        <v>1185</v>
       </c>
       <c r="R289" t="s">
         <v>31</v>
@@ -15724,13 +15721,13 @@
     </row>
     <row r="290" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B290" t="s">
         <v>1172</v>
       </c>
-      <c r="B290" t="s">
-        <v>1173</v>
-      </c>
       <c r="D290" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="E290" t="s">
         <v>74</v>
@@ -15739,13 +15736,13 @@
         <v>91</v>
       </c>
       <c r="J290" t="s">
+        <v>1186</v>
+      </c>
+      <c r="K290" t="s">
         <v>1187</v>
       </c>
-      <c r="K290" t="s">
+      <c r="L290" s="3" t="s">
         <v>1188</v>
-      </c>
-      <c r="L290" s="3" t="s">
-        <v>1189</v>
       </c>
       <c r="R290" t="s">
         <v>31</v>

--- a/quizzes/peinture-18e.xlsx
+++ b/quizzes/peinture-18e.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EEDF940-899B-4547-891E-35755279AEC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{630A197D-A2E5-4908-BCC8-4C2B9377413B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="345" windowWidth="16275" windowHeight="15060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="1140" windowWidth="16275" windowHeight="15060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2856" uniqueCount="1194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2857" uniqueCount="1195">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -1478,9 +1478,6 @@
     <t>1781</t>
   </si>
   <si>
-    <t>Detroit Institute of Arts</t>
-  </si>
-  <si>
     <t>"Le Cauchemar"</t>
   </si>
   <si>
@@ -3615,6 +3612,12 @@
   </si>
   <si>
     <t>Le Parc d'Ermenonville</t>
+  </si>
+  <si>
+    <t>Institute of Arts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detroit </t>
   </si>
 </sst>
 </file>
@@ -8332,17 +8335,20 @@
       <c r="D106" t="s">
         <v>480</v>
       </c>
+      <c r="E106" t="s">
+        <v>1194</v>
+      </c>
       <c r="F106" t="s">
+        <v>1193</v>
+      </c>
+      <c r="J106" t="s">
         <v>481</v>
       </c>
-      <c r="J106" t="s">
+      <c r="K106" t="s">
         <v>482</v>
       </c>
-      <c r="K106" t="s">
+      <c r="L106" s="3" t="s">
         <v>483</v>
-      </c>
-      <c r="L106" s="3" t="s">
-        <v>484</v>
       </c>
       <c r="R106" t="s">
         <v>31</v>
@@ -8377,13 +8383,13 @@
         <v>122</v>
       </c>
       <c r="J107" t="s">
+        <v>484</v>
+      </c>
+      <c r="K107" t="s">
         <v>485</v>
       </c>
-      <c r="K107" t="s">
+      <c r="L107" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="L107" s="3" t="s">
-        <v>487</v>
       </c>
       <c r="R107" t="s">
         <v>31</v>
@@ -8412,22 +8418,22 @@
         <v>286</v>
       </c>
       <c r="E108" t="s">
+        <v>487</v>
+      </c>
+      <c r="F108" t="s">
         <v>488</v>
       </c>
-      <c r="F108" t="s">
+      <c r="J108" t="s">
         <v>489</v>
       </c>
-      <c r="J108" t="s">
+      <c r="K108" t="s">
         <v>490</v>
       </c>
-      <c r="K108" t="s">
+      <c r="L108" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="L108" s="3" t="s">
+      <c r="M108" t="s">
         <v>492</v>
-      </c>
-      <c r="M108" t="s">
-        <v>493</v>
       </c>
       <c r="R108" t="s">
         <v>31</v>
@@ -8456,19 +8462,19 @@
         <v>306</v>
       </c>
       <c r="E109" t="s">
+        <v>487</v>
+      </c>
+      <c r="F109" t="s">
         <v>488</v>
       </c>
-      <c r="F109" t="s">
-        <v>489</v>
-      </c>
       <c r="J109" t="s">
+        <v>493</v>
+      </c>
+      <c r="K109" t="s">
         <v>494</v>
       </c>
-      <c r="K109" t="s">
+      <c r="L109" s="3" t="s">
         <v>495</v>
-      </c>
-      <c r="L109" s="3" t="s">
-        <v>496</v>
       </c>
       <c r="R109" t="s">
         <v>31</v>
@@ -8488,10 +8494,10 @@
     </row>
     <row r="110" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>496</v>
+      </c>
+      <c r="B110" t="s">
         <v>497</v>
-      </c>
-      <c r="B110" t="s">
-        <v>498</v>
       </c>
       <c r="D110" t="s">
         <v>128</v>
@@ -8503,13 +8509,13 @@
         <v>75</v>
       </c>
       <c r="J110" t="s">
+        <v>498</v>
+      </c>
+      <c r="K110" t="s">
         <v>499</v>
       </c>
-      <c r="K110" t="s">
+      <c r="L110" s="3" t="s">
         <v>500</v>
-      </c>
-      <c r="L110" s="3" t="s">
-        <v>501</v>
       </c>
       <c r="R110" t="s">
         <v>31</v>
@@ -8529,28 +8535,28 @@
     </row>
     <row r="111" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>496</v>
+      </c>
+      <c r="B111" t="s">
         <v>497</v>
-      </c>
-      <c r="B111" t="s">
-        <v>498</v>
       </c>
       <c r="D111" t="s">
         <v>61</v>
       </c>
       <c r="E111" t="s">
+        <v>501</v>
+      </c>
+      <c r="F111" t="s">
         <v>502</v>
       </c>
-      <c r="F111" t="s">
+      <c r="J111" t="s">
         <v>503</v>
       </c>
-      <c r="J111" t="s">
+      <c r="K111" t="s">
         <v>504</v>
       </c>
-      <c r="K111" t="s">
+      <c r="L111" s="3" t="s">
         <v>505</v>
-      </c>
-      <c r="L111" s="3" t="s">
-        <v>506</v>
       </c>
       <c r="R111" t="s">
         <v>31</v>
@@ -8570,28 +8576,28 @@
     </row>
     <row r="112" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>496</v>
+      </c>
+      <c r="B112" t="s">
         <v>497</v>
       </c>
-      <c r="B112" t="s">
-        <v>498</v>
-      </c>
       <c r="D112" t="s">
+        <v>506</v>
+      </c>
+      <c r="E112" t="s">
         <v>507</v>
       </c>
-      <c r="E112" t="s">
+      <c r="F112" t="s">
         <v>508</v>
       </c>
-      <c r="F112" t="s">
+      <c r="J112" t="s">
         <v>509</v>
       </c>
-      <c r="J112" t="s">
+      <c r="K112" t="s">
         <v>510</v>
       </c>
-      <c r="K112" t="s">
+      <c r="L112" s="3" t="s">
         <v>511</v>
-      </c>
-      <c r="L112" s="3" t="s">
-        <v>512</v>
       </c>
       <c r="R112" t="s">
         <v>31</v>
@@ -8611,13 +8617,13 @@
     </row>
     <row r="113" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
+        <v>496</v>
+      </c>
+      <c r="B113" t="s">
         <v>497</v>
       </c>
-      <c r="B113" t="s">
-        <v>498</v>
-      </c>
       <c r="D113" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E113" t="s">
         <v>74</v>
@@ -8626,13 +8632,13 @@
         <v>75</v>
       </c>
       <c r="J113" t="s">
+        <v>513</v>
+      </c>
+      <c r="K113" t="s">
         <v>514</v>
       </c>
-      <c r="K113" t="s">
+      <c r="L113" s="3" t="s">
         <v>515</v>
-      </c>
-      <c r="L113" s="3" t="s">
-        <v>516</v>
       </c>
       <c r="R113" t="s">
         <v>31</v>
@@ -8652,10 +8658,10 @@
     </row>
     <row r="114" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>516</v>
+      </c>
+      <c r="B114" t="s">
         <v>517</v>
-      </c>
-      <c r="B114" t="s">
-        <v>518</v>
       </c>
       <c r="D114" t="s">
         <v>295</v>
@@ -8667,10 +8673,10 @@
         <v>122</v>
       </c>
       <c r="J114" t="s">
+        <v>518</v>
+      </c>
+      <c r="L114" s="3" t="s">
         <v>519</v>
-      </c>
-      <c r="L114" s="3" t="s">
-        <v>520</v>
       </c>
       <c r="R114" t="s">
         <v>31</v>
@@ -8690,13 +8696,13 @@
     </row>
     <row r="115" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>516</v>
+      </c>
+      <c r="B115" t="s">
         <v>517</v>
       </c>
-      <c r="B115" t="s">
-        <v>518</v>
-      </c>
       <c r="D115" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E115" t="s">
         <v>121</v>
@@ -8705,13 +8711,13 @@
         <v>122</v>
       </c>
       <c r="J115" t="s">
+        <v>521</v>
+      </c>
+      <c r="K115" t="s">
+        <v>521</v>
+      </c>
+      <c r="L115" s="3" t="s">
         <v>522</v>
-      </c>
-      <c r="K115" t="s">
-        <v>522</v>
-      </c>
-      <c r="L115" s="3" t="s">
-        <v>523</v>
       </c>
       <c r="R115" t="s">
         <v>31</v>
@@ -8731,10 +8737,10 @@
     </row>
     <row r="116" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>516</v>
+      </c>
+      <c r="B116" t="s">
         <v>517</v>
-      </c>
-      <c r="B116" t="s">
-        <v>518</v>
       </c>
       <c r="D116" t="s">
         <v>436</v>
@@ -8746,13 +8752,13 @@
         <v>122</v>
       </c>
       <c r="J116" t="s">
+        <v>523</v>
+      </c>
+      <c r="K116" t="s">
+        <v>523</v>
+      </c>
+      <c r="L116" s="3" t="s">
         <v>524</v>
-      </c>
-      <c r="K116" t="s">
-        <v>524</v>
-      </c>
-      <c r="L116" s="3" t="s">
-        <v>525</v>
       </c>
       <c r="R116" t="s">
         <v>31</v>
@@ -8772,37 +8778,37 @@
     </row>
     <row r="117" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
+        <v>516</v>
+      </c>
+      <c r="B117" t="s">
         <v>517</v>
       </c>
-      <c r="B117" t="s">
-        <v>518</v>
-      </c>
       <c r="D117" t="s">
+        <v>525</v>
+      </c>
+      <c r="E117" t="s">
         <v>526</v>
       </c>
-      <c r="E117" t="s">
+      <c r="F117" t="s">
         <v>527</v>
       </c>
-      <c r="F117" t="s">
+      <c r="J117" t="s">
         <v>528</v>
       </c>
-      <c r="J117" t="s">
+      <c r="K117" t="s">
+        <v>528</v>
+      </c>
+      <c r="L117" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="K117" t="s">
-        <v>529</v>
-      </c>
-      <c r="L117" s="3" t="s">
+      <c r="R117" t="s">
+        <v>31</v>
+      </c>
+      <c r="S117" t="s">
+        <v>32</v>
+      </c>
+      <c r="T117" s="1" t="s">
         <v>530</v>
-      </c>
-      <c r="R117" t="s">
-        <v>31</v>
-      </c>
-      <c r="S117" t="s">
-        <v>32</v>
-      </c>
-      <c r="T117" s="1" t="s">
-        <v>531</v>
       </c>
       <c r="U117" s="1">
         <v>124</v>
@@ -8813,28 +8819,28 @@
     </row>
     <row r="118" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>531</v>
+      </c>
+      <c r="B118" t="s">
         <v>532</v>
       </c>
-      <c r="B118" t="s">
+      <c r="D118" t="s">
         <v>533</v>
-      </c>
-      <c r="D118" t="s">
-        <v>534</v>
       </c>
       <c r="E118" t="s">
         <v>56</v>
       </c>
       <c r="F118" t="s">
+        <v>534</v>
+      </c>
+      <c r="J118" t="s">
         <v>535</v>
       </c>
-      <c r="J118" t="s">
+      <c r="K118" t="s">
         <v>536</v>
       </c>
-      <c r="K118" t="s">
+      <c r="L118" s="3" t="s">
         <v>537</v>
-      </c>
-      <c r="L118" s="3" t="s">
-        <v>538</v>
       </c>
       <c r="R118" t="s">
         <v>31</v>
@@ -8854,28 +8860,28 @@
     </row>
     <row r="119" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>531</v>
+      </c>
+      <c r="B119" t="s">
         <v>532</v>
-      </c>
-      <c r="B119" t="s">
-        <v>533</v>
       </c>
       <c r="D119" t="s">
         <v>248</v>
       </c>
       <c r="E119" t="s">
+        <v>538</v>
+      </c>
+      <c r="F119" t="s">
         <v>539</v>
       </c>
-      <c r="F119" t="s">
+      <c r="J119" t="s">
         <v>540</v>
       </c>
-      <c r="J119" t="s">
+      <c r="K119" t="s">
         <v>541</v>
       </c>
-      <c r="K119" t="s">
+      <c r="L119" s="3" t="s">
         <v>542</v>
-      </c>
-      <c r="L119" s="3" t="s">
-        <v>543</v>
       </c>
       <c r="R119" t="s">
         <v>31</v>
@@ -8895,10 +8901,10 @@
     </row>
     <row r="120" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>531</v>
+      </c>
+      <c r="B120" t="s">
         <v>532</v>
-      </c>
-      <c r="B120" t="s">
-        <v>533</v>
       </c>
       <c r="D120" t="s">
         <v>82</v>
@@ -8907,16 +8913,16 @@
         <v>56</v>
       </c>
       <c r="F120" t="s">
+        <v>543</v>
+      </c>
+      <c r="J120" t="s">
         <v>544</v>
       </c>
-      <c r="J120" t="s">
+      <c r="K120" t="s">
         <v>545</v>
       </c>
-      <c r="K120" t="s">
+      <c r="L120" s="3" t="s">
         <v>546</v>
-      </c>
-      <c r="L120" s="3" t="s">
-        <v>547</v>
       </c>
       <c r="R120" t="s">
         <v>31</v>
@@ -8936,10 +8942,10 @@
     </row>
     <row r="121" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>531</v>
+      </c>
+      <c r="B121" t="s">
         <v>532</v>
-      </c>
-      <c r="B121" t="s">
-        <v>533</v>
       </c>
       <c r="D121" t="s">
         <v>480</v>
@@ -8948,16 +8954,16 @@
         <v>56</v>
       </c>
       <c r="F121" t="s">
+        <v>547</v>
+      </c>
+      <c r="J121" t="s">
         <v>548</v>
       </c>
-      <c r="J121" t="s">
+      <c r="K121" t="s">
         <v>549</v>
       </c>
-      <c r="K121" t="s">
+      <c r="L121" s="3" t="s">
         <v>550</v>
-      </c>
-      <c r="L121" s="3" t="s">
-        <v>551</v>
       </c>
       <c r="R121" t="s">
         <v>31</v>
@@ -8977,10 +8983,10 @@
     </row>
     <row r="122" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>551</v>
+      </c>
+      <c r="B122" t="s">
         <v>552</v>
-      </c>
-      <c r="B122" t="s">
-        <v>553</v>
       </c>
       <c r="D122" t="s">
         <v>41</v>
@@ -8992,10 +8998,10 @@
         <v>122</v>
       </c>
       <c r="J122" t="s">
+        <v>553</v>
+      </c>
+      <c r="L122" s="3" t="s">
         <v>554</v>
-      </c>
-      <c r="L122" s="3" t="s">
-        <v>555</v>
       </c>
       <c r="R122" t="s">
         <v>31</v>
@@ -9015,10 +9021,10 @@
     </row>
     <row r="123" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
+        <v>551</v>
+      </c>
+      <c r="B123" t="s">
         <v>552</v>
-      </c>
-      <c r="B123" t="s">
-        <v>553</v>
       </c>
       <c r="D123" t="s">
         <v>274</v>
@@ -9030,10 +9036,10 @@
         <v>122</v>
       </c>
       <c r="J123" t="s">
+        <v>555</v>
+      </c>
+      <c r="L123" s="3" t="s">
         <v>556</v>
-      </c>
-      <c r="L123" s="3" t="s">
-        <v>557</v>
       </c>
       <c r="R123" t="s">
         <v>31</v>
@@ -9053,10 +9059,10 @@
     </row>
     <row r="124" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
+        <v>551</v>
+      </c>
+      <c r="B124" t="s">
         <v>552</v>
-      </c>
-      <c r="B124" t="s">
-        <v>553</v>
       </c>
       <c r="D124" t="s">
         <v>147</v>
@@ -9068,13 +9074,13 @@
         <v>122</v>
       </c>
       <c r="J124" t="s">
+        <v>557</v>
+      </c>
+      <c r="K124" t="s">
+        <v>557</v>
+      </c>
+      <c r="L124" s="3" t="s">
         <v>558</v>
-      </c>
-      <c r="K124" t="s">
-        <v>558</v>
-      </c>
-      <c r="L124" s="3" t="s">
-        <v>559</v>
       </c>
       <c r="R124" t="s">
         <v>31</v>
@@ -9094,10 +9100,10 @@
     </row>
     <row r="125" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
+        <v>551</v>
+      </c>
+      <c r="B125" t="s">
         <v>552</v>
-      </c>
-      <c r="B125" t="s">
-        <v>553</v>
       </c>
       <c r="D125" t="s">
         <v>282</v>
@@ -9109,13 +9115,13 @@
         <v>122</v>
       </c>
       <c r="J125" t="s">
+        <v>559</v>
+      </c>
+      <c r="K125" t="s">
+        <v>559</v>
+      </c>
+      <c r="L125" s="3" t="s">
         <v>560</v>
-      </c>
-      <c r="K125" t="s">
-        <v>560</v>
-      </c>
-      <c r="L125" s="3" t="s">
-        <v>561</v>
       </c>
       <c r="R125" t="s">
         <v>31</v>
@@ -9135,10 +9141,10 @@
     </row>
     <row r="126" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
+        <v>551</v>
+      </c>
+      <c r="B126" t="s">
         <v>552</v>
-      </c>
-      <c r="B126" t="s">
-        <v>553</v>
       </c>
       <c r="D126" t="s">
         <v>282</v>
@@ -9150,13 +9156,13 @@
         <v>75</v>
       </c>
       <c r="J126" t="s">
+        <v>561</v>
+      </c>
+      <c r="K126" t="s">
         <v>562</v>
       </c>
-      <c r="K126" t="s">
+      <c r="L126" s="3" t="s">
         <v>563</v>
-      </c>
-      <c r="L126" s="3" t="s">
-        <v>564</v>
       </c>
       <c r="R126" t="s">
         <v>31</v>
@@ -9176,10 +9182,10 @@
     </row>
     <row r="127" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
+        <v>551</v>
+      </c>
+      <c r="B127" t="s">
         <v>552</v>
-      </c>
-      <c r="B127" t="s">
-        <v>553</v>
       </c>
       <c r="D127">
         <v>1771</v>
@@ -9191,13 +9197,13 @@
         <v>122</v>
       </c>
       <c r="J127" t="s">
+        <v>564</v>
+      </c>
+      <c r="K127" t="s">
+        <v>564</v>
+      </c>
+      <c r="L127" s="3" t="s">
         <v>565</v>
-      </c>
-      <c r="K127" t="s">
-        <v>565</v>
-      </c>
-      <c r="L127" s="3" t="s">
-        <v>566</v>
       </c>
       <c r="R127" t="s">
         <v>31</v>
@@ -9217,13 +9223,13 @@
     </row>
     <row r="128" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>551</v>
+      </c>
+      <c r="B128" t="s">
         <v>552</v>
       </c>
-      <c r="B128" t="s">
-        <v>553</v>
-      </c>
       <c r="D128" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E128" t="s">
         <v>67</v>
@@ -9232,13 +9238,13 @@
         <v>68</v>
       </c>
       <c r="J128" t="s">
+        <v>567</v>
+      </c>
+      <c r="K128" t="s">
+        <v>567</v>
+      </c>
+      <c r="L128" s="3" t="s">
         <v>568</v>
-      </c>
-      <c r="K128" t="s">
-        <v>568</v>
-      </c>
-      <c r="L128" s="3" t="s">
-        <v>569</v>
       </c>
       <c r="R128" t="s">
         <v>31</v>
@@ -9258,10 +9264,10 @@
     </row>
     <row r="129" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
+        <v>551</v>
+      </c>
+      <c r="B129" t="s">
         <v>552</v>
-      </c>
-      <c r="B129" t="s">
-        <v>553</v>
       </c>
       <c r="D129" t="s">
         <v>402</v>
@@ -9270,16 +9276,16 @@
         <v>42</v>
       </c>
       <c r="F129" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="J129" t="s">
         <v>254</v>
       </c>
       <c r="K129" t="s">
+        <v>570</v>
+      </c>
+      <c r="L129" s="3" t="s">
         <v>571</v>
-      </c>
-      <c r="L129" s="3" t="s">
-        <v>572</v>
       </c>
       <c r="R129" t="s">
         <v>31</v>
@@ -9299,13 +9305,13 @@
     </row>
     <row r="130" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
+        <v>572</v>
+      </c>
+      <c r="B130" t="s">
         <v>573</v>
       </c>
-      <c r="B130" t="s">
+      <c r="D130" t="s">
         <v>574</v>
-      </c>
-      <c r="D130" t="s">
-        <v>575</v>
       </c>
       <c r="E130" t="s">
         <v>121</v>
@@ -9314,13 +9320,13 @@
         <v>122</v>
       </c>
       <c r="J130" t="s">
+        <v>575</v>
+      </c>
+      <c r="K130" t="s">
         <v>576</v>
       </c>
-      <c r="K130" t="s">
+      <c r="L130" s="3" t="s">
         <v>577</v>
-      </c>
-      <c r="L130" s="3" t="s">
-        <v>578</v>
       </c>
       <c r="R130" t="s">
         <v>31</v>
@@ -9340,19 +9346,19 @@
     </row>
     <row r="131" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
+        <v>572</v>
+      </c>
+      <c r="B131" t="s">
         <v>573</v>
       </c>
-      <c r="B131" t="s">
+      <c r="D131" t="s">
         <v>574</v>
       </c>
-      <c r="D131" t="s">
-        <v>575</v>
-      </c>
       <c r="E131" t="s">
+        <v>578</v>
+      </c>
+      <c r="F131" t="s">
         <v>579</v>
-      </c>
-      <c r="F131" t="s">
-        <v>580</v>
       </c>
       <c r="J131" t="s">
         <v>172</v>
@@ -9361,7 +9367,7 @@
         <v>173</v>
       </c>
       <c r="L131" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="R131" t="s">
         <v>31</v>
@@ -9381,13 +9387,13 @@
     </row>
     <row r="132" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
+        <v>572</v>
+      </c>
+      <c r="B132" t="s">
         <v>573</v>
       </c>
-      <c r="B132" t="s">
-        <v>574</v>
-      </c>
       <c r="D132" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E132" t="s">
         <v>186</v>
@@ -9396,13 +9402,13 @@
         <v>187</v>
       </c>
       <c r="J132" t="s">
+        <v>582</v>
+      </c>
+      <c r="K132" t="s">
         <v>583</v>
       </c>
-      <c r="K132" t="s">
+      <c r="L132" s="3" t="s">
         <v>584</v>
-      </c>
-      <c r="L132" s="3" t="s">
-        <v>585</v>
       </c>
       <c r="R132" t="s">
         <v>31</v>
@@ -9422,13 +9428,13 @@
     </row>
     <row r="133" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
+        <v>572</v>
+      </c>
+      <c r="B133" t="s">
         <v>573</v>
       </c>
-      <c r="B133" t="s">
-        <v>574</v>
-      </c>
       <c r="D133" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E133" t="s">
         <v>134</v>
@@ -9437,13 +9443,13 @@
         <v>135</v>
       </c>
       <c r="J133" t="s">
+        <v>586</v>
+      </c>
+      <c r="K133" t="s">
         <v>587</v>
       </c>
-      <c r="K133" t="s">
+      <c r="L133" s="3" t="s">
         <v>588</v>
-      </c>
-      <c r="L133" s="3" t="s">
-        <v>589</v>
       </c>
       <c r="R133" t="s">
         <v>31</v>
@@ -9466,7 +9472,7 @@
         <v>80</v>
       </c>
       <c r="B134" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D134" t="s">
         <v>125</v>
@@ -9478,13 +9484,13 @@
         <v>75</v>
       </c>
       <c r="J134" t="s">
+        <v>590</v>
+      </c>
+      <c r="K134" t="s">
         <v>591</v>
       </c>
-      <c r="K134" t="s">
+      <c r="L134" s="3" t="s">
         <v>592</v>
-      </c>
-      <c r="L134" s="3" t="s">
-        <v>593</v>
       </c>
       <c r="R134" t="s">
         <v>31</v>
@@ -9507,10 +9513,10 @@
         <v>80</v>
       </c>
       <c r="B135" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D135" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E135" t="s">
         <v>74</v>
@@ -9519,13 +9525,13 @@
         <v>75</v>
       </c>
       <c r="J135" t="s">
+        <v>594</v>
+      </c>
+      <c r="K135" t="s">
         <v>595</v>
       </c>
-      <c r="K135" t="s">
+      <c r="L135" s="3" t="s">
         <v>596</v>
-      </c>
-      <c r="L135" s="3" t="s">
-        <v>597</v>
       </c>
       <c r="R135" t="s">
         <v>31</v>
@@ -9548,10 +9554,10 @@
         <v>80</v>
       </c>
       <c r="B136" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D136" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E136" t="s">
         <v>74</v>
@@ -9560,13 +9566,13 @@
         <v>91</v>
       </c>
       <c r="J136" t="s">
+        <v>598</v>
+      </c>
+      <c r="K136" t="s">
         <v>599</v>
       </c>
-      <c r="K136" t="s">
+      <c r="L136" s="3" t="s">
         <v>600</v>
-      </c>
-      <c r="L136" s="3" t="s">
-        <v>601</v>
       </c>
       <c r="R136" t="s">
         <v>31</v>
@@ -9589,10 +9595,10 @@
         <v>80</v>
       </c>
       <c r="B137" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D137" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E137" t="s">
         <v>74</v>
@@ -9601,16 +9607,16 @@
         <v>75</v>
       </c>
       <c r="J137" t="s">
+        <v>601</v>
+      </c>
+      <c r="K137" t="s">
         <v>602</v>
       </c>
-      <c r="K137" t="s">
+      <c r="L137" s="3" t="s">
         <v>603</v>
       </c>
-      <c r="L137" s="3" t="s">
+      <c r="M137" t="s">
         <v>604</v>
-      </c>
-      <c r="M137" t="s">
-        <v>605</v>
       </c>
       <c r="R137" t="s">
         <v>31</v>
@@ -9633,10 +9639,10 @@
         <v>80</v>
       </c>
       <c r="B138" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D138" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E138" t="s">
         <v>74</v>
@@ -9645,16 +9651,16 @@
         <v>75</v>
       </c>
       <c r="J138" t="s">
+        <v>605</v>
+      </c>
+      <c r="K138" t="s">
         <v>606</v>
       </c>
-      <c r="K138" t="s">
+      <c r="L138" s="3" t="s">
         <v>607</v>
       </c>
-      <c r="L138" s="3" t="s">
-        <v>608</v>
-      </c>
       <c r="M138" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="R138" t="s">
         <v>31</v>
@@ -9677,10 +9683,10 @@
         <v>80</v>
       </c>
       <c r="B139" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D139" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E139" t="s">
         <v>74</v>
@@ -9689,16 +9695,16 @@
         <v>75</v>
       </c>
       <c r="J139" t="s">
+        <v>608</v>
+      </c>
+      <c r="K139" t="s">
         <v>609</v>
       </c>
-      <c r="K139" t="s">
+      <c r="L139" s="3" t="s">
         <v>610</v>
       </c>
-      <c r="L139" s="3" t="s">
-        <v>611</v>
-      </c>
       <c r="M139" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="R139" t="s">
         <v>31</v>
@@ -9721,10 +9727,10 @@
         <v>80</v>
       </c>
       <c r="B140" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D140" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E140" t="s">
         <v>74</v>
@@ -9733,16 +9739,16 @@
         <v>75</v>
       </c>
       <c r="J140" t="s">
+        <v>611</v>
+      </c>
+      <c r="K140" t="s">
         <v>612</v>
       </c>
-      <c r="K140" t="s">
+      <c r="L140" s="3" t="s">
         <v>613</v>
       </c>
-      <c r="L140" s="3" t="s">
-        <v>614</v>
-      </c>
       <c r="M140" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="R140" t="s">
         <v>31</v>
@@ -9765,10 +9771,10 @@
         <v>80</v>
       </c>
       <c r="B141" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D141" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E141" t="s">
         <v>74</v>
@@ -9777,16 +9783,16 @@
         <v>75</v>
       </c>
       <c r="J141" t="s">
+        <v>614</v>
+      </c>
+      <c r="K141" t="s">
         <v>615</v>
       </c>
-      <c r="K141" t="s">
+      <c r="L141" s="3" t="s">
         <v>616</v>
       </c>
-      <c r="L141" s="3" t="s">
-        <v>617</v>
-      </c>
       <c r="M141" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="R141" t="s">
         <v>31</v>
@@ -9806,28 +9812,28 @@
     </row>
     <row r="142" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
+        <v>617</v>
+      </c>
+      <c r="B142" t="s">
         <v>618</v>
       </c>
-      <c r="B142" t="s">
+      <c r="D142" t="s">
+        <v>566</v>
+      </c>
+      <c r="E142" t="s">
         <v>619</v>
       </c>
-      <c r="D142" t="s">
-        <v>567</v>
-      </c>
-      <c r="E142" t="s">
+      <c r="F142" t="s">
         <v>620</v>
       </c>
-      <c r="F142" t="s">
+      <c r="J142" t="s">
         <v>621</v>
       </c>
-      <c r="J142" t="s">
+      <c r="K142" t="s">
         <v>622</v>
       </c>
-      <c r="K142" t="s">
+      <c r="L142" s="3" t="s">
         <v>623</v>
-      </c>
-      <c r="L142" s="3" t="s">
-        <v>624</v>
       </c>
       <c r="R142" t="s">
         <v>31</v>
@@ -9847,28 +9853,28 @@
     </row>
     <row r="143" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
+        <v>617</v>
+      </c>
+      <c r="B143" t="s">
         <v>618</v>
       </c>
-      <c r="B143" t="s">
-        <v>619</v>
-      </c>
       <c r="D143" t="s">
+        <v>624</v>
+      </c>
+      <c r="E143" t="s">
         <v>625</v>
       </c>
-      <c r="E143" t="s">
+      <c r="F143" t="s">
         <v>626</v>
       </c>
-      <c r="F143" t="s">
+      <c r="J143" t="s">
         <v>627</v>
       </c>
-      <c r="J143" t="s">
+      <c r="K143" t="s">
         <v>628</v>
       </c>
-      <c r="K143" t="s">
+      <c r="L143" s="3" t="s">
         <v>629</v>
-      </c>
-      <c r="L143" s="3" t="s">
-        <v>630</v>
       </c>
       <c r="R143" t="s">
         <v>31</v>
@@ -9888,31 +9894,31 @@
     </row>
     <row r="144" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
+        <v>617</v>
+      </c>
+      <c r="B144" t="s">
         <v>618</v>
       </c>
-      <c r="B144" t="s">
-        <v>619</v>
-      </c>
       <c r="D144" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="E144" t="s">
         <v>74</v>
       </c>
       <c r="F144" t="s">
+        <v>631</v>
+      </c>
+      <c r="J144" t="s">
         <v>632</v>
       </c>
-      <c r="J144" t="s">
+      <c r="K144" t="s">
         <v>633</v>
       </c>
-      <c r="K144" t="s">
+      <c r="L144" s="3" t="s">
         <v>634</v>
       </c>
-      <c r="L144" s="3" t="s">
+      <c r="M144" t="s">
         <v>635</v>
-      </c>
-      <c r="M144" t="s">
-        <v>636</v>
       </c>
       <c r="R144" t="s">
         <v>31</v>
@@ -9932,10 +9938,10 @@
     </row>
     <row r="145" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
+        <v>617</v>
+      </c>
+      <c r="B145" t="s">
         <v>618</v>
-      </c>
-      <c r="B145" t="s">
-        <v>619</v>
       </c>
       <c r="D145" t="s">
         <v>286</v>
@@ -9944,16 +9950,16 @@
         <v>42</v>
       </c>
       <c r="F145" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="J145" t="s">
+        <v>636</v>
+      </c>
+      <c r="K145" t="s">
         <v>637</v>
       </c>
-      <c r="K145" t="s">
+      <c r="L145" s="3" t="s">
         <v>638</v>
-      </c>
-      <c r="L145" s="3" t="s">
-        <v>639</v>
       </c>
       <c r="R145" t="s">
         <v>31</v>
@@ -9973,13 +9979,13 @@
     </row>
     <row r="146" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
+        <v>639</v>
+      </c>
+      <c r="B146" t="s">
         <v>640</v>
       </c>
-      <c r="B146" t="s">
-        <v>641</v>
-      </c>
       <c r="D146" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E146" t="s">
         <v>42</v>
@@ -9988,10 +9994,10 @@
         <v>43</v>
       </c>
       <c r="J146" t="s">
+        <v>641</v>
+      </c>
+      <c r="L146" s="3" t="s">
         <v>642</v>
-      </c>
-      <c r="L146" s="3" t="s">
-        <v>643</v>
       </c>
       <c r="R146" t="s">
         <v>31</v>
@@ -10011,22 +10017,22 @@
     </row>
     <row r="147" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
+        <v>639</v>
+      </c>
+      <c r="B147" t="s">
         <v>640</v>
       </c>
-      <c r="B147" t="s">
-        <v>641</v>
-      </c>
       <c r="D147" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="F147" t="s">
         <v>296</v>
       </c>
       <c r="J147" t="s">
+        <v>644</v>
+      </c>
+      <c r="L147" s="3" t="s">
         <v>645</v>
-      </c>
-      <c r="L147" s="3" t="s">
-        <v>646</v>
       </c>
       <c r="R147" t="s">
         <v>31</v>
@@ -10046,13 +10052,13 @@
     </row>
     <row r="148" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
+        <v>639</v>
+      </c>
+      <c r="B148" t="s">
         <v>640</v>
       </c>
-      <c r="B148" t="s">
-        <v>641</v>
-      </c>
       <c r="D148" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E148" t="s">
         <v>121</v>
@@ -10061,13 +10067,13 @@
         <v>122</v>
       </c>
       <c r="J148" t="s">
+        <v>646</v>
+      </c>
+      <c r="K148" t="s">
         <v>647</v>
       </c>
-      <c r="K148" t="s">
+      <c r="L148" s="3" t="s">
         <v>648</v>
-      </c>
-      <c r="L148" s="3" t="s">
-        <v>649</v>
       </c>
       <c r="R148" t="s">
         <v>31</v>
@@ -10087,10 +10093,10 @@
     </row>
     <row r="149" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
+        <v>639</v>
+      </c>
+      <c r="B149" t="s">
         <v>640</v>
-      </c>
-      <c r="B149" t="s">
-        <v>641</v>
       </c>
       <c r="D149" t="s">
         <v>90</v>
@@ -10102,13 +10108,13 @@
         <v>122</v>
       </c>
       <c r="J149" t="s">
+        <v>649</v>
+      </c>
+      <c r="K149" t="s">
+        <v>649</v>
+      </c>
+      <c r="L149" s="3" t="s">
         <v>650</v>
-      </c>
-      <c r="K149" t="s">
-        <v>650</v>
-      </c>
-      <c r="L149" s="3" t="s">
-        <v>651</v>
       </c>
       <c r="R149" t="s">
         <v>31</v>
@@ -10131,19 +10137,19 @@
         <v>377</v>
       </c>
       <c r="B150" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D150" t="s">
         <v>260</v>
       </c>
       <c r="F150" t="s">
+        <v>652</v>
+      </c>
+      <c r="J150" t="s">
         <v>653</v>
       </c>
-      <c r="J150" t="s">
+      <c r="L150" s="3" t="s">
         <v>654</v>
-      </c>
-      <c r="L150" s="3" t="s">
-        <v>655</v>
       </c>
       <c r="R150" t="s">
         <v>31</v>
@@ -10166,10 +10172,10 @@
         <v>377</v>
       </c>
       <c r="B151" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D151" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E151" t="s">
         <v>74</v>
@@ -10178,13 +10184,13 @@
         <v>390</v>
       </c>
       <c r="J151" t="s">
+        <v>656</v>
+      </c>
+      <c r="K151" t="s">
         <v>657</v>
       </c>
-      <c r="K151" t="s">
+      <c r="L151" s="3" t="s">
         <v>658</v>
-      </c>
-      <c r="L151" s="3" t="s">
-        <v>659</v>
       </c>
       <c r="R151" t="s">
         <v>31</v>
@@ -10207,22 +10213,22 @@
         <v>377</v>
       </c>
       <c r="B152" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D152" t="s">
         <v>198</v>
       </c>
       <c r="E152" t="s">
+        <v>659</v>
+      </c>
+      <c r="F152" t="s">
         <v>660</v>
       </c>
-      <c r="F152" t="s">
+      <c r="J152" t="s">
         <v>661</v>
       </c>
-      <c r="J152" t="s">
+      <c r="L152" s="3" t="s">
         <v>662</v>
-      </c>
-      <c r="L152" s="3" t="s">
-        <v>663</v>
       </c>
       <c r="R152" t="s">
         <v>31</v>
@@ -10245,7 +10251,7 @@
         <v>377</v>
       </c>
       <c r="B153" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D153" t="s">
         <v>175</v>
@@ -10263,7 +10269,7 @@
         <v>154</v>
       </c>
       <c r="L153" s="3" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="M153" t="s">
         <v>152</v>
@@ -10286,10 +10292,10 @@
     </row>
     <row r="154" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B154" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D154" t="s">
         <v>295</v>
@@ -10301,13 +10307,13 @@
         <v>43</v>
       </c>
       <c r="J154" t="s">
+        <v>665</v>
+      </c>
+      <c r="K154" t="s">
         <v>666</v>
       </c>
-      <c r="K154" t="s">
+      <c r="L154" s="3" t="s">
         <v>667</v>
-      </c>
-      <c r="L154" s="3" t="s">
-        <v>668</v>
       </c>
       <c r="R154" t="s">
         <v>31</v>
@@ -10327,13 +10333,13 @@
     </row>
     <row r="155" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B155" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D155" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="E155" t="s">
         <v>74</v>
@@ -10342,13 +10348,13 @@
         <v>75</v>
       </c>
       <c r="J155" t="s">
+        <v>669</v>
+      </c>
+      <c r="K155" t="s">
         <v>670</v>
       </c>
-      <c r="K155" t="s">
+      <c r="L155" s="3" t="s">
         <v>671</v>
-      </c>
-      <c r="L155" s="3" t="s">
-        <v>672</v>
       </c>
       <c r="R155" t="s">
         <v>31</v>
@@ -10368,13 +10374,13 @@
     </row>
     <row r="156" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B156" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D156" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="E156" t="s">
         <v>193</v>
@@ -10383,13 +10389,13 @@
         <v>194</v>
       </c>
       <c r="J156" t="s">
+        <v>673</v>
+      </c>
+      <c r="K156" t="s">
         <v>674</v>
       </c>
-      <c r="K156" t="s">
+      <c r="L156" s="3" t="s">
         <v>675</v>
-      </c>
-      <c r="L156" s="3" t="s">
-        <v>676</v>
       </c>
       <c r="R156" t="s">
         <v>31</v>
@@ -10409,13 +10415,13 @@
     </row>
     <row r="157" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B157" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D157" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="E157" t="s">
         <v>74</v>
@@ -10424,13 +10430,13 @@
         <v>75</v>
       </c>
       <c r="J157" t="s">
+        <v>677</v>
+      </c>
+      <c r="K157" t="s">
         <v>678</v>
       </c>
-      <c r="K157" t="s">
+      <c r="L157" s="3" t="s">
         <v>679</v>
-      </c>
-      <c r="L157" s="3" t="s">
-        <v>680</v>
       </c>
       <c r="R157" t="s">
         <v>31</v>
@@ -10450,28 +10456,28 @@
     </row>
     <row r="158" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
+        <v>680</v>
+      </c>
+      <c r="B158" t="s">
         <v>681</v>
       </c>
-      <c r="B158" t="s">
+      <c r="D158" t="s">
         <v>682</v>
-      </c>
-      <c r="D158" t="s">
-        <v>683</v>
       </c>
       <c r="E158" t="s">
         <v>368</v>
       </c>
       <c r="F158" t="s">
+        <v>683</v>
+      </c>
+      <c r="J158" t="s">
         <v>684</v>
       </c>
-      <c r="J158" t="s">
+      <c r="K158" t="s">
         <v>685</v>
       </c>
-      <c r="K158" t="s">
+      <c r="L158" s="3" t="s">
         <v>686</v>
-      </c>
-      <c r="L158" s="3" t="s">
-        <v>687</v>
       </c>
       <c r="R158" t="s">
         <v>31</v>
@@ -10491,13 +10497,13 @@
     </row>
     <row r="159" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
+        <v>680</v>
+      </c>
+      <c r="B159" t="s">
         <v>681</v>
       </c>
-      <c r="B159" t="s">
-        <v>682</v>
-      </c>
       <c r="D159" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="E159" t="s">
         <v>102</v>
@@ -10506,13 +10512,13 @@
         <v>103</v>
       </c>
       <c r="J159" t="s">
+        <v>688</v>
+      </c>
+      <c r="K159" t="s">
         <v>689</v>
       </c>
-      <c r="K159" t="s">
+      <c r="L159" s="3" t="s">
         <v>690</v>
-      </c>
-      <c r="L159" s="3" t="s">
-        <v>691</v>
       </c>
       <c r="R159" t="s">
         <v>31</v>
@@ -10532,10 +10538,10 @@
     </row>
     <row r="160" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
+        <v>680</v>
+      </c>
+      <c r="B160" t="s">
         <v>681</v>
-      </c>
-      <c r="B160" t="s">
-        <v>682</v>
       </c>
       <c r="D160" t="s">
         <v>286</v>
@@ -10547,13 +10553,13 @@
         <v>103</v>
       </c>
       <c r="J160" t="s">
+        <v>691</v>
+      </c>
+      <c r="K160" t="s">
         <v>692</v>
       </c>
-      <c r="K160" t="s">
+      <c r="L160" s="3" t="s">
         <v>693</v>
-      </c>
-      <c r="L160" s="3" t="s">
-        <v>694</v>
       </c>
       <c r="R160" t="s">
         <v>31</v>
@@ -10573,31 +10579,31 @@
     </row>
     <row r="161" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
+        <v>680</v>
+      </c>
+      <c r="B161" t="s">
         <v>681</v>
       </c>
-      <c r="B161" t="s">
-        <v>682</v>
-      </c>
       <c r="D161" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="E161" t="s">
         <v>107</v>
       </c>
       <c r="F161" t="s">
+        <v>694</v>
+      </c>
+      <c r="J161" t="s">
         <v>695</v>
       </c>
-      <c r="J161" t="s">
+      <c r="K161" t="s">
         <v>696</v>
       </c>
-      <c r="K161" t="s">
+      <c r="L161" s="3" t="s">
         <v>697</v>
       </c>
-      <c r="L161" s="3" t="s">
+      <c r="M161" t="s">
         <v>698</v>
-      </c>
-      <c r="M161" t="s">
-        <v>699</v>
       </c>
       <c r="R161" t="s">
         <v>31</v>
@@ -10617,10 +10623,10 @@
     </row>
     <row r="162" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
+        <v>699</v>
+      </c>
+      <c r="B162" t="s">
         <v>700</v>
-      </c>
-      <c r="B162" t="s">
-        <v>701</v>
       </c>
       <c r="D162" t="s">
         <v>125</v>
@@ -10629,13 +10635,13 @@
         <v>368</v>
       </c>
       <c r="F162" t="s">
+        <v>701</v>
+      </c>
+      <c r="J162" t="s">
         <v>702</v>
       </c>
-      <c r="J162" t="s">
+      <c r="L162" s="3" t="s">
         <v>703</v>
-      </c>
-      <c r="L162" s="3" t="s">
-        <v>704</v>
       </c>
       <c r="R162" t="s">
         <v>31</v>
@@ -10655,13 +10661,13 @@
     </row>
     <row r="163" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
+        <v>699</v>
+      </c>
+      <c r="B163" t="s">
         <v>700</v>
       </c>
-      <c r="B163" t="s">
-        <v>701</v>
-      </c>
       <c r="D163" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E163" t="s">
         <v>56</v>
@@ -10670,16 +10676,16 @@
         <v>57</v>
       </c>
       <c r="J163" t="s">
+        <v>705</v>
+      </c>
+      <c r="L163" s="3" t="s">
         <v>706</v>
       </c>
-      <c r="L163" s="3" t="s">
+      <c r="R163" t="s">
+        <v>31</v>
+      </c>
+      <c r="S163" t="s">
         <v>707</v>
-      </c>
-      <c r="R163" t="s">
-        <v>31</v>
-      </c>
-      <c r="S163" t="s">
-        <v>708</v>
       </c>
       <c r="T163" s="1">
         <v>83</v>
@@ -10693,34 +10699,34 @@
     </row>
     <row r="164" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
+        <v>699</v>
+      </c>
+      <c r="B164" t="s">
         <v>700</v>
       </c>
-      <c r="B164" t="s">
-        <v>701</v>
-      </c>
       <c r="D164" t="s">
+        <v>708</v>
+      </c>
+      <c r="E164" t="s">
         <v>709</v>
       </c>
-      <c r="E164" t="s">
+      <c r="F164" t="s">
         <v>710</v>
       </c>
-      <c r="F164" t="s">
+      <c r="J164" t="s">
         <v>711</v>
       </c>
-      <c r="J164" t="s">
+      <c r="K164" t="s">
         <v>712</v>
       </c>
-      <c r="K164" t="s">
+      <c r="L164" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="L164" s="3" t="s">
-        <v>714</v>
-      </c>
       <c r="R164" t="s">
         <v>31</v>
       </c>
       <c r="S164" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="T164" s="1">
         <v>54</v>
@@ -10734,28 +10740,28 @@
     </row>
     <row r="165" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
+        <v>699</v>
+      </c>
+      <c r="B165" t="s">
         <v>700</v>
       </c>
-      <c r="B165" t="s">
-        <v>701</v>
-      </c>
       <c r="D165" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E165" t="s">
         <v>368</v>
       </c>
       <c r="F165" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="J165" t="s">
+        <v>715</v>
+      </c>
+      <c r="K165" t="s">
+        <v>715</v>
+      </c>
+      <c r="L165" s="3" t="s">
         <v>716</v>
-      </c>
-      <c r="K165" t="s">
-        <v>716</v>
-      </c>
-      <c r="L165" s="3" t="s">
-        <v>717</v>
       </c>
       <c r="R165" t="s">
         <v>31</v>
@@ -10775,10 +10781,10 @@
     </row>
     <row r="166" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
+        <v>717</v>
+      </c>
+      <c r="B166" t="s">
         <v>718</v>
-      </c>
-      <c r="B166" t="s">
-        <v>719</v>
       </c>
       <c r="D166" t="s">
         <v>128</v>
@@ -10790,13 +10796,13 @@
         <v>187</v>
       </c>
       <c r="J166" t="s">
+        <v>719</v>
+      </c>
+      <c r="K166" t="s">
         <v>720</v>
       </c>
-      <c r="K166" t="s">
+      <c r="L166" s="3" t="s">
         <v>721</v>
-      </c>
-      <c r="L166" s="3" t="s">
-        <v>722</v>
       </c>
       <c r="R166" t="s">
         <v>31</v>
@@ -10816,10 +10822,10 @@
     </row>
     <row r="167" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
+        <v>717</v>
+      </c>
+      <c r="B167" t="s">
         <v>718</v>
-      </c>
-      <c r="B167" t="s">
-        <v>719</v>
       </c>
       <c r="D167" t="s">
         <v>372</v>
@@ -10831,13 +10837,13 @@
         <v>187</v>
       </c>
       <c r="J167" t="s">
+        <v>722</v>
+      </c>
+      <c r="K167" t="s">
         <v>723</v>
       </c>
-      <c r="K167" t="s">
+      <c r="L167" s="3" t="s">
         <v>724</v>
-      </c>
-      <c r="L167" s="3" t="s">
-        <v>725</v>
       </c>
       <c r="R167" t="s">
         <v>31</v>
@@ -10857,13 +10863,13 @@
     </row>
     <row r="168" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
+        <v>717</v>
+      </c>
+      <c r="B168" t="s">
         <v>718</v>
       </c>
-      <c r="B168" t="s">
-        <v>719</v>
-      </c>
       <c r="D168" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E168" t="s">
         <v>186</v>
@@ -10872,13 +10878,13 @@
         <v>187</v>
       </c>
       <c r="J168" t="s">
+        <v>725</v>
+      </c>
+      <c r="K168" t="s">
         <v>726</v>
       </c>
-      <c r="K168" t="s">
+      <c r="L168" s="3" t="s">
         <v>727</v>
-      </c>
-      <c r="L168" s="3" t="s">
-        <v>728</v>
       </c>
       <c r="R168" t="s">
         <v>31</v>
@@ -10898,13 +10904,13 @@
     </row>
     <row r="169" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
+        <v>717</v>
+      </c>
+      <c r="B169" t="s">
         <v>718</v>
       </c>
-      <c r="B169" t="s">
-        <v>719</v>
-      </c>
       <c r="D169" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E169" t="s">
         <v>186</v>
@@ -10913,13 +10919,13 @@
         <v>187</v>
       </c>
       <c r="J169" t="s">
+        <v>728</v>
+      </c>
+      <c r="K169" t="s">
         <v>729</v>
       </c>
-      <c r="K169" t="s">
+      <c r="L169" s="3" t="s">
         <v>730</v>
-      </c>
-      <c r="L169" s="3" t="s">
-        <v>731</v>
       </c>
       <c r="R169" t="s">
         <v>31</v>
@@ -10939,13 +10945,13 @@
     </row>
     <row r="170" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
+        <v>731</v>
+      </c>
+      <c r="B170" t="s">
         <v>732</v>
       </c>
-      <c r="B170" t="s">
+      <c r="D170" t="s">
         <v>733</v>
-      </c>
-      <c r="D170" t="s">
-        <v>734</v>
       </c>
       <c r="E170" t="s">
         <v>42</v>
@@ -10954,13 +10960,13 @@
         <v>43</v>
       </c>
       <c r="J170" t="s">
+        <v>734</v>
+      </c>
+      <c r="K170" t="s">
         <v>735</v>
       </c>
-      <c r="K170" t="s">
+      <c r="L170" s="3" t="s">
         <v>736</v>
-      </c>
-      <c r="L170" s="3" t="s">
-        <v>737</v>
       </c>
       <c r="R170" t="s">
         <v>31</v>
@@ -10980,28 +10986,28 @@
     </row>
     <row r="171" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
+        <v>731</v>
+      </c>
+      <c r="B171" t="s">
         <v>732</v>
       </c>
-      <c r="B171" t="s">
-        <v>733</v>
-      </c>
       <c r="D171" t="s">
+        <v>737</v>
+      </c>
+      <c r="E171" t="s">
         <v>738</v>
       </c>
-      <c r="E171" t="s">
+      <c r="F171" t="s">
         <v>739</v>
       </c>
-      <c r="F171" t="s">
+      <c r="J171" t="s">
         <v>740</v>
       </c>
-      <c r="J171" t="s">
+      <c r="K171" t="s">
         <v>741</v>
       </c>
-      <c r="K171" t="s">
+      <c r="L171" s="3" t="s">
         <v>742</v>
-      </c>
-      <c r="L171" s="3" t="s">
-        <v>743</v>
       </c>
       <c r="R171" t="s">
         <v>31</v>
@@ -11021,13 +11027,13 @@
     </row>
     <row r="172" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
+        <v>731</v>
+      </c>
+      <c r="B172" t="s">
         <v>732</v>
       </c>
-      <c r="B172" t="s">
-        <v>733</v>
-      </c>
       <c r="D172" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E172" t="s">
         <v>121</v>
@@ -11036,13 +11042,13 @@
         <v>122</v>
       </c>
       <c r="J172" t="s">
+        <v>744</v>
+      </c>
+      <c r="K172" t="s">
+        <v>744</v>
+      </c>
+      <c r="L172" s="3" t="s">
         <v>745</v>
-      </c>
-      <c r="K172" t="s">
-        <v>745</v>
-      </c>
-      <c r="L172" s="3" t="s">
-        <v>746</v>
       </c>
       <c r="R172" t="s">
         <v>31</v>
@@ -11062,13 +11068,13 @@
     </row>
     <row r="173" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
+        <v>731</v>
+      </c>
+      <c r="B173" t="s">
         <v>732</v>
       </c>
-      <c r="B173" t="s">
-        <v>733</v>
-      </c>
       <c r="D173" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="E173" t="s">
         <v>121</v>
@@ -11077,13 +11083,13 @@
         <v>122</v>
       </c>
       <c r="J173" t="s">
+        <v>747</v>
+      </c>
+      <c r="K173" t="s">
+        <v>747</v>
+      </c>
+      <c r="L173" s="3" t="s">
         <v>748</v>
-      </c>
-      <c r="K173" t="s">
-        <v>748</v>
-      </c>
-      <c r="L173" s="3" t="s">
-        <v>749</v>
       </c>
       <c r="R173" t="s">
         <v>31</v>
@@ -11103,13 +11109,13 @@
     </row>
     <row r="174" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
+        <v>749</v>
+      </c>
+      <c r="B174" t="s">
         <v>750</v>
       </c>
-      <c r="B174" t="s">
-        <v>751</v>
-      </c>
       <c r="D174" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E174" t="s">
         <v>121</v>
@@ -11124,7 +11130,7 @@
         <v>318</v>
       </c>
       <c r="L174" s="3" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="R174" t="s">
         <v>31</v>
@@ -11144,10 +11150,10 @@
     </row>
     <row r="175" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
+        <v>749</v>
+      </c>
+      <c r="B175" t="s">
         <v>750</v>
-      </c>
-      <c r="B175" t="s">
-        <v>751</v>
       </c>
       <c r="D175" t="s">
         <v>61</v>
@@ -11159,13 +11165,13 @@
         <v>122</v>
       </c>
       <c r="J175" t="s">
+        <v>752</v>
+      </c>
+      <c r="K175" t="s">
         <v>753</v>
       </c>
-      <c r="K175" t="s">
+      <c r="L175" s="3" t="s">
         <v>754</v>
-      </c>
-      <c r="L175" s="3" t="s">
-        <v>755</v>
       </c>
       <c r="R175" t="s">
         <v>31</v>
@@ -11185,13 +11191,13 @@
     </row>
     <row r="176" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
+        <v>749</v>
+      </c>
+      <c r="B176" t="s">
         <v>750</v>
       </c>
-      <c r="B176" t="s">
-        <v>751</v>
-      </c>
       <c r="D176" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="E176" t="s">
         <v>312</v>
@@ -11200,16 +11206,16 @@
         <v>313</v>
       </c>
       <c r="J176" t="s">
+        <v>756</v>
+      </c>
+      <c r="K176" t="s">
         <v>757</v>
       </c>
-      <c r="K176" t="s">
+      <c r="L176" s="3" t="s">
         <v>758</v>
       </c>
-      <c r="L176" s="3" t="s">
+      <c r="M176" t="s">
         <v>759</v>
-      </c>
-      <c r="M176" t="s">
-        <v>760</v>
       </c>
       <c r="R176" t="s">
         <v>31</v>
@@ -11229,13 +11235,13 @@
     </row>
     <row r="177" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
+        <v>749</v>
+      </c>
+      <c r="B177" t="s">
         <v>750</v>
       </c>
-      <c r="B177" t="s">
-        <v>751</v>
-      </c>
       <c r="D177" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="E177" t="s">
         <v>312</v>
@@ -11244,16 +11250,16 @@
         <v>313</v>
       </c>
       <c r="J177" t="s">
+        <v>761</v>
+      </c>
+      <c r="K177" t="s">
         <v>762</v>
       </c>
-      <c r="K177" t="s">
+      <c r="L177" s="3" t="s">
         <v>763</v>
       </c>
-      <c r="L177" s="3" t="s">
-        <v>764</v>
-      </c>
       <c r="M177" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="R177" t="s">
         <v>31</v>
@@ -11273,34 +11279,34 @@
     </row>
     <row r="178" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
+        <v>764</v>
+      </c>
+      <c r="B178" t="s">
         <v>765</v>
-      </c>
-      <c r="B178" t="s">
-        <v>766</v>
       </c>
       <c r="D178" t="s">
         <v>41</v>
       </c>
       <c r="E178" t="s">
+        <v>766</v>
+      </c>
+      <c r="F178" t="s">
         <v>767</v>
       </c>
-      <c r="F178" t="s">
+      <c r="J178" t="s">
         <v>768</v>
       </c>
-      <c r="J178" t="s">
+      <c r="K178" t="s">
         <v>769</v>
       </c>
-      <c r="K178" t="s">
+      <c r="L178" s="3" t="s">
         <v>770</v>
       </c>
-      <c r="L178" s="3" t="s">
+      <c r="R178" t="s">
         <v>771</v>
       </c>
-      <c r="R178" t="s">
-        <v>772</v>
-      </c>
       <c r="S178" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="T178" s="1">
         <v>313</v>
@@ -11314,13 +11320,13 @@
     </row>
     <row r="179" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
+        <v>764</v>
+      </c>
+      <c r="B179" t="s">
         <v>765</v>
       </c>
-      <c r="B179" t="s">
-        <v>766</v>
-      </c>
       <c r="D179" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="E179" t="s">
         <v>107</v>
@@ -11332,10 +11338,10 @@
         <v>218</v>
       </c>
       <c r="K179" t="s">
+        <v>773</v>
+      </c>
+      <c r="L179" s="3" t="s">
         <v>774</v>
-      </c>
-      <c r="L179" s="3" t="s">
-        <v>775</v>
       </c>
       <c r="R179" t="s">
         <v>31</v>
@@ -11355,10 +11361,10 @@
     </row>
     <row r="180" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
+        <v>764</v>
+      </c>
+      <c r="B180" t="s">
         <v>765</v>
-      </c>
-      <c r="B180" t="s">
-        <v>766</v>
       </c>
       <c r="D180" t="s">
         <v>282</v>
@@ -11370,13 +11376,13 @@
         <v>313</v>
       </c>
       <c r="J180" t="s">
+        <v>775</v>
+      </c>
+      <c r="K180" t="s">
         <v>776</v>
       </c>
-      <c r="K180" t="s">
+      <c r="L180" s="3" t="s">
         <v>777</v>
-      </c>
-      <c r="L180" s="3" t="s">
-        <v>778</v>
       </c>
       <c r="R180" t="s">
         <v>31</v>
@@ -11396,10 +11402,10 @@
     </row>
     <row r="181" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
+        <v>764</v>
+      </c>
+      <c r="B181" t="s">
         <v>765</v>
-      </c>
-      <c r="B181" t="s">
-        <v>766</v>
       </c>
       <c r="D181" t="s">
         <v>25</v>
@@ -11411,13 +11417,13 @@
         <v>253</v>
       </c>
       <c r="J181" t="s">
+        <v>778</v>
+      </c>
+      <c r="K181" t="s">
         <v>779</v>
       </c>
-      <c r="K181" t="s">
+      <c r="L181" s="3" t="s">
         <v>780</v>
-      </c>
-      <c r="L181" s="3" t="s">
-        <v>781</v>
       </c>
       <c r="R181" t="s">
         <v>31</v>
@@ -11437,22 +11443,22 @@
     </row>
     <row r="182" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
+        <v>781</v>
+      </c>
+      <c r="B182" t="s">
         <v>782</v>
-      </c>
-      <c r="B182" t="s">
-        <v>783</v>
       </c>
       <c r="D182" t="s">
         <v>260</v>
       </c>
       <c r="F182" t="s">
+        <v>783</v>
+      </c>
+      <c r="J182" t="s">
         <v>784</v>
       </c>
-      <c r="J182" t="s">
+      <c r="L182" s="3" t="s">
         <v>785</v>
-      </c>
-      <c r="L182" s="3" t="s">
-        <v>786</v>
       </c>
       <c r="R182" t="s">
         <v>31</v>
@@ -11472,13 +11478,13 @@
     </row>
     <row r="183" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
+        <v>781</v>
+      </c>
+      <c r="B183" t="s">
         <v>782</v>
       </c>
-      <c r="B183" t="s">
-        <v>783</v>
-      </c>
       <c r="D183" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E183" t="s">
         <v>121</v>
@@ -11487,13 +11493,13 @@
         <v>122</v>
       </c>
       <c r="J183" t="s">
+        <v>786</v>
+      </c>
+      <c r="K183" t="s">
+        <v>786</v>
+      </c>
+      <c r="L183" s="3" t="s">
         <v>787</v>
-      </c>
-      <c r="K183" t="s">
-        <v>787</v>
-      </c>
-      <c r="L183" s="3" t="s">
-        <v>788</v>
       </c>
       <c r="R183" t="s">
         <v>31</v>
@@ -11513,13 +11519,13 @@
     </row>
     <row r="184" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
+        <v>781</v>
+      </c>
+      <c r="B184" t="s">
         <v>782</v>
       </c>
-      <c r="B184" t="s">
-        <v>783</v>
-      </c>
       <c r="D184" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="E184" t="s">
         <v>121</v>
@@ -11528,13 +11534,13 @@
         <v>122</v>
       </c>
       <c r="J184" t="s">
+        <v>789</v>
+      </c>
+      <c r="K184" t="s">
+        <v>789</v>
+      </c>
+      <c r="L184" s="3" t="s">
         <v>790</v>
-      </c>
-      <c r="K184" t="s">
-        <v>790</v>
-      </c>
-      <c r="L184" s="3" t="s">
-        <v>791</v>
       </c>
       <c r="R184" t="s">
         <v>31</v>
@@ -11554,25 +11560,25 @@
     </row>
     <row r="185" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
+        <v>791</v>
+      </c>
+      <c r="B185" t="s">
         <v>792</v>
       </c>
-      <c r="B185" t="s">
+      <c r="D185" t="s">
         <v>793</v>
       </c>
-      <c r="D185" t="s">
+      <c r="E185" t="s">
         <v>794</v>
       </c>
-      <c r="E185" t="s">
+      <c r="F185" t="s">
         <v>795</v>
       </c>
-      <c r="F185" t="s">
+      <c r="J185" t="s">
         <v>796</v>
       </c>
-      <c r="J185" t="s">
+      <c r="L185" s="3" t="s">
         <v>797</v>
-      </c>
-      <c r="L185" s="3" t="s">
-        <v>798</v>
       </c>
       <c r="R185" t="s">
         <v>31</v>
@@ -11592,22 +11598,22 @@
     </row>
     <row r="186" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
+        <v>798</v>
+      </c>
+      <c r="B186" t="s">
         <v>799</v>
       </c>
-      <c r="B186" t="s">
-        <v>800</v>
-      </c>
       <c r="D186" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="F186" t="s">
         <v>296</v>
       </c>
       <c r="J186" t="s">
+        <v>800</v>
+      </c>
+      <c r="L186" s="3" t="s">
         <v>801</v>
-      </c>
-      <c r="L186" s="3" t="s">
-        <v>802</v>
       </c>
       <c r="R186" t="s">
         <v>31</v>
@@ -11627,10 +11633,10 @@
     </row>
     <row r="187" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
+        <v>798</v>
+      </c>
+      <c r="B187" t="s">
         <v>799</v>
-      </c>
-      <c r="B187" t="s">
-        <v>800</v>
       </c>
       <c r="D187" t="s">
         <v>55</v>
@@ -11642,13 +11648,13 @@
         <v>122</v>
       </c>
       <c r="J187" t="s">
+        <v>802</v>
+      </c>
+      <c r="K187" t="s">
         <v>803</v>
       </c>
-      <c r="K187" t="s">
+      <c r="L187" s="3" t="s">
         <v>804</v>
-      </c>
-      <c r="L187" s="3" t="s">
-        <v>805</v>
       </c>
       <c r="R187" t="s">
         <v>31</v>
@@ -11668,10 +11674,10 @@
     </row>
     <row r="188" spans="1:23" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="8" t="s">
+        <v>798</v>
+      </c>
+      <c r="B188" s="8" t="s">
         <v>799</v>
-      </c>
-      <c r="B188" s="8" t="s">
-        <v>800</v>
       </c>
       <c r="D188" s="8" t="s">
         <v>125</v>
@@ -11680,16 +11686,16 @@
         <v>411</v>
       </c>
       <c r="F188" s="8" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="J188" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="K188" s="8" t="s">
         <v>806</v>
       </c>
-      <c r="K188" s="8" t="s">
+      <c r="L188" s="9" t="s">
         <v>807</v>
-      </c>
-      <c r="L188" s="9" t="s">
-        <v>808</v>
       </c>
       <c r="R188" s="8" t="s">
         <v>31</v>
@@ -11709,10 +11715,10 @@
     </row>
     <row r="189" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
+        <v>798</v>
+      </c>
+      <c r="B189" t="s">
         <v>799</v>
-      </c>
-      <c r="B189" t="s">
-        <v>800</v>
       </c>
       <c r="D189" t="s">
         <v>365</v>
@@ -11721,16 +11727,16 @@
         <v>403</v>
       </c>
       <c r="F189" t="s">
+        <v>808</v>
+      </c>
+      <c r="J189" t="s">
         <v>809</v>
       </c>
-      <c r="J189" t="s">
+      <c r="K189" t="s">
+        <v>809</v>
+      </c>
+      <c r="L189" s="3" t="s">
         <v>810</v>
-      </c>
-      <c r="K189" t="s">
-        <v>810</v>
-      </c>
-      <c r="L189" s="3" t="s">
-        <v>811</v>
       </c>
       <c r="R189" t="s">
         <v>31</v>
@@ -11750,10 +11756,10 @@
     </row>
     <row r="190" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B190" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D190" t="s">
         <v>222</v>
@@ -11765,22 +11771,22 @@
         <v>390</v>
       </c>
       <c r="J190" t="s">
+        <v>812</v>
+      </c>
+      <c r="L190" s="3" t="s">
         <v>813</v>
       </c>
-      <c r="L190" s="3" t="s">
+      <c r="R190" t="s">
+        <v>31</v>
+      </c>
+      <c r="S190" t="s">
+        <v>32</v>
+      </c>
+      <c r="T190" s="1" t="s">
         <v>814</v>
       </c>
-      <c r="R190" t="s">
-        <v>31</v>
-      </c>
-      <c r="S190" t="s">
-        <v>32</v>
-      </c>
-      <c r="T190" s="1" t="s">
+      <c r="U190" s="1" t="s">
         <v>815</v>
-      </c>
-      <c r="U190" s="1" t="s">
-        <v>816</v>
       </c>
       <c r="W190" s="1">
         <v>3</v>
@@ -11788,22 +11794,22 @@
     </row>
     <row r="191" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B191" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D191" t="s">
         <v>55</v>
       </c>
       <c r="F191" t="s">
+        <v>816</v>
+      </c>
+      <c r="J191" t="s">
         <v>817</v>
       </c>
-      <c r="J191" t="s">
+      <c r="L191" s="3" t="s">
         <v>818</v>
-      </c>
-      <c r="L191" s="3" t="s">
-        <v>819</v>
       </c>
       <c r="R191" t="s">
         <v>31</v>
@@ -11823,28 +11829,28 @@
     </row>
     <row r="192" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B192" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D192" t="s">
         <v>120</v>
       </c>
       <c r="E192" t="s">
+        <v>819</v>
+      </c>
+      <c r="F192" t="s">
         <v>820</v>
       </c>
-      <c r="F192" t="s">
+      <c r="J192" t="s">
         <v>821</v>
       </c>
-      <c r="J192" t="s">
+      <c r="K192" t="s">
         <v>822</v>
       </c>
-      <c r="K192" t="s">
+      <c r="L192" s="3" t="s">
         <v>823</v>
-      </c>
-      <c r="L192" s="3" t="s">
-        <v>824</v>
       </c>
       <c r="R192" t="s">
         <v>31</v>
@@ -11864,25 +11870,25 @@
     </row>
     <row r="193" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B193" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D193" t="s">
         <v>222</v>
       </c>
       <c r="E193" t="s">
+        <v>824</v>
+      </c>
+      <c r="F193" t="s">
         <v>825</v>
       </c>
-      <c r="F193" t="s">
+      <c r="J193" t="s">
         <v>826</v>
       </c>
-      <c r="J193" t="s">
+      <c r="L193" s="3" t="s">
         <v>827</v>
-      </c>
-      <c r="L193" s="3" t="s">
-        <v>828</v>
       </c>
       <c r="R193" t="s">
         <v>31</v>
@@ -11902,25 +11908,25 @@
     </row>
     <row r="194" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
+        <v>828</v>
+      </c>
+      <c r="B194" t="s">
         <v>829</v>
       </c>
-      <c r="B194" t="s">
+      <c r="D194" t="s">
         <v>830</v>
       </c>
-      <c r="D194" t="s">
+      <c r="F194" t="s">
         <v>831</v>
       </c>
-      <c r="F194" t="s">
+      <c r="J194" t="s">
         <v>832</v>
       </c>
-      <c r="J194" t="s">
+      <c r="K194" t="s">
         <v>833</v>
       </c>
-      <c r="K194" t="s">
+      <c r="L194" s="3" t="s">
         <v>834</v>
-      </c>
-      <c r="L194" s="3" t="s">
-        <v>835</v>
       </c>
       <c r="R194" t="s">
         <v>31</v>
@@ -11940,28 +11946,28 @@
     </row>
     <row r="195" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
+        <v>828</v>
+      </c>
+      <c r="B195" t="s">
         <v>829</v>
       </c>
-      <c r="B195" t="s">
-        <v>830</v>
-      </c>
       <c r="D195" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="E195" t="s">
+        <v>835</v>
+      </c>
+      <c r="F195" t="s">
         <v>836</v>
       </c>
-      <c r="F195" t="s">
+      <c r="J195" t="s">
         <v>837</v>
       </c>
-      <c r="J195" t="s">
+      <c r="K195" t="s">
         <v>838</v>
       </c>
-      <c r="K195" t="s">
+      <c r="L195" s="3" t="s">
         <v>839</v>
-      </c>
-      <c r="L195" s="3" t="s">
-        <v>840</v>
       </c>
       <c r="R195" t="s">
         <v>31</v>
@@ -11981,28 +11987,28 @@
     </row>
     <row r="196" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
+        <v>828</v>
+      </c>
+      <c r="B196" t="s">
         <v>829</v>
-      </c>
-      <c r="B196" t="s">
-        <v>830</v>
       </c>
       <c r="D196" t="s">
         <v>90</v>
       </c>
       <c r="E196" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="F196" t="s">
+        <v>840</v>
+      </c>
+      <c r="J196" t="s">
         <v>841</v>
       </c>
-      <c r="J196" t="s">
+      <c r="K196" t="s">
         <v>842</v>
       </c>
-      <c r="K196" t="s">
+      <c r="L196" s="3" t="s">
         <v>843</v>
-      </c>
-      <c r="L196" s="3" t="s">
-        <v>844</v>
       </c>
       <c r="R196" t="s">
         <v>31</v>
@@ -12022,28 +12028,28 @@
     </row>
     <row r="197" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
+        <v>828</v>
+      </c>
+      <c r="B197" t="s">
         <v>829</v>
       </c>
-      <c r="B197" t="s">
-        <v>830</v>
-      </c>
       <c r="D197" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="E197" t="s">
+        <v>844</v>
+      </c>
+      <c r="F197" t="s">
         <v>845</v>
       </c>
-      <c r="F197" t="s">
+      <c r="J197" t="s">
         <v>846</v>
       </c>
-      <c r="J197" t="s">
+      <c r="K197" t="s">
         <v>847</v>
       </c>
-      <c r="K197" t="s">
+      <c r="L197" s="3" t="s">
         <v>848</v>
-      </c>
-      <c r="L197" s="3" t="s">
-        <v>849</v>
       </c>
       <c r="R197" t="s">
         <v>31</v>
@@ -12063,28 +12069,28 @@
     </row>
     <row r="198" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
+        <v>828</v>
+      </c>
+      <c r="B198" t="s">
         <v>829</v>
       </c>
-      <c r="B198" t="s">
-        <v>830</v>
-      </c>
       <c r="D198" t="s">
+        <v>849</v>
+      </c>
+      <c r="E198" t="s">
         <v>850</v>
-      </c>
-      <c r="E198" t="s">
-        <v>851</v>
       </c>
       <c r="F198" t="s">
         <v>68</v>
       </c>
       <c r="J198" t="s">
+        <v>851</v>
+      </c>
+      <c r="K198" t="s">
         <v>852</v>
       </c>
-      <c r="K198" t="s">
+      <c r="L198" s="3" t="s">
         <v>853</v>
-      </c>
-      <c r="L198" s="3" t="s">
-        <v>854</v>
       </c>
       <c r="R198" t="s">
         <v>31</v>
@@ -12104,25 +12110,25 @@
     </row>
     <row r="199" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B199" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="D199" t="s">
         <v>138</v>
       </c>
       <c r="E199" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="F199" t="s">
         <v>253</v>
       </c>
       <c r="J199" t="s">
+        <v>856</v>
+      </c>
+      <c r="L199" s="3" t="s">
         <v>857</v>
-      </c>
-      <c r="L199" s="3" t="s">
-        <v>858</v>
       </c>
       <c r="R199" t="s">
         <v>31</v>
@@ -12142,13 +12148,13 @@
     </row>
     <row r="200" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B200" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="D200" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="E200" t="s">
         <v>121</v>
@@ -12157,19 +12163,19 @@
         <v>122</v>
       </c>
       <c r="J200" t="s">
+        <v>859</v>
+      </c>
+      <c r="K200" t="s">
         <v>860</v>
       </c>
-      <c r="K200" t="s">
+      <c r="L200" s="2" t="s">
         <v>861</v>
       </c>
-      <c r="L200" s="2" t="s">
+      <c r="R200" t="s">
+        <v>31</v>
+      </c>
+      <c r="S200" t="s">
         <v>862</v>
-      </c>
-      <c r="R200" t="s">
-        <v>31</v>
-      </c>
-      <c r="S200" t="s">
-        <v>863</v>
       </c>
       <c r="T200" s="1">
         <v>47</v>
@@ -12183,13 +12189,13 @@
     </row>
     <row r="201" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B201" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="D201" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E201" t="s">
         <v>74</v>
@@ -12198,13 +12204,13 @@
         <v>75</v>
       </c>
       <c r="J201" t="s">
+        <v>863</v>
+      </c>
+      <c r="K201" t="s">
         <v>864</v>
       </c>
-      <c r="K201" t="s">
+      <c r="L201" s="3" t="s">
         <v>865</v>
-      </c>
-      <c r="L201" s="3" t="s">
-        <v>866</v>
       </c>
       <c r="R201" t="s">
         <v>31</v>
@@ -12224,13 +12230,13 @@
     </row>
     <row r="202" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B202" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="D202" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="E202" t="s">
         <v>121</v>
@@ -12239,13 +12245,13 @@
         <v>122</v>
       </c>
       <c r="J202" t="s">
+        <v>866</v>
+      </c>
+      <c r="K202" t="s">
+        <v>866</v>
+      </c>
+      <c r="L202" s="3" t="s">
         <v>867</v>
-      </c>
-      <c r="K202" t="s">
-        <v>867</v>
-      </c>
-      <c r="L202" s="3" t="s">
-        <v>868</v>
       </c>
       <c r="R202" t="s">
         <v>31</v>
@@ -12268,22 +12274,22 @@
         <v>478</v>
       </c>
       <c r="B203" t="s">
+        <v>868</v>
+      </c>
+      <c r="D203" t="s">
         <v>869</v>
       </c>
-      <c r="D203" t="s">
+      <c r="E203" t="s">
         <v>870</v>
       </c>
-      <c r="E203" t="s">
+      <c r="F203" t="s">
         <v>871</v>
       </c>
-      <c r="F203" t="s">
+      <c r="J203" t="s">
         <v>872</v>
       </c>
-      <c r="J203" t="s">
+      <c r="L203" s="3" t="s">
         <v>873</v>
-      </c>
-      <c r="L203" s="3" t="s">
-        <v>874</v>
       </c>
       <c r="R203" t="s">
         <v>31</v>
@@ -12306,25 +12312,25 @@
         <v>478</v>
       </c>
       <c r="B204" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="D204" t="s">
         <v>90</v>
       </c>
       <c r="E204" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="F204" t="s">
+        <v>874</v>
+      </c>
+      <c r="J204" t="s">
         <v>875</v>
       </c>
-      <c r="J204" t="s">
+      <c r="K204" t="s">
         <v>876</v>
       </c>
-      <c r="K204" t="s">
+      <c r="L204" s="3" t="s">
         <v>877</v>
-      </c>
-      <c r="L204" s="3" t="s">
-        <v>878</v>
       </c>
       <c r="R204" t="s">
         <v>31</v>
@@ -12347,7 +12353,7 @@
         <v>478</v>
       </c>
       <c r="B205" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="D205" t="s">
         <v>300</v>
@@ -12359,13 +12365,13 @@
         <v>122</v>
       </c>
       <c r="J205" t="s">
+        <v>878</v>
+      </c>
+      <c r="K205" t="s">
         <v>879</v>
       </c>
-      <c r="K205" t="s">
+      <c r="L205" s="3" t="s">
         <v>880</v>
-      </c>
-      <c r="L205" s="3" t="s">
-        <v>881</v>
       </c>
       <c r="R205" t="s">
         <v>31</v>
@@ -12388,10 +12394,10 @@
         <v>478</v>
       </c>
       <c r="B206" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="D206" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="E206" t="s">
         <v>129</v>
@@ -12400,10 +12406,10 @@
         <v>130</v>
       </c>
       <c r="J206" t="s">
+        <v>882</v>
+      </c>
+      <c r="L206" s="3" t="s">
         <v>883</v>
-      </c>
-      <c r="L206" s="3" t="s">
-        <v>884</v>
       </c>
       <c r="R206" t="s">
         <v>31</v>
@@ -12423,28 +12429,28 @@
     </row>
     <row r="207" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
+        <v>884</v>
+      </c>
+      <c r="B207" t="s">
         <v>885</v>
       </c>
-      <c r="B207" t="s">
+      <c r="D207" t="s">
         <v>886</v>
-      </c>
-      <c r="D207" t="s">
-        <v>887</v>
       </c>
       <c r="E207" t="s">
         <v>193</v>
       </c>
       <c r="F207" t="s">
+        <v>887</v>
+      </c>
+      <c r="J207" t="s">
         <v>888</v>
       </c>
-      <c r="J207" t="s">
+      <c r="K207" t="s">
         <v>889</v>
       </c>
-      <c r="K207" t="s">
+      <c r="L207" s="3" t="s">
         <v>890</v>
-      </c>
-      <c r="L207" s="3" t="s">
-        <v>891</v>
       </c>
       <c r="R207" t="s">
         <v>31</v>
@@ -12464,28 +12470,28 @@
     </row>
     <row r="208" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
+        <v>884</v>
+      </c>
+      <c r="B208" t="s">
         <v>885</v>
       </c>
-      <c r="B208" t="s">
-        <v>886</v>
-      </c>
       <c r="D208" t="s">
+        <v>891</v>
+      </c>
+      <c r="E208" t="s">
+        <v>870</v>
+      </c>
+      <c r="F208" t="s">
         <v>892</v>
       </c>
-      <c r="E208" t="s">
-        <v>871</v>
-      </c>
-      <c r="F208" t="s">
+      <c r="J208" t="s">
         <v>893</v>
       </c>
-      <c r="J208" t="s">
+      <c r="K208" t="s">
         <v>894</v>
       </c>
-      <c r="K208" t="s">
+      <c r="L208" s="3" t="s">
         <v>895</v>
-      </c>
-      <c r="L208" s="3" t="s">
-        <v>896</v>
       </c>
       <c r="R208" t="s">
         <v>31</v>
@@ -12505,28 +12511,28 @@
     </row>
     <row r="209" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
+        <v>884</v>
+      </c>
+      <c r="B209" t="s">
         <v>885</v>
       </c>
-      <c r="B209" t="s">
-        <v>886</v>
-      </c>
       <c r="D209" t="s">
+        <v>896</v>
+      </c>
+      <c r="E209" t="s">
+        <v>870</v>
+      </c>
+      <c r="F209" t="s">
+        <v>871</v>
+      </c>
+      <c r="J209" t="s">
         <v>897</v>
       </c>
-      <c r="E209" t="s">
-        <v>871</v>
-      </c>
-      <c r="F209" t="s">
-        <v>872</v>
-      </c>
-      <c r="J209" t="s">
+      <c r="K209" t="s">
         <v>898</v>
       </c>
-      <c r="K209" t="s">
+      <c r="L209" s="3" t="s">
         <v>899</v>
-      </c>
-      <c r="L209" s="3" t="s">
-        <v>900</v>
       </c>
       <c r="R209" t="s">
         <v>31</v>
@@ -12546,28 +12552,28 @@
     </row>
     <row r="210" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
+        <v>884</v>
+      </c>
+      <c r="B210" t="s">
         <v>885</v>
       </c>
-      <c r="B210" t="s">
-        <v>886</v>
-      </c>
       <c r="D210" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="E210" t="s">
+        <v>870</v>
+      </c>
+      <c r="F210" t="s">
         <v>871</v>
       </c>
-      <c r="F210" t="s">
-        <v>872</v>
-      </c>
       <c r="J210" t="s">
+        <v>900</v>
+      </c>
+      <c r="K210" t="s">
         <v>901</v>
       </c>
-      <c r="K210" t="s">
+      <c r="L210" s="3" t="s">
         <v>902</v>
-      </c>
-      <c r="L210" s="3" t="s">
-        <v>903</v>
       </c>
       <c r="R210" t="s">
         <v>31</v>
@@ -12587,28 +12593,28 @@
     </row>
     <row r="211" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
+        <v>903</v>
+      </c>
+      <c r="B211" t="s">
         <v>904</v>
-      </c>
-      <c r="B211" t="s">
-        <v>905</v>
       </c>
       <c r="D211" t="s">
         <v>165</v>
       </c>
       <c r="E211" t="s">
+        <v>905</v>
+      </c>
+      <c r="F211" t="s">
         <v>906</v>
       </c>
-      <c r="F211" t="s">
+      <c r="J211" t="s">
         <v>907</v>
       </c>
-      <c r="J211" t="s">
+      <c r="K211" t="s">
         <v>908</v>
       </c>
-      <c r="K211" t="s">
+      <c r="L211" s="3" t="s">
         <v>909</v>
-      </c>
-      <c r="L211" s="3" t="s">
-        <v>910</v>
       </c>
       <c r="R211" t="s">
         <v>31</v>
@@ -12628,13 +12634,13 @@
     </row>
     <row r="212" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
+        <v>903</v>
+      </c>
+      <c r="B212" t="s">
         <v>904</v>
       </c>
-      <c r="B212" t="s">
-        <v>905</v>
-      </c>
       <c r="D212" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="E212" t="s">
         <v>121</v>
@@ -12643,10 +12649,10 @@
         <v>122</v>
       </c>
       <c r="J212" t="s">
+        <v>911</v>
+      </c>
+      <c r="L212" s="3" t="s">
         <v>912</v>
-      </c>
-      <c r="L212" s="3" t="s">
-        <v>913</v>
       </c>
       <c r="R212" t="s">
         <v>31</v>
@@ -12666,13 +12672,13 @@
     </row>
     <row r="213" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
+        <v>903</v>
+      </c>
+      <c r="B213" t="s">
         <v>904</v>
       </c>
-      <c r="B213" t="s">
-        <v>905</v>
-      </c>
       <c r="D213" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="E213" t="s">
         <v>74</v>
@@ -12681,13 +12687,13 @@
         <v>75</v>
       </c>
       <c r="J213" t="s">
+        <v>913</v>
+      </c>
+      <c r="K213" t="s">
         <v>914</v>
       </c>
-      <c r="K213" t="s">
+      <c r="L213" s="3" t="s">
         <v>915</v>
-      </c>
-      <c r="L213" s="3" t="s">
-        <v>916</v>
       </c>
       <c r="R213" t="s">
         <v>31</v>
@@ -12707,13 +12713,13 @@
     </row>
     <row r="214" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
+        <v>903</v>
+      </c>
+      <c r="B214" t="s">
         <v>904</v>
       </c>
-      <c r="B214" t="s">
-        <v>905</v>
-      </c>
       <c r="D214" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="E214" t="s">
         <v>107</v>
@@ -12722,13 +12728,13 @@
         <v>253</v>
       </c>
       <c r="J214" t="s">
+        <v>917</v>
+      </c>
+      <c r="K214" t="s">
         <v>918</v>
       </c>
-      <c r="K214" t="s">
+      <c r="L214" s="3" t="s">
         <v>919</v>
-      </c>
-      <c r="L214" s="3" t="s">
-        <v>920</v>
       </c>
       <c r="R214" t="s">
         <v>31</v>
@@ -12748,22 +12754,22 @@
     </row>
     <row r="215" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
+        <v>920</v>
+      </c>
+      <c r="B215" t="s">
         <v>921</v>
       </c>
-      <c r="B215" t="s">
+      <c r="D215" t="s">
         <v>922</v>
-      </c>
-      <c r="D215" t="s">
-        <v>923</v>
       </c>
       <c r="F215" t="s">
         <v>296</v>
       </c>
       <c r="J215" t="s">
+        <v>923</v>
+      </c>
+      <c r="L215" s="3" t="s">
         <v>924</v>
-      </c>
-      <c r="L215" s="3" t="s">
-        <v>925</v>
       </c>
       <c r="R215" t="s">
         <v>31</v>
@@ -12783,28 +12789,28 @@
     </row>
     <row r="216" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
+        <v>920</v>
+      </c>
+      <c r="B216" t="s">
         <v>921</v>
       </c>
-      <c r="B216" t="s">
-        <v>922</v>
-      </c>
       <c r="D216" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="E216" t="s">
         <v>403</v>
       </c>
       <c r="F216" t="s">
+        <v>926</v>
+      </c>
+      <c r="J216" t="s">
         <v>927</v>
       </c>
-      <c r="J216" t="s">
+      <c r="K216" t="s">
+        <v>927</v>
+      </c>
+      <c r="L216" s="3" t="s">
         <v>928</v>
-      </c>
-      <c r="K216" t="s">
-        <v>928</v>
-      </c>
-      <c r="L216" s="3" t="s">
-        <v>929</v>
       </c>
       <c r="R216" t="s">
         <v>31</v>
@@ -12824,13 +12830,13 @@
     </row>
     <row r="217" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
+        <v>920</v>
+      </c>
+      <c r="B217" t="s">
         <v>921</v>
       </c>
-      <c r="B217" t="s">
-        <v>922</v>
-      </c>
       <c r="D217" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="E217" t="s">
         <v>121</v>
@@ -12839,13 +12845,13 @@
         <v>122</v>
       </c>
       <c r="J217" t="s">
+        <v>930</v>
+      </c>
+      <c r="K217" t="s">
         <v>931</v>
       </c>
-      <c r="K217" t="s">
+      <c r="L217" s="3" t="s">
         <v>932</v>
-      </c>
-      <c r="L217" s="3" t="s">
-        <v>933</v>
       </c>
       <c r="R217" t="s">
         <v>31</v>
@@ -12865,10 +12871,10 @@
     </row>
     <row r="218" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
+        <v>920</v>
+      </c>
+      <c r="B218" t="s">
         <v>921</v>
-      </c>
-      <c r="B218" t="s">
-        <v>922</v>
       </c>
       <c r="D218" t="s">
         <v>237</v>
@@ -12880,13 +12886,13 @@
         <v>122</v>
       </c>
       <c r="J218" t="s">
+        <v>933</v>
+      </c>
+      <c r="K218" t="s">
+        <v>933</v>
+      </c>
+      <c r="L218" s="3" t="s">
         <v>934</v>
-      </c>
-      <c r="K218" t="s">
-        <v>934</v>
-      </c>
-      <c r="L218" s="3" t="s">
-        <v>935</v>
       </c>
       <c r="R218" t="s">
         <v>31</v>
@@ -12906,13 +12912,13 @@
     </row>
     <row r="219" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
+        <v>935</v>
+      </c>
+      <c r="B219" t="s">
         <v>936</v>
       </c>
-      <c r="B219" t="s">
+      <c r="D219" t="s">
         <v>937</v>
-      </c>
-      <c r="D219" t="s">
-        <v>938</v>
       </c>
       <c r="E219" t="s">
         <v>121</v>
@@ -12921,10 +12927,10 @@
         <v>122</v>
       </c>
       <c r="J219" t="s">
+        <v>938</v>
+      </c>
+      <c r="L219" s="3" t="s">
         <v>939</v>
-      </c>
-      <c r="L219" s="3" t="s">
-        <v>940</v>
       </c>
       <c r="R219" t="s">
         <v>31</v>
@@ -12944,13 +12950,13 @@
     </row>
     <row r="220" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
+        <v>935</v>
+      </c>
+      <c r="B220" t="s">
         <v>936</v>
       </c>
-      <c r="B220" t="s">
+      <c r="D220" t="s">
         <v>937</v>
-      </c>
-      <c r="D220" t="s">
-        <v>938</v>
       </c>
       <c r="E220" t="s">
         <v>121</v>
@@ -12959,13 +12965,13 @@
         <v>122</v>
       </c>
       <c r="J220" t="s">
+        <v>940</v>
+      </c>
+      <c r="K220" t="s">
+        <v>940</v>
+      </c>
+      <c r="L220" s="3" t="s">
         <v>941</v>
-      </c>
-      <c r="K220" t="s">
-        <v>941</v>
-      </c>
-      <c r="L220" s="3" t="s">
-        <v>942</v>
       </c>
       <c r="R220" t="s">
         <v>31</v>
@@ -12985,13 +12991,13 @@
     </row>
     <row r="221" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
+        <v>935</v>
+      </c>
+      <c r="B221" t="s">
         <v>936</v>
       </c>
-      <c r="B221" t="s">
-        <v>937</v>
-      </c>
       <c r="D221" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="E221" t="s">
         <v>48</v>
@@ -13000,13 +13006,13 @@
         <v>49</v>
       </c>
       <c r="J221" t="s">
+        <v>943</v>
+      </c>
+      <c r="K221" t="s">
         <v>944</v>
       </c>
-      <c r="K221" t="s">
+      <c r="L221" s="3" t="s">
         <v>945</v>
-      </c>
-      <c r="L221" s="3" t="s">
-        <v>946</v>
       </c>
       <c r="R221" t="s">
         <v>31</v>
@@ -13026,28 +13032,28 @@
     </row>
     <row r="222" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
+        <v>935</v>
+      </c>
+      <c r="B222" t="s">
         <v>936</v>
       </c>
-      <c r="B222" t="s">
-        <v>937</v>
-      </c>
       <c r="D222" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="E222" t="s">
         <v>42</v>
       </c>
       <c r="F222" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="J222" t="s">
+        <v>947</v>
+      </c>
+      <c r="K222" t="s">
         <v>948</v>
       </c>
-      <c r="K222" t="s">
+      <c r="L222" s="3" t="s">
         <v>949</v>
-      </c>
-      <c r="L222" s="3" t="s">
-        <v>950</v>
       </c>
       <c r="R222" t="s">
         <v>31</v>
@@ -13067,13 +13073,13 @@
     </row>
     <row r="223" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
+        <v>935</v>
+      </c>
+      <c r="B223" t="s">
         <v>936</v>
       </c>
-      <c r="B223" t="s">
-        <v>937</v>
-      </c>
       <c r="D223" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="E223" t="s">
         <v>121</v>
@@ -13082,13 +13088,13 @@
         <v>122</v>
       </c>
       <c r="J223" t="s">
+        <v>951</v>
+      </c>
+      <c r="K223" t="s">
+        <v>951</v>
+      </c>
+      <c r="L223" s="3" t="s">
         <v>952</v>
-      </c>
-      <c r="K223" t="s">
-        <v>952</v>
-      </c>
-      <c r="L223" s="3" t="s">
-        <v>953</v>
       </c>
       <c r="R223" t="s">
         <v>31</v>
@@ -13108,13 +13114,13 @@
     </row>
     <row r="224" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
+        <v>935</v>
+      </c>
+      <c r="B224" t="s">
         <v>936</v>
       </c>
-      <c r="B224" t="s">
-        <v>937</v>
-      </c>
       <c r="D224" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="E224" t="s">
         <v>121</v>
@@ -13123,13 +13129,13 @@
         <v>122</v>
       </c>
       <c r="J224" t="s">
+        <v>954</v>
+      </c>
+      <c r="K224" t="s">
+        <v>954</v>
+      </c>
+      <c r="L224" s="3" t="s">
         <v>955</v>
-      </c>
-      <c r="K224" t="s">
-        <v>955</v>
-      </c>
-      <c r="L224" s="3" t="s">
-        <v>956</v>
       </c>
       <c r="R224" t="s">
         <v>31</v>
@@ -13149,13 +13155,13 @@
     </row>
     <row r="225" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
+        <v>935</v>
+      </c>
+      <c r="B225" t="s">
         <v>936</v>
       </c>
-      <c r="B225" t="s">
-        <v>937</v>
-      </c>
       <c r="D225" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="E225" t="s">
         <v>121</v>
@@ -13164,13 +13170,13 @@
         <v>122</v>
       </c>
       <c r="J225" t="s">
+        <v>956</v>
+      </c>
+      <c r="K225" t="s">
+        <v>956</v>
+      </c>
+      <c r="L225" s="3" t="s">
         <v>957</v>
-      </c>
-      <c r="K225" t="s">
-        <v>957</v>
-      </c>
-      <c r="L225" s="3" t="s">
-        <v>958</v>
       </c>
       <c r="R225" t="s">
         <v>31</v>
@@ -13190,25 +13196,25 @@
     </row>
     <row r="226" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
+        <v>935</v>
+      </c>
+      <c r="B226" t="s">
         <v>936</v>
-      </c>
-      <c r="B226" t="s">
-        <v>937</v>
       </c>
       <c r="D226">
         <v>1780</v>
       </c>
       <c r="F226" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="J226" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="K226" t="s">
+        <v>958</v>
+      </c>
+      <c r="L226" s="3" t="s">
         <v>959</v>
-      </c>
-      <c r="L226" s="3" t="s">
-        <v>960</v>
       </c>
       <c r="R226" t="s">
         <v>31</v>
@@ -13228,13 +13234,13 @@
     </row>
     <row r="227" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
+        <v>960</v>
+      </c>
+      <c r="B227" t="s">
         <v>961</v>
       </c>
-      <c r="B227" t="s">
+      <c r="D227" t="s">
         <v>962</v>
-      </c>
-      <c r="D227" t="s">
-        <v>963</v>
       </c>
       <c r="E227" t="s">
         <v>102</v>
@@ -13243,13 +13249,13 @@
         <v>103</v>
       </c>
       <c r="J227" t="s">
+        <v>963</v>
+      </c>
+      <c r="K227" t="s">
         <v>964</v>
       </c>
-      <c r="K227" t="s">
+      <c r="L227" s="3" t="s">
         <v>965</v>
-      </c>
-      <c r="L227" s="3" t="s">
-        <v>966</v>
       </c>
       <c r="R227" t="s">
         <v>31</v>
@@ -13269,13 +13275,13 @@
     </row>
     <row r="228" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
+        <v>960</v>
+      </c>
+      <c r="B228" t="s">
         <v>961</v>
       </c>
-      <c r="B228" t="s">
-        <v>962</v>
-      </c>
       <c r="D228" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="E228" t="s">
         <v>102</v>
@@ -13284,13 +13290,13 @@
         <v>103</v>
       </c>
       <c r="J228" t="s">
+        <v>966</v>
+      </c>
+      <c r="K228" t="s">
         <v>967</v>
       </c>
-      <c r="K228" t="s">
+      <c r="L228" s="3" t="s">
         <v>968</v>
-      </c>
-      <c r="L228" s="3" t="s">
-        <v>969</v>
       </c>
       <c r="R228" t="s">
         <v>31</v>
@@ -13310,10 +13316,10 @@
     </row>
     <row r="229" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
+        <v>960</v>
+      </c>
+      <c r="B229" t="s">
         <v>961</v>
-      </c>
-      <c r="B229" t="s">
-        <v>962</v>
       </c>
       <c r="D229" t="s">
         <v>402</v>
@@ -13325,13 +13331,13 @@
         <v>103</v>
       </c>
       <c r="J229" t="s">
+        <v>969</v>
+      </c>
+      <c r="K229" t="s">
         <v>970</v>
       </c>
-      <c r="K229" t="s">
+      <c r="L229" s="3" t="s">
         <v>971</v>
-      </c>
-      <c r="L229" s="3" t="s">
-        <v>972</v>
       </c>
       <c r="R229" t="s">
         <v>31</v>
@@ -13351,10 +13357,10 @@
     </row>
     <row r="230" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
+        <v>960</v>
+      </c>
+      <c r="B230" t="s">
         <v>961</v>
-      </c>
-      <c r="B230" t="s">
-        <v>962</v>
       </c>
       <c r="D230" t="s">
         <v>243</v>
@@ -13366,13 +13372,13 @@
         <v>103</v>
       </c>
       <c r="J230" t="s">
+        <v>972</v>
+      </c>
+      <c r="K230" t="s">
         <v>973</v>
       </c>
-      <c r="K230" t="s">
+      <c r="L230" s="3" t="s">
         <v>974</v>
-      </c>
-      <c r="L230" s="3" t="s">
-        <v>975</v>
       </c>
       <c r="R230" t="s">
         <v>31</v>
@@ -13392,10 +13398,10 @@
     </row>
     <row r="231" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
+        <v>975</v>
+      </c>
+      <c r="B231" t="s">
         <v>976</v>
-      </c>
-      <c r="B231" t="s">
-        <v>977</v>
       </c>
       <c r="D231" t="s">
         <v>278</v>
@@ -13407,13 +13413,13 @@
         <v>140</v>
       </c>
       <c r="J231" t="s">
+        <v>977</v>
+      </c>
+      <c r="K231" t="s">
         <v>978</v>
       </c>
-      <c r="K231" t="s">
+      <c r="L231" s="3" t="s">
         <v>979</v>
-      </c>
-      <c r="L231" s="3" t="s">
-        <v>980</v>
       </c>
       <c r="R231" t="s">
         <v>31</v>
@@ -13433,28 +13439,28 @@
     </row>
     <row r="232" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
+        <v>975</v>
+      </c>
+      <c r="B232" t="s">
         <v>976</v>
       </c>
-      <c r="B232" t="s">
-        <v>977</v>
-      </c>
       <c r="D232" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E232" t="s">
         <v>121</v>
       </c>
       <c r="F232" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="J232" t="s">
         <v>218</v>
       </c>
       <c r="K232" t="s">
+        <v>981</v>
+      </c>
+      <c r="L232" s="3" t="s">
         <v>982</v>
-      </c>
-      <c r="L232" s="3" t="s">
-        <v>983</v>
       </c>
       <c r="R232" t="s">
         <v>31</v>
@@ -13474,28 +13480,28 @@
     </row>
     <row r="233" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
+        <v>975</v>
+      </c>
+      <c r="B233" t="s">
         <v>976</v>
       </c>
-      <c r="B233" t="s">
-        <v>977</v>
-      </c>
       <c r="D233" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="E233" t="s">
+        <v>983</v>
+      </c>
+      <c r="F233" t="s">
         <v>984</v>
       </c>
-      <c r="F233" t="s">
+      <c r="J233" t="s">
         <v>985</v>
       </c>
-      <c r="J233" t="s">
+      <c r="K233" t="s">
         <v>986</v>
       </c>
-      <c r="K233" t="s">
+      <c r="L233" s="3" t="s">
         <v>987</v>
-      </c>
-      <c r="L233" s="3" t="s">
-        <v>988</v>
       </c>
       <c r="R233" t="s">
         <v>31</v>
@@ -13515,28 +13521,28 @@
     </row>
     <row r="234" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
+        <v>975</v>
+      </c>
+      <c r="B234" t="s">
         <v>976</v>
-      </c>
-      <c r="B234" t="s">
-        <v>977</v>
       </c>
       <c r="D234" t="s">
         <v>402</v>
       </c>
       <c r="E234" t="s">
+        <v>988</v>
+      </c>
+      <c r="F234" t="s">
         <v>989</v>
       </c>
-      <c r="F234" t="s">
+      <c r="J234" t="s">
         <v>990</v>
       </c>
-      <c r="J234" t="s">
+      <c r="K234" t="s">
         <v>991</v>
       </c>
-      <c r="K234" t="s">
+      <c r="L234" s="3" t="s">
         <v>992</v>
-      </c>
-      <c r="L234" s="3" t="s">
-        <v>993</v>
       </c>
       <c r="R234" t="s">
         <v>31</v>
@@ -13556,28 +13562,28 @@
     </row>
     <row r="235" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
+        <v>993</v>
+      </c>
+      <c r="B235" t="s">
         <v>994</v>
       </c>
-      <c r="B235" t="s">
-        <v>995</v>
-      </c>
       <c r="D235" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="E235" t="s">
         <v>129</v>
       </c>
       <c r="F235" t="s">
+        <v>995</v>
+      </c>
+      <c r="J235" t="s">
         <v>996</v>
       </c>
-      <c r="J235" t="s">
+      <c r="K235" t="s">
         <v>997</v>
       </c>
-      <c r="K235" t="s">
+      <c r="L235" s="3" t="s">
         <v>998</v>
-      </c>
-      <c r="L235" s="3" t="s">
-        <v>999</v>
       </c>
       <c r="R235" t="s">
         <v>31</v>
@@ -13597,13 +13603,13 @@
     </row>
     <row r="236" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
+        <v>993</v>
+      </c>
+      <c r="B236" t="s">
         <v>994</v>
       </c>
-      <c r="B236" t="s">
-        <v>995</v>
-      </c>
       <c r="D236" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E236" t="s">
         <v>129</v>
@@ -13612,13 +13618,13 @@
         <v>130</v>
       </c>
       <c r="J236" t="s">
+        <v>999</v>
+      </c>
+      <c r="K236" t="s">
         <v>1000</v>
       </c>
-      <c r="K236" t="s">
+      <c r="L236" s="3" t="s">
         <v>1001</v>
-      </c>
-      <c r="L236" s="3" t="s">
-        <v>1002</v>
       </c>
       <c r="R236" t="s">
         <v>31</v>
@@ -13638,28 +13644,28 @@
     </row>
     <row r="237" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
+        <v>993</v>
+      </c>
+      <c r="B237" t="s">
         <v>994</v>
       </c>
-      <c r="B237" t="s">
-        <v>995</v>
-      </c>
       <c r="D237" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="E237" t="s">
+        <v>1002</v>
+      </c>
+      <c r="F237" t="s">
         <v>1003</v>
       </c>
-      <c r="F237" t="s">
+      <c r="J237" t="s">
         <v>1004</v>
       </c>
-      <c r="J237" t="s">
+      <c r="K237" t="s">
         <v>1005</v>
       </c>
-      <c r="K237" t="s">
+      <c r="L237" s="3" t="s">
         <v>1006</v>
-      </c>
-      <c r="L237" s="3" t="s">
-        <v>1007</v>
       </c>
       <c r="R237" t="s">
         <v>31</v>
@@ -13679,28 +13685,28 @@
     </row>
     <row r="238" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
+        <v>993</v>
+      </c>
+      <c r="B238" t="s">
         <v>994</v>
       </c>
-      <c r="B238" t="s">
-        <v>995</v>
-      </c>
       <c r="D238" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="E238" t="s">
         <v>42</v>
       </c>
       <c r="F238" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="J238" t="s">
+        <v>1008</v>
+      </c>
+      <c r="K238" t="s">
         <v>1009</v>
       </c>
-      <c r="K238" t="s">
+      <c r="L238" s="3" t="s">
         <v>1010</v>
-      </c>
-      <c r="L238" s="3" t="s">
-        <v>1011</v>
       </c>
       <c r="R238" t="s">
         <v>31</v>
@@ -13720,13 +13726,13 @@
     </row>
     <row r="239" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B239" t="s">
         <v>1012</v>
       </c>
-      <c r="B239" t="s">
-        <v>1013</v>
-      </c>
       <c r="D239" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E239" t="s">
         <v>74</v>
@@ -13735,10 +13741,10 @@
         <v>75</v>
       </c>
       <c r="J239" t="s">
+        <v>1013</v>
+      </c>
+      <c r="L239" s="3" t="s">
         <v>1014</v>
-      </c>
-      <c r="L239" s="3" t="s">
-        <v>1015</v>
       </c>
       <c r="R239" t="s">
         <v>31</v>
@@ -13758,28 +13764,28 @@
     </row>
     <row r="240" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B240" t="s">
         <v>1012</v>
       </c>
-      <c r="B240" t="s">
-        <v>1013</v>
-      </c>
       <c r="D240" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E240" t="s">
+        <v>1015</v>
+      </c>
+      <c r="F240" t="s">
         <v>1016</v>
       </c>
-      <c r="F240" t="s">
+      <c r="J240" t="s">
         <v>1017</v>
       </c>
-      <c r="J240" t="s">
+      <c r="K240" t="s">
         <v>1018</v>
       </c>
-      <c r="K240" t="s">
+      <c r="L240" s="3" t="s">
         <v>1019</v>
-      </c>
-      <c r="L240" s="3" t="s">
-        <v>1020</v>
       </c>
       <c r="R240" t="s">
         <v>31</v>
@@ -13799,28 +13805,28 @@
     </row>
     <row r="241" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B241" t="s">
         <v>1012</v>
       </c>
-      <c r="B241" t="s">
-        <v>1013</v>
-      </c>
       <c r="D241" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E241" t="s">
+        <v>1015</v>
+      </c>
+      <c r="F241" t="s">
         <v>1016</v>
       </c>
-      <c r="F241" t="s">
-        <v>1017</v>
-      </c>
       <c r="J241" t="s">
+        <v>1020</v>
+      </c>
+      <c r="K241" t="s">
         <v>1021</v>
       </c>
-      <c r="K241" t="s">
+      <c r="L241" s="3" t="s">
         <v>1022</v>
-      </c>
-      <c r="L241" s="3" t="s">
-        <v>1023</v>
       </c>
       <c r="R241" t="s">
         <v>31</v>
@@ -13840,13 +13846,13 @@
     </row>
     <row r="242" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B242" t="s">
         <v>1012</v>
       </c>
-      <c r="B242" t="s">
-        <v>1013</v>
-      </c>
       <c r="D242" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E242" t="s">
         <v>74</v>
@@ -13855,13 +13861,13 @@
         <v>91</v>
       </c>
       <c r="J242" t="s">
+        <v>1023</v>
+      </c>
+      <c r="K242" t="s">
         <v>1024</v>
       </c>
-      <c r="K242" t="s">
+      <c r="L242" s="3" t="s">
         <v>1025</v>
-      </c>
-      <c r="L242" s="3" t="s">
-        <v>1026</v>
       </c>
       <c r="R242" t="s">
         <v>31</v>
@@ -13881,28 +13887,28 @@
     </row>
     <row r="243" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B243" t="s">
         <v>1027</v>
       </c>
-      <c r="B243" t="s">
+      <c r="D243" t="s">
         <v>1028</v>
       </c>
-      <c r="D243" t="s">
+      <c r="E243" t="s">
         <v>1029</v>
       </c>
-      <c r="E243" t="s">
+      <c r="F243" t="s">
         <v>1030</v>
       </c>
-      <c r="F243" t="s">
+      <c r="J243" t="s">
         <v>1031</v>
       </c>
-      <c r="J243" t="s">
+      <c r="K243" t="s">
         <v>1032</v>
       </c>
-      <c r="K243" t="s">
+      <c r="L243" s="3" t="s">
         <v>1033</v>
-      </c>
-      <c r="L243" s="3" t="s">
-        <v>1034</v>
       </c>
       <c r="R243" t="s">
         <v>31</v>
@@ -13922,13 +13928,13 @@
     </row>
     <row r="244" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B244" t="s">
         <v>1027</v>
       </c>
-      <c r="B244" t="s">
-        <v>1028</v>
-      </c>
       <c r="D244" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="E244" t="s">
         <v>312</v>
@@ -13937,13 +13943,13 @@
         <v>313</v>
       </c>
       <c r="J244" t="s">
+        <v>1035</v>
+      </c>
+      <c r="K244" t="s">
         <v>1036</v>
       </c>
-      <c r="K244" t="s">
+      <c r="L244" s="3" t="s">
         <v>1037</v>
-      </c>
-      <c r="L244" s="3" t="s">
-        <v>1038</v>
       </c>
       <c r="R244" t="s">
         <v>31</v>
@@ -13963,13 +13969,13 @@
     </row>
     <row r="245" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B245" t="s">
         <v>1027</v>
       </c>
-      <c r="B245" t="s">
-        <v>1028</v>
-      </c>
       <c r="D245" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="E245" t="s">
         <v>42</v>
@@ -13978,16 +13984,16 @@
         <v>43</v>
       </c>
       <c r="J245" t="s">
+        <v>1039</v>
+      </c>
+      <c r="K245" t="s">
         <v>1040</v>
       </c>
-      <c r="K245" t="s">
+      <c r="L245" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="L245" s="3" t="s">
+      <c r="M245" t="s">
         <v>1042</v>
-      </c>
-      <c r="M245" t="s">
-        <v>1043</v>
       </c>
       <c r="R245" t="s">
         <v>31</v>
@@ -14007,28 +14013,28 @@
     </row>
     <row r="246" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B246" t="s">
         <v>1027</v>
-      </c>
-      <c r="B246" t="s">
-        <v>1028</v>
       </c>
       <c r="D246" t="s">
         <v>147</v>
       </c>
       <c r="E246" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="F246" t="s">
         <v>57</v>
       </c>
       <c r="J246" t="s">
+        <v>1044</v>
+      </c>
+      <c r="K246" t="s">
         <v>1045</v>
       </c>
-      <c r="K246" t="s">
+      <c r="L246" s="3" t="s">
         <v>1046</v>
-      </c>
-      <c r="L246" s="3" t="s">
-        <v>1047</v>
       </c>
       <c r="R246" t="s">
         <v>31</v>
@@ -14048,10 +14054,10 @@
     </row>
     <row r="247" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B247" t="s">
         <v>1048</v>
-      </c>
-      <c r="B247" t="s">
-        <v>1049</v>
       </c>
       <c r="D247" t="s">
         <v>162</v>
@@ -14063,10 +14069,10 @@
         <v>122</v>
       </c>
       <c r="J247" t="s">
+        <v>1049</v>
+      </c>
+      <c r="L247" s="3" t="s">
         <v>1050</v>
-      </c>
-      <c r="L247" s="3" t="s">
-        <v>1051</v>
       </c>
       <c r="R247" t="s">
         <v>31</v>
@@ -14086,10 +14092,10 @@
     </row>
     <row r="248" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B248" t="s">
         <v>1048</v>
-      </c>
-      <c r="B248" t="s">
-        <v>1049</v>
       </c>
       <c r="D248" t="s">
         <v>147</v>
@@ -14101,10 +14107,10 @@
         <v>253</v>
       </c>
       <c r="J248" t="s">
+        <v>1051</v>
+      </c>
+      <c r="L248" s="3" t="s">
         <v>1052</v>
-      </c>
-      <c r="L248" s="3" t="s">
-        <v>1053</v>
       </c>
       <c r="R248" t="s">
         <v>31</v>
@@ -14124,13 +14130,13 @@
     </row>
     <row r="249" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B249" t="s">
         <v>1048</v>
       </c>
-      <c r="B249" t="s">
-        <v>1049</v>
-      </c>
       <c r="D249" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="E249" t="s">
         <v>373</v>
@@ -14139,13 +14145,13 @@
         <v>374</v>
       </c>
       <c r="J249" t="s">
+        <v>1054</v>
+      </c>
+      <c r="K249" t="s">
+        <v>1054</v>
+      </c>
+      <c r="L249" s="3" t="s">
         <v>1055</v>
-      </c>
-      <c r="K249" t="s">
-        <v>1055</v>
-      </c>
-      <c r="L249" s="3" t="s">
-        <v>1056</v>
       </c>
       <c r="R249" t="s">
         <v>31</v>
@@ -14165,13 +14171,13 @@
     </row>
     <row r="250" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B250" t="s">
         <v>1048</v>
       </c>
-      <c r="B250" t="s">
-        <v>1049</v>
-      </c>
       <c r="D250" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E250" t="s">
         <v>403</v>
@@ -14180,13 +14186,13 @@
         <v>296</v>
       </c>
       <c r="J250" t="s">
+        <v>1056</v>
+      </c>
+      <c r="K250" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L250" s="3" t="s">
         <v>1057</v>
-      </c>
-      <c r="K250" t="s">
-        <v>1057</v>
-      </c>
-      <c r="L250" s="3" t="s">
-        <v>1058</v>
       </c>
       <c r="R250" t="s">
         <v>31</v>
@@ -14206,25 +14212,25 @@
     </row>
     <row r="251" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B251" t="s">
         <v>1059</v>
       </c>
-      <c r="B251" t="s">
-        <v>1060</v>
-      </c>
       <c r="D251" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="E251" t="s">
         <v>121</v>
       </c>
       <c r="F251" t="s">
+        <v>1060</v>
+      </c>
+      <c r="J251" t="s">
         <v>1061</v>
       </c>
-      <c r="J251" t="s">
+      <c r="L251" s="3" t="s">
         <v>1062</v>
-      </c>
-      <c r="L251" s="3" t="s">
-        <v>1063</v>
       </c>
       <c r="R251" t="s">
         <v>31</v>
@@ -14244,13 +14250,13 @@
     </row>
     <row r="252" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B252" t="s">
         <v>1059</v>
       </c>
-      <c r="B252" t="s">
-        <v>1060</v>
-      </c>
       <c r="D252" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="E252" t="s">
         <v>129</v>
@@ -14259,10 +14265,10 @@
         <v>130</v>
       </c>
       <c r="J252" t="s">
+        <v>1063</v>
+      </c>
+      <c r="L252" s="3" t="s">
         <v>1064</v>
-      </c>
-      <c r="L252" s="3" t="s">
-        <v>1065</v>
       </c>
       <c r="R252" t="s">
         <v>31</v>
@@ -14282,13 +14288,13 @@
     </row>
     <row r="253" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B253" t="s">
         <v>1059</v>
       </c>
-      <c r="B253" t="s">
-        <v>1060</v>
-      </c>
       <c r="D253" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="E253" t="s">
         <v>74</v>
@@ -14297,10 +14303,10 @@
         <v>75</v>
       </c>
       <c r="J253" t="s">
+        <v>1065</v>
+      </c>
+      <c r="L253" s="3" t="s">
         <v>1066</v>
-      </c>
-      <c r="L253" s="3" t="s">
-        <v>1067</v>
       </c>
       <c r="R253" t="s">
         <v>31</v>
@@ -14320,10 +14326,10 @@
     </row>
     <row r="254" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B254" t="s">
         <v>1059</v>
-      </c>
-      <c r="B254" t="s">
-        <v>1060</v>
       </c>
       <c r="D254" t="s">
         <v>365</v>
@@ -14335,10 +14341,10 @@
         <v>68</v>
       </c>
       <c r="J254" t="s">
+        <v>1067</v>
+      </c>
+      <c r="L254" s="3" t="s">
         <v>1068</v>
-      </c>
-      <c r="L254" s="3" t="s">
-        <v>1069</v>
       </c>
       <c r="R254" t="s">
         <v>31</v>
@@ -14358,13 +14364,13 @@
     </row>
     <row r="255" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B255" t="s">
         <v>1070</v>
       </c>
-      <c r="B255" t="s">
+      <c r="D255" t="s">
         <v>1071</v>
-      </c>
-      <c r="D255" t="s">
-        <v>1072</v>
       </c>
       <c r="E255" t="s">
         <v>74</v>
@@ -14373,10 +14379,10 @@
         <v>75</v>
       </c>
       <c r="J255" t="s">
+        <v>1072</v>
+      </c>
+      <c r="L255" s="3" t="s">
         <v>1073</v>
-      </c>
-      <c r="L255" s="3" t="s">
-        <v>1074</v>
       </c>
       <c r="R255" t="s">
         <v>31</v>
@@ -14396,10 +14402,10 @@
     </row>
     <row r="256" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B256" t="s">
         <v>1070</v>
-      </c>
-      <c r="B256" t="s">
-        <v>1071</v>
       </c>
       <c r="D256" t="s">
         <v>286</v>
@@ -14408,10 +14414,10 @@
         <v>296</v>
       </c>
       <c r="J256" t="s">
+        <v>1074</v>
+      </c>
+      <c r="L256" s="3" t="s">
         <v>1075</v>
-      </c>
-      <c r="L256" s="3" t="s">
-        <v>1076</v>
       </c>
       <c r="R256" t="s">
         <v>31</v>
@@ -14431,13 +14437,13 @@
     </row>
     <row r="257" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B257" t="s">
         <v>1070</v>
       </c>
-      <c r="B257" t="s">
-        <v>1071</v>
-      </c>
       <c r="D257" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="E257" t="s">
         <v>121</v>
@@ -14446,16 +14452,16 @@
         <v>122</v>
       </c>
       <c r="J257" t="s">
+        <v>1076</v>
+      </c>
+      <c r="L257" s="3" t="s">
         <v>1077</v>
       </c>
-      <c r="L257" s="3" t="s">
+      <c r="R257" t="s">
+        <v>31</v>
+      </c>
+      <c r="S257" t="s">
         <v>1078</v>
-      </c>
-      <c r="R257" t="s">
-        <v>31</v>
-      </c>
-      <c r="S257" t="s">
-        <v>1079</v>
       </c>
       <c r="T257" s="1">
         <v>130</v>
@@ -14469,22 +14475,22 @@
     </row>
     <row r="258" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B258" t="s">
         <v>1070</v>
       </c>
-      <c r="B258" t="s">
-        <v>1071</v>
-      </c>
       <c r="D258" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="F258" t="s">
         <v>296</v>
       </c>
       <c r="J258" t="s">
+        <v>1079</v>
+      </c>
+      <c r="L258" s="3" t="s">
         <v>1080</v>
-      </c>
-      <c r="L258" s="3" t="s">
-        <v>1081</v>
       </c>
       <c r="R258" t="s">
         <v>31</v>
@@ -14504,13 +14510,13 @@
     </row>
     <row r="259" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B259" t="s">
         <v>1070</v>
       </c>
-      <c r="B259" t="s">
-        <v>1071</v>
-      </c>
       <c r="D259" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="E259" t="s">
         <v>121</v>
@@ -14519,10 +14525,10 @@
         <v>122</v>
       </c>
       <c r="J259" t="s">
+        <v>1081</v>
+      </c>
+      <c r="L259" s="3" t="s">
         <v>1082</v>
-      </c>
-      <c r="L259" s="3" t="s">
-        <v>1083</v>
       </c>
       <c r="R259" t="s">
         <v>31</v>
@@ -14542,13 +14548,13 @@
     </row>
     <row r="260" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B260" t="s">
         <v>1070</v>
       </c>
-      <c r="B260" t="s">
-        <v>1071</v>
-      </c>
       <c r="D260" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="E260" t="s">
         <v>121</v>
@@ -14557,10 +14563,10 @@
         <v>122</v>
       </c>
       <c r="J260" t="s">
+        <v>1084</v>
+      </c>
+      <c r="L260" s="3" t="s">
         <v>1085</v>
-      </c>
-      <c r="L260" s="3" t="s">
-        <v>1086</v>
       </c>
       <c r="R260" t="s">
         <v>31</v>
@@ -14580,10 +14586,10 @@
     </row>
     <row r="261" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B261" t="s">
         <v>1070</v>
-      </c>
-      <c r="B261" t="s">
-        <v>1071</v>
       </c>
       <c r="D261" t="s">
         <v>337</v>
@@ -14595,16 +14601,16 @@
         <v>122</v>
       </c>
       <c r="J261" t="s">
+        <v>1086</v>
+      </c>
+      <c r="L261" s="3" t="s">
         <v>1087</v>
       </c>
-      <c r="L261" s="3" t="s">
-        <v>1088</v>
-      </c>
       <c r="R261" t="s">
         <v>31</v>
       </c>
       <c r="S261" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="T261" s="1">
         <v>105</v>
@@ -14618,22 +14624,22 @@
     </row>
     <row r="262" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B262" t="s">
         <v>1070</v>
       </c>
-      <c r="B262" t="s">
-        <v>1071</v>
-      </c>
       <c r="D262" t="s">
+        <v>1088</v>
+      </c>
+      <c r="F262" t="s">
         <v>1089</v>
       </c>
-      <c r="F262" t="s">
+      <c r="J262" t="s">
         <v>1090</v>
       </c>
-      <c r="J262" t="s">
+      <c r="L262" s="3" t="s">
         <v>1091</v>
-      </c>
-      <c r="L262" s="3" t="s">
-        <v>1092</v>
       </c>
       <c r="R262" t="s">
         <v>31</v>
@@ -14653,13 +14659,13 @@
     </row>
     <row r="263" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B263" t="s">
         <v>1093</v>
       </c>
-      <c r="B263" t="s">
+      <c r="D263" t="s">
         <v>1094</v>
-      </c>
-      <c r="D263" t="s">
-        <v>1095</v>
       </c>
       <c r="E263" t="s">
         <v>121</v>
@@ -14668,10 +14674,10 @@
         <v>122</v>
       </c>
       <c r="J263" t="s">
+        <v>1095</v>
+      </c>
+      <c r="L263" s="3" t="s">
         <v>1096</v>
-      </c>
-      <c r="L263" s="3" t="s">
-        <v>1097</v>
       </c>
       <c r="R263" t="s">
         <v>31</v>
@@ -14691,13 +14697,13 @@
     </row>
     <row r="264" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B264" t="s">
         <v>1093</v>
       </c>
-      <c r="B264" t="s">
+      <c r="D264" t="s">
         <v>1094</v>
-      </c>
-      <c r="D264" t="s">
-        <v>1095</v>
       </c>
       <c r="E264" t="s">
         <v>121</v>
@@ -14706,10 +14712,10 @@
         <v>122</v>
       </c>
       <c r="J264" t="s">
+        <v>1097</v>
+      </c>
+      <c r="L264" s="3" t="s">
         <v>1098</v>
-      </c>
-      <c r="L264" s="3" t="s">
-        <v>1099</v>
       </c>
       <c r="R264" t="s">
         <v>31</v>
@@ -14729,13 +14735,13 @@
     </row>
     <row r="265" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B265" t="s">
         <v>1093</v>
       </c>
-      <c r="B265" t="s">
-        <v>1094</v>
-      </c>
       <c r="D265" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="E265" t="s">
         <v>121</v>
@@ -14744,10 +14750,10 @@
         <v>122</v>
       </c>
       <c r="J265" t="s">
+        <v>1100</v>
+      </c>
+      <c r="L265" s="3" t="s">
         <v>1101</v>
-      </c>
-      <c r="L265" s="3" t="s">
-        <v>1102</v>
       </c>
       <c r="R265" t="s">
         <v>31</v>
@@ -14767,13 +14773,13 @@
     </row>
     <row r="266" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B266" t="s">
         <v>1093</v>
       </c>
-      <c r="B266" t="s">
-        <v>1094</v>
-      </c>
       <c r="D266" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="E266" t="s">
         <v>42</v>
@@ -14782,10 +14788,10 @@
         <v>43</v>
       </c>
       <c r="J266" t="s">
+        <v>1103</v>
+      </c>
+      <c r="L266" s="3" t="s">
         <v>1104</v>
-      </c>
-      <c r="L266" s="3" t="s">
-        <v>1105</v>
       </c>
       <c r="R266" t="s">
         <v>31</v>
@@ -14805,25 +14811,25 @@
     </row>
     <row r="267" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B267" t="s">
         <v>1093</v>
-      </c>
-      <c r="B267" t="s">
-        <v>1094</v>
       </c>
       <c r="D267" t="s">
         <v>171</v>
       </c>
       <c r="E267" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="F267" t="s">
+        <v>1105</v>
+      </c>
+      <c r="J267" t="s">
         <v>1106</v>
       </c>
-      <c r="J267" t="s">
+      <c r="L267" s="3" t="s">
         <v>1107</v>
-      </c>
-      <c r="L267" s="3" t="s">
-        <v>1108</v>
       </c>
       <c r="R267" t="s">
         <v>31</v>
@@ -14843,13 +14849,13 @@
     </row>
     <row r="268" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B268" t="s">
         <v>1093</v>
       </c>
-      <c r="B268" t="s">
-        <v>1094</v>
-      </c>
       <c r="D268" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="E268" t="s">
         <v>74</v>
@@ -14858,10 +14864,10 @@
         <v>75</v>
       </c>
       <c r="J268" t="s">
+        <v>1109</v>
+      </c>
+      <c r="L268" s="3" t="s">
         <v>1110</v>
-      </c>
-      <c r="L268" s="3" t="s">
-        <v>1111</v>
       </c>
       <c r="R268" t="s">
         <v>31</v>
@@ -14881,13 +14887,13 @@
     </row>
     <row r="269" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B269" t="s">
         <v>1093</v>
       </c>
-      <c r="B269" t="s">
-        <v>1094</v>
-      </c>
       <c r="D269" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="E269" t="s">
         <v>352</v>
@@ -14896,10 +14902,10 @@
         <v>390</v>
       </c>
       <c r="J269" t="s">
+        <v>1112</v>
+      </c>
+      <c r="L269" s="3" t="s">
         <v>1113</v>
-      </c>
-      <c r="L269" s="3" t="s">
-        <v>1114</v>
       </c>
       <c r="R269" t="s">
         <v>31</v>
@@ -14919,25 +14925,25 @@
     </row>
     <row r="270" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B270" t="s">
         <v>1093</v>
       </c>
-      <c r="B270" t="s">
+      <c r="D270" t="s">
         <v>1094</v>
       </c>
-      <c r="D270" t="s">
-        <v>1095</v>
-      </c>
       <c r="E270" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="F270" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="J270" t="s">
+        <v>1114</v>
+      </c>
+      <c r="L270" s="3" t="s">
         <v>1115</v>
-      </c>
-      <c r="L270" s="3" t="s">
-        <v>1116</v>
       </c>
       <c r="R270" t="s">
         <v>31</v>
@@ -14957,13 +14963,13 @@
     </row>
     <row r="271" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B271" t="s">
         <v>1093</v>
       </c>
-      <c r="B271" t="s">
-        <v>1094</v>
-      </c>
       <c r="D271" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="E271" t="s">
         <v>352</v>
@@ -14972,10 +14978,10 @@
         <v>390</v>
       </c>
       <c r="J271" t="s">
+        <v>1117</v>
+      </c>
+      <c r="L271" s="3" t="s">
         <v>1118</v>
-      </c>
-      <c r="L271" s="3" t="s">
-        <v>1119</v>
       </c>
       <c r="R271" t="s">
         <v>31</v>
@@ -14995,13 +15001,13 @@
     </row>
     <row r="272" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B272" t="s">
         <v>1093</v>
       </c>
-      <c r="B272" t="s">
-        <v>1094</v>
-      </c>
       <c r="D272" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="E272" t="s">
         <v>121</v>
@@ -15010,10 +15016,10 @@
         <v>122</v>
       </c>
       <c r="J272" t="s">
+        <v>1119</v>
+      </c>
+      <c r="L272" s="3" t="s">
         <v>1120</v>
-      </c>
-      <c r="L272" s="3" t="s">
-        <v>1121</v>
       </c>
       <c r="R272" t="s">
         <v>31</v>
@@ -15033,13 +15039,13 @@
     </row>
     <row r="273" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B273" t="s">
         <v>1093</v>
       </c>
-      <c r="B273" t="s">
+      <c r="D273" t="s">
         <v>1094</v>
-      </c>
-      <c r="D273" t="s">
-        <v>1095</v>
       </c>
       <c r="E273" t="s">
         <v>129</v>
@@ -15048,10 +15054,10 @@
         <v>130</v>
       </c>
       <c r="J273" t="s">
+        <v>1121</v>
+      </c>
+      <c r="L273" s="3" t="s">
         <v>1122</v>
-      </c>
-      <c r="L273" s="3" t="s">
-        <v>1123</v>
       </c>
       <c r="R273" t="s">
         <v>31</v>
@@ -15071,13 +15077,13 @@
     </row>
     <row r="274" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B274" t="s">
         <v>1093</v>
       </c>
-      <c r="B274" t="s">
-        <v>1094</v>
-      </c>
       <c r="D274" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="E274" t="s">
         <v>176</v>
@@ -15086,10 +15092,10 @@
         <v>177</v>
       </c>
       <c r="J274" t="s">
+        <v>1123</v>
+      </c>
+      <c r="L274" s="3" t="s">
         <v>1124</v>
-      </c>
-      <c r="L274" s="3" t="s">
-        <v>1125</v>
       </c>
       <c r="R274" t="s">
         <v>31</v>
@@ -15109,28 +15115,28 @@
     </row>
     <row r="275" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B275" t="s">
         <v>1126</v>
-      </c>
-      <c r="B275" t="s">
-        <v>1127</v>
       </c>
       <c r="D275" t="s">
         <v>61</v>
       </c>
       <c r="E275" t="s">
+        <v>1127</v>
+      </c>
+      <c r="F275" t="s">
         <v>1128</v>
       </c>
-      <c r="F275" t="s">
+      <c r="J275" t="s">
         <v>1129</v>
       </c>
-      <c r="J275" t="s">
+      <c r="K275" t="s">
         <v>1130</v>
       </c>
-      <c r="K275" t="s">
+      <c r="L275" s="3" t="s">
         <v>1131</v>
-      </c>
-      <c r="L275" s="3" t="s">
-        <v>1132</v>
       </c>
       <c r="R275" t="s">
         <v>31</v>
@@ -15150,28 +15156,28 @@
     </row>
     <row r="276" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B276" t="s">
         <v>1126</v>
-      </c>
-      <c r="B276" t="s">
-        <v>1127</v>
       </c>
       <c r="D276" t="s">
         <v>452</v>
       </c>
       <c r="E276" t="s">
+        <v>835</v>
+      </c>
+      <c r="F276" t="s">
         <v>836</v>
       </c>
-      <c r="F276" t="s">
-        <v>837</v>
-      </c>
       <c r="J276" t="s">
+        <v>1132</v>
+      </c>
+      <c r="K276" t="s">
         <v>1133</v>
       </c>
-      <c r="K276" t="s">
+      <c r="L276" s="3" t="s">
         <v>1134</v>
-      </c>
-      <c r="L276" s="3" t="s">
-        <v>1135</v>
       </c>
       <c r="R276" t="s">
         <v>31</v>
@@ -15191,28 +15197,28 @@
     </row>
     <row r="277" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B277" t="s">
         <v>1126</v>
-      </c>
-      <c r="B277" t="s">
-        <v>1127</v>
       </c>
       <c r="D277" t="s">
         <v>278</v>
       </c>
       <c r="E277" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="F277" t="s">
+        <v>1135</v>
+      </c>
+      <c r="J277" t="s">
         <v>1136</v>
       </c>
-      <c r="J277" t="s">
+      <c r="K277" t="s">
         <v>1137</v>
       </c>
-      <c r="K277" t="s">
+      <c r="L277" s="3" t="s">
         <v>1138</v>
-      </c>
-      <c r="L277" s="3" t="s">
-        <v>1139</v>
       </c>
       <c r="R277" t="s">
         <v>31</v>
@@ -15232,13 +15238,13 @@
     </row>
     <row r="278" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B278" t="s">
         <v>1126</v>
       </c>
-      <c r="B278" t="s">
-        <v>1127</v>
-      </c>
       <c r="D278" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="E278" t="s">
         <v>74</v>
@@ -15247,13 +15253,13 @@
         <v>91</v>
       </c>
       <c r="J278" t="s">
+        <v>1139</v>
+      </c>
+      <c r="K278" t="s">
         <v>1140</v>
       </c>
-      <c r="K278" t="s">
+      <c r="L278" s="3" t="s">
         <v>1141</v>
-      </c>
-      <c r="L278" s="3" t="s">
-        <v>1142</v>
       </c>
       <c r="R278" t="s">
         <v>31</v>
@@ -15273,28 +15279,28 @@
     </row>
     <row r="279" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B279" t="s">
         <v>1143</v>
-      </c>
-      <c r="B279" t="s">
-        <v>1144</v>
       </c>
       <c r="D279" t="s">
         <v>365</v>
       </c>
       <c r="E279" t="s">
+        <v>1015</v>
+      </c>
+      <c r="F279" t="s">
         <v>1016</v>
       </c>
-      <c r="F279" t="s">
-        <v>1017</v>
-      </c>
       <c r="J279" t="s">
+        <v>1144</v>
+      </c>
+      <c r="K279" t="s">
+        <v>1144</v>
+      </c>
+      <c r="L279" s="3" t="s">
         <v>1145</v>
-      </c>
-      <c r="K279" t="s">
-        <v>1145</v>
-      </c>
-      <c r="L279" s="3" t="s">
-        <v>1146</v>
       </c>
       <c r="R279" t="s">
         <v>31</v>
@@ -15314,10 +15320,10 @@
     </row>
     <row r="280" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B280" t="s">
         <v>1143</v>
-      </c>
-      <c r="B280" t="s">
-        <v>1144</v>
       </c>
       <c r="D280" t="s">
         <v>35</v>
@@ -15329,10 +15335,10 @@
         <v>91</v>
       </c>
       <c r="J280" t="s">
+        <v>1146</v>
+      </c>
+      <c r="L280" s="3" t="s">
         <v>1147</v>
-      </c>
-      <c r="L280" s="3" t="s">
-        <v>1148</v>
       </c>
       <c r="R280" t="s">
         <v>31</v>
@@ -15352,28 +15358,28 @@
     </row>
     <row r="281" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B281" t="s">
         <v>1143</v>
       </c>
-      <c r="B281" t="s">
-        <v>1144</v>
-      </c>
       <c r="D281" t="s">
+        <v>1188</v>
+      </c>
+      <c r="E281" t="s">
         <v>1189</v>
       </c>
-      <c r="E281" t="s">
+      <c r="F281" t="s">
         <v>1190</v>
       </c>
-      <c r="F281" t="s">
-        <v>1191</v>
-      </c>
       <c r="J281" t="s">
+        <v>1148</v>
+      </c>
+      <c r="K281" t="s">
         <v>1149</v>
       </c>
-      <c r="K281" t="s">
+      <c r="L281" s="3" t="s">
         <v>1150</v>
-      </c>
-      <c r="L281" s="3" t="s">
-        <v>1151</v>
       </c>
       <c r="R281" t="s">
         <v>31</v>
@@ -15393,10 +15399,10 @@
     </row>
     <row r="282" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B282" t="s">
         <v>1143</v>
-      </c>
-      <c r="B282" t="s">
-        <v>1144</v>
       </c>
       <c r="D282">
         <v>1714</v>
@@ -15408,13 +15414,13 @@
         <v>75</v>
       </c>
       <c r="J282" t="s">
+        <v>1151</v>
+      </c>
+      <c r="K282" t="s">
         <v>1152</v>
       </c>
-      <c r="K282" t="s">
+      <c r="L282" s="3" t="s">
         <v>1153</v>
-      </c>
-      <c r="L282" s="3" t="s">
-        <v>1154</v>
       </c>
       <c r="R282" t="s">
         <v>31</v>
@@ -15437,7 +15443,7 @@
         <v>409</v>
       </c>
       <c r="B283" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="D283" t="s">
         <v>278</v>
@@ -15449,13 +15455,13 @@
         <v>75</v>
       </c>
       <c r="J283" t="s">
+        <v>1155</v>
+      </c>
+      <c r="K283" t="s">
         <v>1156</v>
       </c>
-      <c r="K283" t="s">
+      <c r="L283" s="3" t="s">
         <v>1157</v>
-      </c>
-      <c r="L283" s="3" t="s">
-        <v>1158</v>
       </c>
       <c r="R283" t="s">
         <v>31</v>
@@ -15478,10 +15484,10 @@
         <v>409</v>
       </c>
       <c r="B284" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="D284" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="E284" t="s">
         <v>74</v>
@@ -15490,13 +15496,13 @@
         <v>91</v>
       </c>
       <c r="J284" t="s">
+        <v>1159</v>
+      </c>
+      <c r="K284" t="s">
         <v>1160</v>
       </c>
-      <c r="K284" t="s">
+      <c r="L284" s="3" t="s">
         <v>1161</v>
-      </c>
-      <c r="L284" s="3" t="s">
-        <v>1162</v>
       </c>
       <c r="R284" t="s">
         <v>31</v>
@@ -15519,25 +15525,25 @@
         <v>409</v>
       </c>
       <c r="B285" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="D285" t="s">
         <v>248</v>
       </c>
       <c r="E285" t="s">
+        <v>1162</v>
+      </c>
+      <c r="F285" t="s">
         <v>1163</v>
       </c>
-      <c r="F285" t="s">
+      <c r="J285" t="s">
         <v>1164</v>
       </c>
-      <c r="J285" t="s">
+      <c r="K285" t="s">
         <v>1165</v>
       </c>
-      <c r="K285" t="s">
+      <c r="L285" s="3" t="s">
         <v>1166</v>
-      </c>
-      <c r="L285" s="3" t="s">
-        <v>1167</v>
       </c>
       <c r="R285" t="s">
         <v>31</v>
@@ -15560,10 +15566,10 @@
         <v>409</v>
       </c>
       <c r="B286" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="D286" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="E286" t="s">
         <v>74</v>
@@ -15572,13 +15578,13 @@
         <v>91</v>
       </c>
       <c r="J286" t="s">
+        <v>1167</v>
+      </c>
+      <c r="K286" t="s">
         <v>1168</v>
       </c>
-      <c r="K286" t="s">
+      <c r="L286" s="3" t="s">
         <v>1169</v>
-      </c>
-      <c r="L286" s="3" t="s">
-        <v>1170</v>
       </c>
       <c r="R286" t="s">
         <v>31</v>
@@ -15598,10 +15604,10 @@
     </row>
     <row r="287" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B287" t="s">
         <v>1171</v>
-      </c>
-      <c r="B287" t="s">
-        <v>1172</v>
       </c>
       <c r="D287" t="s">
         <v>452</v>
@@ -15610,16 +15616,16 @@
         <v>193</v>
       </c>
       <c r="F287" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J287" t="s">
+        <v>1172</v>
+      </c>
+      <c r="K287" t="s">
         <v>1173</v>
       </c>
-      <c r="K287" t="s">
+      <c r="L287" s="3" t="s">
         <v>1174</v>
-      </c>
-      <c r="L287" s="3" t="s">
-        <v>1175</v>
       </c>
       <c r="R287" t="s">
         <v>31</v>
@@ -15639,28 +15645,28 @@
     </row>
     <row r="288" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B288" t="s">
         <v>1171</v>
       </c>
-      <c r="B288" t="s">
-        <v>1172</v>
-      </c>
       <c r="D288" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="E288" t="s">
         <v>193</v>
       </c>
       <c r="F288" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J288" t="s">
+        <v>1176</v>
+      </c>
+      <c r="K288" t="s">
         <v>1177</v>
       </c>
-      <c r="K288" t="s">
+      <c r="L288" s="3" t="s">
         <v>1178</v>
-      </c>
-      <c r="L288" s="3" t="s">
-        <v>1179</v>
       </c>
       <c r="R288" t="s">
         <v>31</v>
@@ -15680,28 +15686,28 @@
     </row>
     <row r="289" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B289" t="s">
         <v>1171</v>
       </c>
-      <c r="B289" t="s">
-        <v>1172</v>
-      </c>
       <c r="D289" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E289" t="s">
+        <v>1179</v>
+      </c>
+      <c r="F289" t="s">
         <v>1180</v>
       </c>
-      <c r="F289" t="s">
+      <c r="J289" t="s">
         <v>1181</v>
       </c>
-      <c r="J289" t="s">
+      <c r="K289" t="s">
         <v>1182</v>
       </c>
-      <c r="K289" t="s">
+      <c r="L289" s="3" t="s">
         <v>1183</v>
-      </c>
-      <c r="L289" s="3" t="s">
-        <v>1184</v>
       </c>
       <c r="R289" t="s">
         <v>31</v>
@@ -15721,13 +15727,13 @@
     </row>
     <row r="290" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B290" t="s">
         <v>1171</v>
       </c>
-      <c r="B290" t="s">
-        <v>1172</v>
-      </c>
       <c r="D290" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="E290" t="s">
         <v>74</v>
@@ -15736,13 +15742,13 @@
         <v>91</v>
       </c>
       <c r="J290" t="s">
+        <v>1185</v>
+      </c>
+      <c r="K290" t="s">
         <v>1186</v>
       </c>
-      <c r="K290" t="s">
+      <c r="L290" s="3" t="s">
         <v>1187</v>
-      </c>
-      <c r="L290" s="3" t="s">
-        <v>1188</v>
       </c>
       <c r="R290" t="s">
         <v>31</v>

--- a/quizzes/peinture-18e.xlsx
+++ b/quizzes/peinture-18e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B0639A3-A1FE-4249-8963-48585CE495EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D48238-2C49-4526-BA62-E7A10F653EF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2857" uniqueCount="1194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2857" uniqueCount="1193">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -1268,9 +1268,6 @@
     <t>Los Angeles</t>
   </si>
   <si>
-    <t>The J. Paul Getty Museum</t>
-  </si>
-  <si>
     <t>"Autoportrait en bâilleur"</t>
   </si>
   <si>
@@ -2342,9 +2339,6 @@
     <t>"Der Parnass"</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/7/73/Anton_Raphael_Mengs_-_Parnassus_%28FondazioneTorlonia%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Fresque</t>
   </si>
   <si>
@@ -3605,9 +3599,6 @@
     <t>Château</t>
   </si>
   <si>
-    <t>Getty Center</t>
-  </si>
-  <si>
     <t>Le Parc d'Ermenonville</t>
   </si>
   <si>
@@ -3615,6 +3606,12 @@
   </si>
   <si>
     <t xml:space="preserve">Detroit </t>
+  </si>
+  <si>
+    <t>Centre Getty</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/18/Mengs_Parnasus.jpg/1280px-Mengs_Parnasus.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -3678,7 +3675,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3703,6 +3700,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4612,7 +4613,7 @@
         <v>107</v>
       </c>
       <c r="F14" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="J14" t="s">
         <v>108</v>
@@ -4653,7 +4654,7 @@
         <v>107</v>
       </c>
       <c r="F15" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="J15" t="s">
         <v>111</v>
@@ -5412,7 +5413,7 @@
         <v>77</v>
       </c>
       <c r="U33" s="1">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="W33" s="1">
         <v>2</v>
@@ -7523,41 +7524,41 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
+    <row r="86" spans="1:23" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="8" t="s">
         <v>408</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="8" t="s">
         <v>409</v>
       </c>
-      <c r="D86" t="s">
+      <c r="D86" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="E86" t="s">
+      <c r="E86" s="8" t="s">
         <v>410</v>
       </c>
-      <c r="F86" t="s">
+      <c r="F86" s="8" t="s">
+        <v>1191</v>
+      </c>
+      <c r="J86" s="8" t="s">
         <v>411</v>
       </c>
-      <c r="J86" t="s">
+      <c r="L86" s="9" t="s">
         <v>412</v>
       </c>
-      <c r="L86" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="R86" t="s">
-        <v>31</v>
-      </c>
-      <c r="S86" t="s">
-        <v>32</v>
-      </c>
-      <c r="T86" s="1">
-        <v>118</v>
-      </c>
-      <c r="U86" s="1">
-        <v>91</v>
-      </c>
-      <c r="W86" s="1">
+      <c r="R86" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="S86" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="T86" s="10">
+        <v>114</v>
+      </c>
+      <c r="U86" s="10">
+        <v>89</v>
+      </c>
+      <c r="W86" s="10">
         <v>3</v>
       </c>
     </row>
@@ -7578,10 +7579,10 @@
         <v>121</v>
       </c>
       <c r="J87" t="s">
+        <v>413</v>
+      </c>
+      <c r="L87" s="3" t="s">
         <v>414</v>
-      </c>
-      <c r="L87" s="3" t="s">
-        <v>415</v>
       </c>
       <c r="R87" t="s">
         <v>31</v>
@@ -7607,7 +7608,7 @@
         <v>409</v>
       </c>
       <c r="D88" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E88" t="s">
         <v>402</v>
@@ -7616,19 +7617,19 @@
         <v>295</v>
       </c>
       <c r="J88" t="s">
+        <v>416</v>
+      </c>
+      <c r="K88" t="s">
         <v>417</v>
       </c>
-      <c r="K88" t="s">
+      <c r="L88" s="3" t="s">
         <v>418</v>
-      </c>
-      <c r="L88" s="3" t="s">
-        <v>419</v>
       </c>
       <c r="R88" s="7" t="s">
         <v>298</v>
       </c>
       <c r="S88" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="T88" s="1">
         <v>50</v>
@@ -7657,13 +7658,13 @@
         <v>295</v>
       </c>
       <c r="J89" t="s">
+        <v>420</v>
+      </c>
+      <c r="K89" t="s">
         <v>421</v>
       </c>
-      <c r="K89" t="s">
+      <c r="L89" s="3" t="s">
         <v>422</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>423</v>
       </c>
       <c r="R89" t="s">
         <v>31</v>
@@ -7683,10 +7684,10 @@
     </row>
     <row r="90" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>423</v>
+      </c>
+      <c r="B90" t="s">
         <v>424</v>
-      </c>
-      <c r="B90" t="s">
-        <v>425</v>
       </c>
       <c r="D90" t="s">
         <v>82</v>
@@ -7698,10 +7699,10 @@
         <v>216</v>
       </c>
       <c r="J90" t="s">
+        <v>425</v>
+      </c>
+      <c r="L90" s="3" t="s">
         <v>426</v>
-      </c>
-      <c r="L90" s="3" t="s">
-        <v>427</v>
       </c>
       <c r="R90" t="s">
         <v>31</v>
@@ -7721,28 +7722,28 @@
     </row>
     <row r="91" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>423</v>
+      </c>
+      <c r="B91" t="s">
         <v>424</v>
-      </c>
-      <c r="B91" t="s">
-        <v>425</v>
       </c>
       <c r="D91" t="s">
         <v>294</v>
       </c>
       <c r="E91" t="s">
+        <v>427</v>
+      </c>
+      <c r="F91" t="s">
         <v>428</v>
       </c>
-      <c r="F91" t="s">
+      <c r="J91" t="s">
         <v>429</v>
       </c>
-      <c r="J91" t="s">
+      <c r="K91" t="s">
+        <v>429</v>
+      </c>
+      <c r="L91" s="3" t="s">
         <v>430</v>
-      </c>
-      <c r="K91" t="s">
-        <v>430</v>
-      </c>
-      <c r="L91" s="3" t="s">
-        <v>431</v>
       </c>
       <c r="R91" t="s">
         <v>31</v>
@@ -7762,10 +7763,10 @@
     </row>
     <row r="92" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>423</v>
+      </c>
+      <c r="B92" t="s">
         <v>424</v>
-      </c>
-      <c r="B92" t="s">
-        <v>425</v>
       </c>
       <c r="D92" t="s">
         <v>299</v>
@@ -7777,13 +7778,13 @@
         <v>216</v>
       </c>
       <c r="J92" t="s">
+        <v>431</v>
+      </c>
+      <c r="K92" t="s">
         <v>432</v>
       </c>
-      <c r="K92" t="s">
+      <c r="L92" s="3" t="s">
         <v>433</v>
-      </c>
-      <c r="L92" s="3" t="s">
-        <v>434</v>
       </c>
       <c r="R92" t="s">
         <v>31</v>
@@ -7803,28 +7804,28 @@
     </row>
     <row r="93" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>423</v>
+      </c>
+      <c r="B93" t="s">
         <v>424</v>
       </c>
-      <c r="B93" t="s">
-        <v>425</v>
-      </c>
       <c r="D93" t="s">
+        <v>434</v>
+      </c>
+      <c r="E93" t="s">
+        <v>427</v>
+      </c>
+      <c r="F93" t="s">
+        <v>428</v>
+      </c>
+      <c r="J93" t="s">
         <v>435</v>
       </c>
-      <c r="E93" t="s">
-        <v>428</v>
-      </c>
-      <c r="F93" t="s">
-        <v>429</v>
-      </c>
-      <c r="J93" t="s">
+      <c r="K93" t="s">
+        <v>435</v>
+      </c>
+      <c r="L93" s="3" t="s">
         <v>436</v>
-      </c>
-      <c r="K93" t="s">
-        <v>436</v>
-      </c>
-      <c r="L93" s="3" t="s">
-        <v>437</v>
       </c>
       <c r="R93" t="s">
         <v>31</v>
@@ -7844,13 +7845,13 @@
     </row>
     <row r="94" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>437</v>
+      </c>
+      <c r="B94" t="s">
         <v>438</v>
       </c>
-      <c r="B94" t="s">
+      <c r="D94" t="s">
         <v>439</v>
-      </c>
-      <c r="D94" t="s">
-        <v>440</v>
       </c>
       <c r="E94" t="s">
         <v>74</v>
@@ -7859,10 +7860,10 @@
         <v>389</v>
       </c>
       <c r="J94" t="s">
+        <v>440</v>
+      </c>
+      <c r="L94" s="3" t="s">
         <v>441</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>442</v>
       </c>
       <c r="R94" t="s">
         <v>31</v>
@@ -7882,13 +7883,13 @@
     </row>
     <row r="95" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>437</v>
+      </c>
+      <c r="B95" t="s">
         <v>438</v>
       </c>
-      <c r="B95" t="s">
-        <v>439</v>
-      </c>
       <c r="D95" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E95" t="s">
         <v>128</v>
@@ -7897,10 +7898,10 @@
         <v>129</v>
       </c>
       <c r="J95" t="s">
+        <v>443</v>
+      </c>
+      <c r="L95" s="3" t="s">
         <v>444</v>
-      </c>
-      <c r="L95" s="3" t="s">
-        <v>445</v>
       </c>
       <c r="R95" t="s">
         <v>31</v>
@@ -7920,10 +7921,10 @@
     </row>
     <row r="96" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>437</v>
+      </c>
+      <c r="B96" t="s">
         <v>438</v>
-      </c>
-      <c r="B96" t="s">
-        <v>439</v>
       </c>
       <c r="D96" t="s">
         <v>310</v>
@@ -7935,10 +7936,10 @@
         <v>121</v>
       </c>
       <c r="J96" t="s">
+        <v>445</v>
+      </c>
+      <c r="L96" s="3" t="s">
         <v>446</v>
-      </c>
-      <c r="L96" s="3" t="s">
-        <v>447</v>
       </c>
       <c r="R96" t="s">
         <v>31</v>
@@ -7958,13 +7959,13 @@
     </row>
     <row r="97" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>437</v>
+      </c>
+      <c r="B97" t="s">
         <v>438</v>
       </c>
-      <c r="B97" t="s">
-        <v>439</v>
-      </c>
       <c r="D97" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E97" t="s">
         <v>107</v>
@@ -7973,10 +7974,10 @@
         <v>252</v>
       </c>
       <c r="J97" t="s">
+        <v>448</v>
+      </c>
+      <c r="L97" s="3" t="s">
         <v>449</v>
-      </c>
-      <c r="L97" s="3" t="s">
-        <v>450</v>
       </c>
       <c r="R97" t="s">
         <v>31</v>
@@ -7996,28 +7997,28 @@
     </row>
     <row r="98" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>437</v>
+      </c>
+      <c r="B98" t="s">
         <v>438</v>
       </c>
-      <c r="B98" t="s">
-        <v>439</v>
-      </c>
       <c r="D98" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E98" t="s">
         <v>42</v>
       </c>
       <c r="F98" t="s">
+        <v>451</v>
+      </c>
+      <c r="J98" t="s">
         <v>452</v>
       </c>
-      <c r="J98" t="s">
+      <c r="K98" t="s">
         <v>453</v>
       </c>
-      <c r="K98" t="s">
+      <c r="L98" s="3" t="s">
         <v>454</v>
-      </c>
-      <c r="L98" s="3" t="s">
-        <v>455</v>
       </c>
       <c r="R98" t="s">
         <v>31</v>
@@ -8037,28 +8038,28 @@
     </row>
     <row r="99" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>437</v>
+      </c>
+      <c r="B99" t="s">
         <v>438</v>
       </c>
-      <c r="B99" t="s">
-        <v>439</v>
-      </c>
       <c r="D99" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E99" t="s">
         <v>42</v>
       </c>
       <c r="F99" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J99" t="s">
+        <v>455</v>
+      </c>
+      <c r="K99" t="s">
         <v>456</v>
       </c>
-      <c r="K99" t="s">
+      <c r="L99" s="3" t="s">
         <v>457</v>
-      </c>
-      <c r="L99" s="3" t="s">
-        <v>458</v>
       </c>
       <c r="R99" t="s">
         <v>31</v>
@@ -8078,28 +8079,28 @@
     </row>
     <row r="100" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>437</v>
+      </c>
+      <c r="B100" t="s">
         <v>438</v>
       </c>
-      <c r="B100" t="s">
-        <v>439</v>
-      </c>
       <c r="D100" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E100" t="s">
         <v>42</v>
       </c>
       <c r="F100" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J100" t="s">
+        <v>458</v>
+      </c>
+      <c r="K100" t="s">
         <v>459</v>
       </c>
-      <c r="K100" t="s">
+      <c r="L100" s="3" t="s">
         <v>460</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>461</v>
       </c>
       <c r="R100" t="s">
         <v>31</v>
@@ -8119,28 +8120,28 @@
     </row>
     <row r="101" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>437</v>
+      </c>
+      <c r="B101" t="s">
         <v>438</v>
       </c>
-      <c r="B101" t="s">
-        <v>439</v>
-      </c>
       <c r="D101" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E101" t="s">
         <v>42</v>
       </c>
       <c r="F101" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J101" t="s">
+        <v>461</v>
+      </c>
+      <c r="K101" t="s">
         <v>462</v>
       </c>
-      <c r="K101" t="s">
+      <c r="L101" s="3" t="s">
         <v>463</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>464</v>
       </c>
       <c r="R101" t="s">
         <v>31</v>
@@ -8160,13 +8161,13 @@
     </row>
     <row r="102" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>437</v>
+      </c>
+      <c r="B102" t="s">
         <v>438</v>
       </c>
-      <c r="B102" t="s">
-        <v>439</v>
-      </c>
       <c r="D102" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E102" t="s">
         <v>120</v>
@@ -8175,13 +8176,13 @@
         <v>121</v>
       </c>
       <c r="J102" t="s">
+        <v>465</v>
+      </c>
+      <c r="K102" t="s">
         <v>466</v>
       </c>
-      <c r="K102" t="s">
+      <c r="L102" s="3" t="s">
         <v>467</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>468</v>
       </c>
       <c r="R102" t="s">
         <v>31</v>
@@ -8201,10 +8202,10 @@
     </row>
     <row r="103" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>437</v>
+      </c>
+      <c r="B103" t="s">
         <v>438</v>
-      </c>
-      <c r="B103" t="s">
-        <v>439</v>
       </c>
       <c r="D103" t="s">
         <v>25</v>
@@ -8216,13 +8217,13 @@
         <v>121</v>
       </c>
       <c r="J103" t="s">
+        <v>468</v>
+      </c>
+      <c r="K103" t="s">
         <v>469</v>
       </c>
-      <c r="K103" t="s">
+      <c r="L103" s="3" t="s">
         <v>470</v>
-      </c>
-      <c r="L103" s="3" t="s">
-        <v>471</v>
       </c>
       <c r="R103" t="s">
         <v>31</v>
@@ -8242,10 +8243,10 @@
     </row>
     <row r="104" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
+        <v>437</v>
+      </c>
+      <c r="B104" t="s">
         <v>438</v>
-      </c>
-      <c r="B104" t="s">
-        <v>439</v>
       </c>
       <c r="D104" t="s">
         <v>281</v>
@@ -8257,13 +8258,13 @@
         <v>121</v>
       </c>
       <c r="J104" t="s">
+        <v>471</v>
+      </c>
+      <c r="K104" t="s">
         <v>472</v>
       </c>
-      <c r="K104" t="s">
+      <c r="L104" s="3" t="s">
         <v>473</v>
-      </c>
-      <c r="L104" s="3" t="s">
-        <v>474</v>
       </c>
       <c r="R104" t="s">
         <v>31</v>
@@ -8283,10 +8284,10 @@
     </row>
     <row r="105" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>437</v>
+      </c>
+      <c r="B105" t="s">
         <v>438</v>
-      </c>
-      <c r="B105" t="s">
-        <v>439</v>
       </c>
       <c r="D105" t="s">
         <v>281</v>
@@ -8298,13 +8299,13 @@
         <v>121</v>
       </c>
       <c r="J105" t="s">
+        <v>474</v>
+      </c>
+      <c r="K105" t="s">
+        <v>474</v>
+      </c>
+      <c r="L105" s="3" t="s">
         <v>475</v>
-      </c>
-      <c r="K105" t="s">
-        <v>475</v>
-      </c>
-      <c r="L105" s="3" t="s">
-        <v>476</v>
       </c>
       <c r="R105" t="s">
         <v>31</v>
@@ -8324,28 +8325,28 @@
     </row>
     <row r="106" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
+        <v>476</v>
+      </c>
+      <c r="B106" t="s">
         <v>477</v>
       </c>
-      <c r="B106" t="s">
+      <c r="D106" t="s">
         <v>478</v>
       </c>
-      <c r="D106" t="s">
+      <c r="E106" t="s">
+        <v>1190</v>
+      </c>
+      <c r="F106" t="s">
+        <v>1189</v>
+      </c>
+      <c r="J106" t="s">
         <v>479</v>
       </c>
-      <c r="E106" t="s">
-        <v>1193</v>
-      </c>
-      <c r="F106" t="s">
-        <v>1192</v>
-      </c>
-      <c r="J106" t="s">
+      <c r="K106" t="s">
         <v>480</v>
       </c>
-      <c r="K106" t="s">
+      <c r="L106" s="3" t="s">
         <v>481</v>
-      </c>
-      <c r="L106" s="3" t="s">
-        <v>482</v>
       </c>
       <c r="R106" t="s">
         <v>31</v>
@@ -8365,10 +8366,10 @@
     </row>
     <row r="107" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>476</v>
+      </c>
+      <c r="B107" t="s">
         <v>477</v>
-      </c>
-      <c r="B107" t="s">
-        <v>478</v>
       </c>
       <c r="D107" t="s">
         <v>291</v>
@@ -8380,13 +8381,13 @@
         <v>121</v>
       </c>
       <c r="J107" t="s">
+        <v>482</v>
+      </c>
+      <c r="K107" t="s">
         <v>483</v>
       </c>
-      <c r="K107" t="s">
+      <c r="L107" s="3" t="s">
         <v>484</v>
-      </c>
-      <c r="L107" s="3" t="s">
-        <v>485</v>
       </c>
       <c r="R107" t="s">
         <v>31</v>
@@ -8406,31 +8407,31 @@
     </row>
     <row r="108" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>476</v>
+      </c>
+      <c r="B108" t="s">
         <v>477</v>
-      </c>
-      <c r="B108" t="s">
-        <v>478</v>
       </c>
       <c r="D108" t="s">
         <v>285</v>
       </c>
       <c r="E108" t="s">
+        <v>485</v>
+      </c>
+      <c r="F108" t="s">
         <v>486</v>
       </c>
-      <c r="F108" t="s">
+      <c r="J108" t="s">
         <v>487</v>
       </c>
-      <c r="J108" t="s">
+      <c r="K108" t="s">
         <v>488</v>
       </c>
-      <c r="K108" t="s">
+      <c r="L108" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="L108" s="3" t="s">
+      <c r="M108" t="s">
         <v>490</v>
-      </c>
-      <c r="M108" t="s">
-        <v>491</v>
       </c>
       <c r="R108" t="s">
         <v>31</v>
@@ -8450,28 +8451,28 @@
     </row>
     <row r="109" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
+        <v>476</v>
+      </c>
+      <c r="B109" t="s">
         <v>477</v>
-      </c>
-      <c r="B109" t="s">
-        <v>478</v>
       </c>
       <c r="D109" t="s">
         <v>305</v>
       </c>
       <c r="E109" t="s">
+        <v>485</v>
+      </c>
+      <c r="F109" t="s">
         <v>486</v>
       </c>
-      <c r="F109" t="s">
-        <v>487</v>
-      </c>
       <c r="J109" t="s">
+        <v>491</v>
+      </c>
+      <c r="K109" t="s">
         <v>492</v>
       </c>
-      <c r="K109" t="s">
+      <c r="L109" s="3" t="s">
         <v>493</v>
-      </c>
-      <c r="L109" s="3" t="s">
-        <v>494</v>
       </c>
       <c r="R109" t="s">
         <v>31</v>
@@ -8491,10 +8492,10 @@
     </row>
     <row r="110" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>494</v>
+      </c>
+      <c r="B110" t="s">
         <v>495</v>
-      </c>
-      <c r="B110" t="s">
-        <v>496</v>
       </c>
       <c r="D110" t="s">
         <v>127</v>
@@ -8506,13 +8507,13 @@
         <v>75</v>
       </c>
       <c r="J110" t="s">
+        <v>496</v>
+      </c>
+      <c r="K110" t="s">
         <v>497</v>
       </c>
-      <c r="K110" t="s">
+      <c r="L110" s="3" t="s">
         <v>498</v>
-      </c>
-      <c r="L110" s="3" t="s">
-        <v>499</v>
       </c>
       <c r="R110" t="s">
         <v>31</v>
@@ -8532,28 +8533,28 @@
     </row>
     <row r="111" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>494</v>
+      </c>
+      <c r="B111" t="s">
         <v>495</v>
-      </c>
-      <c r="B111" t="s">
-        <v>496</v>
       </c>
       <c r="D111" t="s">
         <v>61</v>
       </c>
       <c r="E111" t="s">
+        <v>499</v>
+      </c>
+      <c r="F111" t="s">
         <v>500</v>
       </c>
-      <c r="F111" t="s">
+      <c r="J111" t="s">
         <v>501</v>
       </c>
-      <c r="J111" t="s">
+      <c r="K111" t="s">
         <v>502</v>
       </c>
-      <c r="K111" t="s">
+      <c r="L111" s="3" t="s">
         <v>503</v>
-      </c>
-      <c r="L111" s="3" t="s">
-        <v>504</v>
       </c>
       <c r="R111" t="s">
         <v>31</v>
@@ -8573,28 +8574,28 @@
     </row>
     <row r="112" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>494</v>
+      </c>
+      <c r="B112" t="s">
         <v>495</v>
       </c>
-      <c r="B112" t="s">
-        <v>496</v>
-      </c>
       <c r="D112" t="s">
+        <v>504</v>
+      </c>
+      <c r="E112" t="s">
         <v>505</v>
       </c>
-      <c r="E112" t="s">
+      <c r="F112" t="s">
         <v>506</v>
       </c>
-      <c r="F112" t="s">
+      <c r="J112" t="s">
         <v>507</v>
       </c>
-      <c r="J112" t="s">
+      <c r="K112" t="s">
         <v>508</v>
       </c>
-      <c r="K112" t="s">
+      <c r="L112" s="3" t="s">
         <v>509</v>
-      </c>
-      <c r="L112" s="3" t="s">
-        <v>510</v>
       </c>
       <c r="R112" t="s">
         <v>31</v>
@@ -8614,13 +8615,13 @@
     </row>
     <row r="113" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
+        <v>494</v>
+      </c>
+      <c r="B113" t="s">
         <v>495</v>
       </c>
-      <c r="B113" t="s">
-        <v>496</v>
-      </c>
       <c r="D113" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="E113" t="s">
         <v>74</v>
@@ -8629,13 +8630,13 @@
         <v>75</v>
       </c>
       <c r="J113" t="s">
+        <v>511</v>
+      </c>
+      <c r="K113" t="s">
         <v>512</v>
       </c>
-      <c r="K113" t="s">
+      <c r="L113" s="3" t="s">
         <v>513</v>
-      </c>
-      <c r="L113" s="3" t="s">
-        <v>514</v>
       </c>
       <c r="R113" t="s">
         <v>31</v>
@@ -8655,10 +8656,10 @@
     </row>
     <row r="114" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>514</v>
+      </c>
+      <c r="B114" t="s">
         <v>515</v>
-      </c>
-      <c r="B114" t="s">
-        <v>516</v>
       </c>
       <c r="D114" t="s">
         <v>294</v>
@@ -8670,10 +8671,10 @@
         <v>121</v>
       </c>
       <c r="J114" t="s">
+        <v>516</v>
+      </c>
+      <c r="L114" s="3" t="s">
         <v>517</v>
-      </c>
-      <c r="L114" s="3" t="s">
-        <v>518</v>
       </c>
       <c r="R114" t="s">
         <v>31</v>
@@ -8693,13 +8694,13 @@
     </row>
     <row r="115" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>514</v>
+      </c>
+      <c r="B115" t="s">
         <v>515</v>
       </c>
-      <c r="B115" t="s">
-        <v>516</v>
-      </c>
       <c r="D115" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E115" t="s">
         <v>120</v>
@@ -8708,14 +8709,14 @@
         <v>121</v>
       </c>
       <c r="J115" t="s">
+        <v>519</v>
+      </c>
+      <c r="K115" t="s">
+        <v>519</v>
+      </c>
+      <c r="L115" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="K115" t="s">
-        <v>520</v>
-      </c>
-      <c r="L115" s="3" t="s">
-        <v>521</v>
-      </c>
       <c r="R115" t="s">
         <v>31</v>
       </c>
@@ -8723,7 +8724,7 @@
         <v>32</v>
       </c>
       <c r="T115" s="1">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="U115" s="1">
         <v>341</v>
@@ -8734,13 +8735,13 @@
     </row>
     <row r="116" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>514</v>
+      </c>
+      <c r="B116" t="s">
         <v>515</v>
       </c>
-      <c r="B116" t="s">
-        <v>516</v>
-      </c>
       <c r="D116" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E116" t="s">
         <v>120</v>
@@ -8749,13 +8750,13 @@
         <v>121</v>
       </c>
       <c r="J116" t="s">
+        <v>521</v>
+      </c>
+      <c r="K116" t="s">
+        <v>521</v>
+      </c>
+      <c r="L116" s="3" t="s">
         <v>522</v>
-      </c>
-      <c r="K116" t="s">
-        <v>522</v>
-      </c>
-      <c r="L116" s="3" t="s">
-        <v>523</v>
       </c>
       <c r="R116" t="s">
         <v>31</v>
@@ -8775,37 +8776,37 @@
     </row>
     <row r="117" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
+        <v>514</v>
+      </c>
+      <c r="B117" t="s">
         <v>515</v>
       </c>
-      <c r="B117" t="s">
-        <v>516</v>
-      </c>
       <c r="D117" t="s">
+        <v>523</v>
+      </c>
+      <c r="E117" t="s">
         <v>524</v>
       </c>
-      <c r="E117" t="s">
+      <c r="F117" t="s">
         <v>525</v>
       </c>
-      <c r="F117" t="s">
+      <c r="J117" t="s">
         <v>526</v>
       </c>
-      <c r="J117" t="s">
+      <c r="K117" t="s">
+        <v>526</v>
+      </c>
+      <c r="L117" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="K117" t="s">
-        <v>527</v>
-      </c>
-      <c r="L117" s="3" t="s">
+      <c r="R117" t="s">
+        <v>31</v>
+      </c>
+      <c r="S117" t="s">
+        <v>32</v>
+      </c>
+      <c r="T117" s="1" t="s">
         <v>528</v>
-      </c>
-      <c r="R117" t="s">
-        <v>31</v>
-      </c>
-      <c r="S117" t="s">
-        <v>32</v>
-      </c>
-      <c r="T117" s="1" t="s">
-        <v>529</v>
       </c>
       <c r="U117" s="1">
         <v>124</v>
@@ -8816,28 +8817,28 @@
     </row>
     <row r="118" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>529</v>
+      </c>
+      <c r="B118" t="s">
         <v>530</v>
       </c>
-      <c r="B118" t="s">
+      <c r="D118" t="s">
         <v>531</v>
-      </c>
-      <c r="D118" t="s">
-        <v>532</v>
       </c>
       <c r="E118" t="s">
         <v>56</v>
       </c>
       <c r="F118" t="s">
+        <v>532</v>
+      </c>
+      <c r="J118" t="s">
         <v>533</v>
       </c>
-      <c r="J118" t="s">
+      <c r="K118" t="s">
         <v>534</v>
       </c>
-      <c r="K118" t="s">
+      <c r="L118" s="3" t="s">
         <v>535</v>
-      </c>
-      <c r="L118" s="3" t="s">
-        <v>536</v>
       </c>
       <c r="R118" t="s">
         <v>31</v>
@@ -8857,28 +8858,28 @@
     </row>
     <row r="119" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>529</v>
+      </c>
+      <c r="B119" t="s">
         <v>530</v>
-      </c>
-      <c r="B119" t="s">
-        <v>531</v>
       </c>
       <c r="D119" t="s">
         <v>247</v>
       </c>
       <c r="E119" t="s">
+        <v>536</v>
+      </c>
+      <c r="F119" t="s">
         <v>537</v>
       </c>
-      <c r="F119" t="s">
+      <c r="J119" t="s">
         <v>538</v>
       </c>
-      <c r="J119" t="s">
+      <c r="K119" t="s">
         <v>539</v>
       </c>
-      <c r="K119" t="s">
+      <c r="L119" s="3" t="s">
         <v>540</v>
-      </c>
-      <c r="L119" s="3" t="s">
-        <v>541</v>
       </c>
       <c r="R119" t="s">
         <v>31</v>
@@ -8898,10 +8899,10 @@
     </row>
     <row r="120" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>529</v>
+      </c>
+      <c r="B120" t="s">
         <v>530</v>
-      </c>
-      <c r="B120" t="s">
-        <v>531</v>
       </c>
       <c r="D120" t="s">
         <v>82</v>
@@ -8910,16 +8911,16 @@
         <v>56</v>
       </c>
       <c r="F120" t="s">
+        <v>541</v>
+      </c>
+      <c r="J120" t="s">
         <v>542</v>
       </c>
-      <c r="J120" t="s">
+      <c r="K120" t="s">
         <v>543</v>
       </c>
-      <c r="K120" t="s">
+      <c r="L120" s="3" t="s">
         <v>544</v>
-      </c>
-      <c r="L120" s="3" t="s">
-        <v>545</v>
       </c>
       <c r="R120" t="s">
         <v>31</v>
@@ -8939,28 +8940,28 @@
     </row>
     <row r="121" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>529</v>
+      </c>
+      <c r="B121" t="s">
         <v>530</v>
       </c>
-      <c r="B121" t="s">
-        <v>531</v>
-      </c>
       <c r="D121" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E121" t="s">
         <v>56</v>
       </c>
       <c r="F121" t="s">
+        <v>545</v>
+      </c>
+      <c r="J121" t="s">
         <v>546</v>
       </c>
-      <c r="J121" t="s">
+      <c r="K121" t="s">
         <v>547</v>
       </c>
-      <c r="K121" t="s">
+      <c r="L121" s="3" t="s">
         <v>548</v>
-      </c>
-      <c r="L121" s="3" t="s">
-        <v>549</v>
       </c>
       <c r="R121" t="s">
         <v>31</v>
@@ -8980,10 +8981,10 @@
     </row>
     <row r="122" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>549</v>
+      </c>
+      <c r="B122" t="s">
         <v>550</v>
-      </c>
-      <c r="B122" t="s">
-        <v>551</v>
       </c>
       <c r="D122" t="s">
         <v>41</v>
@@ -8995,10 +8996,10 @@
         <v>121</v>
       </c>
       <c r="J122" t="s">
+        <v>551</v>
+      </c>
+      <c r="L122" s="3" t="s">
         <v>552</v>
-      </c>
-      <c r="L122" s="3" t="s">
-        <v>553</v>
       </c>
       <c r="R122" t="s">
         <v>31</v>
@@ -9018,10 +9019,10 @@
     </row>
     <row r="123" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
+        <v>549</v>
+      </c>
+      <c r="B123" t="s">
         <v>550</v>
-      </c>
-      <c r="B123" t="s">
-        <v>551</v>
       </c>
       <c r="D123" t="s">
         <v>273</v>
@@ -9033,10 +9034,10 @@
         <v>121</v>
       </c>
       <c r="J123" t="s">
+        <v>553</v>
+      </c>
+      <c r="L123" s="3" t="s">
         <v>554</v>
-      </c>
-      <c r="L123" s="3" t="s">
-        <v>555</v>
       </c>
       <c r="R123" t="s">
         <v>31</v>
@@ -9056,10 +9057,10 @@
     </row>
     <row r="124" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
+        <v>549</v>
+      </c>
+      <c r="B124" t="s">
         <v>550</v>
-      </c>
-      <c r="B124" t="s">
-        <v>551</v>
       </c>
       <c r="D124" t="s">
         <v>146</v>
@@ -9071,13 +9072,13 @@
         <v>121</v>
       </c>
       <c r="J124" t="s">
+        <v>555</v>
+      </c>
+      <c r="K124" t="s">
+        <v>555</v>
+      </c>
+      <c r="L124" s="3" t="s">
         <v>556</v>
-      </c>
-      <c r="K124" t="s">
-        <v>556</v>
-      </c>
-      <c r="L124" s="3" t="s">
-        <v>557</v>
       </c>
       <c r="R124" t="s">
         <v>31</v>
@@ -9097,10 +9098,10 @@
     </row>
     <row r="125" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
+        <v>549</v>
+      </c>
+      <c r="B125" t="s">
         <v>550</v>
-      </c>
-      <c r="B125" t="s">
-        <v>551</v>
       </c>
       <c r="D125" t="s">
         <v>281</v>
@@ -9112,13 +9113,13 @@
         <v>121</v>
       </c>
       <c r="J125" t="s">
+        <v>557</v>
+      </c>
+      <c r="K125" t="s">
+        <v>557</v>
+      </c>
+      <c r="L125" s="3" t="s">
         <v>558</v>
-      </c>
-      <c r="K125" t="s">
-        <v>558</v>
-      </c>
-      <c r="L125" s="3" t="s">
-        <v>559</v>
       </c>
       <c r="R125" t="s">
         <v>31</v>
@@ -9138,10 +9139,10 @@
     </row>
     <row r="126" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
+        <v>549</v>
+      </c>
+      <c r="B126" t="s">
         <v>550</v>
-      </c>
-      <c r="B126" t="s">
-        <v>551</v>
       </c>
       <c r="D126" t="s">
         <v>281</v>
@@ -9153,13 +9154,13 @@
         <v>75</v>
       </c>
       <c r="J126" t="s">
+        <v>559</v>
+      </c>
+      <c r="K126" t="s">
         <v>560</v>
       </c>
-      <c r="K126" t="s">
+      <c r="L126" s="3" t="s">
         <v>561</v>
-      </c>
-      <c r="L126" s="3" t="s">
-        <v>562</v>
       </c>
       <c r="R126" t="s">
         <v>31</v>
@@ -9179,10 +9180,10 @@
     </row>
     <row r="127" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
+        <v>549</v>
+      </c>
+      <c r="B127" t="s">
         <v>550</v>
-      </c>
-      <c r="B127" t="s">
-        <v>551</v>
       </c>
       <c r="D127">
         <v>1771</v>
@@ -9194,13 +9195,13 @@
         <v>121</v>
       </c>
       <c r="J127" t="s">
+        <v>562</v>
+      </c>
+      <c r="K127" t="s">
+        <v>562</v>
+      </c>
+      <c r="L127" s="3" t="s">
         <v>563</v>
-      </c>
-      <c r="K127" t="s">
-        <v>563</v>
-      </c>
-      <c r="L127" s="3" t="s">
-        <v>564</v>
       </c>
       <c r="R127" t="s">
         <v>31</v>
@@ -9220,13 +9221,13 @@
     </row>
     <row r="128" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>549</v>
+      </c>
+      <c r="B128" t="s">
         <v>550</v>
       </c>
-      <c r="B128" t="s">
-        <v>551</v>
-      </c>
       <c r="D128" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E128" t="s">
         <v>67</v>
@@ -9235,13 +9236,13 @@
         <v>68</v>
       </c>
       <c r="J128" t="s">
+        <v>565</v>
+      </c>
+      <c r="K128" t="s">
+        <v>565</v>
+      </c>
+      <c r="L128" s="3" t="s">
         <v>566</v>
-      </c>
-      <c r="K128" t="s">
-        <v>566</v>
-      </c>
-      <c r="L128" s="3" t="s">
-        <v>567</v>
       </c>
       <c r="R128" t="s">
         <v>31</v>
@@ -9261,10 +9262,10 @@
     </row>
     <row r="129" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
+        <v>549</v>
+      </c>
+      <c r="B129" t="s">
         <v>550</v>
-      </c>
-      <c r="B129" t="s">
-        <v>551</v>
       </c>
       <c r="D129" t="s">
         <v>401</v>
@@ -9273,16 +9274,16 @@
         <v>42</v>
       </c>
       <c r="F129" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="J129" t="s">
         <v>253</v>
       </c>
       <c r="K129" t="s">
+        <v>568</v>
+      </c>
+      <c r="L129" s="3" t="s">
         <v>569</v>
-      </c>
-      <c r="L129" s="3" t="s">
-        <v>570</v>
       </c>
       <c r="R129" t="s">
         <v>31</v>
@@ -9302,13 +9303,13 @@
     </row>
     <row r="130" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
+        <v>570</v>
+      </c>
+      <c r="B130" t="s">
         <v>571</v>
       </c>
-      <c r="B130" t="s">
+      <c r="D130" t="s">
         <v>572</v>
-      </c>
-      <c r="D130" t="s">
-        <v>573</v>
       </c>
       <c r="E130" t="s">
         <v>120</v>
@@ -9317,13 +9318,13 @@
         <v>121</v>
       </c>
       <c r="J130" t="s">
+        <v>573</v>
+      </c>
+      <c r="K130" t="s">
         <v>574</v>
       </c>
-      <c r="K130" t="s">
+      <c r="L130" s="3" t="s">
         <v>575</v>
-      </c>
-      <c r="L130" s="3" t="s">
-        <v>576</v>
       </c>
       <c r="R130" t="s">
         <v>31</v>
@@ -9343,19 +9344,19 @@
     </row>
     <row r="131" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
+        <v>570</v>
+      </c>
+      <c r="B131" t="s">
         <v>571</v>
       </c>
-      <c r="B131" t="s">
+      <c r="D131" t="s">
         <v>572</v>
       </c>
-      <c r="D131" t="s">
-        <v>573</v>
-      </c>
       <c r="E131" t="s">
+        <v>576</v>
+      </c>
+      <c r="F131" t="s">
         <v>577</v>
-      </c>
-      <c r="F131" t="s">
-        <v>578</v>
       </c>
       <c r="J131" t="s">
         <v>171</v>
@@ -9364,7 +9365,7 @@
         <v>172</v>
       </c>
       <c r="L131" s="3" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="R131" t="s">
         <v>31</v>
@@ -9384,13 +9385,13 @@
     </row>
     <row r="132" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
+        <v>570</v>
+      </c>
+      <c r="B132" t="s">
         <v>571</v>
       </c>
-      <c r="B132" t="s">
-        <v>572</v>
-      </c>
       <c r="D132" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E132" t="s">
         <v>185</v>
@@ -9399,13 +9400,13 @@
         <v>186</v>
       </c>
       <c r="J132" t="s">
+        <v>580</v>
+      </c>
+      <c r="K132" t="s">
         <v>581</v>
       </c>
-      <c r="K132" t="s">
+      <c r="L132" s="3" t="s">
         <v>582</v>
-      </c>
-      <c r="L132" s="3" t="s">
-        <v>583</v>
       </c>
       <c r="R132" t="s">
         <v>31</v>
@@ -9425,13 +9426,13 @@
     </row>
     <row r="133" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
+        <v>570</v>
+      </c>
+      <c r="B133" t="s">
         <v>571</v>
       </c>
-      <c r="B133" t="s">
-        <v>572</v>
-      </c>
       <c r="D133" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E133" t="s">
         <v>133</v>
@@ -9440,13 +9441,13 @@
         <v>134</v>
       </c>
       <c r="J133" t="s">
+        <v>584</v>
+      </c>
+      <c r="K133" t="s">
         <v>585</v>
       </c>
-      <c r="K133" t="s">
+      <c r="L133" s="3" t="s">
         <v>586</v>
-      </c>
-      <c r="L133" s="3" t="s">
-        <v>587</v>
       </c>
       <c r="R133" t="s">
         <v>31</v>
@@ -9469,7 +9470,7 @@
         <v>80</v>
       </c>
       <c r="B134" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D134" t="s">
         <v>124</v>
@@ -9481,13 +9482,13 @@
         <v>75</v>
       </c>
       <c r="J134" t="s">
+        <v>588</v>
+      </c>
+      <c r="K134" t="s">
         <v>589</v>
       </c>
-      <c r="K134" t="s">
+      <c r="L134" s="3" t="s">
         <v>590</v>
-      </c>
-      <c r="L134" s="3" t="s">
-        <v>591</v>
       </c>
       <c r="R134" t="s">
         <v>31</v>
@@ -9510,10 +9511,10 @@
         <v>80</v>
       </c>
       <c r="B135" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D135" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E135" t="s">
         <v>74</v>
@@ -9522,13 +9523,13 @@
         <v>75</v>
       </c>
       <c r="J135" t="s">
+        <v>592</v>
+      </c>
+      <c r="K135" t="s">
         <v>593</v>
       </c>
-      <c r="K135" t="s">
+      <c r="L135" s="3" t="s">
         <v>594</v>
-      </c>
-      <c r="L135" s="3" t="s">
-        <v>595</v>
       </c>
       <c r="R135" t="s">
         <v>31</v>
@@ -9551,10 +9552,10 @@
         <v>80</v>
       </c>
       <c r="B136" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D136" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E136" t="s">
         <v>74</v>
@@ -9563,13 +9564,13 @@
         <v>91</v>
       </c>
       <c r="J136" t="s">
+        <v>596</v>
+      </c>
+      <c r="K136" t="s">
         <v>597</v>
       </c>
-      <c r="K136" t="s">
+      <c r="L136" s="3" t="s">
         <v>598</v>
-      </c>
-      <c r="L136" s="3" t="s">
-        <v>599</v>
       </c>
       <c r="R136" t="s">
         <v>31</v>
@@ -9592,10 +9593,10 @@
         <v>80</v>
       </c>
       <c r="B137" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D137" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E137" t="s">
         <v>74</v>
@@ -9604,16 +9605,16 @@
         <v>75</v>
       </c>
       <c r="J137" t="s">
+        <v>599</v>
+      </c>
+      <c r="K137" t="s">
         <v>600</v>
       </c>
-      <c r="K137" t="s">
+      <c r="L137" s="3" t="s">
         <v>601</v>
       </c>
-      <c r="L137" s="3" t="s">
+      <c r="M137" t="s">
         <v>602</v>
-      </c>
-      <c r="M137" t="s">
-        <v>603</v>
       </c>
       <c r="R137" t="s">
         <v>31</v>
@@ -9636,10 +9637,10 @@
         <v>80</v>
       </c>
       <c r="B138" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D138" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E138" t="s">
         <v>74</v>
@@ -9648,16 +9649,16 @@
         <v>75</v>
       </c>
       <c r="J138" t="s">
+        <v>603</v>
+      </c>
+      <c r="K138" t="s">
         <v>604</v>
       </c>
-      <c r="K138" t="s">
+      <c r="L138" s="3" t="s">
         <v>605</v>
       </c>
-      <c r="L138" s="3" t="s">
-        <v>606</v>
-      </c>
       <c r="M138" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="R138" t="s">
         <v>31</v>
@@ -9680,10 +9681,10 @@
         <v>80</v>
       </c>
       <c r="B139" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D139" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E139" t="s">
         <v>74</v>
@@ -9692,16 +9693,16 @@
         <v>75</v>
       </c>
       <c r="J139" t="s">
+        <v>606</v>
+      </c>
+      <c r="K139" t="s">
         <v>607</v>
       </c>
-      <c r="K139" t="s">
+      <c r="L139" s="3" t="s">
         <v>608</v>
       </c>
-      <c r="L139" s="3" t="s">
-        <v>609</v>
-      </c>
       <c r="M139" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="R139" t="s">
         <v>31</v>
@@ -9724,10 +9725,10 @@
         <v>80</v>
       </c>
       <c r="B140" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D140" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E140" t="s">
         <v>74</v>
@@ -9736,16 +9737,16 @@
         <v>75</v>
       </c>
       <c r="J140" t="s">
+        <v>609</v>
+      </c>
+      <c r="K140" t="s">
         <v>610</v>
       </c>
-      <c r="K140" t="s">
+      <c r="L140" s="3" t="s">
         <v>611</v>
       </c>
-      <c r="L140" s="3" t="s">
-        <v>612</v>
-      </c>
       <c r="M140" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="R140" t="s">
         <v>31</v>
@@ -9768,10 +9769,10 @@
         <v>80</v>
       </c>
       <c r="B141" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D141" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E141" t="s">
         <v>74</v>
@@ -9780,16 +9781,16 @@
         <v>75</v>
       </c>
       <c r="J141" t="s">
+        <v>612</v>
+      </c>
+      <c r="K141" t="s">
         <v>613</v>
       </c>
-      <c r="K141" t="s">
+      <c r="L141" s="3" t="s">
         <v>614</v>
       </c>
-      <c r="L141" s="3" t="s">
-        <v>615</v>
-      </c>
       <c r="M141" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="R141" t="s">
         <v>31</v>
@@ -9809,28 +9810,28 @@
     </row>
     <row r="142" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
+        <v>615</v>
+      </c>
+      <c r="B142" t="s">
         <v>616</v>
       </c>
-      <c r="B142" t="s">
+      <c r="D142" t="s">
+        <v>564</v>
+      </c>
+      <c r="E142" t="s">
         <v>617</v>
       </c>
-      <c r="D142" t="s">
-        <v>565</v>
-      </c>
-      <c r="E142" t="s">
+      <c r="F142" t="s">
         <v>618</v>
       </c>
-      <c r="F142" t="s">
+      <c r="J142" t="s">
         <v>619</v>
       </c>
-      <c r="J142" t="s">
+      <c r="K142" t="s">
         <v>620</v>
       </c>
-      <c r="K142" t="s">
+      <c r="L142" s="3" t="s">
         <v>621</v>
-      </c>
-      <c r="L142" s="3" t="s">
-        <v>622</v>
       </c>
       <c r="R142" t="s">
         <v>31</v>
@@ -9850,28 +9851,28 @@
     </row>
     <row r="143" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
+        <v>615</v>
+      </c>
+      <c r="B143" t="s">
         <v>616</v>
       </c>
-      <c r="B143" t="s">
-        <v>617</v>
-      </c>
       <c r="D143" t="s">
+        <v>622</v>
+      </c>
+      <c r="E143" t="s">
         <v>623</v>
       </c>
-      <c r="E143" t="s">
+      <c r="F143" t="s">
         <v>624</v>
       </c>
-      <c r="F143" t="s">
+      <c r="J143" t="s">
         <v>625</v>
       </c>
-      <c r="J143" t="s">
+      <c r="K143" t="s">
         <v>626</v>
       </c>
-      <c r="K143" t="s">
+      <c r="L143" s="3" t="s">
         <v>627</v>
-      </c>
-      <c r="L143" s="3" t="s">
-        <v>628</v>
       </c>
       <c r="R143" t="s">
         <v>31</v>
@@ -9891,31 +9892,31 @@
     </row>
     <row r="144" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
+        <v>615</v>
+      </c>
+      <c r="B144" t="s">
         <v>616</v>
       </c>
-      <c r="B144" t="s">
-        <v>617</v>
-      </c>
       <c r="D144" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E144" t="s">
         <v>74</v>
       </c>
       <c r="F144" t="s">
+        <v>629</v>
+      </c>
+      <c r="J144" t="s">
         <v>630</v>
       </c>
-      <c r="J144" t="s">
+      <c r="K144" t="s">
         <v>631</v>
       </c>
-      <c r="K144" t="s">
+      <c r="L144" s="3" t="s">
         <v>632</v>
       </c>
-      <c r="L144" s="3" t="s">
+      <c r="M144" t="s">
         <v>633</v>
-      </c>
-      <c r="M144" t="s">
-        <v>634</v>
       </c>
       <c r="R144" t="s">
         <v>31</v>
@@ -9935,10 +9936,10 @@
     </row>
     <row r="145" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
+        <v>615</v>
+      </c>
+      <c r="B145" t="s">
         <v>616</v>
-      </c>
-      <c r="B145" t="s">
-        <v>617</v>
       </c>
       <c r="D145" t="s">
         <v>285</v>
@@ -9947,16 +9948,16 @@
         <v>42</v>
       </c>
       <c r="F145" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="J145" t="s">
+        <v>634</v>
+      </c>
+      <c r="K145" t="s">
         <v>635</v>
       </c>
-      <c r="K145" t="s">
+      <c r="L145" s="3" t="s">
         <v>636</v>
-      </c>
-      <c r="L145" s="3" t="s">
-        <v>637</v>
       </c>
       <c r="R145" t="s">
         <v>31</v>
@@ -9976,13 +9977,13 @@
     </row>
     <row r="146" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
+        <v>637</v>
+      </c>
+      <c r="B146" t="s">
         <v>638</v>
       </c>
-      <c r="B146" t="s">
-        <v>639</v>
-      </c>
       <c r="D146" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E146" t="s">
         <v>42</v>
@@ -9991,10 +9992,10 @@
         <v>43</v>
       </c>
       <c r="J146" t="s">
+        <v>639</v>
+      </c>
+      <c r="L146" s="3" t="s">
         <v>640</v>
-      </c>
-      <c r="L146" s="3" t="s">
-        <v>641</v>
       </c>
       <c r="R146" t="s">
         <v>31</v>
@@ -10014,22 +10015,22 @@
     </row>
     <row r="147" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
+        <v>637</v>
+      </c>
+      <c r="B147" t="s">
         <v>638</v>
       </c>
-      <c r="B147" t="s">
-        <v>639</v>
-      </c>
       <c r="D147" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="F147" t="s">
         <v>295</v>
       </c>
       <c r="J147" t="s">
+        <v>642</v>
+      </c>
+      <c r="L147" s="3" t="s">
         <v>643</v>
-      </c>
-      <c r="L147" s="3" t="s">
-        <v>644</v>
       </c>
       <c r="R147" t="s">
         <v>31</v>
@@ -10049,13 +10050,13 @@
     </row>
     <row r="148" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
+        <v>637</v>
+      </c>
+      <c r="B148" t="s">
         <v>638</v>
       </c>
-      <c r="B148" t="s">
-        <v>639</v>
-      </c>
       <c r="D148" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E148" t="s">
         <v>120</v>
@@ -10064,13 +10065,13 @@
         <v>121</v>
       </c>
       <c r="J148" t="s">
+        <v>644</v>
+      </c>
+      <c r="K148" t="s">
         <v>645</v>
       </c>
-      <c r="K148" t="s">
+      <c r="L148" s="3" t="s">
         <v>646</v>
-      </c>
-      <c r="L148" s="3" t="s">
-        <v>647</v>
       </c>
       <c r="R148" t="s">
         <v>31</v>
@@ -10090,10 +10091,10 @@
     </row>
     <row r="149" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
+        <v>637</v>
+      </c>
+      <c r="B149" t="s">
         <v>638</v>
-      </c>
-      <c r="B149" t="s">
-        <v>639</v>
       </c>
       <c r="D149" t="s">
         <v>90</v>
@@ -10105,13 +10106,13 @@
         <v>121</v>
       </c>
       <c r="J149" t="s">
+        <v>647</v>
+      </c>
+      <c r="K149" t="s">
+        <v>647</v>
+      </c>
+      <c r="L149" s="3" t="s">
         <v>648</v>
-      </c>
-      <c r="K149" t="s">
-        <v>648</v>
-      </c>
-      <c r="L149" s="3" t="s">
-        <v>649</v>
       </c>
       <c r="R149" t="s">
         <v>31</v>
@@ -10134,19 +10135,19 @@
         <v>376</v>
       </c>
       <c r="B150" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D150" t="s">
         <v>259</v>
       </c>
       <c r="F150" t="s">
+        <v>650</v>
+      </c>
+      <c r="J150" t="s">
         <v>651</v>
       </c>
-      <c r="J150" t="s">
+      <c r="L150" s="3" t="s">
         <v>652</v>
-      </c>
-      <c r="L150" s="3" t="s">
-        <v>653</v>
       </c>
       <c r="R150" t="s">
         <v>31</v>
@@ -10169,10 +10170,10 @@
         <v>376</v>
       </c>
       <c r="B151" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D151" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="E151" t="s">
         <v>74</v>
@@ -10181,13 +10182,13 @@
         <v>389</v>
       </c>
       <c r="J151" t="s">
+        <v>654</v>
+      </c>
+      <c r="K151" t="s">
         <v>655</v>
       </c>
-      <c r="K151" t="s">
+      <c r="L151" s="3" t="s">
         <v>656</v>
-      </c>
-      <c r="L151" s="3" t="s">
-        <v>657</v>
       </c>
       <c r="R151" t="s">
         <v>31</v>
@@ -10210,22 +10211,22 @@
         <v>376</v>
       </c>
       <c r="B152" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D152" t="s">
         <v>197</v>
       </c>
       <c r="E152" t="s">
+        <v>657</v>
+      </c>
+      <c r="F152" t="s">
         <v>658</v>
       </c>
-      <c r="F152" t="s">
+      <c r="J152" t="s">
         <v>659</v>
       </c>
-      <c r="J152" t="s">
+      <c r="L152" s="3" t="s">
         <v>660</v>
-      </c>
-      <c r="L152" s="3" t="s">
-        <v>661</v>
       </c>
       <c r="R152" t="s">
         <v>31</v>
@@ -10248,7 +10249,7 @@
         <v>376</v>
       </c>
       <c r="B153" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D153" t="s">
         <v>174</v>
@@ -10266,7 +10267,7 @@
         <v>153</v>
       </c>
       <c r="L153" s="3" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="M153" t="s">
         <v>151</v>
@@ -10289,10 +10290,10 @@
     </row>
     <row r="154" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B154" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D154" t="s">
         <v>294</v>
@@ -10304,13 +10305,13 @@
         <v>43</v>
       </c>
       <c r="J154" t="s">
+        <v>663</v>
+      </c>
+      <c r="K154" t="s">
         <v>664</v>
       </c>
-      <c r="K154" t="s">
+      <c r="L154" s="3" t="s">
         <v>665</v>
-      </c>
-      <c r="L154" s="3" t="s">
-        <v>666</v>
       </c>
       <c r="R154" t="s">
         <v>31</v>
@@ -10330,13 +10331,13 @@
     </row>
     <row r="155" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B155" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D155" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E155" t="s">
         <v>74</v>
@@ -10345,13 +10346,13 @@
         <v>75</v>
       </c>
       <c r="J155" t="s">
+        <v>667</v>
+      </c>
+      <c r="K155" t="s">
         <v>668</v>
       </c>
-      <c r="K155" t="s">
+      <c r="L155" s="3" t="s">
         <v>669</v>
-      </c>
-      <c r="L155" s="3" t="s">
-        <v>670</v>
       </c>
       <c r="R155" t="s">
         <v>31</v>
@@ -10371,13 +10372,13 @@
     </row>
     <row r="156" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B156" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D156" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E156" t="s">
         <v>192</v>
@@ -10386,13 +10387,13 @@
         <v>193</v>
       </c>
       <c r="J156" t="s">
+        <v>671</v>
+      </c>
+      <c r="K156" t="s">
         <v>672</v>
       </c>
-      <c r="K156" t="s">
+      <c r="L156" s="3" t="s">
         <v>673</v>
-      </c>
-      <c r="L156" s="3" t="s">
-        <v>674</v>
       </c>
       <c r="R156" t="s">
         <v>31</v>
@@ -10412,13 +10413,13 @@
     </row>
     <row r="157" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B157" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D157" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="E157" t="s">
         <v>74</v>
@@ -10427,13 +10428,13 @@
         <v>75</v>
       </c>
       <c r="J157" t="s">
+        <v>675</v>
+      </c>
+      <c r="K157" t="s">
         <v>676</v>
       </c>
-      <c r="K157" t="s">
+      <c r="L157" s="3" t="s">
         <v>677</v>
-      </c>
-      <c r="L157" s="3" t="s">
-        <v>678</v>
       </c>
       <c r="R157" t="s">
         <v>31</v>
@@ -10453,28 +10454,28 @@
     </row>
     <row r="158" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
+        <v>678</v>
+      </c>
+      <c r="B158" t="s">
         <v>679</v>
       </c>
-      <c r="B158" t="s">
+      <c r="D158" t="s">
         <v>680</v>
-      </c>
-      <c r="D158" t="s">
-        <v>681</v>
       </c>
       <c r="E158" t="s">
         <v>367</v>
       </c>
       <c r="F158" t="s">
+        <v>681</v>
+      </c>
+      <c r="J158" t="s">
         <v>682</v>
       </c>
-      <c r="J158" t="s">
+      <c r="K158" t="s">
         <v>683</v>
       </c>
-      <c r="K158" t="s">
+      <c r="L158" s="3" t="s">
         <v>684</v>
-      </c>
-      <c r="L158" s="3" t="s">
-        <v>685</v>
       </c>
       <c r="R158" t="s">
         <v>31</v>
@@ -10494,13 +10495,13 @@
     </row>
     <row r="159" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
+        <v>678</v>
+      </c>
+      <c r="B159" t="s">
         <v>679</v>
       </c>
-      <c r="B159" t="s">
-        <v>680</v>
-      </c>
       <c r="D159" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E159" t="s">
         <v>102</v>
@@ -10509,13 +10510,13 @@
         <v>103</v>
       </c>
       <c r="J159" t="s">
+        <v>686</v>
+      </c>
+      <c r="K159" t="s">
         <v>687</v>
       </c>
-      <c r="K159" t="s">
+      <c r="L159" s="3" t="s">
         <v>688</v>
-      </c>
-      <c r="L159" s="3" t="s">
-        <v>689</v>
       </c>
       <c r="R159" t="s">
         <v>31</v>
@@ -10535,10 +10536,10 @@
     </row>
     <row r="160" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
+        <v>678</v>
+      </c>
+      <c r="B160" t="s">
         <v>679</v>
-      </c>
-      <c r="B160" t="s">
-        <v>680</v>
       </c>
       <c r="D160" t="s">
         <v>285</v>
@@ -10550,13 +10551,13 @@
         <v>103</v>
       </c>
       <c r="J160" t="s">
+        <v>689</v>
+      </c>
+      <c r="K160" t="s">
         <v>690</v>
       </c>
-      <c r="K160" t="s">
+      <c r="L160" s="3" t="s">
         <v>691</v>
-      </c>
-      <c r="L160" s="3" t="s">
-        <v>692</v>
       </c>
       <c r="R160" t="s">
         <v>31</v>
@@ -10576,31 +10577,31 @@
     </row>
     <row r="161" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
+        <v>678</v>
+      </c>
+      <c r="B161" t="s">
         <v>679</v>
       </c>
-      <c r="B161" t="s">
-        <v>680</v>
-      </c>
       <c r="D161" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E161" t="s">
         <v>107</v>
       </c>
       <c r="F161" t="s">
+        <v>692</v>
+      </c>
+      <c r="J161" t="s">
         <v>693</v>
       </c>
-      <c r="J161" t="s">
+      <c r="K161" t="s">
         <v>694</v>
       </c>
-      <c r="K161" t="s">
+      <c r="L161" s="3" t="s">
         <v>695</v>
       </c>
-      <c r="L161" s="3" t="s">
+      <c r="M161" t="s">
         <v>696</v>
-      </c>
-      <c r="M161" t="s">
-        <v>697</v>
       </c>
       <c r="R161" t="s">
         <v>31</v>
@@ -10620,10 +10621,10 @@
     </row>
     <row r="162" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
+        <v>697</v>
+      </c>
+      <c r="B162" t="s">
         <v>698</v>
-      </c>
-      <c r="B162" t="s">
-        <v>699</v>
       </c>
       <c r="D162" t="s">
         <v>124</v>
@@ -10632,13 +10633,13 @@
         <v>367</v>
       </c>
       <c r="F162" t="s">
+        <v>699</v>
+      </c>
+      <c r="J162" t="s">
         <v>700</v>
       </c>
-      <c r="J162" t="s">
+      <c r="L162" s="3" t="s">
         <v>701</v>
-      </c>
-      <c r="L162" s="3" t="s">
-        <v>702</v>
       </c>
       <c r="R162" t="s">
         <v>31</v>
@@ -10658,13 +10659,13 @@
     </row>
     <row r="163" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
+        <v>697</v>
+      </c>
+      <c r="B163" t="s">
         <v>698</v>
       </c>
-      <c r="B163" t="s">
-        <v>699</v>
-      </c>
       <c r="D163" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="E163" t="s">
         <v>56</v>
@@ -10673,16 +10674,16 @@
         <v>57</v>
       </c>
       <c r="J163" t="s">
+        <v>703</v>
+      </c>
+      <c r="L163" s="3" t="s">
         <v>704</v>
       </c>
-      <c r="L163" s="3" t="s">
+      <c r="R163" t="s">
+        <v>31</v>
+      </c>
+      <c r="S163" t="s">
         <v>705</v>
-      </c>
-      <c r="R163" t="s">
-        <v>31</v>
-      </c>
-      <c r="S163" t="s">
-        <v>706</v>
       </c>
       <c r="T163" s="1">
         <v>83</v>
@@ -10696,34 +10697,34 @@
     </row>
     <row r="164" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
+        <v>697</v>
+      </c>
+      <c r="B164" t="s">
         <v>698</v>
       </c>
-      <c r="B164" t="s">
-        <v>699</v>
-      </c>
       <c r="D164" t="s">
+        <v>706</v>
+      </c>
+      <c r="E164" t="s">
         <v>707</v>
       </c>
-      <c r="E164" t="s">
+      <c r="F164" t="s">
         <v>708</v>
       </c>
-      <c r="F164" t="s">
+      <c r="J164" t="s">
         <v>709</v>
       </c>
-      <c r="J164" t="s">
+      <c r="K164" t="s">
         <v>710</v>
       </c>
-      <c r="K164" t="s">
+      <c r="L164" s="3" t="s">
         <v>711</v>
       </c>
-      <c r="L164" s="3" t="s">
-        <v>712</v>
-      </c>
       <c r="R164" t="s">
         <v>31</v>
       </c>
       <c r="S164" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="T164" s="1">
         <v>54</v>
@@ -10737,28 +10738,28 @@
     </row>
     <row r="165" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
+        <v>697</v>
+      </c>
+      <c r="B165" t="s">
         <v>698</v>
       </c>
-      <c r="B165" t="s">
-        <v>699</v>
-      </c>
       <c r="D165" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E165" t="s">
         <v>367</v>
       </c>
       <c r="F165" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="J165" t="s">
+        <v>713</v>
+      </c>
+      <c r="K165" t="s">
+        <v>713</v>
+      </c>
+      <c r="L165" s="3" t="s">
         <v>714</v>
-      </c>
-      <c r="K165" t="s">
-        <v>714</v>
-      </c>
-      <c r="L165" s="3" t="s">
-        <v>715</v>
       </c>
       <c r="R165" t="s">
         <v>31</v>
@@ -10778,10 +10779,10 @@
     </row>
     <row r="166" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
+        <v>715</v>
+      </c>
+      <c r="B166" t="s">
         <v>716</v>
-      </c>
-      <c r="B166" t="s">
-        <v>717</v>
       </c>
       <c r="D166" t="s">
         <v>127</v>
@@ -10793,13 +10794,13 @@
         <v>186</v>
       </c>
       <c r="J166" t="s">
+        <v>717</v>
+      </c>
+      <c r="K166" t="s">
         <v>718</v>
       </c>
-      <c r="K166" t="s">
+      <c r="L166" s="3" t="s">
         <v>719</v>
-      </c>
-      <c r="L166" s="3" t="s">
-        <v>720</v>
       </c>
       <c r="R166" t="s">
         <v>31</v>
@@ -10819,10 +10820,10 @@
     </row>
     <row r="167" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
+        <v>715</v>
+      </c>
+      <c r="B167" t="s">
         <v>716</v>
-      </c>
-      <c r="B167" t="s">
-        <v>717</v>
       </c>
       <c r="D167" t="s">
         <v>371</v>
@@ -10834,13 +10835,13 @@
         <v>186</v>
       </c>
       <c r="J167" t="s">
+        <v>720</v>
+      </c>
+      <c r="K167" t="s">
         <v>721</v>
       </c>
-      <c r="K167" t="s">
+      <c r="L167" s="3" t="s">
         <v>722</v>
-      </c>
-      <c r="L167" s="3" t="s">
-        <v>723</v>
       </c>
       <c r="R167" t="s">
         <v>31</v>
@@ -10860,13 +10861,13 @@
     </row>
     <row r="168" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
+        <v>715</v>
+      </c>
+      <c r="B168" t="s">
         <v>716</v>
       </c>
-      <c r="B168" t="s">
-        <v>717</v>
-      </c>
       <c r="D168" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="E168" t="s">
         <v>185</v>
@@ -10875,13 +10876,13 @@
         <v>186</v>
       </c>
       <c r="J168" t="s">
+        <v>723</v>
+      </c>
+      <c r="K168" t="s">
         <v>724</v>
       </c>
-      <c r="K168" t="s">
+      <c r="L168" s="3" t="s">
         <v>725</v>
-      </c>
-      <c r="L168" s="3" t="s">
-        <v>726</v>
       </c>
       <c r="R168" t="s">
         <v>31</v>
@@ -10901,13 +10902,13 @@
     </row>
     <row r="169" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
+        <v>715</v>
+      </c>
+      <c r="B169" t="s">
         <v>716</v>
       </c>
-      <c r="B169" t="s">
-        <v>717</v>
-      </c>
       <c r="D169" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E169" t="s">
         <v>185</v>
@@ -10916,13 +10917,13 @@
         <v>186</v>
       </c>
       <c r="J169" t="s">
+        <v>726</v>
+      </c>
+      <c r="K169" t="s">
         <v>727</v>
       </c>
-      <c r="K169" t="s">
+      <c r="L169" s="3" t="s">
         <v>728</v>
-      </c>
-      <c r="L169" s="3" t="s">
-        <v>729</v>
       </c>
       <c r="R169" t="s">
         <v>31</v>
@@ -10942,13 +10943,13 @@
     </row>
     <row r="170" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
+        <v>729</v>
+      </c>
+      <c r="B170" t="s">
         <v>730</v>
       </c>
-      <c r="B170" t="s">
+      <c r="D170" t="s">
         <v>731</v>
-      </c>
-      <c r="D170" t="s">
-        <v>732</v>
       </c>
       <c r="E170" t="s">
         <v>42</v>
@@ -10957,13 +10958,13 @@
         <v>43</v>
       </c>
       <c r="J170" t="s">
+        <v>732</v>
+      </c>
+      <c r="K170" t="s">
         <v>733</v>
       </c>
-      <c r="K170" t="s">
+      <c r="L170" s="3" t="s">
         <v>734</v>
-      </c>
-      <c r="L170" s="3" t="s">
-        <v>735</v>
       </c>
       <c r="R170" t="s">
         <v>31</v>
@@ -10983,28 +10984,28 @@
     </row>
     <row r="171" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
+        <v>729</v>
+      </c>
+      <c r="B171" t="s">
         <v>730</v>
       </c>
-      <c r="B171" t="s">
-        <v>731</v>
-      </c>
       <c r="D171" t="s">
+        <v>735</v>
+      </c>
+      <c r="E171" t="s">
         <v>736</v>
       </c>
-      <c r="E171" t="s">
+      <c r="F171" t="s">
         <v>737</v>
       </c>
-      <c r="F171" t="s">
+      <c r="J171" t="s">
         <v>738</v>
       </c>
-      <c r="J171" t="s">
+      <c r="K171" t="s">
         <v>739</v>
       </c>
-      <c r="K171" t="s">
+      <c r="L171" s="3" t="s">
         <v>740</v>
-      </c>
-      <c r="L171" s="3" t="s">
-        <v>741</v>
       </c>
       <c r="R171" t="s">
         <v>31</v>
@@ -11024,13 +11025,13 @@
     </row>
     <row r="172" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
+        <v>729</v>
+      </c>
+      <c r="B172" t="s">
         <v>730</v>
       </c>
-      <c r="B172" t="s">
-        <v>731</v>
-      </c>
       <c r="D172" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="E172" t="s">
         <v>120</v>
@@ -11039,13 +11040,13 @@
         <v>121</v>
       </c>
       <c r="J172" t="s">
+        <v>742</v>
+      </c>
+      <c r="K172" t="s">
+        <v>742</v>
+      </c>
+      <c r="L172" s="3" t="s">
         <v>743</v>
-      </c>
-      <c r="K172" t="s">
-        <v>743</v>
-      </c>
-      <c r="L172" s="3" t="s">
-        <v>744</v>
       </c>
       <c r="R172" t="s">
         <v>31</v>
@@ -11065,13 +11066,13 @@
     </row>
     <row r="173" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
+        <v>729</v>
+      </c>
+      <c r="B173" t="s">
         <v>730</v>
       </c>
-      <c r="B173" t="s">
-        <v>731</v>
-      </c>
       <c r="D173" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="E173" t="s">
         <v>120</v>
@@ -11080,13 +11081,13 @@
         <v>121</v>
       </c>
       <c r="J173" t="s">
+        <v>745</v>
+      </c>
+      <c r="K173" t="s">
+        <v>745</v>
+      </c>
+      <c r="L173" s="3" t="s">
         <v>746</v>
-      </c>
-      <c r="K173" t="s">
-        <v>746</v>
-      </c>
-      <c r="L173" s="3" t="s">
-        <v>747</v>
       </c>
       <c r="R173" t="s">
         <v>31</v>
@@ -11106,13 +11107,13 @@
     </row>
     <row r="174" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
+        <v>747</v>
+      </c>
+      <c r="B174" t="s">
         <v>748</v>
       </c>
-      <c r="B174" t="s">
-        <v>749</v>
-      </c>
       <c r="D174" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="E174" t="s">
         <v>120</v>
@@ -11127,7 +11128,7 @@
         <v>317</v>
       </c>
       <c r="L174" s="3" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="R174" t="s">
         <v>31</v>
@@ -11147,10 +11148,10 @@
     </row>
     <row r="175" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
+        <v>747</v>
+      </c>
+      <c r="B175" t="s">
         <v>748</v>
-      </c>
-      <c r="B175" t="s">
-        <v>749</v>
       </c>
       <c r="D175" t="s">
         <v>61</v>
@@ -11162,13 +11163,13 @@
         <v>121</v>
       </c>
       <c r="J175" t="s">
+        <v>750</v>
+      </c>
+      <c r="K175" t="s">
         <v>751</v>
       </c>
-      <c r="K175" t="s">
+      <c r="L175" s="3" t="s">
         <v>752</v>
-      </c>
-      <c r="L175" s="3" t="s">
-        <v>753</v>
       </c>
       <c r="R175" t="s">
         <v>31</v>
@@ -11188,13 +11189,13 @@
     </row>
     <row r="176" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
+        <v>747</v>
+      </c>
+      <c r="B176" t="s">
         <v>748</v>
       </c>
-      <c r="B176" t="s">
-        <v>749</v>
-      </c>
       <c r="D176" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E176" t="s">
         <v>311</v>
@@ -11203,16 +11204,16 @@
         <v>312</v>
       </c>
       <c r="J176" t="s">
+        <v>754</v>
+      </c>
+      <c r="K176" t="s">
         <v>755</v>
       </c>
-      <c r="K176" t="s">
+      <c r="L176" s="3" t="s">
         <v>756</v>
       </c>
-      <c r="L176" s="3" t="s">
+      <c r="M176" t="s">
         <v>757</v>
-      </c>
-      <c r="M176" t="s">
-        <v>758</v>
       </c>
       <c r="R176" t="s">
         <v>31</v>
@@ -11232,13 +11233,13 @@
     </row>
     <row r="177" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
+        <v>747</v>
+      </c>
+      <c r="B177" t="s">
         <v>748</v>
       </c>
-      <c r="B177" t="s">
-        <v>749</v>
-      </c>
       <c r="D177" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E177" t="s">
         <v>311</v>
@@ -11247,16 +11248,16 @@
         <v>312</v>
       </c>
       <c r="J177" t="s">
+        <v>759</v>
+      </c>
+      <c r="K177" t="s">
         <v>760</v>
       </c>
-      <c r="K177" t="s">
+      <c r="L177" s="3" t="s">
         <v>761</v>
       </c>
-      <c r="L177" s="3" t="s">
-        <v>762</v>
-      </c>
       <c r="M177" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="R177" t="s">
         <v>31</v>
@@ -11276,34 +11277,34 @@
     </row>
     <row r="178" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
+        <v>762</v>
+      </c>
+      <c r="B178" t="s">
         <v>763</v>
-      </c>
-      <c r="B178" t="s">
-        <v>764</v>
       </c>
       <c r="D178" t="s">
         <v>41</v>
       </c>
       <c r="E178" t="s">
+        <v>764</v>
+      </c>
+      <c r="F178" t="s">
         <v>765</v>
       </c>
-      <c r="F178" t="s">
+      <c r="J178" t="s">
         <v>766</v>
       </c>
-      <c r="J178" t="s">
+      <c r="K178" t="s">
         <v>767</v>
       </c>
-      <c r="K178" t="s">
+      <c r="L178" s="11" t="s">
+        <v>1192</v>
+      </c>
+      <c r="R178" t="s">
         <v>768</v>
       </c>
-      <c r="L178" s="3" t="s">
-        <v>769</v>
-      </c>
-      <c r="R178" t="s">
-        <v>770</v>
-      </c>
       <c r="S178" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="T178" s="1">
         <v>313</v>
@@ -11317,13 +11318,13 @@
     </row>
     <row r="179" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
+        <v>762</v>
+      </c>
+      <c r="B179" t="s">
         <v>763</v>
       </c>
-      <c r="B179" t="s">
-        <v>764</v>
-      </c>
       <c r="D179" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="E179" t="s">
         <v>107</v>
@@ -11335,10 +11336,10 @@
         <v>217</v>
       </c>
       <c r="K179" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="L179" s="3" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="R179" t="s">
         <v>31</v>
@@ -11358,10 +11359,10 @@
     </row>
     <row r="180" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
+        <v>762</v>
+      </c>
+      <c r="B180" t="s">
         <v>763</v>
-      </c>
-      <c r="B180" t="s">
-        <v>764</v>
       </c>
       <c r="D180" t="s">
         <v>281</v>
@@ -11373,13 +11374,13 @@
         <v>312</v>
       </c>
       <c r="J180" t="s">
+        <v>772</v>
+      </c>
+      <c r="K180" t="s">
+        <v>773</v>
+      </c>
+      <c r="L180" s="3" t="s">
         <v>774</v>
-      </c>
-      <c r="K180" t="s">
-        <v>775</v>
-      </c>
-      <c r="L180" s="3" t="s">
-        <v>776</v>
       </c>
       <c r="R180" t="s">
         <v>31</v>
@@ -11399,10 +11400,10 @@
     </row>
     <row r="181" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
+        <v>762</v>
+      </c>
+      <c r="B181" t="s">
         <v>763</v>
-      </c>
-      <c r="B181" t="s">
-        <v>764</v>
       </c>
       <c r="D181" t="s">
         <v>25</v>
@@ -11414,13 +11415,13 @@
         <v>252</v>
       </c>
       <c r="J181" t="s">
+        <v>775</v>
+      </c>
+      <c r="K181" t="s">
+        <v>776</v>
+      </c>
+      <c r="L181" s="3" t="s">
         <v>777</v>
-      </c>
-      <c r="K181" t="s">
-        <v>778</v>
-      </c>
-      <c r="L181" s="3" t="s">
-        <v>779</v>
       </c>
       <c r="R181" t="s">
         <v>31</v>
@@ -11440,22 +11441,22 @@
     </row>
     <row r="182" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="B182" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="D182" t="s">
         <v>259</v>
       </c>
       <c r="F182" t="s">
+        <v>780</v>
+      </c>
+      <c r="J182" t="s">
+        <v>781</v>
+      </c>
+      <c r="L182" s="3" t="s">
         <v>782</v>
-      </c>
-      <c r="J182" t="s">
-        <v>783</v>
-      </c>
-      <c r="L182" s="3" t="s">
-        <v>784</v>
       </c>
       <c r="R182" t="s">
         <v>31</v>
@@ -11475,13 +11476,13 @@
     </row>
     <row r="183" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="B183" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="D183" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E183" t="s">
         <v>120</v>
@@ -11490,13 +11491,13 @@
         <v>121</v>
       </c>
       <c r="J183" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="K183" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="L183" s="3" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="R183" t="s">
         <v>31</v>
@@ -11516,13 +11517,13 @@
     </row>
     <row r="184" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="B184" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="D184" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="E184" t="s">
         <v>120</v>
@@ -11531,13 +11532,13 @@
         <v>121</v>
       </c>
       <c r="J184" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="K184" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="L184" s="3" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="R184" t="s">
         <v>31</v>
@@ -11557,25 +11558,25 @@
     </row>
     <row r="185" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
+        <v>788</v>
+      </c>
+      <c r="B185" t="s">
+        <v>789</v>
+      </c>
+      <c r="D185" t="s">
         <v>790</v>
       </c>
-      <c r="B185" t="s">
+      <c r="E185" t="s">
         <v>791</v>
       </c>
-      <c r="D185" t="s">
+      <c r="F185" t="s">
         <v>792</v>
       </c>
-      <c r="E185" t="s">
+      <c r="J185" t="s">
         <v>793</v>
       </c>
-      <c r="F185" t="s">
+      <c r="L185" s="3" t="s">
         <v>794</v>
-      </c>
-      <c r="J185" t="s">
-        <v>795</v>
-      </c>
-      <c r="L185" s="3" t="s">
-        <v>796</v>
       </c>
       <c r="R185" t="s">
         <v>31</v>
@@ -11595,22 +11596,22 @@
     </row>
     <row r="186" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B186" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="D186" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F186" t="s">
         <v>295</v>
       </c>
       <c r="J186" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="L186" s="3" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="R186" t="s">
         <v>31</v>
@@ -11630,10 +11631,10 @@
     </row>
     <row r="187" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B187" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="D187" t="s">
         <v>55</v>
@@ -11645,13 +11646,13 @@
         <v>121</v>
       </c>
       <c r="J187" t="s">
+        <v>799</v>
+      </c>
+      <c r="K187" t="s">
+        <v>800</v>
+      </c>
+      <c r="L187" s="3" t="s">
         <v>801</v>
-      </c>
-      <c r="K187" t="s">
-        <v>802</v>
-      </c>
-      <c r="L187" s="3" t="s">
-        <v>803</v>
       </c>
       <c r="R187" t="s">
         <v>31</v>
@@ -11671,10 +11672,10 @@
     </row>
     <row r="188" spans="1:23" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="8" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B188" s="8" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="D188" s="8" t="s">
         <v>124</v>
@@ -11683,16 +11684,16 @@
         <v>410</v>
       </c>
       <c r="F188" s="8" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="J188" s="8" t="s">
+        <v>802</v>
+      </c>
+      <c r="K188" s="8" t="s">
+        <v>803</v>
+      </c>
+      <c r="L188" s="9" t="s">
         <v>804</v>
-      </c>
-      <c r="K188" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="L188" s="9" t="s">
-        <v>806</v>
       </c>
       <c r="R188" s="8" t="s">
         <v>31</v>
@@ -11712,10 +11713,10 @@
     </row>
     <row r="189" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B189" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="D189" t="s">
         <v>364</v>
@@ -11724,16 +11725,16 @@
         <v>402</v>
       </c>
       <c r="F189" t="s">
+        <v>805</v>
+      </c>
+      <c r="J189" t="s">
+        <v>806</v>
+      </c>
+      <c r="K189" t="s">
+        <v>806</v>
+      </c>
+      <c r="L189" s="3" t="s">
         <v>807</v>
-      </c>
-      <c r="J189" t="s">
-        <v>808</v>
-      </c>
-      <c r="K189" t="s">
-        <v>808</v>
-      </c>
-      <c r="L189" s="3" t="s">
-        <v>809</v>
       </c>
       <c r="R189" t="s">
         <v>31</v>
@@ -11753,10 +11754,10 @@
     </row>
     <row r="190" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B190" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="D190" t="s">
         <v>221</v>
@@ -11768,22 +11769,22 @@
         <v>389</v>
       </c>
       <c r="J190" t="s">
+        <v>809</v>
+      </c>
+      <c r="L190" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="R190" t="s">
+        <v>31</v>
+      </c>
+      <c r="S190" t="s">
+        <v>32</v>
+      </c>
+      <c r="T190" s="1" t="s">
         <v>811</v>
       </c>
-      <c r="L190" s="3" t="s">
+      <c r="U190" s="1" t="s">
         <v>812</v>
-      </c>
-      <c r="R190" t="s">
-        <v>31</v>
-      </c>
-      <c r="S190" t="s">
-        <v>32</v>
-      </c>
-      <c r="T190" s="1" t="s">
-        <v>813</v>
-      </c>
-      <c r="U190" s="1" t="s">
-        <v>814</v>
       </c>
       <c r="W190" s="1">
         <v>3</v>
@@ -11791,22 +11792,22 @@
     </row>
     <row r="191" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B191" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="D191" t="s">
         <v>55</v>
       </c>
       <c r="F191" t="s">
+        <v>813</v>
+      </c>
+      <c r="J191" t="s">
+        <v>814</v>
+      </c>
+      <c r="L191" s="3" t="s">
         <v>815</v>
-      </c>
-      <c r="J191" t="s">
-        <v>816</v>
-      </c>
-      <c r="L191" s="3" t="s">
-        <v>817</v>
       </c>
       <c r="R191" t="s">
         <v>31</v>
@@ -11826,28 +11827,28 @@
     </row>
     <row r="192" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B192" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="D192" t="s">
         <v>119</v>
       </c>
       <c r="E192" t="s">
+        <v>816</v>
+      </c>
+      <c r="F192" t="s">
+        <v>817</v>
+      </c>
+      <c r="J192" t="s">
         <v>818</v>
       </c>
-      <c r="F192" t="s">
+      <c r="K192" t="s">
         <v>819</v>
       </c>
-      <c r="J192" t="s">
+      <c r="L192" s="3" t="s">
         <v>820</v>
-      </c>
-      <c r="K192" t="s">
-        <v>821</v>
-      </c>
-      <c r="L192" s="3" t="s">
-        <v>822</v>
       </c>
       <c r="R192" t="s">
         <v>31</v>
@@ -11867,25 +11868,25 @@
     </row>
     <row r="193" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B193" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="D193" t="s">
         <v>221</v>
       </c>
       <c r="E193" t="s">
+        <v>821</v>
+      </c>
+      <c r="F193" t="s">
+        <v>822</v>
+      </c>
+      <c r="J193" t="s">
         <v>823</v>
       </c>
-      <c r="F193" t="s">
+      <c r="L193" s="3" t="s">
         <v>824</v>
-      </c>
-      <c r="J193" t="s">
-        <v>825</v>
-      </c>
-      <c r="L193" s="3" t="s">
-        <v>826</v>
       </c>
       <c r="R193" t="s">
         <v>31</v>
@@ -11905,25 +11906,25 @@
     </row>
     <row r="194" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
+        <v>825</v>
+      </c>
+      <c r="B194" t="s">
+        <v>826</v>
+      </c>
+      <c r="D194" t="s">
         <v>827</v>
       </c>
-      <c r="B194" t="s">
+      <c r="F194" t="s">
         <v>828</v>
       </c>
-      <c r="D194" t="s">
+      <c r="J194" t="s">
         <v>829</v>
       </c>
-      <c r="F194" t="s">
+      <c r="K194" t="s">
         <v>830</v>
       </c>
-      <c r="J194" t="s">
+      <c r="L194" s="3" t="s">
         <v>831</v>
-      </c>
-      <c r="K194" t="s">
-        <v>832</v>
-      </c>
-      <c r="L194" s="3" t="s">
-        <v>833</v>
       </c>
       <c r="R194" t="s">
         <v>31</v>
@@ -11943,28 +11944,28 @@
     </row>
     <row r="195" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="B195" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="D195" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E195" t="s">
+        <v>832</v>
+      </c>
+      <c r="F195" t="s">
+        <v>833</v>
+      </c>
+      <c r="J195" t="s">
         <v>834</v>
       </c>
-      <c r="F195" t="s">
+      <c r="K195" t="s">
         <v>835</v>
       </c>
-      <c r="J195" t="s">
+      <c r="L195" s="3" t="s">
         <v>836</v>
-      </c>
-      <c r="K195" t="s">
-        <v>837</v>
-      </c>
-      <c r="L195" s="3" t="s">
-        <v>838</v>
       </c>
       <c r="R195" t="s">
         <v>31</v>
@@ -11984,28 +11985,28 @@
     </row>
     <row r="196" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="B196" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="D196" t="s">
         <v>90</v>
       </c>
       <c r="E196" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="F196" t="s">
+        <v>837</v>
+      </c>
+      <c r="J196" t="s">
+        <v>838</v>
+      </c>
+      <c r="K196" t="s">
         <v>839</v>
       </c>
-      <c r="J196" t="s">
+      <c r="L196" s="3" t="s">
         <v>840</v>
-      </c>
-      <c r="K196" t="s">
-        <v>841</v>
-      </c>
-      <c r="L196" s="3" t="s">
-        <v>842</v>
       </c>
       <c r="R196" t="s">
         <v>31</v>
@@ -12025,28 +12026,28 @@
     </row>
     <row r="197" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="B197" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="D197" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E197" t="s">
+        <v>841</v>
+      </c>
+      <c r="F197" t="s">
+        <v>842</v>
+      </c>
+      <c r="J197" t="s">
         <v>843</v>
       </c>
-      <c r="F197" t="s">
+      <c r="K197" t="s">
         <v>844</v>
       </c>
-      <c r="J197" t="s">
+      <c r="L197" s="3" t="s">
         <v>845</v>
-      </c>
-      <c r="K197" t="s">
-        <v>846</v>
-      </c>
-      <c r="L197" s="3" t="s">
-        <v>847</v>
       </c>
       <c r="R197" t="s">
         <v>31</v>
@@ -12066,28 +12067,28 @@
     </row>
     <row r="198" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="B198" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="D198" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="E198" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="F198" t="s">
         <v>68</v>
       </c>
       <c r="J198" t="s">
+        <v>848</v>
+      </c>
+      <c r="K198" t="s">
+        <v>849</v>
+      </c>
+      <c r="L198" s="3" t="s">
         <v>850</v>
-      </c>
-      <c r="K198" t="s">
-        <v>851</v>
-      </c>
-      <c r="L198" s="3" t="s">
-        <v>852</v>
       </c>
       <c r="R198" t="s">
         <v>31</v>
@@ -12107,25 +12108,25 @@
     </row>
     <row r="199" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B199" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="D199" t="s">
         <v>137</v>
       </c>
       <c r="E199" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="F199" t="s">
         <v>252</v>
       </c>
       <c r="J199" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="L199" s="3" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="R199" t="s">
         <v>31</v>
@@ -12145,13 +12146,13 @@
     </row>
     <row r="200" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B200" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="D200" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="E200" t="s">
         <v>120</v>
@@ -12160,19 +12161,19 @@
         <v>121</v>
       </c>
       <c r="J200" t="s">
+        <v>856</v>
+      </c>
+      <c r="K200" t="s">
+        <v>857</v>
+      </c>
+      <c r="L200" s="2" t="s">
         <v>858</v>
       </c>
-      <c r="K200" t="s">
+      <c r="R200" t="s">
+        <v>31</v>
+      </c>
+      <c r="S200" t="s">
         <v>859</v>
-      </c>
-      <c r="L200" s="2" t="s">
-        <v>860</v>
-      </c>
-      <c r="R200" t="s">
-        <v>31</v>
-      </c>
-      <c r="S200" t="s">
-        <v>861</v>
       </c>
       <c r="T200" s="1">
         <v>47</v>
@@ -12186,13 +12187,13 @@
     </row>
     <row r="201" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B201" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="D201" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E201" t="s">
         <v>74</v>
@@ -12201,13 +12202,13 @@
         <v>75</v>
       </c>
       <c r="J201" t="s">
+        <v>860</v>
+      </c>
+      <c r="K201" t="s">
+        <v>861</v>
+      </c>
+      <c r="L201" s="3" t="s">
         <v>862</v>
-      </c>
-      <c r="K201" t="s">
-        <v>863</v>
-      </c>
-      <c r="L201" s="3" t="s">
-        <v>864</v>
       </c>
       <c r="R201" t="s">
         <v>31</v>
@@ -12227,13 +12228,13 @@
     </row>
     <row r="202" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B202" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="D202" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="E202" t="s">
         <v>120</v>
@@ -12242,13 +12243,13 @@
         <v>121</v>
       </c>
       <c r="J202" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="K202" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="L202" s="3" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="R202" t="s">
         <v>31</v>
@@ -12268,25 +12269,25 @@
     </row>
     <row r="203" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B203" t="s">
+        <v>865</v>
+      </c>
+      <c r="D203" t="s">
+        <v>866</v>
+      </c>
+      <c r="E203" t="s">
         <v>867</v>
       </c>
-      <c r="D203" t="s">
+      <c r="F203" t="s">
         <v>868</v>
       </c>
-      <c r="E203" t="s">
+      <c r="J203" t="s">
         <v>869</v>
       </c>
-      <c r="F203" t="s">
+      <c r="L203" s="3" t="s">
         <v>870</v>
-      </c>
-      <c r="J203" t="s">
-        <v>871</v>
-      </c>
-      <c r="L203" s="3" t="s">
-        <v>872</v>
       </c>
       <c r="R203" t="s">
         <v>31</v>
@@ -12306,28 +12307,28 @@
     </row>
     <row r="204" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B204" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="D204" t="s">
         <v>90</v>
       </c>
       <c r="E204" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="F204" t="s">
+        <v>871</v>
+      </c>
+      <c r="J204" t="s">
+        <v>872</v>
+      </c>
+      <c r="K204" t="s">
         <v>873</v>
       </c>
-      <c r="J204" t="s">
+      <c r="L204" s="3" t="s">
         <v>874</v>
-      </c>
-      <c r="K204" t="s">
-        <v>875</v>
-      </c>
-      <c r="L204" s="3" t="s">
-        <v>876</v>
       </c>
       <c r="R204" t="s">
         <v>31</v>
@@ -12347,10 +12348,10 @@
     </row>
     <row r="205" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B205" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="D205" t="s">
         <v>299</v>
@@ -12362,13 +12363,13 @@
         <v>121</v>
       </c>
       <c r="J205" t="s">
+        <v>875</v>
+      </c>
+      <c r="K205" t="s">
+        <v>876</v>
+      </c>
+      <c r="L205" s="3" t="s">
         <v>877</v>
-      </c>
-      <c r="K205" t="s">
-        <v>878</v>
-      </c>
-      <c r="L205" s="3" t="s">
-        <v>879</v>
       </c>
       <c r="R205" t="s">
         <v>31</v>
@@ -12388,13 +12389,13 @@
     </row>
     <row r="206" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B206" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="D206" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="E206" t="s">
         <v>128</v>
@@ -12403,10 +12404,10 @@
         <v>129</v>
       </c>
       <c r="J206" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="L206" s="3" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="R206" t="s">
         <v>31</v>
@@ -12426,28 +12427,28 @@
     </row>
     <row r="207" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
+        <v>881</v>
+      </c>
+      <c r="B207" t="s">
+        <v>882</v>
+      </c>
+      <c r="D207" t="s">
         <v>883</v>
-      </c>
-      <c r="B207" t="s">
-        <v>884</v>
-      </c>
-      <c r="D207" t="s">
-        <v>885</v>
       </c>
       <c r="E207" t="s">
         <v>192</v>
       </c>
       <c r="F207" t="s">
+        <v>884</v>
+      </c>
+      <c r="J207" t="s">
+        <v>885</v>
+      </c>
+      <c r="K207" t="s">
         <v>886</v>
       </c>
-      <c r="J207" t="s">
+      <c r="L207" s="3" t="s">
         <v>887</v>
-      </c>
-      <c r="K207" t="s">
-        <v>888</v>
-      </c>
-      <c r="L207" s="3" t="s">
-        <v>889</v>
       </c>
       <c r="R207" t="s">
         <v>31</v>
@@ -12467,28 +12468,28 @@
     </row>
     <row r="208" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="B208" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="D208" t="s">
+        <v>888</v>
+      </c>
+      <c r="E208" t="s">
+        <v>867</v>
+      </c>
+      <c r="F208" t="s">
+        <v>889</v>
+      </c>
+      <c r="J208" t="s">
         <v>890</v>
       </c>
-      <c r="E208" t="s">
-        <v>869</v>
-      </c>
-      <c r="F208" t="s">
+      <c r="K208" t="s">
         <v>891</v>
       </c>
-      <c r="J208" t="s">
+      <c r="L208" s="3" t="s">
         <v>892</v>
-      </c>
-      <c r="K208" t="s">
-        <v>893</v>
-      </c>
-      <c r="L208" s="3" t="s">
-        <v>894</v>
       </c>
       <c r="R208" t="s">
         <v>31</v>
@@ -12508,28 +12509,28 @@
     </row>
     <row r="209" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="B209" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="D209" t="s">
+        <v>893</v>
+      </c>
+      <c r="E209" t="s">
+        <v>867</v>
+      </c>
+      <c r="F209" t="s">
+        <v>868</v>
+      </c>
+      <c r="J209" t="s">
+        <v>894</v>
+      </c>
+      <c r="K209" t="s">
         <v>895</v>
       </c>
-      <c r="E209" t="s">
-        <v>869</v>
-      </c>
-      <c r="F209" t="s">
-        <v>870</v>
-      </c>
-      <c r="J209" t="s">
+      <c r="L209" s="3" t="s">
         <v>896</v>
-      </c>
-      <c r="K209" t="s">
-        <v>897</v>
-      </c>
-      <c r="L209" s="3" t="s">
-        <v>898</v>
       </c>
       <c r="R209" t="s">
         <v>31</v>
@@ -12549,28 +12550,28 @@
     </row>
     <row r="210" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="B210" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="D210" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="E210" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="F210" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="J210" t="s">
+        <v>897</v>
+      </c>
+      <c r="K210" t="s">
+        <v>898</v>
+      </c>
+      <c r="L210" s="3" t="s">
         <v>899</v>
-      </c>
-      <c r="K210" t="s">
-        <v>900</v>
-      </c>
-      <c r="L210" s="3" t="s">
-        <v>901</v>
       </c>
       <c r="R210" t="s">
         <v>31</v>
@@ -12590,28 +12591,28 @@
     </row>
     <row r="211" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="B211" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="D211" t="s">
         <v>164</v>
       </c>
       <c r="E211" t="s">
+        <v>902</v>
+      </c>
+      <c r="F211" t="s">
+        <v>903</v>
+      </c>
+      <c r="J211" t="s">
         <v>904</v>
       </c>
-      <c r="F211" t="s">
+      <c r="K211" t="s">
         <v>905</v>
       </c>
-      <c r="J211" t="s">
+      <c r="L211" s="3" t="s">
         <v>906</v>
-      </c>
-      <c r="K211" t="s">
-        <v>907</v>
-      </c>
-      <c r="L211" s="3" t="s">
-        <v>908</v>
       </c>
       <c r="R211" t="s">
         <v>31</v>
@@ -12631,13 +12632,13 @@
     </row>
     <row r="212" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="B212" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="D212" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="E212" t="s">
         <v>120</v>
@@ -12646,10 +12647,10 @@
         <v>121</v>
       </c>
       <c r="J212" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="L212" s="3" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="R212" t="s">
         <v>31</v>
@@ -12669,13 +12670,13 @@
     </row>
     <row r="213" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="B213" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="D213" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E213" t="s">
         <v>74</v>
@@ -12684,13 +12685,13 @@
         <v>75</v>
       </c>
       <c r="J213" t="s">
+        <v>910</v>
+      </c>
+      <c r="K213" t="s">
+        <v>911</v>
+      </c>
+      <c r="L213" s="3" t="s">
         <v>912</v>
-      </c>
-      <c r="K213" t="s">
-        <v>913</v>
-      </c>
-      <c r="L213" s="3" t="s">
-        <v>914</v>
       </c>
       <c r="R213" t="s">
         <v>31</v>
@@ -12710,13 +12711,13 @@
     </row>
     <row r="214" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="B214" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="D214" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="E214" t="s">
         <v>107</v>
@@ -12725,13 +12726,13 @@
         <v>252</v>
       </c>
       <c r="J214" t="s">
+        <v>914</v>
+      </c>
+      <c r="K214" t="s">
+        <v>915</v>
+      </c>
+      <c r="L214" s="3" t="s">
         <v>916</v>
-      </c>
-      <c r="K214" t="s">
-        <v>917</v>
-      </c>
-      <c r="L214" s="3" t="s">
-        <v>918</v>
       </c>
       <c r="R214" t="s">
         <v>31</v>
@@ -12751,22 +12752,22 @@
     </row>
     <row r="215" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
+        <v>917</v>
+      </c>
+      <c r="B215" t="s">
+        <v>918</v>
+      </c>
+      <c r="D215" t="s">
         <v>919</v>
-      </c>
-      <c r="B215" t="s">
-        <v>920</v>
-      </c>
-      <c r="D215" t="s">
-        <v>921</v>
       </c>
       <c r="F215" t="s">
         <v>295</v>
       </c>
       <c r="J215" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="L215" s="3" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="R215" t="s">
         <v>31</v>
@@ -12786,28 +12787,28 @@
     </row>
     <row r="216" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="B216" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="D216" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="E216" t="s">
         <v>402</v>
       </c>
       <c r="F216" t="s">
+        <v>923</v>
+      </c>
+      <c r="J216" t="s">
+        <v>924</v>
+      </c>
+      <c r="K216" t="s">
+        <v>924</v>
+      </c>
+      <c r="L216" s="3" t="s">
         <v>925</v>
-      </c>
-      <c r="J216" t="s">
-        <v>926</v>
-      </c>
-      <c r="K216" t="s">
-        <v>926</v>
-      </c>
-      <c r="L216" s="3" t="s">
-        <v>927</v>
       </c>
       <c r="R216" t="s">
         <v>31</v>
@@ -12827,13 +12828,13 @@
     </row>
     <row r="217" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="B217" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="D217" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="E217" t="s">
         <v>120</v>
@@ -12842,13 +12843,13 @@
         <v>121</v>
       </c>
       <c r="J217" t="s">
+        <v>927</v>
+      </c>
+      <c r="K217" t="s">
+        <v>928</v>
+      </c>
+      <c r="L217" s="3" t="s">
         <v>929</v>
-      </c>
-      <c r="K217" t="s">
-        <v>930</v>
-      </c>
-      <c r="L217" s="3" t="s">
-        <v>931</v>
       </c>
       <c r="R217" t="s">
         <v>31</v>
@@ -12868,10 +12869,10 @@
     </row>
     <row r="218" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="B218" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="D218" t="s">
         <v>236</v>
@@ -12883,13 +12884,13 @@
         <v>121</v>
       </c>
       <c r="J218" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="K218" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="L218" s="3" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="R218" t="s">
         <v>31</v>
@@ -12909,13 +12910,13 @@
     </row>
     <row r="219" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
+        <v>932</v>
+      </c>
+      <c r="B219" t="s">
+        <v>933</v>
+      </c>
+      <c r="D219" t="s">
         <v>934</v>
-      </c>
-      <c r="B219" t="s">
-        <v>935</v>
-      </c>
-      <c r="D219" t="s">
-        <v>936</v>
       </c>
       <c r="E219" t="s">
         <v>120</v>
@@ -12924,10 +12925,10 @@
         <v>121</v>
       </c>
       <c r="J219" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="L219" s="3" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="R219" t="s">
         <v>31</v>
@@ -12947,13 +12948,13 @@
     </row>
     <row r="220" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
+        <v>932</v>
+      </c>
+      <c r="B220" t="s">
+        <v>933</v>
+      </c>
+      <c r="D220" t="s">
         <v>934</v>
-      </c>
-      <c r="B220" t="s">
-        <v>935</v>
-      </c>
-      <c r="D220" t="s">
-        <v>936</v>
       </c>
       <c r="E220" t="s">
         <v>120</v>
@@ -12962,13 +12963,13 @@
         <v>121</v>
       </c>
       <c r="J220" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="K220" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="L220" s="3" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="R220" t="s">
         <v>31</v>
@@ -12988,13 +12989,13 @@
     </row>
     <row r="221" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="B221" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="D221" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="E221" t="s">
         <v>48</v>
@@ -13003,13 +13004,13 @@
         <v>49</v>
       </c>
       <c r="J221" t="s">
+        <v>940</v>
+      </c>
+      <c r="K221" t="s">
+        <v>941</v>
+      </c>
+      <c r="L221" s="3" t="s">
         <v>942</v>
-      </c>
-      <c r="K221" t="s">
-        <v>943</v>
-      </c>
-      <c r="L221" s="3" t="s">
-        <v>944</v>
       </c>
       <c r="R221" t="s">
         <v>31</v>
@@ -13029,28 +13030,28 @@
     </row>
     <row r="222" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="B222" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="D222" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="E222" t="s">
         <v>42</v>
       </c>
       <c r="F222" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="J222" t="s">
+        <v>944</v>
+      </c>
+      <c r="K222" t="s">
+        <v>945</v>
+      </c>
+      <c r="L222" s="3" t="s">
         <v>946</v>
-      </c>
-      <c r="K222" t="s">
-        <v>947</v>
-      </c>
-      <c r="L222" s="3" t="s">
-        <v>948</v>
       </c>
       <c r="R222" t="s">
         <v>31</v>
@@ -13070,13 +13071,13 @@
     </row>
     <row r="223" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="B223" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="D223" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="E223" t="s">
         <v>120</v>
@@ -13085,13 +13086,13 @@
         <v>121</v>
       </c>
       <c r="J223" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="K223" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="L223" s="3" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="R223" t="s">
         <v>31</v>
@@ -13111,13 +13112,13 @@
     </row>
     <row r="224" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="B224" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="D224" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="E224" t="s">
         <v>120</v>
@@ -13126,13 +13127,13 @@
         <v>121</v>
       </c>
       <c r="J224" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="K224" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="L224" s="3" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="R224" t="s">
         <v>31</v>
@@ -13152,13 +13153,13 @@
     </row>
     <row r="225" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="B225" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="D225" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E225" t="s">
         <v>120</v>
@@ -13167,13 +13168,13 @@
         <v>121</v>
       </c>
       <c r="J225" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="K225" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="L225" s="3" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="R225" t="s">
         <v>31</v>
@@ -13193,25 +13194,25 @@
     </row>
     <row r="226" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="B226" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="D226">
         <v>1780</v>
       </c>
       <c r="F226" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="J226" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="K226" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="L226" s="3" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="R226" t="s">
         <v>31</v>
@@ -13231,13 +13232,13 @@
     </row>
     <row r="227" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
+        <v>957</v>
+      </c>
+      <c r="B227" t="s">
+        <v>958</v>
+      </c>
+      <c r="D227" t="s">
         <v>959</v>
-      </c>
-      <c r="B227" t="s">
-        <v>960</v>
-      </c>
-      <c r="D227" t="s">
-        <v>961</v>
       </c>
       <c r="E227" t="s">
         <v>102</v>
@@ -13246,13 +13247,13 @@
         <v>103</v>
       </c>
       <c r="J227" t="s">
+        <v>960</v>
+      </c>
+      <c r="K227" t="s">
+        <v>961</v>
+      </c>
+      <c r="L227" s="3" t="s">
         <v>962</v>
-      </c>
-      <c r="K227" t="s">
-        <v>963</v>
-      </c>
-      <c r="L227" s="3" t="s">
-        <v>964</v>
       </c>
       <c r="R227" t="s">
         <v>31</v>
@@ -13272,13 +13273,13 @@
     </row>
     <row r="228" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="B228" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="D228" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E228" t="s">
         <v>102</v>
@@ -13287,13 +13288,13 @@
         <v>103</v>
       </c>
       <c r="J228" t="s">
+        <v>963</v>
+      </c>
+      <c r="K228" t="s">
+        <v>964</v>
+      </c>
+      <c r="L228" s="3" t="s">
         <v>965</v>
-      </c>
-      <c r="K228" t="s">
-        <v>966</v>
-      </c>
-      <c r="L228" s="3" t="s">
-        <v>967</v>
       </c>
       <c r="R228" t="s">
         <v>31</v>
@@ -13313,10 +13314,10 @@
     </row>
     <row r="229" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="B229" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="D229" t="s">
         <v>401</v>
@@ -13328,13 +13329,13 @@
         <v>103</v>
       </c>
       <c r="J229" t="s">
+        <v>966</v>
+      </c>
+      <c r="K229" t="s">
+        <v>967</v>
+      </c>
+      <c r="L229" s="3" t="s">
         <v>968</v>
-      </c>
-      <c r="K229" t="s">
-        <v>969</v>
-      </c>
-      <c r="L229" s="3" t="s">
-        <v>970</v>
       </c>
       <c r="R229" t="s">
         <v>31</v>
@@ -13354,10 +13355,10 @@
     </row>
     <row r="230" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="B230" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="D230" t="s">
         <v>242</v>
@@ -13369,13 +13370,13 @@
         <v>103</v>
       </c>
       <c r="J230" t="s">
+        <v>969</v>
+      </c>
+      <c r="K230" t="s">
+        <v>970</v>
+      </c>
+      <c r="L230" s="3" t="s">
         <v>971</v>
-      </c>
-      <c r="K230" t="s">
-        <v>972</v>
-      </c>
-      <c r="L230" s="3" t="s">
-        <v>973</v>
       </c>
       <c r="R230" t="s">
         <v>31</v>
@@ -13395,10 +13396,10 @@
     </row>
     <row r="231" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="B231" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="D231" t="s">
         <v>277</v>
@@ -13410,13 +13411,13 @@
         <v>139</v>
       </c>
       <c r="J231" t="s">
+        <v>974</v>
+      </c>
+      <c r="K231" t="s">
+        <v>975</v>
+      </c>
+      <c r="L231" s="3" t="s">
         <v>976</v>
-      </c>
-      <c r="K231" t="s">
-        <v>977</v>
-      </c>
-      <c r="L231" s="3" t="s">
-        <v>978</v>
       </c>
       <c r="R231" t="s">
         <v>31</v>
@@ -13436,28 +13437,28 @@
     </row>
     <row r="232" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="B232" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="D232" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E232" t="s">
         <v>120</v>
       </c>
       <c r="F232" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="J232" t="s">
         <v>217</v>
       </c>
       <c r="K232" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="L232" s="3" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="R232" t="s">
         <v>31</v>
@@ -13477,28 +13478,28 @@
     </row>
     <row r="233" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="B233" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="D233" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="E233" t="s">
+        <v>980</v>
+      </c>
+      <c r="F233" t="s">
+        <v>981</v>
+      </c>
+      <c r="J233" t="s">
         <v>982</v>
       </c>
-      <c r="F233" t="s">
+      <c r="K233" t="s">
         <v>983</v>
       </c>
-      <c r="J233" t="s">
+      <c r="L233" s="3" t="s">
         <v>984</v>
-      </c>
-      <c r="K233" t="s">
-        <v>985</v>
-      </c>
-      <c r="L233" s="3" t="s">
-        <v>986</v>
       </c>
       <c r="R233" t="s">
         <v>31</v>
@@ -13518,28 +13519,28 @@
     </row>
     <row r="234" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="B234" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="D234" t="s">
         <v>401</v>
       </c>
       <c r="E234" t="s">
+        <v>985</v>
+      </c>
+      <c r="F234" t="s">
+        <v>986</v>
+      </c>
+      <c r="J234" t="s">
         <v>987</v>
       </c>
-      <c r="F234" t="s">
+      <c r="K234" t="s">
         <v>988</v>
       </c>
-      <c r="J234" t="s">
+      <c r="L234" s="3" t="s">
         <v>989</v>
-      </c>
-      <c r="K234" t="s">
-        <v>990</v>
-      </c>
-      <c r="L234" s="3" t="s">
-        <v>991</v>
       </c>
       <c r="R234" t="s">
         <v>31</v>
@@ -13559,28 +13560,28 @@
     </row>
     <row r="235" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B235" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="D235" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="E235" t="s">
         <v>128</v>
       </c>
       <c r="F235" t="s">
+        <v>992</v>
+      </c>
+      <c r="J235" t="s">
+        <v>993</v>
+      </c>
+      <c r="K235" t="s">
         <v>994</v>
       </c>
-      <c r="J235" t="s">
+      <c r="L235" s="3" t="s">
         <v>995</v>
-      </c>
-      <c r="K235" t="s">
-        <v>996</v>
-      </c>
-      <c r="L235" s="3" t="s">
-        <v>997</v>
       </c>
       <c r="R235" t="s">
         <v>31</v>
@@ -13600,13 +13601,13 @@
     </row>
     <row r="236" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B236" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="D236" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E236" t="s">
         <v>128</v>
@@ -13615,13 +13616,13 @@
         <v>129</v>
       </c>
       <c r="J236" t="s">
+        <v>996</v>
+      </c>
+      <c r="K236" t="s">
+        <v>997</v>
+      </c>
+      <c r="L236" s="3" t="s">
         <v>998</v>
-      </c>
-      <c r="K236" t="s">
-        <v>999</v>
-      </c>
-      <c r="L236" s="3" t="s">
-        <v>1000</v>
       </c>
       <c r="R236" t="s">
         <v>31</v>
@@ -13641,28 +13642,28 @@
     </row>
     <row r="237" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B237" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="D237" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="E237" t="s">
+        <v>999</v>
+      </c>
+      <c r="F237" t="s">
+        <v>1000</v>
+      </c>
+      <c r="J237" t="s">
         <v>1001</v>
       </c>
-      <c r="F237" t="s">
+      <c r="K237" t="s">
         <v>1002</v>
       </c>
-      <c r="J237" t="s">
+      <c r="L237" s="3" t="s">
         <v>1003</v>
-      </c>
-      <c r="K237" t="s">
-        <v>1004</v>
-      </c>
-      <c r="L237" s="3" t="s">
-        <v>1005</v>
       </c>
       <c r="R237" t="s">
         <v>31</v>
@@ -13682,28 +13683,28 @@
     </row>
     <row r="238" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B238" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="D238" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="E238" t="s">
         <v>42</v>
       </c>
       <c r="F238" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="J238" t="s">
+        <v>1005</v>
+      </c>
+      <c r="K238" t="s">
+        <v>1006</v>
+      </c>
+      <c r="L238" s="3" t="s">
         <v>1007</v>
-      </c>
-      <c r="K238" t="s">
-        <v>1008</v>
-      </c>
-      <c r="L238" s="3" t="s">
-        <v>1009</v>
       </c>
       <c r="R238" t="s">
         <v>31</v>
@@ -13723,13 +13724,13 @@
     </row>
     <row r="239" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B239" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="D239" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="E239" t="s">
         <v>74</v>
@@ -13738,10 +13739,10 @@
         <v>75</v>
       </c>
       <c r="J239" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="L239" s="3" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="R239" t="s">
         <v>31</v>
@@ -13761,28 +13762,28 @@
     </row>
     <row r="240" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B240" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="D240" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="E240" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F240" t="s">
+        <v>1013</v>
+      </c>
+      <c r="J240" t="s">
         <v>1014</v>
       </c>
-      <c r="F240" t="s">
+      <c r="K240" t="s">
         <v>1015</v>
       </c>
-      <c r="J240" t="s">
+      <c r="L240" s="3" t="s">
         <v>1016</v>
-      </c>
-      <c r="K240" t="s">
-        <v>1017</v>
-      </c>
-      <c r="L240" s="3" t="s">
-        <v>1018</v>
       </c>
       <c r="R240" t="s">
         <v>31</v>
@@ -13802,28 +13803,28 @@
     </row>
     <row r="241" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B241" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="D241" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="E241" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F241" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="J241" t="s">
+        <v>1017</v>
+      </c>
+      <c r="K241" t="s">
+        <v>1018</v>
+      </c>
+      <c r="L241" s="3" t="s">
         <v>1019</v>
-      </c>
-      <c r="K241" t="s">
-        <v>1020</v>
-      </c>
-      <c r="L241" s="3" t="s">
-        <v>1021</v>
       </c>
       <c r="R241" t="s">
         <v>31</v>
@@ -13843,13 +13844,13 @@
     </row>
     <row r="242" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B242" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="D242" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E242" t="s">
         <v>74</v>
@@ -13858,13 +13859,13 @@
         <v>91</v>
       </c>
       <c r="J242" t="s">
+        <v>1020</v>
+      </c>
+      <c r="K242" t="s">
+        <v>1021</v>
+      </c>
+      <c r="L242" s="3" t="s">
         <v>1022</v>
-      </c>
-      <c r="K242" t="s">
-        <v>1023</v>
-      </c>
-      <c r="L242" s="3" t="s">
-        <v>1024</v>
       </c>
       <c r="R242" t="s">
         <v>31</v>
@@ -13884,28 +13885,28 @@
     </row>
     <row r="243" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B243" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D243" t="s">
         <v>1025</v>
       </c>
-      <c r="B243" t="s">
+      <c r="E243" t="s">
         <v>1026</v>
       </c>
-      <c r="D243" t="s">
+      <c r="F243" t="s">
         <v>1027</v>
       </c>
-      <c r="E243" t="s">
+      <c r="J243" t="s">
         <v>1028</v>
       </c>
-      <c r="F243" t="s">
+      <c r="K243" t="s">
         <v>1029</v>
       </c>
-      <c r="J243" t="s">
+      <c r="L243" s="3" t="s">
         <v>1030</v>
-      </c>
-      <c r="K243" t="s">
-        <v>1031</v>
-      </c>
-      <c r="L243" s="3" t="s">
-        <v>1032</v>
       </c>
       <c r="R243" t="s">
         <v>31</v>
@@ -13925,13 +13926,13 @@
     </row>
     <row r="244" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="B244" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="D244" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="E244" t="s">
         <v>311</v>
@@ -13940,13 +13941,13 @@
         <v>312</v>
       </c>
       <c r="J244" t="s">
+        <v>1032</v>
+      </c>
+      <c r="K244" t="s">
+        <v>1033</v>
+      </c>
+      <c r="L244" s="3" t="s">
         <v>1034</v>
-      </c>
-      <c r="K244" t="s">
-        <v>1035</v>
-      </c>
-      <c r="L244" s="3" t="s">
-        <v>1036</v>
       </c>
       <c r="R244" t="s">
         <v>31</v>
@@ -13966,13 +13967,13 @@
     </row>
     <row r="245" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="B245" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="D245" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="E245" t="s">
         <v>42</v>
@@ -13981,16 +13982,16 @@
         <v>43</v>
       </c>
       <c r="J245" t="s">
+        <v>1036</v>
+      </c>
+      <c r="K245" t="s">
+        <v>1037</v>
+      </c>
+      <c r="L245" s="3" t="s">
         <v>1038</v>
       </c>
-      <c r="K245" t="s">
+      <c r="M245" t="s">
         <v>1039</v>
-      </c>
-      <c r="L245" s="3" t="s">
-        <v>1040</v>
-      </c>
-      <c r="M245" t="s">
-        <v>1041</v>
       </c>
       <c r="R245" t="s">
         <v>31</v>
@@ -14010,28 +14011,28 @@
     </row>
     <row r="246" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="B246" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="D246" t="s">
         <v>146</v>
       </c>
       <c r="E246" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="F246" t="s">
         <v>57</v>
       </c>
       <c r="J246" t="s">
+        <v>1041</v>
+      </c>
+      <c r="K246" t="s">
+        <v>1042</v>
+      </c>
+      <c r="L246" s="3" t="s">
         <v>1043</v>
-      </c>
-      <c r="K246" t="s">
-        <v>1044</v>
-      </c>
-      <c r="L246" s="3" t="s">
-        <v>1045</v>
       </c>
       <c r="R246" t="s">
         <v>31</v>
@@ -14051,10 +14052,10 @@
     </row>
     <row r="247" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="B247" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="D247" t="s">
         <v>161</v>
@@ -14066,10 +14067,10 @@
         <v>121</v>
       </c>
       <c r="J247" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="L247" s="3" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="R247" t="s">
         <v>31</v>
@@ -14089,10 +14090,10 @@
     </row>
     <row r="248" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="B248" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="D248" t="s">
         <v>146</v>
@@ -14104,10 +14105,10 @@
         <v>252</v>
       </c>
       <c r="J248" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="L248" s="3" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="R248" t="s">
         <v>31</v>
@@ -14127,13 +14128,13 @@
     </row>
     <row r="249" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="B249" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="D249" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="E249" t="s">
         <v>372</v>
@@ -14142,13 +14143,13 @@
         <v>373</v>
       </c>
       <c r="J249" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="K249" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="L249" s="3" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="R249" t="s">
         <v>31</v>
@@ -14168,13 +14169,13 @@
     </row>
     <row r="250" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="B250" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="D250" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="E250" t="s">
         <v>402</v>
@@ -14183,13 +14184,13 @@
         <v>295</v>
       </c>
       <c r="J250" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="K250" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="L250" s="3" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="R250" t="s">
         <v>31</v>
@@ -14209,25 +14210,25 @@
     </row>
     <row r="251" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="B251" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="D251" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="E251" t="s">
         <v>120</v>
       </c>
       <c r="F251" t="s">
+        <v>1057</v>
+      </c>
+      <c r="J251" t="s">
+        <v>1058</v>
+      </c>
+      <c r="L251" s="3" t="s">
         <v>1059</v>
-      </c>
-      <c r="J251" t="s">
-        <v>1060</v>
-      </c>
-      <c r="L251" s="3" t="s">
-        <v>1061</v>
       </c>
       <c r="R251" t="s">
         <v>31</v>
@@ -14247,13 +14248,13 @@
     </row>
     <row r="252" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="B252" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="D252" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E252" t="s">
         <v>128</v>
@@ -14262,10 +14263,10 @@
         <v>129</v>
       </c>
       <c r="J252" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="L252" s="3" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="R252" t="s">
         <v>31</v>
@@ -14285,13 +14286,13 @@
     </row>
     <row r="253" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="B253" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="D253" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E253" t="s">
         <v>74</v>
@@ -14300,10 +14301,10 @@
         <v>75</v>
       </c>
       <c r="J253" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="L253" s="3" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="R253" t="s">
         <v>31</v>
@@ -14323,10 +14324,10 @@
     </row>
     <row r="254" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="B254" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="D254" t="s">
         <v>364</v>
@@ -14338,10 +14339,10 @@
         <v>68</v>
       </c>
       <c r="J254" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="L254" s="3" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="R254" t="s">
         <v>31</v>
@@ -14361,13 +14362,13 @@
     </row>
     <row r="255" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B255" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D255" t="s">
         <v>1068</v>
-      </c>
-      <c r="B255" t="s">
-        <v>1069</v>
-      </c>
-      <c r="D255" t="s">
-        <v>1070</v>
       </c>
       <c r="E255" t="s">
         <v>74</v>
@@ -14376,10 +14377,10 @@
         <v>75</v>
       </c>
       <c r="J255" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="L255" s="3" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="R255" t="s">
         <v>31</v>
@@ -14399,10 +14400,10 @@
     </row>
     <row r="256" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="B256" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="D256" t="s">
         <v>285</v>
@@ -14411,10 +14412,10 @@
         <v>295</v>
       </c>
       <c r="J256" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="L256" s="3" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="R256" t="s">
         <v>31</v>
@@ -14434,13 +14435,13 @@
     </row>
     <row r="257" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="B257" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="D257" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E257" t="s">
         <v>120</v>
@@ -14449,16 +14450,16 @@
         <v>121</v>
       </c>
       <c r="J257" t="s">
+        <v>1073</v>
+      </c>
+      <c r="L257" s="3" t="s">
+        <v>1074</v>
+      </c>
+      <c r="R257" t="s">
+        <v>31</v>
+      </c>
+      <c r="S257" t="s">
         <v>1075</v>
-      </c>
-      <c r="L257" s="3" t="s">
-        <v>1076</v>
-      </c>
-      <c r="R257" t="s">
-        <v>31</v>
-      </c>
-      <c r="S257" t="s">
-        <v>1077</v>
       </c>
       <c r="T257" s="1">
         <v>130</v>
@@ -14472,22 +14473,22 @@
     </row>
     <row r="258" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="B258" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="D258" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="F258" t="s">
         <v>295</v>
       </c>
       <c r="J258" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="L258" s="3" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="R258" t="s">
         <v>31</v>
@@ -14507,13 +14508,13 @@
     </row>
     <row r="259" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="B259" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="D259" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E259" t="s">
         <v>120</v>
@@ -14522,10 +14523,10 @@
         <v>121</v>
       </c>
       <c r="J259" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="L259" s="3" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="R259" t="s">
         <v>31</v>
@@ -14545,13 +14546,13 @@
     </row>
     <row r="260" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="B260" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="D260" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="E260" t="s">
         <v>120</v>
@@ -14560,10 +14561,10 @@
         <v>121</v>
       </c>
       <c r="J260" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="L260" s="3" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="R260" t="s">
         <v>31</v>
@@ -14583,10 +14584,10 @@
     </row>
     <row r="261" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="B261" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="D261" t="s">
         <v>336</v>
@@ -14598,16 +14599,16 @@
         <v>121</v>
       </c>
       <c r="J261" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="L261" s="3" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="R261" t="s">
         <v>31</v>
       </c>
       <c r="S261" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="T261" s="1">
         <v>105</v>
@@ -14621,22 +14622,22 @@
     </row>
     <row r="262" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="B262" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="D262" t="s">
+        <v>1085</v>
+      </c>
+      <c r="F262" t="s">
+        <v>1086</v>
+      </c>
+      <c r="J262" t="s">
         <v>1087</v>
       </c>
-      <c r="F262" t="s">
+      <c r="L262" s="3" t="s">
         <v>1088</v>
-      </c>
-      <c r="J262" t="s">
-        <v>1089</v>
-      </c>
-      <c r="L262" s="3" t="s">
-        <v>1090</v>
       </c>
       <c r="R262" t="s">
         <v>31</v>
@@ -14656,13 +14657,13 @@
     </row>
     <row r="263" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B263" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D263" t="s">
         <v>1091</v>
-      </c>
-      <c r="B263" t="s">
-        <v>1092</v>
-      </c>
-      <c r="D263" t="s">
-        <v>1093</v>
       </c>
       <c r="E263" t="s">
         <v>120</v>
@@ -14671,10 +14672,10 @@
         <v>121</v>
       </c>
       <c r="J263" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="L263" s="3" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="R263" t="s">
         <v>31</v>
@@ -14694,13 +14695,13 @@
     </row>
     <row r="264" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B264" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D264" t="s">
         <v>1091</v>
-      </c>
-      <c r="B264" t="s">
-        <v>1092</v>
-      </c>
-      <c r="D264" t="s">
-        <v>1093</v>
       </c>
       <c r="E264" t="s">
         <v>120</v>
@@ -14709,10 +14710,10 @@
         <v>121</v>
       </c>
       <c r="J264" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="L264" s="3" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="R264" t="s">
         <v>31</v>
@@ -14732,13 +14733,13 @@
     </row>
     <row r="265" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="B265" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="D265" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="E265" t="s">
         <v>120</v>
@@ -14747,10 +14748,10 @@
         <v>121</v>
       </c>
       <c r="J265" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="L265" s="3" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="R265" t="s">
         <v>31</v>
@@ -14770,13 +14771,13 @@
     </row>
     <row r="266" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="B266" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="D266" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="E266" t="s">
         <v>42</v>
@@ -14785,10 +14786,10 @@
         <v>43</v>
       </c>
       <c r="J266" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="L266" s="3" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="R266" t="s">
         <v>31</v>
@@ -14808,25 +14809,25 @@
     </row>
     <row r="267" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="B267" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="D267" t="s">
         <v>170</v>
       </c>
       <c r="E267" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="F267" t="s">
+        <v>1102</v>
+      </c>
+      <c r="J267" t="s">
+        <v>1103</v>
+      </c>
+      <c r="L267" s="3" t="s">
         <v>1104</v>
-      </c>
-      <c r="J267" t="s">
-        <v>1105</v>
-      </c>
-      <c r="L267" s="3" t="s">
-        <v>1106</v>
       </c>
       <c r="R267" t="s">
         <v>31</v>
@@ -14846,13 +14847,13 @@
     </row>
     <row r="268" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="B268" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="D268" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="E268" t="s">
         <v>74</v>
@@ -14861,10 +14862,10 @@
         <v>75</v>
       </c>
       <c r="J268" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="L268" s="3" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="R268" t="s">
         <v>31</v>
@@ -14884,13 +14885,13 @@
     </row>
     <row r="269" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="B269" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="D269" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="E269" t="s">
         <v>351</v>
@@ -14899,10 +14900,10 @@
         <v>389</v>
       </c>
       <c r="J269" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="L269" s="3" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="R269" t="s">
         <v>31</v>
@@ -14922,25 +14923,25 @@
     </row>
     <row r="270" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B270" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D270" t="s">
         <v>1091</v>
       </c>
-      <c r="B270" t="s">
-        <v>1092</v>
-      </c>
-      <c r="D270" t="s">
-        <v>1093</v>
-      </c>
       <c r="E270" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="F270" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="J270" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="L270" s="3" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="R270" t="s">
         <v>31</v>
@@ -14960,13 +14961,13 @@
     </row>
     <row r="271" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="B271" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="D271" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="E271" t="s">
         <v>351</v>
@@ -14975,10 +14976,10 @@
         <v>389</v>
       </c>
       <c r="J271" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="L271" s="3" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="R271" t="s">
         <v>31</v>
@@ -14998,13 +14999,13 @@
     </row>
     <row r="272" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="B272" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="D272" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="E272" t="s">
         <v>120</v>
@@ -15013,10 +15014,10 @@
         <v>121</v>
       </c>
       <c r="J272" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="L272" s="3" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="R272" t="s">
         <v>31</v>
@@ -15036,13 +15037,13 @@
     </row>
     <row r="273" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B273" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D273" t="s">
         <v>1091</v>
-      </c>
-      <c r="B273" t="s">
-        <v>1092</v>
-      </c>
-      <c r="D273" t="s">
-        <v>1093</v>
       </c>
       <c r="E273" t="s">
         <v>128</v>
@@ -15051,10 +15052,10 @@
         <v>129</v>
       </c>
       <c r="J273" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="L273" s="3" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="R273" t="s">
         <v>31</v>
@@ -15074,13 +15075,13 @@
     </row>
     <row r="274" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="B274" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="D274" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="E274" t="s">
         <v>175</v>
@@ -15089,10 +15090,10 @@
         <v>176</v>
       </c>
       <c r="J274" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="L274" s="3" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="R274" t="s">
         <v>31</v>
@@ -15112,28 +15113,28 @@
     </row>
     <row r="275" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="B275" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="D275" t="s">
         <v>61</v>
       </c>
       <c r="E275" t="s">
+        <v>1124</v>
+      </c>
+      <c r="F275" t="s">
+        <v>1125</v>
+      </c>
+      <c r="J275" t="s">
         <v>1126</v>
       </c>
-      <c r="F275" t="s">
+      <c r="K275" t="s">
         <v>1127</v>
       </c>
-      <c r="J275" t="s">
+      <c r="L275" s="3" t="s">
         <v>1128</v>
-      </c>
-      <c r="K275" t="s">
-        <v>1129</v>
-      </c>
-      <c r="L275" s="3" t="s">
-        <v>1130</v>
       </c>
       <c r="R275" t="s">
         <v>31</v>
@@ -15153,28 +15154,28 @@
     </row>
     <row r="276" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="B276" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="D276" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E276" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="F276" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="J276" t="s">
+        <v>1129</v>
+      </c>
+      <c r="K276" t="s">
+        <v>1130</v>
+      </c>
+      <c r="L276" s="3" t="s">
         <v>1131</v>
-      </c>
-      <c r="K276" t="s">
-        <v>1132</v>
-      </c>
-      <c r="L276" s="3" t="s">
-        <v>1133</v>
       </c>
       <c r="R276" t="s">
         <v>31</v>
@@ -15194,28 +15195,28 @@
     </row>
     <row r="277" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="B277" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="D277" t="s">
         <v>277</v>
       </c>
       <c r="E277" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F277" t="s">
+        <v>1132</v>
+      </c>
+      <c r="J277" t="s">
+        <v>1133</v>
+      </c>
+      <c r="K277" t="s">
         <v>1134</v>
       </c>
-      <c r="J277" t="s">
+      <c r="L277" s="3" t="s">
         <v>1135</v>
-      </c>
-      <c r="K277" t="s">
-        <v>1136</v>
-      </c>
-      <c r="L277" s="3" t="s">
-        <v>1137</v>
       </c>
       <c r="R277" t="s">
         <v>31</v>
@@ -15235,13 +15236,13 @@
     </row>
     <row r="278" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="B278" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="D278" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="E278" t="s">
         <v>74</v>
@@ -15250,13 +15251,13 @@
         <v>91</v>
       </c>
       <c r="J278" t="s">
+        <v>1136</v>
+      </c>
+      <c r="K278" t="s">
+        <v>1137</v>
+      </c>
+      <c r="L278" s="3" t="s">
         <v>1138</v>
-      </c>
-      <c r="K278" t="s">
-        <v>1139</v>
-      </c>
-      <c r="L278" s="3" t="s">
-        <v>1140</v>
       </c>
       <c r="R278" t="s">
         <v>31</v>
@@ -15276,28 +15277,28 @@
     </row>
     <row r="279" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="B279" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="D279" t="s">
         <v>364</v>
       </c>
       <c r="E279" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F279" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="J279" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="K279" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="L279" s="3" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="R279" t="s">
         <v>31</v>
@@ -15317,10 +15318,10 @@
     </row>
     <row r="280" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="B280" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="D280" t="s">
         <v>35</v>
@@ -15332,10 +15333,10 @@
         <v>91</v>
       </c>
       <c r="J280" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="L280" s="3" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="R280" t="s">
         <v>31</v>
@@ -15355,28 +15356,28 @@
     </row>
     <row r="281" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="B281" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="D281" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E281" t="s">
+        <v>1186</v>
+      </c>
+      <c r="F281" t="s">
         <v>1187</v>
       </c>
-      <c r="E281" t="s">
-        <v>1188</v>
-      </c>
-      <c r="F281" t="s">
-        <v>1189</v>
-      </c>
       <c r="J281" t="s">
+        <v>1145</v>
+      </c>
+      <c r="K281" t="s">
+        <v>1146</v>
+      </c>
+      <c r="L281" s="3" t="s">
         <v>1147</v>
-      </c>
-      <c r="K281" t="s">
-        <v>1148</v>
-      </c>
-      <c r="L281" s="3" t="s">
-        <v>1149</v>
       </c>
       <c r="R281" t="s">
         <v>31</v>
@@ -15396,10 +15397,10 @@
     </row>
     <row r="282" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="B282" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="D282">
         <v>1714</v>
@@ -15411,13 +15412,13 @@
         <v>75</v>
       </c>
       <c r="J282" t="s">
+        <v>1148</v>
+      </c>
+      <c r="K282" t="s">
+        <v>1149</v>
+      </c>
+      <c r="L282" s="3" t="s">
         <v>1150</v>
-      </c>
-      <c r="K282" t="s">
-        <v>1151</v>
-      </c>
-      <c r="L282" s="3" t="s">
-        <v>1152</v>
       </c>
       <c r="R282" t="s">
         <v>31</v>
@@ -15440,7 +15441,7 @@
         <v>408</v>
       </c>
       <c r="B283" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="D283" t="s">
         <v>277</v>
@@ -15452,13 +15453,13 @@
         <v>75</v>
       </c>
       <c r="J283" t="s">
+        <v>1152</v>
+      </c>
+      <c r="K283" t="s">
+        <v>1153</v>
+      </c>
+      <c r="L283" s="3" t="s">
         <v>1154</v>
-      </c>
-      <c r="K283" t="s">
-        <v>1155</v>
-      </c>
-      <c r="L283" s="3" t="s">
-        <v>1156</v>
       </c>
       <c r="R283" t="s">
         <v>31</v>
@@ -15481,10 +15482,10 @@
         <v>408</v>
       </c>
       <c r="B284" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="D284" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="E284" t="s">
         <v>74</v>
@@ -15493,13 +15494,13 @@
         <v>91</v>
       </c>
       <c r="J284" t="s">
+        <v>1156</v>
+      </c>
+      <c r="K284" t="s">
+        <v>1157</v>
+      </c>
+      <c r="L284" s="3" t="s">
         <v>1158</v>
-      </c>
-      <c r="K284" t="s">
-        <v>1159</v>
-      </c>
-      <c r="L284" s="3" t="s">
-        <v>1160</v>
       </c>
       <c r="R284" t="s">
         <v>31</v>
@@ -15522,25 +15523,25 @@
         <v>408</v>
       </c>
       <c r="B285" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="D285" t="s">
         <v>247</v>
       </c>
       <c r="E285" t="s">
+        <v>1159</v>
+      </c>
+      <c r="F285" t="s">
+        <v>1160</v>
+      </c>
+      <c r="J285" t="s">
         <v>1161</v>
       </c>
-      <c r="F285" t="s">
+      <c r="K285" t="s">
         <v>1162</v>
       </c>
-      <c r="J285" t="s">
+      <c r="L285" s="3" t="s">
         <v>1163</v>
-      </c>
-      <c r="K285" t="s">
-        <v>1164</v>
-      </c>
-      <c r="L285" s="3" t="s">
-        <v>1165</v>
       </c>
       <c r="R285" t="s">
         <v>31</v>
@@ -15563,10 +15564,10 @@
         <v>408</v>
       </c>
       <c r="B286" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="D286" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E286" t="s">
         <v>74</v>
@@ -15575,13 +15576,13 @@
         <v>91</v>
       </c>
       <c r="J286" t="s">
+        <v>1164</v>
+      </c>
+      <c r="K286" t="s">
+        <v>1165</v>
+      </c>
+      <c r="L286" s="3" t="s">
         <v>1166</v>
-      </c>
-      <c r="K286" t="s">
-        <v>1167</v>
-      </c>
-      <c r="L286" s="3" t="s">
-        <v>1168</v>
       </c>
       <c r="R286" t="s">
         <v>31</v>
@@ -15601,28 +15602,28 @@
     </row>
     <row r="287" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="B287" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="D287" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E287" t="s">
         <v>192</v>
       </c>
       <c r="F287" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="J287" t="s">
+        <v>1169</v>
+      </c>
+      <c r="K287" t="s">
+        <v>1170</v>
+      </c>
+      <c r="L287" s="3" t="s">
         <v>1171</v>
-      </c>
-      <c r="K287" t="s">
-        <v>1172</v>
-      </c>
-      <c r="L287" s="3" t="s">
-        <v>1173</v>
       </c>
       <c r="R287" t="s">
         <v>31</v>
@@ -15642,28 +15643,28 @@
     </row>
     <row r="288" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="B288" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="D288" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="E288" t="s">
         <v>192</v>
       </c>
       <c r="F288" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="J288" t="s">
+        <v>1173</v>
+      </c>
+      <c r="K288" t="s">
+        <v>1174</v>
+      </c>
+      <c r="L288" s="3" t="s">
         <v>1175</v>
-      </c>
-      <c r="K288" t="s">
-        <v>1176</v>
-      </c>
-      <c r="L288" s="3" t="s">
-        <v>1177</v>
       </c>
       <c r="R288" t="s">
         <v>31</v>
@@ -15683,28 +15684,28 @@
     </row>
     <row r="289" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="B289" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="D289" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E289" t="s">
+        <v>1176</v>
+      </c>
+      <c r="F289" t="s">
+        <v>1177</v>
+      </c>
+      <c r="J289" t="s">
         <v>1178</v>
       </c>
-      <c r="F289" t="s">
+      <c r="K289" t="s">
         <v>1179</v>
       </c>
-      <c r="J289" t="s">
+      <c r="L289" s="3" t="s">
         <v>1180</v>
-      </c>
-      <c r="K289" t="s">
-        <v>1181</v>
-      </c>
-      <c r="L289" s="3" t="s">
-        <v>1182</v>
       </c>
       <c r="R289" t="s">
         <v>31</v>
@@ -15724,13 +15725,13 @@
     </row>
     <row r="290" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="B290" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="D290" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="E290" t="s">
         <v>74</v>
@@ -15739,13 +15740,13 @@
         <v>91</v>
       </c>
       <c r="J290" t="s">
+        <v>1182</v>
+      </c>
+      <c r="K290" t="s">
+        <v>1183</v>
+      </c>
+      <c r="L290" s="3" t="s">
         <v>1184</v>
-      </c>
-      <c r="K290" t="s">
-        <v>1185</v>
-      </c>
-      <c r="L290" s="3" t="s">
-        <v>1186</v>
       </c>
       <c r="R290" t="s">
         <v>31</v>
@@ -15940,118 +15941,118 @@
     <hyperlink ref="L175" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
     <hyperlink ref="L176" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
     <hyperlink ref="L177" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="L178" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="L179" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="L180" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
-    <hyperlink ref="L181" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="L182" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="L183" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="L184" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="L185" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="L186" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="L187" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="L188" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="L189" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="L190" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="L191" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="L192" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="L193" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
-    <hyperlink ref="L194" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
-    <hyperlink ref="L195" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
-    <hyperlink ref="L196" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
-    <hyperlink ref="L197" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
-    <hyperlink ref="L198" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
-    <hyperlink ref="L199" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
-    <hyperlink ref="L201" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
-    <hyperlink ref="L202" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
-    <hyperlink ref="L203" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
-    <hyperlink ref="L204" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
-    <hyperlink ref="L205" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
-    <hyperlink ref="L206" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
-    <hyperlink ref="L207" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
-    <hyperlink ref="L208" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
-    <hyperlink ref="L209" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
-    <hyperlink ref="L210" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
-    <hyperlink ref="L211" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
-    <hyperlink ref="L212" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
-    <hyperlink ref="L213" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
-    <hyperlink ref="L214" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
-    <hyperlink ref="L215" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
-    <hyperlink ref="L216" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
-    <hyperlink ref="L217" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
-    <hyperlink ref="L218" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
-    <hyperlink ref="L219" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
-    <hyperlink ref="L220" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
-    <hyperlink ref="L221" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
-    <hyperlink ref="L222" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
-    <hyperlink ref="L223" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
-    <hyperlink ref="L224" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
-    <hyperlink ref="L225" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
-    <hyperlink ref="L226" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
-    <hyperlink ref="L227" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
-    <hyperlink ref="L228" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
-    <hyperlink ref="L229" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
-    <hyperlink ref="L230" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
-    <hyperlink ref="L231" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
-    <hyperlink ref="L232" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
-    <hyperlink ref="L233" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
-    <hyperlink ref="L234" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
-    <hyperlink ref="L235" r:id="rId232" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
-    <hyperlink ref="L236" r:id="rId233" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
-    <hyperlink ref="L237" r:id="rId234" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
-    <hyperlink ref="L238" r:id="rId235" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
-    <hyperlink ref="L239" r:id="rId236" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
-    <hyperlink ref="L240" r:id="rId237" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
-    <hyperlink ref="L241" r:id="rId238" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
-    <hyperlink ref="L242" r:id="rId239" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
-    <hyperlink ref="L243" r:id="rId240" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
-    <hyperlink ref="L244" r:id="rId241" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
-    <hyperlink ref="L245" r:id="rId242" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
-    <hyperlink ref="L246" r:id="rId243" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
-    <hyperlink ref="L247" r:id="rId244" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
-    <hyperlink ref="L248" r:id="rId245" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
-    <hyperlink ref="L249" r:id="rId246" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
-    <hyperlink ref="L250" r:id="rId247" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
-    <hyperlink ref="L251" r:id="rId248" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
-    <hyperlink ref="L252" r:id="rId249" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
-    <hyperlink ref="L253" r:id="rId250" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
-    <hyperlink ref="L254" r:id="rId251" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
-    <hyperlink ref="L255" r:id="rId252" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
-    <hyperlink ref="L256" r:id="rId253" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
-    <hyperlink ref="L257" r:id="rId254" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
-    <hyperlink ref="L258" r:id="rId255" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
-    <hyperlink ref="L259" r:id="rId256" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
-    <hyperlink ref="L260" r:id="rId257" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
-    <hyperlink ref="L261" r:id="rId258" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
-    <hyperlink ref="L262" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
-    <hyperlink ref="L263" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
-    <hyperlink ref="L264" r:id="rId261" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
-    <hyperlink ref="L265" r:id="rId262" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
-    <hyperlink ref="L266" r:id="rId263" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
-    <hyperlink ref="L267" r:id="rId264" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
-    <hyperlink ref="L268" r:id="rId265" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
-    <hyperlink ref="L269" r:id="rId266" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
-    <hyperlink ref="L270" r:id="rId267" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
-    <hyperlink ref="L271" r:id="rId268" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
-    <hyperlink ref="L272" r:id="rId269" xr:uid="{00000000-0004-0000-0000-00000C010000}"/>
-    <hyperlink ref="L273" r:id="rId270" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
-    <hyperlink ref="L274" r:id="rId271" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
-    <hyperlink ref="L275" r:id="rId272" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
-    <hyperlink ref="L276" r:id="rId273" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
-    <hyperlink ref="L277" r:id="rId274" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
-    <hyperlink ref="L278" r:id="rId275" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
-    <hyperlink ref="L279" r:id="rId276" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
-    <hyperlink ref="L280" r:id="rId277" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
-    <hyperlink ref="L281" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
-    <hyperlink ref="L282" r:id="rId279" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
-    <hyperlink ref="L283" r:id="rId280" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
-    <hyperlink ref="L284" r:id="rId281" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
-    <hyperlink ref="L285" r:id="rId282" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
-    <hyperlink ref="L286" r:id="rId283" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
-    <hyperlink ref="L287" r:id="rId284" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
-    <hyperlink ref="L288" r:id="rId285" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
-    <hyperlink ref="L289" r:id="rId286" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
-    <hyperlink ref="L290" r:id="rId287" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
+    <hyperlink ref="L179" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="L180" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="L181" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="L182" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="L183" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="L184" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="L185" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="L186" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="L187" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="L188" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="L189" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="L190" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="L191" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="L192" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="L193" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="L194" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="L195" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="L196" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="L197" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="L198" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
+    <hyperlink ref="L199" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="L201" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
+    <hyperlink ref="L202" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="L203" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
+    <hyperlink ref="L204" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
+    <hyperlink ref="L205" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="L206" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="L207" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="L208" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
+    <hyperlink ref="L209" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="L210" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
+    <hyperlink ref="L211" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
+    <hyperlink ref="L212" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
+    <hyperlink ref="L213" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
+    <hyperlink ref="L214" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
+    <hyperlink ref="L215" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
+    <hyperlink ref="L216" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
+    <hyperlink ref="L217" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
+    <hyperlink ref="L218" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
+    <hyperlink ref="L219" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
+    <hyperlink ref="L220" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
+    <hyperlink ref="L221" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
+    <hyperlink ref="L222" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
+    <hyperlink ref="L223" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
+    <hyperlink ref="L224" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
+    <hyperlink ref="L225" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
+    <hyperlink ref="L226" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
+    <hyperlink ref="L227" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
+    <hyperlink ref="L228" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
+    <hyperlink ref="L229" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
+    <hyperlink ref="L230" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
+    <hyperlink ref="L231" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
+    <hyperlink ref="L232" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
+    <hyperlink ref="L233" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
+    <hyperlink ref="L234" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
+    <hyperlink ref="L235" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
+    <hyperlink ref="L236" r:id="rId232" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
+    <hyperlink ref="L237" r:id="rId233" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
+    <hyperlink ref="L238" r:id="rId234" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
+    <hyperlink ref="L239" r:id="rId235" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
+    <hyperlink ref="L240" r:id="rId236" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
+    <hyperlink ref="L241" r:id="rId237" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
+    <hyperlink ref="L242" r:id="rId238" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
+    <hyperlink ref="L243" r:id="rId239" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
+    <hyperlink ref="L244" r:id="rId240" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
+    <hyperlink ref="L245" r:id="rId241" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
+    <hyperlink ref="L246" r:id="rId242" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
+    <hyperlink ref="L247" r:id="rId243" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
+    <hyperlink ref="L248" r:id="rId244" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
+    <hyperlink ref="L249" r:id="rId245" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
+    <hyperlink ref="L250" r:id="rId246" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
+    <hyperlink ref="L251" r:id="rId247" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
+    <hyperlink ref="L252" r:id="rId248" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
+    <hyperlink ref="L253" r:id="rId249" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
+    <hyperlink ref="L254" r:id="rId250" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
+    <hyperlink ref="L255" r:id="rId251" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
+    <hyperlink ref="L256" r:id="rId252" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
+    <hyperlink ref="L257" r:id="rId253" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
+    <hyperlink ref="L258" r:id="rId254" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
+    <hyperlink ref="L259" r:id="rId255" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
+    <hyperlink ref="L260" r:id="rId256" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
+    <hyperlink ref="L261" r:id="rId257" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
+    <hyperlink ref="L262" r:id="rId258" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
+    <hyperlink ref="L263" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
+    <hyperlink ref="L264" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
+    <hyperlink ref="L265" r:id="rId261" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
+    <hyperlink ref="L266" r:id="rId262" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
+    <hyperlink ref="L267" r:id="rId263" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
+    <hyperlink ref="L268" r:id="rId264" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
+    <hyperlink ref="L269" r:id="rId265" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
+    <hyperlink ref="L270" r:id="rId266" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
+    <hyperlink ref="L271" r:id="rId267" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
+    <hyperlink ref="L272" r:id="rId268" xr:uid="{00000000-0004-0000-0000-00000C010000}"/>
+    <hyperlink ref="L273" r:id="rId269" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
+    <hyperlink ref="L274" r:id="rId270" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
+    <hyperlink ref="L275" r:id="rId271" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
+    <hyperlink ref="L276" r:id="rId272" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
+    <hyperlink ref="L277" r:id="rId273" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
+    <hyperlink ref="L278" r:id="rId274" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
+    <hyperlink ref="L279" r:id="rId275" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
+    <hyperlink ref="L280" r:id="rId276" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
+    <hyperlink ref="L281" r:id="rId277" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
+    <hyperlink ref="L282" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
+    <hyperlink ref="L283" r:id="rId279" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
+    <hyperlink ref="L284" r:id="rId280" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
+    <hyperlink ref="L285" r:id="rId281" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
+    <hyperlink ref="L286" r:id="rId282" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
+    <hyperlink ref="L287" r:id="rId283" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
+    <hyperlink ref="L288" r:id="rId284" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
+    <hyperlink ref="L289" r:id="rId285" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
+    <hyperlink ref="L290" r:id="rId286" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
+    <hyperlink ref="L178" r:id="rId287" xr:uid="{D6F55639-3830-44C8-B04A-3F77F6C9C464}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/peinture-18e.xlsx
+++ b/quizzes/peinture-18e.xlsx
@@ -1228,7 +1228,7 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/7/79/Le-discret-by-ducreux.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>v. 1791</t>
+    <t>1791 environ</t>
   </si>
   <si>
     <t>Portrait de Louis XVI</t>
@@ -2239,7 +2239,7 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/Jean-%C3%89tienne_Liotard_-_La_liseuse.jpg/960px-Jean-%C3%89tienne_Liotard_-_La_liseuse.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>vers 1770</t>
+    <t>1770 environ</t>
   </si>
   <si>
     <t>Liotard riant</t>
@@ -2332,7 +2332,7 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0d/%27The_Tame_Magpie%27%2C_oil_on_canvas_painting_by_Alessandro_Magnasco%2C_c._1707-8%2C_Metropolitan_Museum_of_Art.JPG/1280px-%27The_Tame_Magpie%27%2C_oil_on_canvas_painting_by_Alessandro_Magnasco%2C_c._1707-8%2C_Metropolitan_Museum_of_Art.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Vers 1740</t>
+    <t>1740 environ</t>
   </si>
   <si>
     <t>Gênes</t>
@@ -2359,7 +2359,7 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/8/82/Alessandro_Magnasco_-_Gypsy_Wedding_Banquet_-_WGA13848.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
   <si>
-    <t>Vers 1720</t>
+    <t>1720 environ</t>
   </si>
   <si>
     <t>Funérailles juives</t>
@@ -2404,7 +2404,7 @@
     <t>Série pour le Cabinet d'Histoire Naturelle du Prince des Asturies</t>
   </si>
   <si>
-    <t>Vers 1760</t>
+    <t>1760 environ</t>
   </si>
   <si>
     <t>Nature morte aux oranges, pot de miel, boîtes de douceurs et pastèques</t>
@@ -5839,11 +5839,15 @@
       <c r="D36" s="3">
         <v>1720</v>
       </c>
-      <c r="E36" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>206</v>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Londres</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Palais de Buckingham</t>
+        </is>
       </c>
       <c r="J36" s="3" t="s">
         <v>207</v>
@@ -13215,11 +13219,15 @@
       <c r="D216" s="3" t="s">
         <v>906</v>
       </c>
-      <c r="E216" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="F216" s="3" t="s">
-        <v>907</v>
+      <c r="E216" s="3" t="inlineStr">
+        <is>
+          <t>Londres</t>
+        </is>
+      </c>
+      <c r="F216" s="3" t="inlineStr">
+        <is>
+          <t>Palais de Buckingham</t>
+        </is>
       </c>
       <c r="J216" s="3" t="s">
         <v>908</v>

--- a/quizzes/peinture-18e.xlsx
+++ b/quizzes/peinture-18e.xlsx
@@ -4861,8 +4861,10 @@
       <c r="R12" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>98</v>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gravure à l'eau-forte rehaussée à l'aquarelle et à l'encre sur papier</t>
+        </is>
       </c>
       <c r="T12" s="9">
         <v>23</v>
@@ -4905,8 +4907,10 @@
       <c r="R13" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="S13" s="3" t="s">
-        <v>104</v>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monotype imprimé en couleur, encre et aquarelle sur papier</t>
+        </is>
       </c>
       <c r="T13" s="9">
         <v>46</v>
@@ -4949,8 +4953,10 @@
       <c r="R14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>108</v>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monotype imprimé en couleur, détrempe et aquarelle sur papier</t>
+        </is>
       </c>
       <c r="T14" s="9">
         <v>54</v>
@@ -5001,8 +5007,10 @@
       <c r="R15" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="S15" s="22" t="s">
-        <v>108</v>
+      <c r="S15" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monotype imprimé en couleur, détrempe et aquarelle sur papier</t>
+        </is>
       </c>
       <c r="T15" s="24">
         <v>44</v>
@@ -6027,8 +6035,10 @@
       <c r="R40" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="S40" s="3" t="s">
-        <v>229</v>
+      <c r="S40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pastel sur papier</t>
+        </is>
       </c>
       <c r="T40" s="9">
         <v>71</v>
@@ -6068,8 +6078,10 @@
       <c r="R41" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>229</v>
+      <c r="S41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pastel sur papier</t>
+        </is>
       </c>
       <c r="T41" s="9">
         <v>63</v>
@@ -6302,8 +6314,10 @@
       <c r="R47" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>229</v>
+      <c r="S47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pastel sur papier</t>
+        </is>
       </c>
       <c r="T47" s="9">
         <v>46</v>
@@ -6957,8 +6971,10 @@
       <c r="R63" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="S63" s="3" t="s">
-        <v>229</v>
+      <c r="S63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pastel sur papier</t>
+        </is>
       </c>
       <c r="T63" s="9">
         <v>81</v>
@@ -7326,8 +7342,10 @@
       <c r="R72" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>229</v>
+      <c r="S72" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pastel sur papier</t>
+        </is>
       </c>
       <c r="T72" s="9">
         <v>175</v>
@@ -7364,8 +7382,10 @@
       <c r="R73" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="S73" s="3" t="s">
-        <v>229</v>
+      <c r="S73" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pastel sur papier</t>
+        </is>
       </c>
       <c r="T73" s="9">
         <v>55</v>
@@ -10656,8 +10676,10 @@
       <c r="R153" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="S153" s="3" t="s">
-        <v>229</v>
+      <c r="S153" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pastel sur papier</t>
+        </is>
       </c>
       <c r="T153" s="9">
         <v>74</v>
@@ -11941,8 +11963,10 @@
       <c r="R184" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="S184" s="3" t="s">
-        <v>229</v>
+      <c r="S184" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pastel sur papier</t>
+        </is>
       </c>
       <c r="T184" s="9">
         <v>46</v>
@@ -12152,8 +12176,10 @@
       <c r="R189" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="S189" s="3" t="s">
-        <v>229</v>
+      <c r="S189" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pastel sur papier</t>
+        </is>
       </c>
       <c r="T189" s="9">
         <v>102</v>
@@ -12917,8 +12943,10 @@
       <c r="R208" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="S208" s="3" t="s">
-        <v>229</v>
+      <c r="S208" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pastel sur papier</t>
+        </is>
       </c>
       <c r="T208" s="9">
         <v>63</v>

--- a/quizzes/peinture-18e.xlsx
+++ b/quizzes/peinture-18e.xlsx
@@ -4329,7 +4329,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W305"/>
+  <dimension ref="A1:X305"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" style="3" customWidth="1"/>
@@ -4344,6 +4344,7 @@
     <col min="15" max="18" width="9.140625" style="3" hidden="1" customWidth="1"/>
     <col min="19" max="19" width="9.140625" style="3" customWidth="1"/>
     <col min="20" max="23" width="9.140625" style="9" customWidth="1"/>
+    <col min="24" max="24" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4415,6 +4416,11 @@
       </c>
       <c r="W1" s="7" t="s">
         <v>22</v>
+      </c>
+      <c r="X1" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Artiste associé</t>
+        </is>
       </c>
     </row>
     <row r="2" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
